--- a/매크로_트래커_로우데이터.xlsx
+++ b/매크로_트래커_로우데이터.xlsx
@@ -22432,2580 +22432,8100 @@
       </c>
     </row>
     <row r="850" spans="1:6">
-      <c r="A850" s="6"/>
-      <c r="B850" s="7"/>
-      <c r="C850" s="7"/>
-      <c r="D850" s="7"/>
+      <c r="A850" s="6">
+        <v>44440</v>
+      </c>
+      <c r="B850" s="7" t="inlineStr">
+        <is>
+          <t>일본</t>
+        </is>
+      </c>
+      <c r="C850" s="7" t="inlineStr">
+        <is>
+          <t>CPI 헤드라인</t>
+        </is>
+      </c>
+      <c r="D850" s="7">
+        <v>0.2</v>
+      </c>
       <c r="E850" s="6"/>
-      <c r="F850" s="7"/>
+      <c r="F850" s="7" t="inlineStr">
+        <is>
+          <t>월간</t>
+        </is>
+      </c>
     </row>
     <row r="851" spans="1:6">
-      <c r="A851" s="6"/>
-      <c r="B851" s="7"/>
-      <c r="C851" s="7"/>
-      <c r="D851" s="7"/>
+      <c r="A851" s="6">
+        <v>44470</v>
+      </c>
+      <c r="B851" s="7" t="inlineStr">
+        <is>
+          <t>일본</t>
+        </is>
+      </c>
+      <c r="C851" s="7" t="inlineStr">
+        <is>
+          <t>CPI 헤드라인</t>
+        </is>
+      </c>
+      <c r="D851" s="7">
+        <v>0.1</v>
+      </c>
       <c r="E851" s="6"/>
-      <c r="F851" s="7"/>
+      <c r="F851" s="7" t="inlineStr">
+        <is>
+          <t>월간</t>
+        </is>
+      </c>
     </row>
     <row r="852" spans="1:6">
-      <c r="A852" s="6"/>
-      <c r="B852" s="7"/>
-      <c r="C852" s="7"/>
-      <c r="D852" s="7"/>
+      <c r="A852" s="6">
+        <v>44501</v>
+      </c>
+      <c r="B852" s="7" t="inlineStr">
+        <is>
+          <t>일본</t>
+        </is>
+      </c>
+      <c r="C852" s="7" t="inlineStr">
+        <is>
+          <t>CPI 헤드라인</t>
+        </is>
+      </c>
+      <c r="D852" s="7">
+        <v>0.6</v>
+      </c>
       <c r="E852" s="6"/>
-      <c r="F852" s="7"/>
+      <c r="F852" s="7" t="inlineStr">
+        <is>
+          <t>월간</t>
+        </is>
+      </c>
     </row>
     <row r="853" spans="1:6">
-      <c r="A853" s="6"/>
-      <c r="B853" s="7"/>
-      <c r="C853" s="7"/>
-      <c r="D853" s="7"/>
+      <c r="A853" s="6">
+        <v>44531</v>
+      </c>
+      <c r="B853" s="7" t="inlineStr">
+        <is>
+          <t>일본</t>
+        </is>
+      </c>
+      <c r="C853" s="7" t="inlineStr">
+        <is>
+          <t>CPI 헤드라인</t>
+        </is>
+      </c>
+      <c r="D853" s="7">
+        <v>0.8</v>
+      </c>
       <c r="E853" s="6"/>
-      <c r="F853" s="7"/>
+      <c r="F853" s="7" t="inlineStr">
+        <is>
+          <t>월간</t>
+        </is>
+      </c>
     </row>
     <row r="854" spans="1:6">
-      <c r="A854" s="6"/>
-      <c r="B854" s="7"/>
-      <c r="C854" s="7"/>
-      <c r="D854" s="7"/>
+      <c r="A854" s="6">
+        <v>44562</v>
+      </c>
+      <c r="B854" s="7" t="inlineStr">
+        <is>
+          <t>일본</t>
+        </is>
+      </c>
+      <c r="C854" s="7" t="inlineStr">
+        <is>
+          <t>CPI 헤드라인</t>
+        </is>
+      </c>
+      <c r="D854" s="7">
+        <v>0.5</v>
+      </c>
       <c r="E854" s="6"/>
-      <c r="F854" s="7"/>
+      <c r="F854" s="7" t="inlineStr">
+        <is>
+          <t>월간</t>
+        </is>
+      </c>
     </row>
     <row r="855" spans="1:6">
-      <c r="A855" s="6"/>
-      <c r="B855" s="7"/>
-      <c r="C855" s="7"/>
-      <c r="D855" s="7"/>
+      <c r="A855" s="6">
+        <v>44593</v>
+      </c>
+      <c r="B855" s="7" t="inlineStr">
+        <is>
+          <t>일본</t>
+        </is>
+      </c>
+      <c r="C855" s="7" t="inlineStr">
+        <is>
+          <t>CPI 헤드라인</t>
+        </is>
+      </c>
+      <c r="D855" s="7">
+        <v>0.9</v>
+      </c>
       <c r="E855" s="6"/>
-      <c r="F855" s="7"/>
+      <c r="F855" s="7" t="inlineStr">
+        <is>
+          <t>월간</t>
+        </is>
+      </c>
     </row>
     <row r="856" spans="1:6">
-      <c r="A856" s="6"/>
-      <c r="B856" s="7"/>
-      <c r="C856" s="7"/>
-      <c r="D856" s="7"/>
+      <c r="A856" s="6">
+        <v>44621</v>
+      </c>
+      <c r="B856" s="7" t="inlineStr">
+        <is>
+          <t>일본</t>
+        </is>
+      </c>
+      <c r="C856" s="7" t="inlineStr">
+        <is>
+          <t>CPI 헤드라인</t>
+        </is>
+      </c>
+      <c r="D856" s="7">
+        <v>1.2</v>
+      </c>
       <c r="E856" s="6"/>
-      <c r="F856" s="7"/>
+      <c r="F856" s="7" t="inlineStr">
+        <is>
+          <t>월간</t>
+        </is>
+      </c>
     </row>
     <row r="857" spans="1:6">
-      <c r="A857" s="6"/>
-      <c r="B857" s="7"/>
-      <c r="C857" s="7"/>
-      <c r="D857" s="7"/>
+      <c r="A857" s="6">
+        <v>44652</v>
+      </c>
+      <c r="B857" s="7" t="inlineStr">
+        <is>
+          <t>일본</t>
+        </is>
+      </c>
+      <c r="C857" s="7" t="inlineStr">
+        <is>
+          <t>CPI 헤드라인</t>
+        </is>
+      </c>
+      <c r="D857" s="7">
+        <v>2.5</v>
+      </c>
       <c r="E857" s="6"/>
-      <c r="F857" s="7"/>
+      <c r="F857" s="7" t="inlineStr">
+        <is>
+          <t>월간</t>
+        </is>
+      </c>
     </row>
     <row r="858" spans="1:6">
-      <c r="A858" s="6"/>
-      <c r="B858" s="7"/>
-      <c r="C858" s="7"/>
-      <c r="D858" s="7"/>
+      <c r="A858" s="6">
+        <v>44682</v>
+      </c>
+      <c r="B858" s="7" t="inlineStr">
+        <is>
+          <t>일본</t>
+        </is>
+      </c>
+      <c r="C858" s="7" t="inlineStr">
+        <is>
+          <t>CPI 헤드라인</t>
+        </is>
+      </c>
+      <c r="D858" s="7">
+        <v>2.5</v>
+      </c>
       <c r="E858" s="6"/>
-      <c r="F858" s="7"/>
+      <c r="F858" s="7" t="inlineStr">
+        <is>
+          <t>월간</t>
+        </is>
+      </c>
     </row>
     <row r="859" spans="1:6">
-      <c r="A859" s="6"/>
-      <c r="B859" s="7"/>
-      <c r="C859" s="7"/>
-      <c r="D859" s="7"/>
+      <c r="A859" s="6">
+        <v>44713</v>
+      </c>
+      <c r="B859" s="7" t="inlineStr">
+        <is>
+          <t>일본</t>
+        </is>
+      </c>
+      <c r="C859" s="7" t="inlineStr">
+        <is>
+          <t>CPI 헤드라인</t>
+        </is>
+      </c>
+      <c r="D859" s="7">
+        <v>2.4</v>
+      </c>
       <c r="E859" s="6"/>
-      <c r="F859" s="7"/>
+      <c r="F859" s="7" t="inlineStr">
+        <is>
+          <t>월간</t>
+        </is>
+      </c>
     </row>
     <row r="860" spans="1:6">
-      <c r="A860" s="6"/>
-      <c r="B860" s="7"/>
-      <c r="C860" s="7"/>
-      <c r="D860" s="7"/>
+      <c r="A860" s="6">
+        <v>44743</v>
+      </c>
+      <c r="B860" s="7" t="inlineStr">
+        <is>
+          <t>일본</t>
+        </is>
+      </c>
+      <c r="C860" s="7" t="inlineStr">
+        <is>
+          <t>CPI 헤드라인</t>
+        </is>
+      </c>
+      <c r="D860" s="7">
+        <v>2.6</v>
+      </c>
       <c r="E860" s="6"/>
-      <c r="F860" s="7"/>
+      <c r="F860" s="7" t="inlineStr">
+        <is>
+          <t>월간</t>
+        </is>
+      </c>
     </row>
     <row r="861" spans="1:6">
-      <c r="A861" s="6"/>
-      <c r="B861" s="7"/>
-      <c r="C861" s="7"/>
-      <c r="D861" s="7"/>
+      <c r="A861" s="6">
+        <v>44774</v>
+      </c>
+      <c r="B861" s="7" t="inlineStr">
+        <is>
+          <t>일본</t>
+        </is>
+      </c>
+      <c r="C861" s="7" t="inlineStr">
+        <is>
+          <t>CPI 헤드라인</t>
+        </is>
+      </c>
+      <c r="D861" s="7">
+        <v>3.0</v>
+      </c>
       <c r="E861" s="6"/>
-      <c r="F861" s="7"/>
+      <c r="F861" s="7" t="inlineStr">
+        <is>
+          <t>월간</t>
+        </is>
+      </c>
     </row>
     <row r="862" spans="1:6">
-      <c r="A862" s="6"/>
-      <c r="B862" s="7"/>
-      <c r="C862" s="7"/>
-      <c r="D862" s="7"/>
+      <c r="A862" s="6">
+        <v>44805</v>
+      </c>
+      <c r="B862" s="7" t="inlineStr">
+        <is>
+          <t>일본</t>
+        </is>
+      </c>
+      <c r="C862" s="7" t="inlineStr">
+        <is>
+          <t>CPI 헤드라인</t>
+        </is>
+      </c>
+      <c r="D862" s="7">
+        <v>3.0</v>
+      </c>
       <c r="E862" s="6"/>
-      <c r="F862" s="7"/>
+      <c r="F862" s="7" t="inlineStr">
+        <is>
+          <t>월간</t>
+        </is>
+      </c>
     </row>
     <row r="863" spans="1:6">
-      <c r="A863" s="6"/>
-      <c r="B863" s="7"/>
-      <c r="C863" s="7"/>
-      <c r="D863" s="7"/>
+      <c r="A863" s="6">
+        <v>44835</v>
+      </c>
+      <c r="B863" s="7" t="inlineStr">
+        <is>
+          <t>일본</t>
+        </is>
+      </c>
+      <c r="C863" s="7" t="inlineStr">
+        <is>
+          <t>CPI 헤드라인</t>
+        </is>
+      </c>
+      <c r="D863" s="7">
+        <v>3.7</v>
+      </c>
       <c r="E863" s="6"/>
-      <c r="F863" s="7"/>
+      <c r="F863" s="7" t="inlineStr">
+        <is>
+          <t>월간</t>
+        </is>
+      </c>
     </row>
     <row r="864" spans="1:6">
-      <c r="A864" s="6"/>
-      <c r="B864" s="7"/>
-      <c r="C864" s="7"/>
-      <c r="D864" s="7"/>
+      <c r="A864" s="6">
+        <v>44866</v>
+      </c>
+      <c r="B864" s="7" t="inlineStr">
+        <is>
+          <t>일본</t>
+        </is>
+      </c>
+      <c r="C864" s="7" t="inlineStr">
+        <is>
+          <t>CPI 헤드라인</t>
+        </is>
+      </c>
+      <c r="D864" s="7">
+        <v>3.8</v>
+      </c>
       <c r="E864" s="6"/>
-      <c r="F864" s="7"/>
+      <c r="F864" s="7" t="inlineStr">
+        <is>
+          <t>월간</t>
+        </is>
+      </c>
     </row>
     <row r="865" spans="1:6">
-      <c r="A865" s="6"/>
-      <c r="B865" s="7"/>
-      <c r="C865" s="7"/>
-      <c r="D865" s="7"/>
+      <c r="A865" s="6">
+        <v>44896</v>
+      </c>
+      <c r="B865" s="7" t="inlineStr">
+        <is>
+          <t>일본</t>
+        </is>
+      </c>
+      <c r="C865" s="7" t="inlineStr">
+        <is>
+          <t>CPI 헤드라인</t>
+        </is>
+      </c>
+      <c r="D865" s="7">
+        <v>4.0</v>
+      </c>
       <c r="E865" s="6"/>
-      <c r="F865" s="7"/>
+      <c r="F865" s="7" t="inlineStr">
+        <is>
+          <t>월간</t>
+        </is>
+      </c>
     </row>
     <row r="866" spans="1:6">
-      <c r="A866" s="6"/>
-      <c r="B866" s="7"/>
-      <c r="C866" s="7"/>
-      <c r="D866" s="7"/>
+      <c r="A866" s="6">
+        <v>44927</v>
+      </c>
+      <c r="B866" s="7" t="inlineStr">
+        <is>
+          <t>일본</t>
+        </is>
+      </c>
+      <c r="C866" s="7" t="inlineStr">
+        <is>
+          <t>CPI 헤드라인</t>
+        </is>
+      </c>
+      <c r="D866" s="7">
+        <v>4.3</v>
+      </c>
       <c r="E866" s="6"/>
-      <c r="F866" s="7"/>
+      <c r="F866" s="7" t="inlineStr">
+        <is>
+          <t>월간</t>
+        </is>
+      </c>
     </row>
     <row r="867" spans="1:6">
-      <c r="A867" s="6"/>
-      <c r="B867" s="7"/>
-      <c r="C867" s="7"/>
-      <c r="D867" s="7"/>
+      <c r="A867" s="6">
+        <v>44958</v>
+      </c>
+      <c r="B867" s="7" t="inlineStr">
+        <is>
+          <t>일본</t>
+        </is>
+      </c>
+      <c r="C867" s="7" t="inlineStr">
+        <is>
+          <t>CPI 헤드라인</t>
+        </is>
+      </c>
+      <c r="D867" s="7">
+        <v>3.3</v>
+      </c>
       <c r="E867" s="6"/>
-      <c r="F867" s="7"/>
+      <c r="F867" s="7" t="inlineStr">
+        <is>
+          <t>월간</t>
+        </is>
+      </c>
     </row>
     <row r="868" spans="1:6">
-      <c r="A868" s="6"/>
-      <c r="B868" s="7"/>
-      <c r="C868" s="7"/>
-      <c r="D868" s="7"/>
+      <c r="A868" s="6">
+        <v>44986</v>
+      </c>
+      <c r="B868" s="7" t="inlineStr">
+        <is>
+          <t>일본</t>
+        </is>
+      </c>
+      <c r="C868" s="7" t="inlineStr">
+        <is>
+          <t>CPI 헤드라인</t>
+        </is>
+      </c>
+      <c r="D868" s="7">
+        <v>3.2</v>
+      </c>
       <c r="E868" s="6"/>
-      <c r="F868" s="7"/>
+      <c r="F868" s="7" t="inlineStr">
+        <is>
+          <t>월간</t>
+        </is>
+      </c>
     </row>
     <row r="869" spans="1:6">
-      <c r="A869" s="6"/>
-      <c r="B869" s="7"/>
-      <c r="C869" s="7"/>
-      <c r="D869" s="7"/>
+      <c r="A869" s="6">
+        <v>45017</v>
+      </c>
+      <c r="B869" s="7" t="inlineStr">
+        <is>
+          <t>일본</t>
+        </is>
+      </c>
+      <c r="C869" s="7" t="inlineStr">
+        <is>
+          <t>CPI 헤드라인</t>
+        </is>
+      </c>
+      <c r="D869" s="7">
+        <v>3.5</v>
+      </c>
       <c r="E869" s="6"/>
-      <c r="F869" s="7"/>
+      <c r="F869" s="7" t="inlineStr">
+        <is>
+          <t>월간</t>
+        </is>
+      </c>
     </row>
     <row r="870" spans="1:6">
-      <c r="A870" s="6"/>
-      <c r="B870" s="7"/>
-      <c r="C870" s="7"/>
-      <c r="D870" s="7"/>
+      <c r="A870" s="6">
+        <v>45047</v>
+      </c>
+      <c r="B870" s="7" t="inlineStr">
+        <is>
+          <t>일본</t>
+        </is>
+      </c>
+      <c r="C870" s="7" t="inlineStr">
+        <is>
+          <t>CPI 헤드라인</t>
+        </is>
+      </c>
+      <c r="D870" s="7">
+        <v>3.2</v>
+      </c>
       <c r="E870" s="6"/>
-      <c r="F870" s="7"/>
+      <c r="F870" s="7" t="inlineStr">
+        <is>
+          <t>월간</t>
+        </is>
+      </c>
     </row>
     <row r="871" spans="1:6">
-      <c r="A871" s="6"/>
-      <c r="B871" s="7"/>
-      <c r="C871" s="7"/>
-      <c r="D871" s="7"/>
+      <c r="A871" s="6">
+        <v>45078</v>
+      </c>
+      <c r="B871" s="7" t="inlineStr">
+        <is>
+          <t>일본</t>
+        </is>
+      </c>
+      <c r="C871" s="7" t="inlineStr">
+        <is>
+          <t>CPI 헤드라인</t>
+        </is>
+      </c>
+      <c r="D871" s="7">
+        <v>3.3</v>
+      </c>
       <c r="E871" s="6"/>
-      <c r="F871" s="7"/>
+      <c r="F871" s="7" t="inlineStr">
+        <is>
+          <t>월간</t>
+        </is>
+      </c>
     </row>
     <row r="872" spans="1:6">
-      <c r="A872" s="6"/>
-      <c r="B872" s="7"/>
-      <c r="C872" s="7"/>
-      <c r="D872" s="7"/>
+      <c r="A872" s="6">
+        <v>45108</v>
+      </c>
+      <c r="B872" s="7" t="inlineStr">
+        <is>
+          <t>일본</t>
+        </is>
+      </c>
+      <c r="C872" s="7" t="inlineStr">
+        <is>
+          <t>CPI 헤드라인</t>
+        </is>
+      </c>
+      <c r="D872" s="7">
+        <v>3.3</v>
+      </c>
       <c r="E872" s="6"/>
-      <c r="F872" s="7"/>
+      <c r="F872" s="7" t="inlineStr">
+        <is>
+          <t>월간</t>
+        </is>
+      </c>
     </row>
     <row r="873" spans="1:6">
-      <c r="A873" s="6"/>
-      <c r="B873" s="7"/>
-      <c r="C873" s="7"/>
-      <c r="D873" s="7"/>
+      <c r="A873" s="6">
+        <v>45139</v>
+      </c>
+      <c r="B873" s="7" t="inlineStr">
+        <is>
+          <t>일본</t>
+        </is>
+      </c>
+      <c r="C873" s="7" t="inlineStr">
+        <is>
+          <t>CPI 헤드라인</t>
+        </is>
+      </c>
+      <c r="D873" s="7">
+        <v>3.2</v>
+      </c>
       <c r="E873" s="6"/>
-      <c r="F873" s="7"/>
+      <c r="F873" s="7" t="inlineStr">
+        <is>
+          <t>월간</t>
+        </is>
+      </c>
     </row>
     <row r="874" spans="1:6">
-      <c r="A874" s="6"/>
-      <c r="B874" s="7"/>
-      <c r="C874" s="7"/>
-      <c r="D874" s="7"/>
+      <c r="A874" s="6">
+        <v>45170</v>
+      </c>
+      <c r="B874" s="7" t="inlineStr">
+        <is>
+          <t>일본</t>
+        </is>
+      </c>
+      <c r="C874" s="7" t="inlineStr">
+        <is>
+          <t>CPI 헤드라인</t>
+        </is>
+      </c>
+      <c r="D874" s="7">
+        <v>3.0</v>
+      </c>
       <c r="E874" s="6"/>
-      <c r="F874" s="7"/>
+      <c r="F874" s="7" t="inlineStr">
+        <is>
+          <t>월간</t>
+        </is>
+      </c>
     </row>
     <row r="875" spans="1:6">
-      <c r="A875" s="6"/>
-      <c r="B875" s="7"/>
-      <c r="C875" s="7"/>
-      <c r="D875" s="7"/>
+      <c r="A875" s="6">
+        <v>45200</v>
+      </c>
+      <c r="B875" s="7" t="inlineStr">
+        <is>
+          <t>일본</t>
+        </is>
+      </c>
+      <c r="C875" s="7" t="inlineStr">
+        <is>
+          <t>CPI 헤드라인</t>
+        </is>
+      </c>
+      <c r="D875" s="7">
+        <v>3.3</v>
+      </c>
       <c r="E875" s="6"/>
-      <c r="F875" s="7"/>
+      <c r="F875" s="7" t="inlineStr">
+        <is>
+          <t>월간</t>
+        </is>
+      </c>
     </row>
     <row r="876" spans="1:6">
-      <c r="A876" s="6"/>
-      <c r="B876" s="7"/>
-      <c r="C876" s="7"/>
-      <c r="D876" s="7"/>
+      <c r="A876" s="6">
+        <v>45231</v>
+      </c>
+      <c r="B876" s="7" t="inlineStr">
+        <is>
+          <t>일본</t>
+        </is>
+      </c>
+      <c r="C876" s="7" t="inlineStr">
+        <is>
+          <t>CPI 헤드라인</t>
+        </is>
+      </c>
+      <c r="D876" s="7">
+        <v>2.8</v>
+      </c>
       <c r="E876" s="6"/>
-      <c r="F876" s="7"/>
+      <c r="F876" s="7" t="inlineStr">
+        <is>
+          <t>월간</t>
+        </is>
+      </c>
     </row>
     <row r="877" spans="1:6">
-      <c r="A877" s="6"/>
-      <c r="B877" s="7"/>
-      <c r="C877" s="7"/>
-      <c r="D877" s="7"/>
+      <c r="A877" s="6">
+        <v>45261</v>
+      </c>
+      <c r="B877" s="7" t="inlineStr">
+        <is>
+          <t>일본</t>
+        </is>
+      </c>
+      <c r="C877" s="7" t="inlineStr">
+        <is>
+          <t>CPI 헤드라인</t>
+        </is>
+      </c>
+      <c r="D877" s="7">
+        <v>2.6</v>
+      </c>
       <c r="E877" s="6"/>
-      <c r="F877" s="7"/>
+      <c r="F877" s="7" t="inlineStr">
+        <is>
+          <t>월간</t>
+        </is>
+      </c>
     </row>
     <row r="878" spans="1:6">
-      <c r="A878" s="6"/>
-      <c r="B878" s="7"/>
-      <c r="C878" s="7"/>
-      <c r="D878" s="7"/>
+      <c r="A878" s="6">
+        <v>45292</v>
+      </c>
+      <c r="B878" s="7" t="inlineStr">
+        <is>
+          <t>일본</t>
+        </is>
+      </c>
+      <c r="C878" s="7" t="inlineStr">
+        <is>
+          <t>CPI 헤드라인</t>
+        </is>
+      </c>
+      <c r="D878" s="7">
+        <v>2.2</v>
+      </c>
       <c r="E878" s="6"/>
-      <c r="F878" s="7"/>
+      <c r="F878" s="7" t="inlineStr">
+        <is>
+          <t>월간</t>
+        </is>
+      </c>
     </row>
     <row r="879" spans="1:6">
-      <c r="A879" s="6"/>
-      <c r="B879" s="7"/>
-      <c r="C879" s="7"/>
-      <c r="D879" s="7"/>
+      <c r="A879" s="6">
+        <v>45323</v>
+      </c>
+      <c r="B879" s="7" t="inlineStr">
+        <is>
+          <t>일본</t>
+        </is>
+      </c>
+      <c r="C879" s="7" t="inlineStr">
+        <is>
+          <t>CPI 헤드라인</t>
+        </is>
+      </c>
+      <c r="D879" s="7">
+        <v>2.8</v>
+      </c>
       <c r="E879" s="6"/>
-      <c r="F879" s="7"/>
+      <c r="F879" s="7" t="inlineStr">
+        <is>
+          <t>월간</t>
+        </is>
+      </c>
     </row>
     <row r="880" spans="1:6">
-      <c r="A880" s="6"/>
-      <c r="B880" s="7"/>
-      <c r="C880" s="7"/>
-      <c r="D880" s="7"/>
+      <c r="A880" s="6">
+        <v>45352</v>
+      </c>
+      <c r="B880" s="7" t="inlineStr">
+        <is>
+          <t>일본</t>
+        </is>
+      </c>
+      <c r="C880" s="7" t="inlineStr">
+        <is>
+          <t>CPI 헤드라인</t>
+        </is>
+      </c>
+      <c r="D880" s="7">
+        <v>2.7</v>
+      </c>
       <c r="E880" s="6"/>
-      <c r="F880" s="7"/>
+      <c r="F880" s="7" t="inlineStr">
+        <is>
+          <t>월간</t>
+        </is>
+      </c>
     </row>
     <row r="881" spans="1:6">
-      <c r="A881" s="6"/>
-      <c r="B881" s="7"/>
-      <c r="C881" s="7"/>
-      <c r="D881" s="7"/>
+      <c r="A881" s="6">
+        <v>45383</v>
+      </c>
+      <c r="B881" s="7" t="inlineStr">
+        <is>
+          <t>일본</t>
+        </is>
+      </c>
+      <c r="C881" s="7" t="inlineStr">
+        <is>
+          <t>CPI 헤드라인</t>
+        </is>
+      </c>
+      <c r="D881" s="7">
+        <v>2.5</v>
+      </c>
       <c r="E881" s="6"/>
-      <c r="F881" s="7"/>
+      <c r="F881" s="7" t="inlineStr">
+        <is>
+          <t>월간</t>
+        </is>
+      </c>
     </row>
     <row r="882" spans="1:6">
-      <c r="A882" s="6"/>
-      <c r="B882" s="7"/>
-      <c r="C882" s="7"/>
-      <c r="D882" s="7"/>
+      <c r="A882" s="6">
+        <v>45413</v>
+      </c>
+      <c r="B882" s="7" t="inlineStr">
+        <is>
+          <t>일본</t>
+        </is>
+      </c>
+      <c r="C882" s="7" t="inlineStr">
+        <is>
+          <t>CPI 헤드라인</t>
+        </is>
+      </c>
+      <c r="D882" s="7">
+        <v>2.8</v>
+      </c>
       <c r="E882" s="6"/>
-      <c r="F882" s="7"/>
+      <c r="F882" s="7" t="inlineStr">
+        <is>
+          <t>월간</t>
+        </is>
+      </c>
     </row>
     <row r="883" spans="1:6">
-      <c r="A883" s="6"/>
-      <c r="B883" s="7"/>
-      <c r="C883" s="7"/>
-      <c r="D883" s="7"/>
+      <c r="A883" s="6">
+        <v>45444</v>
+      </c>
+      <c r="B883" s="7" t="inlineStr">
+        <is>
+          <t>일본</t>
+        </is>
+      </c>
+      <c r="C883" s="7" t="inlineStr">
+        <is>
+          <t>CPI 헤드라인</t>
+        </is>
+      </c>
+      <c r="D883" s="7">
+        <v>2.8</v>
+      </c>
       <c r="E883" s="6"/>
-      <c r="F883" s="7"/>
+      <c r="F883" s="7" t="inlineStr">
+        <is>
+          <t>월간</t>
+        </is>
+      </c>
     </row>
     <row r="884" spans="1:6">
-      <c r="A884" s="6"/>
-      <c r="B884" s="7"/>
-      <c r="C884" s="7"/>
-      <c r="D884" s="7"/>
+      <c r="A884" s="6">
+        <v>45474</v>
+      </c>
+      <c r="B884" s="7" t="inlineStr">
+        <is>
+          <t>일본</t>
+        </is>
+      </c>
+      <c r="C884" s="7" t="inlineStr">
+        <is>
+          <t>CPI 헤드라인</t>
+        </is>
+      </c>
+      <c r="D884" s="7">
+        <v>2.8</v>
+      </c>
       <c r="E884" s="6"/>
-      <c r="F884" s="7"/>
+      <c r="F884" s="7" t="inlineStr">
+        <is>
+          <t>월간</t>
+        </is>
+      </c>
     </row>
     <row r="885" spans="1:6">
-      <c r="A885" s="6"/>
-      <c r="B885" s="7"/>
-      <c r="C885" s="7"/>
-      <c r="D885" s="7"/>
+      <c r="A885" s="6">
+        <v>45505</v>
+      </c>
+      <c r="B885" s="7" t="inlineStr">
+        <is>
+          <t>일본</t>
+        </is>
+      </c>
+      <c r="C885" s="7" t="inlineStr">
+        <is>
+          <t>CPI 헤드라인</t>
+        </is>
+      </c>
+      <c r="D885" s="7">
+        <v>3.0</v>
+      </c>
       <c r="E885" s="6"/>
-      <c r="F885" s="7"/>
+      <c r="F885" s="7" t="inlineStr">
+        <is>
+          <t>월간</t>
+        </is>
+      </c>
     </row>
     <row r="886" spans="1:6">
-      <c r="A886" s="6"/>
-      <c r="B886" s="7"/>
-      <c r="C886" s="7"/>
-      <c r="D886" s="7"/>
+      <c r="A886" s="6">
+        <v>45536</v>
+      </c>
+      <c r="B886" s="7" t="inlineStr">
+        <is>
+          <t>일본</t>
+        </is>
+      </c>
+      <c r="C886" s="7" t="inlineStr">
+        <is>
+          <t>CPI 헤드라인</t>
+        </is>
+      </c>
+      <c r="D886" s="7">
+        <v>2.5</v>
+      </c>
       <c r="E886" s="6"/>
-      <c r="F886" s="7"/>
+      <c r="F886" s="7" t="inlineStr">
+        <is>
+          <t>월간</t>
+        </is>
+      </c>
     </row>
     <row r="887" spans="1:6">
-      <c r="A887" s="6"/>
-      <c r="B887" s="7"/>
-      <c r="C887" s="7"/>
-      <c r="D887" s="7"/>
+      <c r="A887" s="6">
+        <v>45566</v>
+      </c>
+      <c r="B887" s="7" t="inlineStr">
+        <is>
+          <t>일본</t>
+        </is>
+      </c>
+      <c r="C887" s="7" t="inlineStr">
+        <is>
+          <t>CPI 헤드라인</t>
+        </is>
+      </c>
+      <c r="D887" s="7">
+        <v>2.3</v>
+      </c>
       <c r="E887" s="6"/>
-      <c r="F887" s="7"/>
+      <c r="F887" s="7" t="inlineStr">
+        <is>
+          <t>월간</t>
+        </is>
+      </c>
     </row>
     <row r="888" spans="1:6">
-      <c r="A888" s="6"/>
-      <c r="B888" s="7"/>
-      <c r="C888" s="7"/>
-      <c r="D888" s="7"/>
+      <c r="A888" s="6">
+        <v>45597</v>
+      </c>
+      <c r="B888" s="7" t="inlineStr">
+        <is>
+          <t>일본</t>
+        </is>
+      </c>
+      <c r="C888" s="7" t="inlineStr">
+        <is>
+          <t>CPI 헤드라인</t>
+        </is>
+      </c>
+      <c r="D888" s="7">
+        <v>2.9</v>
+      </c>
       <c r="E888" s="6"/>
-      <c r="F888" s="7"/>
+      <c r="F888" s="7" t="inlineStr">
+        <is>
+          <t>월간</t>
+        </is>
+      </c>
     </row>
     <row r="889" spans="1:6">
-      <c r="A889" s="6"/>
-      <c r="B889" s="7"/>
-      <c r="C889" s="7"/>
-      <c r="D889" s="7"/>
+      <c r="A889" s="6">
+        <v>45627</v>
+      </c>
+      <c r="B889" s="7" t="inlineStr">
+        <is>
+          <t>일본</t>
+        </is>
+      </c>
+      <c r="C889" s="7" t="inlineStr">
+        <is>
+          <t>CPI 헤드라인</t>
+        </is>
+      </c>
+      <c r="D889" s="7">
+        <v>3.6</v>
+      </c>
       <c r="E889" s="6"/>
-      <c r="F889" s="7"/>
+      <c r="F889" s="7" t="inlineStr">
+        <is>
+          <t>월간</t>
+        </is>
+      </c>
     </row>
     <row r="890" spans="1:6">
-      <c r="A890" s="6"/>
-      <c r="B890" s="7"/>
-      <c r="C890" s="7"/>
-      <c r="D890" s="7"/>
+      <c r="A890" s="6">
+        <v>45658</v>
+      </c>
+      <c r="B890" s="7" t="inlineStr">
+        <is>
+          <t>일본</t>
+        </is>
+      </c>
+      <c r="C890" s="7" t="inlineStr">
+        <is>
+          <t>CPI 헤드라인</t>
+        </is>
+      </c>
+      <c r="D890" s="7">
+        <v>4.0</v>
+      </c>
       <c r="E890" s="6"/>
-      <c r="F890" s="7"/>
+      <c r="F890" s="7" t="inlineStr">
+        <is>
+          <t>월간</t>
+        </is>
+      </c>
     </row>
     <row r="891" spans="1:6">
-      <c r="A891" s="6"/>
-      <c r="B891" s="7"/>
-      <c r="C891" s="7"/>
-      <c r="D891" s="7"/>
+      <c r="A891" s="6">
+        <v>45689</v>
+      </c>
+      <c r="B891" s="7" t="inlineStr">
+        <is>
+          <t>일본</t>
+        </is>
+      </c>
+      <c r="C891" s="7" t="inlineStr">
+        <is>
+          <t>CPI 헤드라인</t>
+        </is>
+      </c>
+      <c r="D891" s="7">
+        <v>3.7</v>
+      </c>
       <c r="E891" s="6"/>
-      <c r="F891" s="7"/>
+      <c r="F891" s="7" t="inlineStr">
+        <is>
+          <t>월간</t>
+        </is>
+      </c>
     </row>
     <row r="892" spans="1:6">
-      <c r="A892" s="6"/>
-      <c r="B892" s="7"/>
-      <c r="C892" s="7"/>
-      <c r="D892" s="7"/>
+      <c r="A892" s="6">
+        <v>45717</v>
+      </c>
+      <c r="B892" s="7" t="inlineStr">
+        <is>
+          <t>일본</t>
+        </is>
+      </c>
+      <c r="C892" s="7" t="inlineStr">
+        <is>
+          <t>CPI 헤드라인</t>
+        </is>
+      </c>
+      <c r="D892" s="7">
+        <v>3.6</v>
+      </c>
       <c r="E892" s="6"/>
-      <c r="F892" s="7"/>
+      <c r="F892" s="7" t="inlineStr">
+        <is>
+          <t>월간</t>
+        </is>
+      </c>
     </row>
     <row r="893" spans="1:6">
-      <c r="A893" s="6"/>
-      <c r="B893" s="7"/>
-      <c r="C893" s="7"/>
-      <c r="D893" s="7"/>
+      <c r="A893" s="6">
+        <v>45748</v>
+      </c>
+      <c r="B893" s="7" t="inlineStr">
+        <is>
+          <t>일본</t>
+        </is>
+      </c>
+      <c r="C893" s="7" t="inlineStr">
+        <is>
+          <t>CPI 헤드라인</t>
+        </is>
+      </c>
+      <c r="D893" s="7">
+        <v>3.6</v>
+      </c>
       <c r="E893" s="6"/>
-      <c r="F893" s="7"/>
+      <c r="F893" s="7" t="inlineStr">
+        <is>
+          <t>월간</t>
+        </is>
+      </c>
     </row>
     <row r="894" spans="1:6">
-      <c r="A894" s="6"/>
-      <c r="B894" s="7"/>
-      <c r="C894" s="7"/>
-      <c r="D894" s="7"/>
+      <c r="A894" s="6">
+        <v>45778</v>
+      </c>
+      <c r="B894" s="7" t="inlineStr">
+        <is>
+          <t>일본</t>
+        </is>
+      </c>
+      <c r="C894" s="7" t="inlineStr">
+        <is>
+          <t>CPI 헤드라인</t>
+        </is>
+      </c>
+      <c r="D894" s="7">
+        <v>3.5</v>
+      </c>
       <c r="E894" s="6"/>
-      <c r="F894" s="7"/>
+      <c r="F894" s="7" t="inlineStr">
+        <is>
+          <t>월간</t>
+        </is>
+      </c>
     </row>
     <row r="895" spans="1:6">
-      <c r="A895" s="6"/>
-      <c r="B895" s="7"/>
-      <c r="C895" s="7"/>
-      <c r="D895" s="7"/>
+      <c r="A895" s="6">
+        <v>45809</v>
+      </c>
+      <c r="B895" s="7" t="inlineStr">
+        <is>
+          <t>일본</t>
+        </is>
+      </c>
+      <c r="C895" s="7" t="inlineStr">
+        <is>
+          <t>CPI 헤드라인</t>
+        </is>
+      </c>
+      <c r="D895" s="7">
+        <v>3.3</v>
+      </c>
       <c r="E895" s="6"/>
-      <c r="F895" s="7"/>
+      <c r="F895" s="7" t="inlineStr">
+        <is>
+          <t>월간</t>
+        </is>
+      </c>
     </row>
     <row r="896" spans="1:6">
-      <c r="A896" s="6"/>
-      <c r="B896" s="7"/>
-      <c r="C896" s="7"/>
-      <c r="D896" s="7"/>
+      <c r="A896" s="6">
+        <v>45839</v>
+      </c>
+      <c r="B896" s="7" t="inlineStr">
+        <is>
+          <t>일본</t>
+        </is>
+      </c>
+      <c r="C896" s="7" t="inlineStr">
+        <is>
+          <t>CPI 헤드라인</t>
+        </is>
+      </c>
+      <c r="D896" s="7">
+        <v>3.1</v>
+      </c>
       <c r="E896" s="6"/>
-      <c r="F896" s="7"/>
+      <c r="F896" s="7" t="inlineStr">
+        <is>
+          <t>월간</t>
+        </is>
+      </c>
     </row>
     <row r="897" spans="1:6">
-      <c r="A897" s="6"/>
-      <c r="B897" s="7"/>
-      <c r="C897" s="7"/>
-      <c r="D897" s="7"/>
+      <c r="A897" s="6">
+        <v>45870</v>
+      </c>
+      <c r="B897" s="7" t="inlineStr">
+        <is>
+          <t>일본</t>
+        </is>
+      </c>
+      <c r="C897" s="7" t="inlineStr">
+        <is>
+          <t>CPI 헤드라인</t>
+        </is>
+      </c>
+      <c r="D897" s="7">
+        <v>2.7</v>
+      </c>
       <c r="E897" s="6"/>
-      <c r="F897" s="7"/>
+      <c r="F897" s="7" t="inlineStr">
+        <is>
+          <t>월간</t>
+        </is>
+      </c>
     </row>
     <row r="898" spans="1:6">
-      <c r="A898" s="6"/>
-      <c r="B898" s="7"/>
-      <c r="C898" s="7"/>
-      <c r="D898" s="7"/>
+      <c r="A898" s="6">
+        <v>45901</v>
+      </c>
+      <c r="B898" s="7" t="inlineStr">
+        <is>
+          <t>일본</t>
+        </is>
+      </c>
+      <c r="C898" s="7" t="inlineStr">
+        <is>
+          <t>CPI 헤드라인</t>
+        </is>
+      </c>
+      <c r="D898" s="7">
+        <v>2.9</v>
+      </c>
       <c r="E898" s="6"/>
-      <c r="F898" s="7"/>
+      <c r="F898" s="7" t="inlineStr">
+        <is>
+          <t>월간</t>
+        </is>
+      </c>
     </row>
     <row r="899" spans="1:6">
-      <c r="A899" s="6"/>
-      <c r="B899" s="7"/>
-      <c r="C899" s="7"/>
-      <c r="D899" s="7"/>
+      <c r="A899" s="6">
+        <v>45931</v>
+      </c>
+      <c r="B899" s="7" t="inlineStr">
+        <is>
+          <t>일본</t>
+        </is>
+      </c>
+      <c r="C899" s="7" t="inlineStr">
+        <is>
+          <t>CPI 헤드라인</t>
+        </is>
+      </c>
+      <c r="D899" s="7">
+        <v>3.0</v>
+      </c>
       <c r="E899" s="6"/>
-      <c r="F899" s="7"/>
+      <c r="F899" s="7" t="inlineStr">
+        <is>
+          <t>월간</t>
+        </is>
+      </c>
     </row>
     <row r="900" spans="1:6">
-      <c r="A900" s="6"/>
-      <c r="B900" s="7"/>
-      <c r="C900" s="7"/>
-      <c r="D900" s="7"/>
+      <c r="A900" s="6">
+        <v>45962</v>
+      </c>
+      <c r="B900" s="7" t="inlineStr">
+        <is>
+          <t>일본</t>
+        </is>
+      </c>
+      <c r="C900" s="7" t="inlineStr">
+        <is>
+          <t>CPI 헤드라인</t>
+        </is>
+      </c>
+      <c r="D900" s="7">
+        <v>2.9</v>
+      </c>
       <c r="E900" s="6"/>
-      <c r="F900" s="7"/>
+      <c r="F900" s="7" t="inlineStr">
+        <is>
+          <t>월간</t>
+        </is>
+      </c>
     </row>
     <row r="901" spans="1:6">
-      <c r="A901" s="6"/>
-      <c r="B901" s="7"/>
-      <c r="C901" s="7"/>
-      <c r="D901" s="7"/>
+      <c r="A901" s="6">
+        <v>45992</v>
+      </c>
+      <c r="B901" s="7" t="inlineStr">
+        <is>
+          <t>일본</t>
+        </is>
+      </c>
+      <c r="C901" s="7" t="inlineStr">
+        <is>
+          <t>CPI 헤드라인</t>
+        </is>
+      </c>
+      <c r="D901" s="7">
+        <v>2.1</v>
+      </c>
       <c r="E901" s="6"/>
-      <c r="F901" s="7"/>
+      <c r="F901" s="7" t="inlineStr">
+        <is>
+          <t>월간</t>
+        </is>
+      </c>
     </row>
     <row r="902" spans="1:6">
-      <c r="A902" s="6"/>
-      <c r="B902" s="7"/>
-      <c r="C902" s="7"/>
-      <c r="D902" s="7"/>
+      <c r="A902" s="6">
+        <v>46023</v>
+      </c>
+      <c r="B902" s="7" t="inlineStr">
+        <is>
+          <t>일본</t>
+        </is>
+      </c>
+      <c r="C902" s="7" t="inlineStr">
+        <is>
+          <t>CPI 헤드라인</t>
+        </is>
+      </c>
+      <c r="D902" s="7">
+        <v>1.5</v>
+      </c>
       <c r="E902" s="6"/>
-      <c r="F902" s="7"/>
+      <c r="F902" s="7" t="inlineStr">
+        <is>
+          <t>월간</t>
+        </is>
+      </c>
     </row>
     <row r="903" spans="1:6">
-      <c r="A903" s="6"/>
-      <c r="B903" s="7"/>
-      <c r="C903" s="7"/>
-      <c r="D903" s="7"/>
+      <c r="A903" s="6">
+        <v>46054</v>
+      </c>
+      <c r="B903" s="7" t="inlineStr">
+        <is>
+          <t>일본</t>
+        </is>
+      </c>
+      <c r="C903" s="7" t="inlineStr">
+        <is>
+          <t>CPI 헤드라인</t>
+        </is>
+      </c>
+      <c r="D903" s="7">
+        <v>1.3</v>
+      </c>
       <c r="E903" s="6"/>
-      <c r="F903" s="7"/>
+      <c r="F903" s="7" t="inlineStr">
+        <is>
+          <t>월간</t>
+        </is>
+      </c>
     </row>
     <row r="904" spans="1:6">
-      <c r="A904" s="6"/>
-      <c r="B904" s="7"/>
-      <c r="C904" s="7"/>
-      <c r="D904" s="7"/>
+      <c r="A904" s="6">
+        <v>46082</v>
+      </c>
+      <c r="B904" s="7" t="inlineStr">
+        <is>
+          <t>일본</t>
+        </is>
+      </c>
+      <c r="C904" s="7" t="inlineStr">
+        <is>
+          <t>CPI 헤드라인</t>
+        </is>
+      </c>
+      <c r="D904" s="7">
+        <v>1.5</v>
+      </c>
       <c r="E904" s="6"/>
-      <c r="F904" s="7"/>
+      <c r="F904" s="7" t="inlineStr">
+        <is>
+          <t>월간</t>
+        </is>
+      </c>
     </row>
     <row r="905" spans="1:6">
-      <c r="A905" s="6"/>
-      <c r="B905" s="7"/>
-      <c r="C905" s="7"/>
-      <c r="D905" s="7"/>
+      <c r="A905" s="6">
+        <v>46113</v>
+      </c>
+      <c r="B905" s="7" t="inlineStr">
+        <is>
+          <t>일본</t>
+        </is>
+      </c>
+      <c r="C905" s="7" t="inlineStr">
+        <is>
+          <t>CPI 헤드라인</t>
+        </is>
+      </c>
+      <c r="D905" s="7">
+        <v>1.4</v>
+      </c>
       <c r="E905" s="6"/>
-      <c r="F905" s="7"/>
+      <c r="F905" s="7" t="inlineStr">
+        <is>
+          <t>월간</t>
+        </is>
+      </c>
     </row>
     <row r="906" spans="1:6">
-      <c r="A906" s="6"/>
-      <c r="B906" s="7"/>
-      <c r="C906" s="7"/>
-      <c r="D906" s="7"/>
+      <c r="A906" s="6">
+        <v>46143</v>
+      </c>
+      <c r="B906" s="7" t="inlineStr">
+        <is>
+          <t>일본</t>
+        </is>
+      </c>
+      <c r="C906" s="7" t="inlineStr">
+        <is>
+          <t>CPI 헤드라인</t>
+        </is>
+      </c>
+      <c r="D906" s="7">
+        <v>1.5</v>
+      </c>
       <c r="E906" s="6"/>
-      <c r="F906" s="7"/>
+      <c r="F906" s="7" t="inlineStr">
+        <is>
+          <t>월간</t>
+        </is>
+      </c>
     </row>
     <row r="907" spans="1:6">
-      <c r="A907" s="6"/>
-      <c r="B907" s="7"/>
-      <c r="C907" s="7"/>
-      <c r="D907" s="7"/>
+      <c r="A907" s="6">
+        <v>46174</v>
+      </c>
+      <c r="B907" s="7" t="inlineStr">
+        <is>
+          <t>일본</t>
+        </is>
+      </c>
+      <c r="C907" s="7" t="inlineStr">
+        <is>
+          <t>CPI 헤드라인</t>
+        </is>
+      </c>
+      <c r="D907" s="7">
+        <v>1.6</v>
+      </c>
       <c r="E907" s="6"/>
-      <c r="F907" s="7"/>
+      <c r="F907" s="7" t="inlineStr">
+        <is>
+          <t>월간</t>
+        </is>
+      </c>
     </row>
     <row r="908" spans="1:6">
-      <c r="A908" s="6"/>
-      <c r="B908" s="7"/>
-      <c r="C908" s="7"/>
-      <c r="D908" s="7"/>
+      <c r="A908" s="6">
+        <v>46204</v>
+      </c>
+      <c r="B908" s="7" t="inlineStr">
+        <is>
+          <t>일본</t>
+        </is>
+      </c>
+      <c r="C908" s="7" t="inlineStr">
+        <is>
+          <t>CPI 헤드라인</t>
+        </is>
+      </c>
+      <c r="D908" s="7">
+        <v>1.9</v>
+      </c>
       <c r="E908" s="6"/>
-      <c r="F908" s="7"/>
+      <c r="F908" s="7" t="inlineStr">
+        <is>
+          <t>월간</t>
+        </is>
+      </c>
     </row>
     <row r="909" spans="1:6">
-      <c r="A909" s="6"/>
-      <c r="B909" s="7"/>
-      <c r="C909" s="7"/>
-      <c r="D909" s="7"/>
+      <c r="A909" s="6">
+        <v>44440</v>
+      </c>
+      <c r="B909" s="7" t="inlineStr">
+        <is>
+          <t>일본</t>
+        </is>
+      </c>
+      <c r="C909" s="7" t="inlineStr">
+        <is>
+          <t>CPI 근원</t>
+        </is>
+      </c>
+      <c r="D909" s="7">
+        <v>0.1</v>
+      </c>
       <c r="E909" s="6"/>
-      <c r="F909" s="7"/>
+      <c r="F909" s="7" t="inlineStr">
+        <is>
+          <t>월간</t>
+        </is>
+      </c>
     </row>
     <row r="910" spans="1:6">
-      <c r="A910" s="6"/>
-      <c r="B910" s="7"/>
-      <c r="C910" s="7"/>
-      <c r="D910" s="7"/>
+      <c r="A910" s="6">
+        <v>44470</v>
+      </c>
+      <c r="B910" s="7" t="inlineStr">
+        <is>
+          <t>일본</t>
+        </is>
+      </c>
+      <c r="C910" s="7" t="inlineStr">
+        <is>
+          <t>CPI 근원</t>
+        </is>
+      </c>
+      <c r="D910" s="7">
+        <v>0.1</v>
+      </c>
       <c r="E910" s="6"/>
-      <c r="F910" s="7"/>
+      <c r="F910" s="7" t="inlineStr">
+        <is>
+          <t>월간</t>
+        </is>
+      </c>
     </row>
     <row r="911" spans="1:6">
-      <c r="A911" s="6"/>
-      <c r="B911" s="7"/>
-      <c r="C911" s="7"/>
-      <c r="D911" s="7"/>
+      <c r="A911" s="6">
+        <v>44501</v>
+      </c>
+      <c r="B911" s="7" t="inlineStr">
+        <is>
+          <t>일본</t>
+        </is>
+      </c>
+      <c r="C911" s="7" t="inlineStr">
+        <is>
+          <t>CPI 근원</t>
+        </is>
+      </c>
+      <c r="D911" s="7">
+        <v>0.5</v>
+      </c>
       <c r="E911" s="6"/>
-      <c r="F911" s="7"/>
+      <c r="F911" s="7" t="inlineStr">
+        <is>
+          <t>월간</t>
+        </is>
+      </c>
     </row>
     <row r="912" spans="1:6">
-      <c r="A912" s="6"/>
-      <c r="B912" s="7"/>
-      <c r="C912" s="7"/>
-      <c r="D912" s="7"/>
+      <c r="A912" s="6">
+        <v>44531</v>
+      </c>
+      <c r="B912" s="7" t="inlineStr">
+        <is>
+          <t>일본</t>
+        </is>
+      </c>
+      <c r="C912" s="7" t="inlineStr">
+        <is>
+          <t>CPI 근원</t>
+        </is>
+      </c>
+      <c r="D912" s="7">
+        <v>0.5</v>
+      </c>
       <c r="E912" s="6"/>
-      <c r="F912" s="7"/>
+      <c r="F912" s="7" t="inlineStr">
+        <is>
+          <t>월간</t>
+        </is>
+      </c>
     </row>
     <row r="913" spans="1:6">
-      <c r="A913" s="6"/>
-      <c r="B913" s="7"/>
-      <c r="C913" s="7"/>
-      <c r="D913" s="7"/>
+      <c r="A913" s="6">
+        <v>44562</v>
+      </c>
+      <c r="B913" s="7" t="inlineStr">
+        <is>
+          <t>일본</t>
+        </is>
+      </c>
+      <c r="C913" s="7" t="inlineStr">
+        <is>
+          <t>CPI 근원</t>
+        </is>
+      </c>
+      <c r="D913" s="7">
+        <v>0.2</v>
+      </c>
       <c r="E913" s="6"/>
-      <c r="F913" s="7"/>
+      <c r="F913" s="7" t="inlineStr">
+        <is>
+          <t>월간</t>
+        </is>
+      </c>
     </row>
     <row r="914" spans="1:6">
-      <c r="A914" s="6"/>
-      <c r="B914" s="7"/>
-      <c r="C914" s="7"/>
-      <c r="D914" s="7"/>
+      <c r="A914" s="6">
+        <v>44593</v>
+      </c>
+      <c r="B914" s="7" t="inlineStr">
+        <is>
+          <t>일본</t>
+        </is>
+      </c>
+      <c r="C914" s="7" t="inlineStr">
+        <is>
+          <t>CPI 근원</t>
+        </is>
+      </c>
+      <c r="D914" s="7">
+        <v>0.6</v>
+      </c>
       <c r="E914" s="6"/>
-      <c r="F914" s="7"/>
+      <c r="F914" s="7" t="inlineStr">
+        <is>
+          <t>월간</t>
+        </is>
+      </c>
     </row>
     <row r="915" spans="1:6">
-      <c r="A915" s="6"/>
-      <c r="B915" s="7"/>
-      <c r="C915" s="7"/>
-      <c r="D915" s="7"/>
+      <c r="A915" s="6">
+        <v>44621</v>
+      </c>
+      <c r="B915" s="7" t="inlineStr">
+        <is>
+          <t>일본</t>
+        </is>
+      </c>
+      <c r="C915" s="7" t="inlineStr">
+        <is>
+          <t>CPI 근원</t>
+        </is>
+      </c>
+      <c r="D915" s="7">
+        <v>0.8</v>
+      </c>
       <c r="E915" s="6"/>
-      <c r="F915" s="7"/>
+      <c r="F915" s="7" t="inlineStr">
+        <is>
+          <t>월간</t>
+        </is>
+      </c>
     </row>
     <row r="916" spans="1:6">
-      <c r="A916" s="6"/>
-      <c r="B916" s="7"/>
-      <c r="C916" s="7"/>
-      <c r="D916" s="7"/>
+      <c r="A916" s="6">
+        <v>44652</v>
+      </c>
+      <c r="B916" s="7" t="inlineStr">
+        <is>
+          <t>일본</t>
+        </is>
+      </c>
+      <c r="C916" s="7" t="inlineStr">
+        <is>
+          <t>CPI 근원</t>
+        </is>
+      </c>
+      <c r="D916" s="7">
+        <v>2.1</v>
+      </c>
       <c r="E916" s="6"/>
-      <c r="F916" s="7"/>
+      <c r="F916" s="7" t="inlineStr">
+        <is>
+          <t>월간</t>
+        </is>
+      </c>
     </row>
     <row r="917" spans="1:6">
-      <c r="A917" s="6"/>
-      <c r="B917" s="7"/>
-      <c r="C917" s="7"/>
-      <c r="D917" s="7"/>
+      <c r="A917" s="6">
+        <v>44682</v>
+      </c>
+      <c r="B917" s="7" t="inlineStr">
+        <is>
+          <t>일본</t>
+        </is>
+      </c>
+      <c r="C917" s="7" t="inlineStr">
+        <is>
+          <t>CPI 근원</t>
+        </is>
+      </c>
+      <c r="D917" s="7">
+        <v>2.1</v>
+      </c>
       <c r="E917" s="6"/>
-      <c r="F917" s="7"/>
+      <c r="F917" s="7" t="inlineStr">
+        <is>
+          <t>월간</t>
+        </is>
+      </c>
     </row>
     <row r="918" spans="1:6">
-      <c r="A918" s="6"/>
-      <c r="B918" s="7"/>
-      <c r="C918" s="7"/>
-      <c r="D918" s="7"/>
+      <c r="A918" s="6">
+        <v>44713</v>
+      </c>
+      <c r="B918" s="7" t="inlineStr">
+        <is>
+          <t>일본</t>
+        </is>
+      </c>
+      <c r="C918" s="7" t="inlineStr">
+        <is>
+          <t>CPI 근원</t>
+        </is>
+      </c>
+      <c r="D918" s="7">
+        <v>2.2</v>
+      </c>
       <c r="E918" s="6"/>
-      <c r="F918" s="7"/>
+      <c r="F918" s="7" t="inlineStr">
+        <is>
+          <t>월간</t>
+        </is>
+      </c>
     </row>
     <row r="919" spans="1:6">
-      <c r="A919" s="6"/>
-      <c r="B919" s="7"/>
-      <c r="C919" s="7"/>
-      <c r="D919" s="7"/>
+      <c r="A919" s="6">
+        <v>44743</v>
+      </c>
+      <c r="B919" s="7" t="inlineStr">
+        <is>
+          <t>일본</t>
+        </is>
+      </c>
+      <c r="C919" s="7" t="inlineStr">
+        <is>
+          <t>CPI 근원</t>
+        </is>
+      </c>
+      <c r="D919" s="7">
+        <v>2.4</v>
+      </c>
       <c r="E919" s="6"/>
-      <c r="F919" s="7"/>
+      <c r="F919" s="7" t="inlineStr">
+        <is>
+          <t>월간</t>
+        </is>
+      </c>
     </row>
     <row r="920" spans="1:6">
-      <c r="A920" s="6"/>
-      <c r="B920" s="7"/>
-      <c r="C920" s="7"/>
-      <c r="D920" s="7"/>
+      <c r="A920" s="6">
+        <v>44774</v>
+      </c>
+      <c r="B920" s="7" t="inlineStr">
+        <is>
+          <t>일본</t>
+        </is>
+      </c>
+      <c r="C920" s="7" t="inlineStr">
+        <is>
+          <t>CPI 근원</t>
+        </is>
+      </c>
+      <c r="D920" s="7">
+        <v>2.8</v>
+      </c>
       <c r="E920" s="6"/>
-      <c r="F920" s="7"/>
+      <c r="F920" s="7" t="inlineStr">
+        <is>
+          <t>월간</t>
+        </is>
+      </c>
     </row>
     <row r="921" spans="1:6">
-      <c r="A921" s="6"/>
-      <c r="B921" s="7"/>
-      <c r="C921" s="7"/>
-      <c r="D921" s="7"/>
+      <c r="A921" s="6">
+        <v>44805</v>
+      </c>
+      <c r="B921" s="7" t="inlineStr">
+        <is>
+          <t>일본</t>
+        </is>
+      </c>
+      <c r="C921" s="7" t="inlineStr">
+        <is>
+          <t>CPI 근원</t>
+        </is>
+      </c>
+      <c r="D921" s="7">
+        <v>3.0</v>
+      </c>
       <c r="E921" s="6"/>
-      <c r="F921" s="7"/>
+      <c r="F921" s="7" t="inlineStr">
+        <is>
+          <t>월간</t>
+        </is>
+      </c>
     </row>
     <row r="922" spans="1:6">
-      <c r="A922" s="6"/>
-      <c r="B922" s="7"/>
-      <c r="C922" s="7"/>
-      <c r="D922" s="7"/>
+      <c r="A922" s="6">
+        <v>44835</v>
+      </c>
+      <c r="B922" s="7" t="inlineStr">
+        <is>
+          <t>일본</t>
+        </is>
+      </c>
+      <c r="C922" s="7" t="inlineStr">
+        <is>
+          <t>CPI 근원</t>
+        </is>
+      </c>
+      <c r="D922" s="7">
+        <v>3.6</v>
+      </c>
       <c r="E922" s="6"/>
-      <c r="F922" s="7"/>
+      <c r="F922" s="7" t="inlineStr">
+        <is>
+          <t>월간</t>
+        </is>
+      </c>
     </row>
     <row r="923" spans="1:6">
-      <c r="A923" s="6"/>
-      <c r="B923" s="7"/>
-      <c r="C923" s="7"/>
-      <c r="D923" s="7"/>
+      <c r="A923" s="6">
+        <v>44866</v>
+      </c>
+      <c r="B923" s="7" t="inlineStr">
+        <is>
+          <t>일본</t>
+        </is>
+      </c>
+      <c r="C923" s="7" t="inlineStr">
+        <is>
+          <t>CPI 근원</t>
+        </is>
+      </c>
+      <c r="D923" s="7">
+        <v>3.7</v>
+      </c>
       <c r="E923" s="6"/>
-      <c r="F923" s="7"/>
+      <c r="F923" s="7" t="inlineStr">
+        <is>
+          <t>월간</t>
+        </is>
+      </c>
     </row>
     <row r="924" spans="1:6">
-      <c r="A924" s="6"/>
-      <c r="B924" s="7"/>
-      <c r="C924" s="7"/>
-      <c r="D924" s="7"/>
+      <c r="A924" s="6">
+        <v>44896</v>
+      </c>
+      <c r="B924" s="7" t="inlineStr">
+        <is>
+          <t>일본</t>
+        </is>
+      </c>
+      <c r="C924" s="7" t="inlineStr">
+        <is>
+          <t>CPI 근원</t>
+        </is>
+      </c>
+      <c r="D924" s="7">
+        <v>4.0</v>
+      </c>
       <c r="E924" s="6"/>
-      <c r="F924" s="7"/>
+      <c r="F924" s="7" t="inlineStr">
+        <is>
+          <t>월간</t>
+        </is>
+      </c>
     </row>
     <row r="925" spans="1:6">
-      <c r="A925" s="6"/>
-      <c r="B925" s="7"/>
-      <c r="C925" s="7"/>
-      <c r="D925" s="7"/>
+      <c r="A925" s="6">
+        <v>44927</v>
+      </c>
+      <c r="B925" s="7" t="inlineStr">
+        <is>
+          <t>일본</t>
+        </is>
+      </c>
+      <c r="C925" s="7" t="inlineStr">
+        <is>
+          <t>CPI 근원</t>
+        </is>
+      </c>
+      <c r="D925" s="7">
+        <v>4.2</v>
+      </c>
       <c r="E925" s="6"/>
-      <c r="F925" s="7"/>
+      <c r="F925" s="7" t="inlineStr">
+        <is>
+          <t>월간</t>
+        </is>
+      </c>
     </row>
     <row r="926" spans="1:6">
-      <c r="A926" s="6"/>
-      <c r="B926" s="7"/>
-      <c r="C926" s="7"/>
-      <c r="D926" s="7"/>
+      <c r="A926" s="6">
+        <v>44958</v>
+      </c>
+      <c r="B926" s="7" t="inlineStr">
+        <is>
+          <t>일본</t>
+        </is>
+      </c>
+      <c r="C926" s="7" t="inlineStr">
+        <is>
+          <t>CPI 근원</t>
+        </is>
+      </c>
+      <c r="D926" s="7">
+        <v>3.1</v>
+      </c>
       <c r="E926" s="6"/>
-      <c r="F926" s="7"/>
+      <c r="F926" s="7" t="inlineStr">
+        <is>
+          <t>월간</t>
+        </is>
+      </c>
     </row>
     <row r="927" spans="1:6">
-      <c r="A927" s="6"/>
-      <c r="B927" s="7"/>
-      <c r="C927" s="7"/>
-      <c r="D927" s="7"/>
+      <c r="A927" s="6">
+        <v>44986</v>
+      </c>
+      <c r="B927" s="7" t="inlineStr">
+        <is>
+          <t>일본</t>
+        </is>
+      </c>
+      <c r="C927" s="7" t="inlineStr">
+        <is>
+          <t>CPI 근원</t>
+        </is>
+      </c>
+      <c r="D927" s="7">
+        <v>3.1</v>
+      </c>
       <c r="E927" s="6"/>
-      <c r="F927" s="7"/>
+      <c r="F927" s="7" t="inlineStr">
+        <is>
+          <t>월간</t>
+        </is>
+      </c>
     </row>
     <row r="928" spans="1:6">
-      <c r="A928" s="6"/>
-      <c r="B928" s="7"/>
-      <c r="C928" s="7"/>
-      <c r="D928" s="7"/>
+      <c r="A928" s="6">
+        <v>45017</v>
+      </c>
+      <c r="B928" s="7" t="inlineStr">
+        <is>
+          <t>일본</t>
+        </is>
+      </c>
+      <c r="C928" s="7" t="inlineStr">
+        <is>
+          <t>CPI 근원</t>
+        </is>
+      </c>
+      <c r="D928" s="7">
+        <v>3.4</v>
+      </c>
       <c r="E928" s="6"/>
-      <c r="F928" s="7"/>
+      <c r="F928" s="7" t="inlineStr">
+        <is>
+          <t>월간</t>
+        </is>
+      </c>
     </row>
     <row r="929" spans="1:6">
-      <c r="A929" s="6"/>
-      <c r="B929" s="7"/>
-      <c r="C929" s="7"/>
-      <c r="D929" s="7"/>
+      <c r="A929" s="6">
+        <v>45047</v>
+      </c>
+      <c r="B929" s="7" t="inlineStr">
+        <is>
+          <t>일본</t>
+        </is>
+      </c>
+      <c r="C929" s="7" t="inlineStr">
+        <is>
+          <t>CPI 근원</t>
+        </is>
+      </c>
+      <c r="D929" s="7">
+        <v>3.2</v>
+      </c>
       <c r="E929" s="6"/>
-      <c r="F929" s="7"/>
+      <c r="F929" s="7" t="inlineStr">
+        <is>
+          <t>월간</t>
+        </is>
+      </c>
     </row>
     <row r="930" spans="1:6">
-      <c r="A930" s="6"/>
-      <c r="B930" s="7"/>
-      <c r="C930" s="7"/>
-      <c r="D930" s="7"/>
+      <c r="A930" s="6">
+        <v>45078</v>
+      </c>
+      <c r="B930" s="7" t="inlineStr">
+        <is>
+          <t>일본</t>
+        </is>
+      </c>
+      <c r="C930" s="7" t="inlineStr">
+        <is>
+          <t>CPI 근원</t>
+        </is>
+      </c>
+      <c r="D930" s="7">
+        <v>3.3</v>
+      </c>
       <c r="E930" s="6"/>
-      <c r="F930" s="7"/>
+      <c r="F930" s="7" t="inlineStr">
+        <is>
+          <t>월간</t>
+        </is>
+      </c>
     </row>
     <row r="931" spans="1:6">
-      <c r="A931" s="6"/>
-      <c r="B931" s="7"/>
-      <c r="C931" s="7"/>
-      <c r="D931" s="7"/>
+      <c r="A931" s="6">
+        <v>45108</v>
+      </c>
+      <c r="B931" s="7" t="inlineStr">
+        <is>
+          <t>일본</t>
+        </is>
+      </c>
+      <c r="C931" s="7" t="inlineStr">
+        <is>
+          <t>CPI 근원</t>
+        </is>
+      </c>
+      <c r="D931" s="7">
+        <v>3.1</v>
+      </c>
       <c r="E931" s="6"/>
-      <c r="F931" s="7"/>
+      <c r="F931" s="7" t="inlineStr">
+        <is>
+          <t>월간</t>
+        </is>
+      </c>
     </row>
     <row r="932" spans="1:6">
-      <c r="A932" s="6"/>
-      <c r="B932" s="7"/>
-      <c r="C932" s="7"/>
-      <c r="D932" s="7"/>
+      <c r="A932" s="6">
+        <v>45139</v>
+      </c>
+      <c r="B932" s="7" t="inlineStr">
+        <is>
+          <t>일본</t>
+        </is>
+      </c>
+      <c r="C932" s="7" t="inlineStr">
+        <is>
+          <t>CPI 근원</t>
+        </is>
+      </c>
+      <c r="D932" s="7">
+        <v>3.1</v>
+      </c>
       <c r="E932" s="6"/>
-      <c r="F932" s="7"/>
+      <c r="F932" s="7" t="inlineStr">
+        <is>
+          <t>월간</t>
+        </is>
+      </c>
     </row>
     <row r="933" spans="1:6">
-      <c r="A933" s="6"/>
-      <c r="B933" s="7"/>
-      <c r="C933" s="7"/>
-      <c r="D933" s="7"/>
+      <c r="A933" s="6">
+        <v>45170</v>
+      </c>
+      <c r="B933" s="7" t="inlineStr">
+        <is>
+          <t>일본</t>
+        </is>
+      </c>
+      <c r="C933" s="7" t="inlineStr">
+        <is>
+          <t>CPI 근원</t>
+        </is>
+      </c>
+      <c r="D933" s="7">
+        <v>2.8</v>
+      </c>
       <c r="E933" s="6"/>
-      <c r="F933" s="7"/>
+      <c r="F933" s="7" t="inlineStr">
+        <is>
+          <t>월간</t>
+        </is>
+      </c>
     </row>
     <row r="934" spans="1:6">
-      <c r="A934" s="6"/>
-      <c r="B934" s="7"/>
-      <c r="C934" s="7"/>
-      <c r="D934" s="7"/>
+      <c r="A934" s="6">
+        <v>45200</v>
+      </c>
+      <c r="B934" s="7" t="inlineStr">
+        <is>
+          <t>일본</t>
+        </is>
+      </c>
+      <c r="C934" s="7" t="inlineStr">
+        <is>
+          <t>CPI 근원</t>
+        </is>
+      </c>
+      <c r="D934" s="7">
+        <v>2.9</v>
+      </c>
       <c r="E934" s="6"/>
-      <c r="F934" s="7"/>
+      <c r="F934" s="7" t="inlineStr">
+        <is>
+          <t>월간</t>
+        </is>
+      </c>
     </row>
     <row r="935" spans="1:6">
-      <c r="A935" s="6"/>
-      <c r="B935" s="7"/>
-      <c r="C935" s="7"/>
-      <c r="D935" s="7"/>
+      <c r="A935" s="6">
+        <v>45231</v>
+      </c>
+      <c r="B935" s="7" t="inlineStr">
+        <is>
+          <t>일본</t>
+        </is>
+      </c>
+      <c r="C935" s="7" t="inlineStr">
+        <is>
+          <t>CPI 근원</t>
+        </is>
+      </c>
+      <c r="D935" s="7">
+        <v>2.5</v>
+      </c>
       <c r="E935" s="6"/>
-      <c r="F935" s="7"/>
+      <c r="F935" s="7" t="inlineStr">
+        <is>
+          <t>월간</t>
+        </is>
+      </c>
     </row>
     <row r="936" spans="1:6">
-      <c r="A936" s="6"/>
-      <c r="B936" s="7"/>
-      <c r="C936" s="7"/>
-      <c r="D936" s="7"/>
+      <c r="A936" s="6">
+        <v>45261</v>
+      </c>
+      <c r="B936" s="7" t="inlineStr">
+        <is>
+          <t>일본</t>
+        </is>
+      </c>
+      <c r="C936" s="7" t="inlineStr">
+        <is>
+          <t>CPI 근원</t>
+        </is>
+      </c>
+      <c r="D936" s="7">
+        <v>2.3</v>
+      </c>
       <c r="E936" s="6"/>
-      <c r="F936" s="7"/>
+      <c r="F936" s="7" t="inlineStr">
+        <is>
+          <t>월간</t>
+        </is>
+      </c>
     </row>
     <row r="937" spans="1:6">
-      <c r="A937" s="6"/>
-      <c r="B937" s="7"/>
-      <c r="C937" s="7"/>
-      <c r="D937" s="7"/>
+      <c r="A937" s="6">
+        <v>45292</v>
+      </c>
+      <c r="B937" s="7" t="inlineStr">
+        <is>
+          <t>일본</t>
+        </is>
+      </c>
+      <c r="C937" s="7" t="inlineStr">
+        <is>
+          <t>CPI 근원</t>
+        </is>
+      </c>
+      <c r="D937" s="7">
+        <v>2.0</v>
+      </c>
       <c r="E937" s="6"/>
-      <c r="F937" s="7"/>
+      <c r="F937" s="7" t="inlineStr">
+        <is>
+          <t>월간</t>
+        </is>
+      </c>
     </row>
     <row r="938" spans="1:6">
-      <c r="A938" s="6"/>
-      <c r="B938" s="7"/>
-      <c r="C938" s="7"/>
-      <c r="D938" s="7"/>
+      <c r="A938" s="6">
+        <v>45323</v>
+      </c>
+      <c r="B938" s="7" t="inlineStr">
+        <is>
+          <t>일본</t>
+        </is>
+      </c>
+      <c r="C938" s="7" t="inlineStr">
+        <is>
+          <t>CPI 근원</t>
+        </is>
+      </c>
+      <c r="D938" s="7">
+        <v>2.8</v>
+      </c>
       <c r="E938" s="6"/>
-      <c r="F938" s="7"/>
+      <c r="F938" s="7" t="inlineStr">
+        <is>
+          <t>월간</t>
+        </is>
+      </c>
     </row>
     <row r="939" spans="1:6">
-      <c r="A939" s="6"/>
-      <c r="B939" s="7"/>
-      <c r="C939" s="7"/>
-      <c r="D939" s="7"/>
+      <c r="A939" s="6">
+        <v>45352</v>
+      </c>
+      <c r="B939" s="7" t="inlineStr">
+        <is>
+          <t>일본</t>
+        </is>
+      </c>
+      <c r="C939" s="7" t="inlineStr">
+        <is>
+          <t>CPI 근원</t>
+        </is>
+      </c>
+      <c r="D939" s="7">
+        <v>2.6</v>
+      </c>
       <c r="E939" s="6"/>
-      <c r="F939" s="7"/>
+      <c r="F939" s="7" t="inlineStr">
+        <is>
+          <t>월간</t>
+        </is>
+      </c>
     </row>
     <row r="940" spans="1:6">
-      <c r="A940" s="6"/>
-      <c r="B940" s="7"/>
-      <c r="C940" s="7"/>
-      <c r="D940" s="7"/>
+      <c r="A940" s="6">
+        <v>45383</v>
+      </c>
+      <c r="B940" s="7" t="inlineStr">
+        <is>
+          <t>일본</t>
+        </is>
+      </c>
+      <c r="C940" s="7" t="inlineStr">
+        <is>
+          <t>CPI 근원</t>
+        </is>
+      </c>
+      <c r="D940" s="7">
+        <v>2.2</v>
+      </c>
       <c r="E940" s="6"/>
-      <c r="F940" s="7"/>
+      <c r="F940" s="7" t="inlineStr">
+        <is>
+          <t>월간</t>
+        </is>
+      </c>
     </row>
     <row r="941" spans="1:6">
-      <c r="A941" s="6"/>
-      <c r="B941" s="7"/>
-      <c r="C941" s="7"/>
-      <c r="D941" s="7"/>
+      <c r="A941" s="6">
+        <v>45413</v>
+      </c>
+      <c r="B941" s="7" t="inlineStr">
+        <is>
+          <t>일본</t>
+        </is>
+      </c>
+      <c r="C941" s="7" t="inlineStr">
+        <is>
+          <t>CPI 근원</t>
+        </is>
+      </c>
+      <c r="D941" s="7">
+        <v>2.5</v>
+      </c>
       <c r="E941" s="6"/>
-      <c r="F941" s="7"/>
+      <c r="F941" s="7" t="inlineStr">
+        <is>
+          <t>월간</t>
+        </is>
+      </c>
     </row>
     <row r="942" spans="1:6">
-      <c r="A942" s="6"/>
-      <c r="B942" s="7"/>
-      <c r="C942" s="7"/>
-      <c r="D942" s="7"/>
+      <c r="A942" s="6">
+        <v>45444</v>
+      </c>
+      <c r="B942" s="7" t="inlineStr">
+        <is>
+          <t>일본</t>
+        </is>
+      </c>
+      <c r="C942" s="7" t="inlineStr">
+        <is>
+          <t>CPI 근원</t>
+        </is>
+      </c>
+      <c r="D942" s="7">
+        <v>2.6</v>
+      </c>
       <c r="E942" s="6"/>
-      <c r="F942" s="7"/>
+      <c r="F942" s="7" t="inlineStr">
+        <is>
+          <t>월간</t>
+        </is>
+      </c>
     </row>
     <row r="943" spans="1:6">
-      <c r="A943" s="6"/>
-      <c r="B943" s="7"/>
-      <c r="C943" s="7"/>
-      <c r="D943" s="7"/>
+      <c r="A943" s="6">
+        <v>45474</v>
+      </c>
+      <c r="B943" s="7" t="inlineStr">
+        <is>
+          <t>일본</t>
+        </is>
+      </c>
+      <c r="C943" s="7" t="inlineStr">
+        <is>
+          <t>CPI 근원</t>
+        </is>
+      </c>
+      <c r="D943" s="7">
+        <v>2.7</v>
+      </c>
       <c r="E943" s="6"/>
-      <c r="F943" s="7"/>
+      <c r="F943" s="7" t="inlineStr">
+        <is>
+          <t>월간</t>
+        </is>
+      </c>
     </row>
     <row r="944" spans="1:6">
-      <c r="A944" s="6"/>
-      <c r="B944" s="7"/>
-      <c r="C944" s="7"/>
-      <c r="D944" s="7"/>
+      <c r="A944" s="6">
+        <v>45505</v>
+      </c>
+      <c r="B944" s="7" t="inlineStr">
+        <is>
+          <t>일본</t>
+        </is>
+      </c>
+      <c r="C944" s="7" t="inlineStr">
+        <is>
+          <t>CPI 근원</t>
+        </is>
+      </c>
+      <c r="D944" s="7">
+        <v>2.8</v>
+      </c>
       <c r="E944" s="6"/>
-      <c r="F944" s="7"/>
+      <c r="F944" s="7" t="inlineStr">
+        <is>
+          <t>월간</t>
+        </is>
+      </c>
     </row>
     <row r="945" spans="1:6">
-      <c r="A945" s="6"/>
-      <c r="B945" s="7"/>
-      <c r="C945" s="7"/>
-      <c r="D945" s="7"/>
+      <c r="A945" s="6">
+        <v>45536</v>
+      </c>
+      <c r="B945" s="7" t="inlineStr">
+        <is>
+          <t>일본</t>
+        </is>
+      </c>
+      <c r="C945" s="7" t="inlineStr">
+        <is>
+          <t>CPI 근원</t>
+        </is>
+      </c>
+      <c r="D945" s="7">
+        <v>2.4</v>
+      </c>
       <c r="E945" s="6"/>
-      <c r="F945" s="7"/>
+      <c r="F945" s="7" t="inlineStr">
+        <is>
+          <t>월간</t>
+        </is>
+      </c>
     </row>
     <row r="946" spans="1:6">
-      <c r="A946" s="6"/>
-      <c r="B946" s="7"/>
-      <c r="C946" s="7"/>
-      <c r="D946" s="7"/>
+      <c r="A946" s="6">
+        <v>45566</v>
+      </c>
+      <c r="B946" s="7" t="inlineStr">
+        <is>
+          <t>일본</t>
+        </is>
+      </c>
+      <c r="C946" s="7" t="inlineStr">
+        <is>
+          <t>CPI 근원</t>
+        </is>
+      </c>
+      <c r="D946" s="7">
+        <v>2.3</v>
+      </c>
       <c r="E946" s="6"/>
-      <c r="F946" s="7"/>
+      <c r="F946" s="7" t="inlineStr">
+        <is>
+          <t>월간</t>
+        </is>
+      </c>
     </row>
     <row r="947" spans="1:6">
-      <c r="A947" s="6"/>
-      <c r="B947" s="7"/>
-      <c r="C947" s="7"/>
-      <c r="D947" s="7"/>
+      <c r="A947" s="6">
+        <v>45597</v>
+      </c>
+      <c r="B947" s="7" t="inlineStr">
+        <is>
+          <t>일본</t>
+        </is>
+      </c>
+      <c r="C947" s="7" t="inlineStr">
+        <is>
+          <t>CPI 근원</t>
+        </is>
+      </c>
+      <c r="D947" s="7">
+        <v>2.7</v>
+      </c>
       <c r="E947" s="6"/>
-      <c r="F947" s="7"/>
+      <c r="F947" s="7" t="inlineStr">
+        <is>
+          <t>월간</t>
+        </is>
+      </c>
     </row>
     <row r="948" spans="1:6">
-      <c r="A948" s="6"/>
-      <c r="B948" s="7"/>
-      <c r="C948" s="7"/>
-      <c r="D948" s="7"/>
+      <c r="A948" s="6">
+        <v>45627</v>
+      </c>
+      <c r="B948" s="7" t="inlineStr">
+        <is>
+          <t>일본</t>
+        </is>
+      </c>
+      <c r="C948" s="7" t="inlineStr">
+        <is>
+          <t>CPI 근원</t>
+        </is>
+      </c>
+      <c r="D948" s="7">
+        <v>3.0</v>
+      </c>
       <c r="E948" s="6"/>
-      <c r="F948" s="7"/>
+      <c r="F948" s="7" t="inlineStr">
+        <is>
+          <t>월간</t>
+        </is>
+      </c>
     </row>
     <row r="949" spans="1:6">
-      <c r="A949" s="6"/>
-      <c r="B949" s="7"/>
-      <c r="C949" s="7"/>
-      <c r="D949" s="7"/>
+      <c r="A949" s="6">
+        <v>45658</v>
+      </c>
+      <c r="B949" s="7" t="inlineStr">
+        <is>
+          <t>일본</t>
+        </is>
+      </c>
+      <c r="C949" s="7" t="inlineStr">
+        <is>
+          <t>CPI 근원</t>
+        </is>
+      </c>
+      <c r="D949" s="7">
+        <v>3.2</v>
+      </c>
       <c r="E949" s="6"/>
-      <c r="F949" s="7"/>
+      <c r="F949" s="7" t="inlineStr">
+        <is>
+          <t>월간</t>
+        </is>
+      </c>
     </row>
     <row r="950" spans="1:6">
-      <c r="A950" s="6"/>
-      <c r="B950" s="7"/>
-      <c r="C950" s="7"/>
-      <c r="D950" s="7"/>
+      <c r="A950" s="6">
+        <v>45689</v>
+      </c>
+      <c r="B950" s="7" t="inlineStr">
+        <is>
+          <t>일본</t>
+        </is>
+      </c>
+      <c r="C950" s="7" t="inlineStr">
+        <is>
+          <t>CPI 근원</t>
+        </is>
+      </c>
+      <c r="D950" s="7">
+        <v>3.0</v>
+      </c>
       <c r="E950" s="6"/>
-      <c r="F950" s="7"/>
+      <c r="F950" s="7" t="inlineStr">
+        <is>
+          <t>월간</t>
+        </is>
+      </c>
     </row>
     <row r="951" spans="1:6">
-      <c r="A951" s="6"/>
-      <c r="B951" s="7"/>
-      <c r="C951" s="7"/>
-      <c r="D951" s="7"/>
+      <c r="A951" s="6">
+        <v>45717</v>
+      </c>
+      <c r="B951" s="7" t="inlineStr">
+        <is>
+          <t>일본</t>
+        </is>
+      </c>
+      <c r="C951" s="7" t="inlineStr">
+        <is>
+          <t>CPI 근원</t>
+        </is>
+      </c>
+      <c r="D951" s="7">
+        <v>3.2</v>
+      </c>
       <c r="E951" s="6"/>
-      <c r="F951" s="7"/>
+      <c r="F951" s="7" t="inlineStr">
+        <is>
+          <t>월간</t>
+        </is>
+      </c>
     </row>
     <row r="952" spans="1:6">
-      <c r="A952" s="6"/>
-      <c r="B952" s="7"/>
-      <c r="C952" s="7"/>
-      <c r="D952" s="7"/>
+      <c r="A952" s="6">
+        <v>45748</v>
+      </c>
+      <c r="B952" s="7" t="inlineStr">
+        <is>
+          <t>일본</t>
+        </is>
+      </c>
+      <c r="C952" s="7" t="inlineStr">
+        <is>
+          <t>CPI 근원</t>
+        </is>
+      </c>
+      <c r="D952" s="7">
+        <v>3.5</v>
+      </c>
       <c r="E952" s="6"/>
-      <c r="F952" s="7"/>
+      <c r="F952" s="7" t="inlineStr">
+        <is>
+          <t>월간</t>
+        </is>
+      </c>
     </row>
     <row r="953" spans="1:6">
-      <c r="A953" s="6"/>
-      <c r="B953" s="7"/>
-      <c r="C953" s="7"/>
-      <c r="D953" s="7"/>
+      <c r="A953" s="6">
+        <v>45778</v>
+      </c>
+      <c r="B953" s="7" t="inlineStr">
+        <is>
+          <t>일본</t>
+        </is>
+      </c>
+      <c r="C953" s="7" t="inlineStr">
+        <is>
+          <t>CPI 근원</t>
+        </is>
+      </c>
+      <c r="D953" s="7">
+        <v>3.7</v>
+      </c>
       <c r="E953" s="6"/>
-      <c r="F953" s="7"/>
+      <c r="F953" s="7" t="inlineStr">
+        <is>
+          <t>월간</t>
+        </is>
+      </c>
     </row>
     <row r="954" spans="1:6">
-      <c r="A954" s="6"/>
-      <c r="B954" s="7"/>
-      <c r="C954" s="7"/>
-      <c r="D954" s="7"/>
+      <c r="A954" s="6">
+        <v>45809</v>
+      </c>
+      <c r="B954" s="7" t="inlineStr">
+        <is>
+          <t>일본</t>
+        </is>
+      </c>
+      <c r="C954" s="7" t="inlineStr">
+        <is>
+          <t>CPI 근원</t>
+        </is>
+      </c>
+      <c r="D954" s="7">
+        <v>3.3</v>
+      </c>
       <c r="E954" s="6"/>
-      <c r="F954" s="7"/>
+      <c r="F954" s="7" t="inlineStr">
+        <is>
+          <t>월간</t>
+        </is>
+      </c>
     </row>
     <row r="955" spans="1:6">
-      <c r="A955" s="6"/>
-      <c r="B955" s="7"/>
-      <c r="C955" s="7"/>
-      <c r="D955" s="7"/>
+      <c r="A955" s="6">
+        <v>45839</v>
+      </c>
+      <c r="B955" s="7" t="inlineStr">
+        <is>
+          <t>일본</t>
+        </is>
+      </c>
+      <c r="C955" s="7" t="inlineStr">
+        <is>
+          <t>CPI 근원</t>
+        </is>
+      </c>
+      <c r="D955" s="7">
+        <v>3.1</v>
+      </c>
       <c r="E955" s="6"/>
-      <c r="F955" s="7"/>
+      <c r="F955" s="7" t="inlineStr">
+        <is>
+          <t>월간</t>
+        </is>
+      </c>
     </row>
     <row r="956" spans="1:6">
-      <c r="A956" s="6"/>
-      <c r="B956" s="7"/>
-      <c r="C956" s="7"/>
-      <c r="D956" s="7"/>
+      <c r="A956" s="6">
+        <v>45870</v>
+      </c>
+      <c r="B956" s="7" t="inlineStr">
+        <is>
+          <t>일본</t>
+        </is>
+      </c>
+      <c r="C956" s="7" t="inlineStr">
+        <is>
+          <t>CPI 근원</t>
+        </is>
+      </c>
+      <c r="D956" s="7">
+        <v>2.7</v>
+      </c>
       <c r="E956" s="6"/>
-      <c r="F956" s="7"/>
+      <c r="F956" s="7" t="inlineStr">
+        <is>
+          <t>월간</t>
+        </is>
+      </c>
     </row>
     <row r="957" spans="1:6">
-      <c r="A957" s="6"/>
-      <c r="B957" s="7"/>
-      <c r="C957" s="7"/>
-      <c r="D957" s="7"/>
+      <c r="A957" s="6">
+        <v>45901</v>
+      </c>
+      <c r="B957" s="7" t="inlineStr">
+        <is>
+          <t>일본</t>
+        </is>
+      </c>
+      <c r="C957" s="7" t="inlineStr">
+        <is>
+          <t>CPI 근원</t>
+        </is>
+      </c>
+      <c r="D957" s="7">
+        <v>2.9</v>
+      </c>
       <c r="E957" s="6"/>
-      <c r="F957" s="7"/>
+      <c r="F957" s="7" t="inlineStr">
+        <is>
+          <t>월간</t>
+        </is>
+      </c>
     </row>
     <row r="958" spans="1:6">
-      <c r="A958" s="6"/>
-      <c r="B958" s="7"/>
-      <c r="C958" s="7"/>
-      <c r="D958" s="7"/>
+      <c r="A958" s="6">
+        <v>45931</v>
+      </c>
+      <c r="B958" s="7" t="inlineStr">
+        <is>
+          <t>일본</t>
+        </is>
+      </c>
+      <c r="C958" s="7" t="inlineStr">
+        <is>
+          <t>CPI 근원</t>
+        </is>
+      </c>
+      <c r="D958" s="7">
+        <v>3.0</v>
+      </c>
       <c r="E958" s="6"/>
-      <c r="F958" s="7"/>
+      <c r="F958" s="7" t="inlineStr">
+        <is>
+          <t>월간</t>
+        </is>
+      </c>
     </row>
     <row r="959" spans="1:6">
-      <c r="A959" s="6"/>
-      <c r="B959" s="7"/>
-      <c r="C959" s="7"/>
-      <c r="D959" s="7"/>
+      <c r="A959" s="6">
+        <v>45962</v>
+      </c>
+      <c r="B959" s="7" t="inlineStr">
+        <is>
+          <t>일본</t>
+        </is>
+      </c>
+      <c r="C959" s="7" t="inlineStr">
+        <is>
+          <t>CPI 근원</t>
+        </is>
+      </c>
+      <c r="D959" s="7">
+        <v>3.0</v>
+      </c>
       <c r="E959" s="6"/>
-      <c r="F959" s="7"/>
+      <c r="F959" s="7" t="inlineStr">
+        <is>
+          <t>월간</t>
+        </is>
+      </c>
     </row>
     <row r="960" spans="1:6">
-      <c r="A960" s="6"/>
-      <c r="B960" s="7"/>
-      <c r="C960" s="7"/>
-      <c r="D960" s="7"/>
+      <c r="A960" s="6">
+        <v>45992</v>
+      </c>
+      <c r="B960" s="7" t="inlineStr">
+        <is>
+          <t>일본</t>
+        </is>
+      </c>
+      <c r="C960" s="7" t="inlineStr">
+        <is>
+          <t>CPI 근원</t>
+        </is>
+      </c>
+      <c r="D960" s="7">
+        <v>2.4</v>
+      </c>
       <c r="E960" s="6"/>
-      <c r="F960" s="7"/>
+      <c r="F960" s="7" t="inlineStr">
+        <is>
+          <t>월간</t>
+        </is>
+      </c>
     </row>
     <row r="961" spans="1:6">
-      <c r="A961" s="6"/>
-      <c r="B961" s="7"/>
-      <c r="C961" s="7"/>
-      <c r="D961" s="7"/>
+      <c r="A961" s="6">
+        <v>46023</v>
+      </c>
+      <c r="B961" s="7" t="inlineStr">
+        <is>
+          <t>일본</t>
+        </is>
+      </c>
+      <c r="C961" s="7" t="inlineStr">
+        <is>
+          <t>CPI 근원</t>
+        </is>
+      </c>
+      <c r="D961" s="7">
+        <v>1.9</v>
+      </c>
       <c r="E961" s="6"/>
-      <c r="F961" s="7"/>
+      <c r="F961" s="7" t="inlineStr">
+        <is>
+          <t>월간</t>
+        </is>
+      </c>
     </row>
     <row r="962" spans="1:6">
-      <c r="A962" s="6"/>
-      <c r="B962" s="7"/>
-      <c r="C962" s="7"/>
-      <c r="D962" s="7"/>
+      <c r="A962" s="6">
+        <v>46054</v>
+      </c>
+      <c r="B962" s="7" t="inlineStr">
+        <is>
+          <t>일본</t>
+        </is>
+      </c>
+      <c r="C962" s="7" t="inlineStr">
+        <is>
+          <t>CPI 근원</t>
+        </is>
+      </c>
+      <c r="D962" s="7">
+        <v>1.5</v>
+      </c>
       <c r="E962" s="6"/>
-      <c r="F962" s="7"/>
+      <c r="F962" s="7" t="inlineStr">
+        <is>
+          <t>월간</t>
+        </is>
+      </c>
     </row>
     <row r="963" spans="1:6">
-      <c r="A963" s="6"/>
-      <c r="B963" s="7"/>
-      <c r="C963" s="7"/>
-      <c r="D963" s="7"/>
+      <c r="A963" s="6">
+        <v>46082</v>
+      </c>
+      <c r="B963" s="7" t="inlineStr">
+        <is>
+          <t>일본</t>
+        </is>
+      </c>
+      <c r="C963" s="7" t="inlineStr">
+        <is>
+          <t>CPI 근원</t>
+        </is>
+      </c>
+      <c r="D963" s="7">
+        <v>1.7</v>
+      </c>
       <c r="E963" s="6"/>
-      <c r="F963" s="7"/>
+      <c r="F963" s="7" t="inlineStr">
+        <is>
+          <t>월간</t>
+        </is>
+      </c>
     </row>
     <row r="964" spans="1:6">
-      <c r="A964" s="6"/>
-      <c r="B964" s="7"/>
-      <c r="C964" s="7"/>
-      <c r="D964" s="7"/>
+      <c r="A964" s="6">
+        <v>46113</v>
+      </c>
+      <c r="B964" s="7" t="inlineStr">
+        <is>
+          <t>일본</t>
+        </is>
+      </c>
+      <c r="C964" s="7" t="inlineStr">
+        <is>
+          <t>CPI 근원</t>
+        </is>
+      </c>
+      <c r="D964" s="7">
+        <v>1.4</v>
+      </c>
       <c r="E964" s="6"/>
-      <c r="F964" s="7"/>
+      <c r="F964" s="7" t="inlineStr">
+        <is>
+          <t>월간</t>
+        </is>
+      </c>
     </row>
     <row r="965" spans="1:6">
-      <c r="A965" s="6"/>
-      <c r="B965" s="7"/>
-      <c r="C965" s="7"/>
-      <c r="D965" s="7"/>
+      <c r="A965" s="6">
+        <v>46143</v>
+      </c>
+      <c r="B965" s="7" t="inlineStr">
+        <is>
+          <t>일본</t>
+        </is>
+      </c>
+      <c r="C965" s="7" t="inlineStr">
+        <is>
+          <t>CPI 근원</t>
+        </is>
+      </c>
+      <c r="D965" s="7">
+        <v>1.4</v>
+      </c>
       <c r="E965" s="6"/>
-      <c r="F965" s="7"/>
+      <c r="F965" s="7" t="inlineStr">
+        <is>
+          <t>월간</t>
+        </is>
+      </c>
     </row>
     <row r="966" spans="1:6">
-      <c r="A966" s="6"/>
-      <c r="B966" s="7"/>
-      <c r="C966" s="7"/>
-      <c r="D966" s="7"/>
+      <c r="A966" s="6">
+        <v>46174</v>
+      </c>
+      <c r="B966" s="7" t="inlineStr">
+        <is>
+          <t>일본</t>
+        </is>
+      </c>
+      <c r="C966" s="7" t="inlineStr">
+        <is>
+          <t>CPI 근원</t>
+        </is>
+      </c>
+      <c r="D966" s="7">
+        <v>1.6</v>
+      </c>
       <c r="E966" s="6"/>
-      <c r="F966" s="7"/>
+      <c r="F966" s="7" t="inlineStr">
+        <is>
+          <t>월간</t>
+        </is>
+      </c>
     </row>
     <row r="967" spans="1:6">
-      <c r="A967" s="6"/>
-      <c r="B967" s="7"/>
-      <c r="C967" s="7"/>
-      <c r="D967" s="7"/>
+      <c r="A967" s="6">
+        <v>46204</v>
+      </c>
+      <c r="B967" s="7" t="inlineStr">
+        <is>
+          <t>일본</t>
+        </is>
+      </c>
+      <c r="C967" s="7" t="inlineStr">
+        <is>
+          <t>CPI 근원</t>
+        </is>
+      </c>
+      <c r="D967" s="7">
+        <v>1.8</v>
+      </c>
       <c r="E967" s="6"/>
-      <c r="F967" s="7"/>
+      <c r="F967" s="7" t="inlineStr">
+        <is>
+          <t>월간</t>
+        </is>
+      </c>
     </row>
     <row r="968" spans="1:6">
-      <c r="A968" s="6"/>
-      <c r="B968" s="7"/>
-      <c r="C968" s="7"/>
-      <c r="D968" s="7"/>
-      <c r="E968" s="6"/>
-      <c r="F968" s="7"/>
+      <c r="A968" s="6">
+        <v>44440</v>
+      </c>
+      <c r="B968" s="7" t="inlineStr">
+        <is>
+          <t>일본</t>
+        </is>
+      </c>
+      <c r="C968" s="7" t="inlineStr">
+        <is>
+          <t>실업률</t>
+        </is>
+      </c>
+      <c r="D968" s="7">
+        <v>2.7</v>
+      </c>
+      <c r="E968" s="6">
+        <v>44511</v>
+      </c>
+      <c r="F968" s="7" t="inlineStr">
+        <is>
+          <t>월간</t>
+        </is>
+      </c>
     </row>
     <row r="969" spans="1:6">
-      <c r="A969" s="6"/>
-      <c r="B969" s="7"/>
-      <c r="C969" s="7"/>
-      <c r="D969" s="7"/>
-      <c r="E969" s="6"/>
-      <c r="F969" s="7"/>
+      <c r="A969" s="6">
+        <v>44470</v>
+      </c>
+      <c r="B969" s="7" t="inlineStr">
+        <is>
+          <t>일본</t>
+        </is>
+      </c>
+      <c r="C969" s="7" t="inlineStr">
+        <is>
+          <t>실업률</t>
+        </is>
+      </c>
+      <c r="D969" s="7">
+        <v>2.7</v>
+      </c>
+      <c r="E969" s="6">
+        <v>44540</v>
+      </c>
+      <c r="F969" s="7" t="inlineStr">
+        <is>
+          <t>월간</t>
+        </is>
+      </c>
     </row>
     <row r="970" spans="1:6">
-      <c r="A970" s="6"/>
-      <c r="B970" s="7"/>
-      <c r="C970" s="7"/>
-      <c r="D970" s="7"/>
-      <c r="E970" s="6"/>
-      <c r="F970" s="7"/>
+      <c r="A970" s="6">
+        <v>44501</v>
+      </c>
+      <c r="B970" s="7" t="inlineStr">
+        <is>
+          <t>일본</t>
+        </is>
+      </c>
+      <c r="C970" s="7" t="inlineStr">
+        <is>
+          <t>실업률</t>
+        </is>
+      </c>
+      <c r="D970" s="7">
+        <v>2.8</v>
+      </c>
+      <c r="E970" s="6">
+        <v>44579</v>
+      </c>
+      <c r="F970" s="7" t="inlineStr">
+        <is>
+          <t>월간</t>
+        </is>
+      </c>
     </row>
     <row r="971" spans="1:6">
-      <c r="A971" s="6"/>
-      <c r="B971" s="7"/>
-      <c r="C971" s="7"/>
-      <c r="D971" s="7"/>
-      <c r="E971" s="6"/>
-      <c r="F971" s="7"/>
+      <c r="A971" s="6">
+        <v>44531</v>
+      </c>
+      <c r="B971" s="7" t="inlineStr">
+        <is>
+          <t>일본</t>
+        </is>
+      </c>
+      <c r="C971" s="7" t="inlineStr">
+        <is>
+          <t>실업률</t>
+        </is>
+      </c>
+      <c r="D971" s="7">
+        <v>2.7</v>
+      </c>
+      <c r="E971" s="6">
+        <v>44603</v>
+      </c>
+      <c r="F971" s="7" t="inlineStr">
+        <is>
+          <t>월간</t>
+        </is>
+      </c>
     </row>
     <row r="972" spans="1:6">
-      <c r="A972" s="6"/>
-      <c r="B972" s="7"/>
-      <c r="C972" s="7"/>
-      <c r="D972" s="7"/>
-      <c r="E972" s="6"/>
-      <c r="F972" s="7"/>
+      <c r="A972" s="6">
+        <v>44562</v>
+      </c>
+      <c r="B972" s="7" t="inlineStr">
+        <is>
+          <t>일본</t>
+        </is>
+      </c>
+      <c r="C972" s="7" t="inlineStr">
+        <is>
+          <t>실업률</t>
+        </is>
+      </c>
+      <c r="D972" s="7">
+        <v>2.8</v>
+      </c>
+      <c r="E972" s="6">
+        <v>44630</v>
+      </c>
+      <c r="F972" s="7" t="inlineStr">
+        <is>
+          <t>월간</t>
+        </is>
+      </c>
     </row>
     <row r="973" spans="1:6">
-      <c r="A973" s="6"/>
-      <c r="B973" s="7"/>
-      <c r="C973" s="7"/>
-      <c r="D973" s="7"/>
-      <c r="E973" s="6"/>
-      <c r="F973" s="7"/>
+      <c r="A973" s="6">
+        <v>44593</v>
+      </c>
+      <c r="B973" s="7" t="inlineStr">
+        <is>
+          <t>일본</t>
+        </is>
+      </c>
+      <c r="C973" s="7" t="inlineStr">
+        <is>
+          <t>실업률</t>
+        </is>
+      </c>
+      <c r="D973" s="7">
+        <v>2.7</v>
+      </c>
+      <c r="E973" s="6">
+        <v>44665</v>
+      </c>
+      <c r="F973" s="7" t="inlineStr">
+        <is>
+          <t>월간</t>
+        </is>
+      </c>
     </row>
     <row r="974" spans="1:6">
-      <c r="A974" s="6"/>
-      <c r="B974" s="7"/>
-      <c r="C974" s="7"/>
-      <c r="D974" s="7"/>
-      <c r="E974" s="6"/>
-      <c r="F974" s="7"/>
+      <c r="A974" s="6">
+        <v>44621</v>
+      </c>
+      <c r="B974" s="7" t="inlineStr">
+        <is>
+          <t>일본</t>
+        </is>
+      </c>
+      <c r="C974" s="7" t="inlineStr">
+        <is>
+          <t>실업률</t>
+        </is>
+      </c>
+      <c r="D974" s="7">
+        <v>2.6</v>
+      </c>
+      <c r="E974" s="6">
+        <v>44692</v>
+      </c>
+      <c r="F974" s="7" t="inlineStr">
+        <is>
+          <t>월간</t>
+        </is>
+      </c>
     </row>
     <row r="975" spans="1:6">
-      <c r="A975" s="6"/>
-      <c r="B975" s="7"/>
-      <c r="C975" s="7"/>
-      <c r="D975" s="7"/>
-      <c r="E975" s="6"/>
-      <c r="F975" s="7"/>
+      <c r="A975" s="6">
+        <v>44652</v>
+      </c>
+      <c r="B975" s="7" t="inlineStr">
+        <is>
+          <t>일본</t>
+        </is>
+      </c>
+      <c r="C975" s="7" t="inlineStr">
+        <is>
+          <t>실업률</t>
+        </is>
+      </c>
+      <c r="D975" s="7">
+        <v>2.6</v>
+      </c>
+      <c r="E975" s="6">
+        <v>44726</v>
+      </c>
+      <c r="F975" s="7" t="inlineStr">
+        <is>
+          <t>월간</t>
+        </is>
+      </c>
     </row>
     <row r="976" spans="1:6">
-      <c r="A976" s="6"/>
-      <c r="B976" s="7"/>
-      <c r="C976" s="7"/>
-      <c r="D976" s="7"/>
-      <c r="E976" s="6"/>
-      <c r="F976" s="7"/>
+      <c r="A976" s="6">
+        <v>44682</v>
+      </c>
+      <c r="B976" s="7" t="inlineStr">
+        <is>
+          <t>일본</t>
+        </is>
+      </c>
+      <c r="C976" s="7" t="inlineStr">
+        <is>
+          <t>실업률</t>
+        </is>
+      </c>
+      <c r="D976" s="7">
+        <v>2.6</v>
+      </c>
+      <c r="E976" s="6">
+        <v>44755</v>
+      </c>
+      <c r="F976" s="7" t="inlineStr">
+        <is>
+          <t>월간</t>
+        </is>
+      </c>
     </row>
     <row r="977" spans="1:6">
-      <c r="A977" s="6"/>
-      <c r="B977" s="7"/>
-      <c r="C977" s="7"/>
-      <c r="D977" s="7"/>
-      <c r="E977" s="6"/>
-      <c r="F977" s="7"/>
+      <c r="A977" s="6">
+        <v>44713</v>
+      </c>
+      <c r="B977" s="7" t="inlineStr">
+        <is>
+          <t>일본</t>
+        </is>
+      </c>
+      <c r="C977" s="7" t="inlineStr">
+        <is>
+          <t>실업률</t>
+        </is>
+      </c>
+      <c r="D977" s="7">
+        <v>2.6</v>
+      </c>
+      <c r="E977" s="6">
+        <v>44783</v>
+      </c>
+      <c r="F977" s="7" t="inlineStr">
+        <is>
+          <t>월간</t>
+        </is>
+      </c>
     </row>
     <row r="978" spans="1:6">
-      <c r="A978" s="6"/>
-      <c r="B978" s="7"/>
-      <c r="C978" s="7"/>
-      <c r="D978" s="7"/>
-      <c r="E978" s="6"/>
-      <c r="F978" s="7"/>
+      <c r="A978" s="6">
+        <v>44743</v>
+      </c>
+      <c r="B978" s="7" t="inlineStr">
+        <is>
+          <t>일본</t>
+        </is>
+      </c>
+      <c r="C978" s="7" t="inlineStr">
+        <is>
+          <t>실업률</t>
+        </is>
+      </c>
+      <c r="D978" s="7">
+        <v>2.5</v>
+      </c>
+      <c r="E978" s="6">
+        <v>44818</v>
+      </c>
+      <c r="F978" s="7" t="inlineStr">
+        <is>
+          <t>월간</t>
+        </is>
+      </c>
     </row>
     <row r="979" spans="1:6">
-      <c r="A979" s="6"/>
-      <c r="B979" s="7"/>
-      <c r="C979" s="7"/>
-      <c r="D979" s="7"/>
-      <c r="E979" s="6"/>
-      <c r="F979" s="7"/>
+      <c r="A979" s="6">
+        <v>44774</v>
+      </c>
+      <c r="B979" s="7" t="inlineStr">
+        <is>
+          <t>일본</t>
+        </is>
+      </c>
+      <c r="C979" s="7" t="inlineStr">
+        <is>
+          <t>실업률</t>
+        </is>
+      </c>
+      <c r="D979" s="7">
+        <v>2.5</v>
+      </c>
+      <c r="E979" s="6">
+        <v>44876</v>
+      </c>
+      <c r="F979" s="7" t="inlineStr">
+        <is>
+          <t>월간</t>
+        </is>
+      </c>
     </row>
     <row r="980" spans="1:6">
-      <c r="A980" s="6"/>
-      <c r="B980" s="7"/>
-      <c r="C980" s="7"/>
-      <c r="D980" s="7"/>
-      <c r="E980" s="6"/>
-      <c r="F980" s="7"/>
+      <c r="A980" s="6">
+        <v>44805</v>
+      </c>
+      <c r="B980" s="7" t="inlineStr">
+        <is>
+          <t>일본</t>
+        </is>
+      </c>
+      <c r="C980" s="7" t="inlineStr">
+        <is>
+          <t>실업률</t>
+        </is>
+      </c>
+      <c r="D980" s="7">
+        <v>2.6</v>
+      </c>
+      <c r="E980" s="6">
+        <v>44876</v>
+      </c>
+      <c r="F980" s="7" t="inlineStr">
+        <is>
+          <t>월간</t>
+        </is>
+      </c>
     </row>
     <row r="981" spans="1:6">
-      <c r="A981" s="6"/>
-      <c r="B981" s="7"/>
-      <c r="C981" s="7"/>
-      <c r="D981" s="7"/>
-      <c r="E981" s="6"/>
-      <c r="F981" s="7"/>
+      <c r="A981" s="6">
+        <v>44835</v>
+      </c>
+      <c r="B981" s="7" t="inlineStr">
+        <is>
+          <t>일본</t>
+        </is>
+      </c>
+      <c r="C981" s="7" t="inlineStr">
+        <is>
+          <t>실업률</t>
+        </is>
+      </c>
+      <c r="D981" s="7">
+        <v>2.6</v>
+      </c>
+      <c r="E981" s="6">
+        <v>44905</v>
+      </c>
+      <c r="F981" s="7" t="inlineStr">
+        <is>
+          <t>월간</t>
+        </is>
+      </c>
     </row>
     <row r="982" spans="1:6">
-      <c r="A982" s="6"/>
-      <c r="B982" s="7"/>
-      <c r="C982" s="7"/>
-      <c r="D982" s="7"/>
-      <c r="E982" s="6"/>
-      <c r="F982" s="7"/>
+      <c r="A982" s="6">
+        <v>44866</v>
+      </c>
+      <c r="B982" s="7" t="inlineStr">
+        <is>
+          <t>일본</t>
+        </is>
+      </c>
+      <c r="C982" s="7" t="inlineStr">
+        <is>
+          <t>실업률</t>
+        </is>
+      </c>
+      <c r="D982" s="7">
+        <v>2.5</v>
+      </c>
+      <c r="E982" s="6">
+        <v>44937</v>
+      </c>
+      <c r="F982" s="7" t="inlineStr">
+        <is>
+          <t>월간</t>
+        </is>
+      </c>
     </row>
     <row r="983" spans="1:6">
-      <c r="A983" s="6"/>
-      <c r="B983" s="7"/>
-      <c r="C983" s="7"/>
-      <c r="D983" s="7"/>
-      <c r="E983" s="6"/>
-      <c r="F983" s="7"/>
+      <c r="A983" s="6">
+        <v>44896</v>
+      </c>
+      <c r="B983" s="7" t="inlineStr">
+        <is>
+          <t>일본</t>
+        </is>
+      </c>
+      <c r="C983" s="7" t="inlineStr">
+        <is>
+          <t>실업률</t>
+        </is>
+      </c>
+      <c r="D983" s="7">
+        <v>2.5</v>
+      </c>
+      <c r="E983" s="6">
+        <v>44970</v>
+      </c>
+      <c r="F983" s="7" t="inlineStr">
+        <is>
+          <t>월간</t>
+        </is>
+      </c>
     </row>
     <row r="984" spans="1:6">
-      <c r="A984" s="6"/>
-      <c r="B984" s="7"/>
-      <c r="C984" s="7"/>
-      <c r="D984" s="7"/>
-      <c r="E984" s="6"/>
-      <c r="F984" s="7"/>
+      <c r="A984" s="6">
+        <v>44927</v>
+      </c>
+      <c r="B984" s="7" t="inlineStr">
+        <is>
+          <t>일본</t>
+        </is>
+      </c>
+      <c r="C984" s="7" t="inlineStr">
+        <is>
+          <t>실업률</t>
+        </is>
+      </c>
+      <c r="D984" s="7">
+        <v>2.5</v>
+      </c>
+      <c r="E984" s="6">
+        <v>44994</v>
+      </c>
+      <c r="F984" s="7" t="inlineStr">
+        <is>
+          <t>월간</t>
+        </is>
+      </c>
     </row>
     <row r="985" spans="1:6">
-      <c r="A985" s="6"/>
-      <c r="B985" s="7"/>
-      <c r="C985" s="7"/>
-      <c r="D985" s="7"/>
-      <c r="E985" s="6"/>
-      <c r="F985" s="7"/>
+      <c r="A985" s="6">
+        <v>44958</v>
+      </c>
+      <c r="B985" s="7" t="inlineStr">
+        <is>
+          <t>일본</t>
+        </is>
+      </c>
+      <c r="C985" s="7" t="inlineStr">
+        <is>
+          <t>실업률</t>
+        </is>
+      </c>
+      <c r="D985" s="7">
+        <v>2.6</v>
+      </c>
+      <c r="E985" s="6">
+        <v>45023</v>
+      </c>
+      <c r="F985" s="7" t="inlineStr">
+        <is>
+          <t>월간</t>
+        </is>
+      </c>
     </row>
     <row r="986" spans="1:6">
-      <c r="A986" s="6"/>
-      <c r="B986" s="7"/>
-      <c r="C986" s="7"/>
-      <c r="D986" s="7"/>
-      <c r="E986" s="6"/>
-      <c r="F986" s="7"/>
+      <c r="A986" s="6">
+        <v>44986</v>
+      </c>
+      <c r="B986" s="7" t="inlineStr">
+        <is>
+          <t>일본</t>
+        </is>
+      </c>
+      <c r="C986" s="7" t="inlineStr">
+        <is>
+          <t>실업률</t>
+        </is>
+      </c>
+      <c r="D986" s="7">
+        <v>2.7</v>
+      </c>
+      <c r="E986" s="6">
+        <v>45056</v>
+      </c>
+      <c r="F986" s="7" t="inlineStr">
+        <is>
+          <t>월간</t>
+        </is>
+      </c>
     </row>
     <row r="987" spans="1:6">
-      <c r="A987" s="6"/>
-      <c r="B987" s="7"/>
-      <c r="C987" s="7"/>
-      <c r="D987" s="7"/>
-      <c r="E987" s="6"/>
-      <c r="F987" s="7"/>
+      <c r="A987" s="6">
+        <v>45017</v>
+      </c>
+      <c r="B987" s="7" t="inlineStr">
+        <is>
+          <t>일본</t>
+        </is>
+      </c>
+      <c r="C987" s="7" t="inlineStr">
+        <is>
+          <t>실업률</t>
+        </is>
+      </c>
+      <c r="D987" s="7">
+        <v>2.6</v>
+      </c>
+      <c r="E987" s="6">
+        <v>45090</v>
+      </c>
+      <c r="F987" s="7" t="inlineStr">
+        <is>
+          <t>월간</t>
+        </is>
+      </c>
     </row>
     <row r="988" spans="1:6">
-      <c r="A988" s="6"/>
-      <c r="B988" s="7"/>
-      <c r="C988" s="7"/>
-      <c r="D988" s="7"/>
-      <c r="E988" s="6"/>
-      <c r="F988" s="7"/>
+      <c r="A988" s="6">
+        <v>45047</v>
+      </c>
+      <c r="B988" s="7" t="inlineStr">
+        <is>
+          <t>일본</t>
+        </is>
+      </c>
+      <c r="C988" s="7" t="inlineStr">
+        <is>
+          <t>실업률</t>
+        </is>
+      </c>
+      <c r="D988" s="7">
+        <v>2.5</v>
+      </c>
+      <c r="E988" s="6">
+        <v>45114</v>
+      </c>
+      <c r="F988" s="7" t="inlineStr">
+        <is>
+          <t>월간</t>
+        </is>
+      </c>
     </row>
     <row r="989" spans="1:6">
-      <c r="A989" s="6"/>
-      <c r="B989" s="7"/>
-      <c r="C989" s="7"/>
-      <c r="D989" s="7"/>
-      <c r="E989" s="6"/>
-      <c r="F989" s="7"/>
+      <c r="A989" s="6">
+        <v>45078</v>
+      </c>
+      <c r="B989" s="7" t="inlineStr">
+        <is>
+          <t>일본</t>
+        </is>
+      </c>
+      <c r="C989" s="7" t="inlineStr">
+        <is>
+          <t>실업률</t>
+        </is>
+      </c>
+      <c r="D989" s="7">
+        <v>2.5</v>
+      </c>
+      <c r="E989" s="6">
+        <v>45148</v>
+      </c>
+      <c r="F989" s="7" t="inlineStr">
+        <is>
+          <t>월간</t>
+        </is>
+      </c>
     </row>
     <row r="990" spans="1:6">
-      <c r="A990" s="6"/>
-      <c r="B990" s="7"/>
-      <c r="C990" s="7"/>
-      <c r="D990" s="7"/>
-      <c r="E990" s="6"/>
-      <c r="F990" s="7"/>
+      <c r="A990" s="6">
+        <v>45108</v>
+      </c>
+      <c r="B990" s="7" t="inlineStr">
+        <is>
+          <t>일본</t>
+        </is>
+      </c>
+      <c r="C990" s="7" t="inlineStr">
+        <is>
+          <t>실업률</t>
+        </is>
+      </c>
+      <c r="D990" s="7">
+        <v>2.6</v>
+      </c>
+      <c r="E990" s="6">
+        <v>45178</v>
+      </c>
+      <c r="F990" s="7" t="inlineStr">
+        <is>
+          <t>월간</t>
+        </is>
+      </c>
     </row>
     <row r="991" spans="1:6">
-      <c r="A991" s="6"/>
-      <c r="B991" s="7"/>
-      <c r="C991" s="7"/>
-      <c r="D991" s="7"/>
-      <c r="E991" s="6"/>
-      <c r="F991" s="7"/>
+      <c r="A991" s="6">
+        <v>45139</v>
+      </c>
+      <c r="B991" s="7" t="inlineStr">
+        <is>
+          <t>일본</t>
+        </is>
+      </c>
+      <c r="C991" s="7" t="inlineStr">
+        <is>
+          <t>실업률</t>
+        </is>
+      </c>
+      <c r="D991" s="7">
+        <v>2.6</v>
+      </c>
+      <c r="E991" s="6">
+        <v>45206</v>
+      </c>
+      <c r="F991" s="7" t="inlineStr">
+        <is>
+          <t>월간</t>
+        </is>
+      </c>
     </row>
     <row r="992" spans="1:6">
-      <c r="A992" s="6"/>
-      <c r="B992" s="7"/>
-      <c r="C992" s="7"/>
-      <c r="D992" s="7"/>
-      <c r="E992" s="6"/>
-      <c r="F992" s="7"/>
+      <c r="A992" s="6">
+        <v>45170</v>
+      </c>
+      <c r="B992" s="7" t="inlineStr">
+        <is>
+          <t>일본</t>
+        </is>
+      </c>
+      <c r="C992" s="7" t="inlineStr">
+        <is>
+          <t>실업률</t>
+        </is>
+      </c>
+      <c r="D992" s="7">
+        <v>2.6</v>
+      </c>
+      <c r="E992" s="6">
+        <v>45240</v>
+      </c>
+      <c r="F992" s="7" t="inlineStr">
+        <is>
+          <t>월간</t>
+        </is>
+      </c>
     </row>
     <row r="993" spans="1:6">
-      <c r="A993" s="6"/>
-      <c r="B993" s="7"/>
-      <c r="C993" s="7"/>
-      <c r="D993" s="7"/>
-      <c r="E993" s="6"/>
-      <c r="F993" s="7"/>
+      <c r="A993" s="6">
+        <v>45200</v>
+      </c>
+      <c r="B993" s="7" t="inlineStr">
+        <is>
+          <t>일본</t>
+        </is>
+      </c>
+      <c r="C993" s="7" t="inlineStr">
+        <is>
+          <t>실업률</t>
+        </is>
+      </c>
+      <c r="D993" s="7">
+        <v>2.5</v>
+      </c>
+      <c r="E993" s="6">
+        <v>45269</v>
+      </c>
+      <c r="F993" s="7" t="inlineStr">
+        <is>
+          <t>월간</t>
+        </is>
+      </c>
     </row>
     <row r="994" spans="1:6">
-      <c r="A994" s="6"/>
-      <c r="B994" s="7"/>
-      <c r="C994" s="7"/>
-      <c r="D994" s="7"/>
-      <c r="E994" s="6"/>
-      <c r="F994" s="7"/>
+      <c r="A994" s="6">
+        <v>45231</v>
+      </c>
+      <c r="B994" s="7" t="inlineStr">
+        <is>
+          <t>일본</t>
+        </is>
+      </c>
+      <c r="C994" s="7" t="inlineStr">
+        <is>
+          <t>실업률</t>
+        </is>
+      </c>
+      <c r="D994" s="7">
+        <v>2.6</v>
+      </c>
+      <c r="E994" s="6">
+        <v>45302</v>
+      </c>
+      <c r="F994" s="7" t="inlineStr">
+        <is>
+          <t>월간</t>
+        </is>
+      </c>
     </row>
     <row r="995" spans="1:6">
-      <c r="A995" s="6"/>
-      <c r="B995" s="7"/>
-      <c r="C995" s="7"/>
-      <c r="D995" s="7"/>
-      <c r="E995" s="6"/>
-      <c r="F995" s="7"/>
+      <c r="A995" s="6">
+        <v>45261</v>
+      </c>
+      <c r="B995" s="7" t="inlineStr">
+        <is>
+          <t>일본</t>
+        </is>
+      </c>
+      <c r="C995" s="7" t="inlineStr">
+        <is>
+          <t>실업률</t>
+        </is>
+      </c>
+      <c r="D995" s="7">
+        <v>2.5</v>
+      </c>
+      <c r="E995" s="6">
+        <v>45392</v>
+      </c>
+      <c r="F995" s="7" t="inlineStr">
+        <is>
+          <t>월간</t>
+        </is>
+      </c>
     </row>
     <row r="996" spans="1:6">
-      <c r="A996" s="6"/>
-      <c r="B996" s="7"/>
-      <c r="C996" s="7"/>
-      <c r="D996" s="7"/>
-      <c r="E996" s="6"/>
-      <c r="F996" s="7"/>
+      <c r="A996" s="6">
+        <v>45292</v>
+      </c>
+      <c r="B996" s="7" t="inlineStr">
+        <is>
+          <t>일본</t>
+        </is>
+      </c>
+      <c r="C996" s="7" t="inlineStr">
+        <is>
+          <t>실업률</t>
+        </is>
+      </c>
+      <c r="D996" s="7">
+        <v>2.5</v>
+      </c>
+      <c r="E996" s="6">
+        <v>45392</v>
+      </c>
+      <c r="F996" s="7" t="inlineStr">
+        <is>
+          <t>월간</t>
+        </is>
+      </c>
     </row>
     <row r="997" spans="1:6">
-      <c r="A997" s="6"/>
-      <c r="B997" s="7"/>
-      <c r="C997" s="7"/>
-      <c r="D997" s="7"/>
-      <c r="E997" s="6"/>
-      <c r="F997" s="7"/>
+      <c r="A997" s="6">
+        <v>45323</v>
+      </c>
+      <c r="B997" s="7" t="inlineStr">
+        <is>
+          <t>일본</t>
+        </is>
+      </c>
+      <c r="C997" s="7" t="inlineStr">
+        <is>
+          <t>실업률</t>
+        </is>
+      </c>
+      <c r="D997" s="7">
+        <v>2.6</v>
+      </c>
+      <c r="E997" s="6">
+        <v>45392</v>
+      </c>
+      <c r="F997" s="7" t="inlineStr">
+        <is>
+          <t>월간</t>
+        </is>
+      </c>
     </row>
     <row r="998" spans="1:6">
-      <c r="A998" s="6"/>
-      <c r="B998" s="7"/>
-      <c r="C998" s="7"/>
-      <c r="D998" s="7"/>
-      <c r="E998" s="6"/>
-      <c r="F998" s="7"/>
+      <c r="A998" s="6">
+        <v>45352</v>
+      </c>
+      <c r="B998" s="7" t="inlineStr">
+        <is>
+          <t>일본</t>
+        </is>
+      </c>
+      <c r="C998" s="7" t="inlineStr">
+        <is>
+          <t>실업률</t>
+        </is>
+      </c>
+      <c r="D998" s="7">
+        <v>2.6</v>
+      </c>
+      <c r="E998" s="6">
+        <v>45427</v>
+      </c>
+      <c r="F998" s="7" t="inlineStr">
+        <is>
+          <t>월간</t>
+        </is>
+      </c>
     </row>
     <row r="999" spans="1:6">
-      <c r="A999" s="6"/>
-      <c r="B999" s="7"/>
-      <c r="C999" s="7"/>
-      <c r="D999" s="7"/>
-      <c r="E999" s="6"/>
-      <c r="F999" s="7"/>
+      <c r="A999" s="6">
+        <v>45383</v>
+      </c>
+      <c r="B999" s="7" t="inlineStr">
+        <is>
+          <t>일본</t>
+        </is>
+      </c>
+      <c r="C999" s="7" t="inlineStr">
+        <is>
+          <t>실업률</t>
+        </is>
+      </c>
+      <c r="D999" s="7">
+        <v>2.6</v>
+      </c>
+      <c r="E999" s="6">
+        <v>45460</v>
+      </c>
+      <c r="F999" s="7" t="inlineStr">
+        <is>
+          <t>월간</t>
+        </is>
+      </c>
     </row>
     <row r="1000" spans="1:6">
-      <c r="A1000" s="6"/>
-      <c r="B1000" s="7"/>
-      <c r="C1000" s="7"/>
-      <c r="D1000" s="7"/>
-      <c r="E1000" s="6"/>
-      <c r="F1000" s="7"/>
+      <c r="A1000" s="6">
+        <v>45413</v>
+      </c>
+      <c r="B1000" s="7" t="inlineStr">
+        <is>
+          <t>일본</t>
+        </is>
+      </c>
+      <c r="C1000" s="7" t="inlineStr">
+        <is>
+          <t>실업률</t>
+        </is>
+      </c>
+      <c r="D1000" s="7">
+        <v>2.6</v>
+      </c>
+      <c r="E1000" s="6">
+        <v>45488</v>
+      </c>
+      <c r="F1000" s="7" t="inlineStr">
+        <is>
+          <t>월간</t>
+        </is>
+      </c>
     </row>
     <row r="1001" spans="1:6">
-      <c r="A1001" s="6"/>
-      <c r="B1001" s="7"/>
-      <c r="C1001" s="7"/>
-      <c r="D1001" s="7"/>
-      <c r="E1001" s="6"/>
-      <c r="F1001" s="7"/>
+      <c r="A1001" s="6">
+        <v>45444</v>
+      </c>
+      <c r="B1001" s="7" t="inlineStr">
+        <is>
+          <t>일본</t>
+        </is>
+      </c>
+      <c r="C1001" s="7" t="inlineStr">
+        <is>
+          <t>실업률</t>
+        </is>
+      </c>
+      <c r="D1001" s="7">
+        <v>2.5</v>
+      </c>
+      <c r="E1001" s="6">
+        <v>45519</v>
+      </c>
+      <c r="F1001" s="7" t="inlineStr">
+        <is>
+          <t>월간</t>
+        </is>
+      </c>
     </row>
     <row r="1002" spans="1:6">
-      <c r="A1002" s="6"/>
-      <c r="B1002" s="7"/>
-      <c r="C1002" s="7"/>
-      <c r="D1002" s="7"/>
-      <c r="E1002" s="6"/>
-      <c r="F1002" s="7"/>
+      <c r="A1002" s="6">
+        <v>45474</v>
+      </c>
+      <c r="B1002" s="7" t="inlineStr">
+        <is>
+          <t>일본</t>
+        </is>
+      </c>
+      <c r="C1002" s="7" t="inlineStr">
+        <is>
+          <t>실업률</t>
+        </is>
+      </c>
+      <c r="D1002" s="7">
+        <v>2.7</v>
+      </c>
+      <c r="E1002" s="6">
+        <v>45551</v>
+      </c>
+      <c r="F1002" s="7" t="inlineStr">
+        <is>
+          <t>월간</t>
+        </is>
+      </c>
     </row>
     <row r="1003" spans="1:6">
-      <c r="A1003" s="6"/>
-      <c r="B1003" s="7"/>
-      <c r="C1003" s="7"/>
-      <c r="D1003" s="7"/>
-      <c r="E1003" s="6"/>
-      <c r="F1003" s="7"/>
+      <c r="A1003" s="6">
+        <v>45505</v>
+      </c>
+      <c r="B1003" s="7" t="inlineStr">
+        <is>
+          <t>일본</t>
+        </is>
+      </c>
+      <c r="C1003" s="7" t="inlineStr">
+        <is>
+          <t>실업률</t>
+        </is>
+      </c>
+      <c r="D1003" s="7">
+        <v>2.5</v>
+      </c>
+      <c r="E1003" s="6">
+        <v>45580</v>
+      </c>
+      <c r="F1003" s="7" t="inlineStr">
+        <is>
+          <t>월간</t>
+        </is>
+      </c>
     </row>
     <row r="1004" spans="1:6">
-      <c r="A1004" s="6"/>
-      <c r="B1004" s="7"/>
-      <c r="C1004" s="7"/>
-      <c r="D1004" s="7"/>
-      <c r="E1004" s="6"/>
-      <c r="F1004" s="7"/>
+      <c r="A1004" s="6">
+        <v>45536</v>
+      </c>
+      <c r="B1004" s="7" t="inlineStr">
+        <is>
+          <t>일본</t>
+        </is>
+      </c>
+      <c r="C1004" s="7" t="inlineStr">
+        <is>
+          <t>실업률</t>
+        </is>
+      </c>
+      <c r="D1004" s="7">
+        <v>2.4</v>
+      </c>
+      <c r="E1004" s="6">
+        <v>45611</v>
+      </c>
+      <c r="F1004" s="7" t="inlineStr">
+        <is>
+          <t>월간</t>
+        </is>
+      </c>
     </row>
     <row r="1005" spans="1:6">
-      <c r="A1005" s="6"/>
-      <c r="B1005" s="7"/>
-      <c r="C1005" s="7"/>
-      <c r="D1005" s="7"/>
-      <c r="E1005" s="6"/>
-      <c r="F1005" s="7"/>
+      <c r="A1005" s="6">
+        <v>45566</v>
+      </c>
+      <c r="B1005" s="7" t="inlineStr">
+        <is>
+          <t>일본</t>
+        </is>
+      </c>
+      <c r="C1005" s="7" t="inlineStr">
+        <is>
+          <t>실업률</t>
+        </is>
+      </c>
+      <c r="D1005" s="7">
+        <v>2.5</v>
+      </c>
+      <c r="E1005" s="6">
+        <v>45642</v>
+      </c>
+      <c r="F1005" s="7" t="inlineStr">
+        <is>
+          <t>월간</t>
+        </is>
+      </c>
     </row>
     <row r="1006" spans="1:6">
-      <c r="A1006" s="6"/>
-      <c r="B1006" s="7"/>
-      <c r="C1006" s="7"/>
-      <c r="D1006" s="7"/>
-      <c r="E1006" s="6"/>
-      <c r="F1006" s="7"/>
+      <c r="A1006" s="6">
+        <v>45597</v>
+      </c>
+      <c r="B1006" s="7" t="inlineStr">
+        <is>
+          <t>일본</t>
+        </is>
+      </c>
+      <c r="C1006" s="7" t="inlineStr">
+        <is>
+          <t>실업률</t>
+        </is>
+      </c>
+      <c r="D1006" s="7">
+        <v>2.5</v>
+      </c>
+      <c r="E1006" s="6">
+        <v>45672</v>
+      </c>
+      <c r="F1006" s="7" t="inlineStr">
+        <is>
+          <t>월간</t>
+        </is>
+      </c>
     </row>
     <row r="1007" spans="1:6">
-      <c r="A1007" s="6"/>
-      <c r="B1007" s="7"/>
-      <c r="C1007" s="7"/>
-      <c r="D1007" s="7"/>
-      <c r="E1007" s="6"/>
-      <c r="F1007" s="7"/>
+      <c r="A1007" s="6">
+        <v>45627</v>
+      </c>
+      <c r="B1007" s="7" t="inlineStr">
+        <is>
+          <t>일본</t>
+        </is>
+      </c>
+      <c r="C1007" s="7" t="inlineStr">
+        <is>
+          <t>실업률</t>
+        </is>
+      </c>
+      <c r="D1007" s="7">
+        <v>2.5</v>
+      </c>
+      <c r="E1007" s="6">
+        <v>45705</v>
+      </c>
+      <c r="F1007" s="7" t="inlineStr">
+        <is>
+          <t>월간</t>
+        </is>
+      </c>
     </row>
     <row r="1008" spans="1:6">
-      <c r="A1008" s="6"/>
-      <c r="B1008" s="7"/>
-      <c r="C1008" s="7"/>
-      <c r="D1008" s="7"/>
-      <c r="E1008" s="6"/>
-      <c r="F1008" s="7"/>
+      <c r="A1008" s="6">
+        <v>45658</v>
+      </c>
+      <c r="B1008" s="7" t="inlineStr">
+        <is>
+          <t>일본</t>
+        </is>
+      </c>
+      <c r="C1008" s="7" t="inlineStr">
+        <is>
+          <t>실업률</t>
+        </is>
+      </c>
+      <c r="D1008" s="7">
+        <v>2.5</v>
+      </c>
+      <c r="E1008" s="6">
+        <v>45733</v>
+      </c>
+      <c r="F1008" s="7" t="inlineStr">
+        <is>
+          <t>월간</t>
+        </is>
+      </c>
     </row>
     <row r="1009" spans="1:6">
-      <c r="A1009" s="6"/>
-      <c r="B1009" s="7"/>
-      <c r="C1009" s="7"/>
-      <c r="D1009" s="7"/>
-      <c r="E1009" s="6"/>
-      <c r="F1009" s="7"/>
+      <c r="A1009" s="6">
+        <v>45689</v>
+      </c>
+      <c r="B1009" s="7" t="inlineStr">
+        <is>
+          <t>일본</t>
+        </is>
+      </c>
+      <c r="C1009" s="7" t="inlineStr">
+        <is>
+          <t>실업률</t>
+        </is>
+      </c>
+      <c r="D1009" s="7">
+        <v>2.4</v>
+      </c>
+      <c r="E1009" s="6">
+        <v>45762</v>
+      </c>
+      <c r="F1009" s="7" t="inlineStr">
+        <is>
+          <t>월간</t>
+        </is>
+      </c>
     </row>
     <row r="1010" spans="1:6">
-      <c r="A1010" s="6"/>
-      <c r="B1010" s="7"/>
-      <c r="C1010" s="7"/>
-      <c r="D1010" s="7"/>
-      <c r="E1010" s="6"/>
-      <c r="F1010" s="7"/>
+      <c r="A1010" s="6">
+        <v>45717</v>
+      </c>
+      <c r="B1010" s="7" t="inlineStr">
+        <is>
+          <t>일본</t>
+        </is>
+      </c>
+      <c r="C1010" s="7" t="inlineStr">
+        <is>
+          <t>실업률</t>
+        </is>
+      </c>
+      <c r="D1010" s="7">
+        <v>2.5</v>
+      </c>
+      <c r="E1010" s="6">
+        <v>45792</v>
+      </c>
+      <c r="F1010" s="7" t="inlineStr">
+        <is>
+          <t>월간</t>
+        </is>
+      </c>
     </row>
     <row r="1011" spans="1:6">
-      <c r="A1011" s="6"/>
-      <c r="B1011" s="7"/>
-      <c r="C1011" s="7"/>
-      <c r="D1011" s="7"/>
-      <c r="E1011" s="6"/>
-      <c r="F1011" s="7"/>
+      <c r="A1011" s="6">
+        <v>45748</v>
+      </c>
+      <c r="B1011" s="7" t="inlineStr">
+        <is>
+          <t>일본</t>
+        </is>
+      </c>
+      <c r="C1011" s="7" t="inlineStr">
+        <is>
+          <t>실업률</t>
+        </is>
+      </c>
+      <c r="D1011" s="7">
+        <v>2.5</v>
+      </c>
+      <c r="E1011" s="6">
+        <v>45824</v>
+      </c>
+      <c r="F1011" s="7" t="inlineStr">
+        <is>
+          <t>월간</t>
+        </is>
+      </c>
     </row>
     <row r="1012" spans="1:6">
-      <c r="A1012" s="6"/>
-      <c r="B1012" s="7"/>
-      <c r="C1012" s="7"/>
-      <c r="D1012" s="7"/>
-      <c r="E1012" s="6"/>
-      <c r="F1012" s="7"/>
+      <c r="A1012" s="6">
+        <v>45778</v>
+      </c>
+      <c r="B1012" s="7" t="inlineStr">
+        <is>
+          <t>일본</t>
+        </is>
+      </c>
+      <c r="C1012" s="7" t="inlineStr">
+        <is>
+          <t>실업률</t>
+        </is>
+      </c>
+      <c r="D1012" s="7">
+        <v>2.5</v>
+      </c>
+      <c r="E1012" s="6">
+        <v>45853</v>
+      </c>
+      <c r="F1012" s="7" t="inlineStr">
+        <is>
+          <t>월간</t>
+        </is>
+      </c>
     </row>
     <row r="1013" spans="1:6">
-      <c r="A1013" s="6"/>
-      <c r="B1013" s="7"/>
-      <c r="C1013" s="7"/>
-      <c r="D1013" s="7"/>
-      <c r="E1013" s="6"/>
-      <c r="F1013" s="7"/>
+      <c r="A1013" s="6">
+        <v>45809</v>
+      </c>
+      <c r="B1013" s="7" t="inlineStr">
+        <is>
+          <t>일본</t>
+        </is>
+      </c>
+      <c r="C1013" s="7" t="inlineStr">
+        <is>
+          <t>실업률</t>
+        </is>
+      </c>
+      <c r="D1013" s="7">
+        <v>2.5</v>
+      </c>
+      <c r="E1013" s="6">
+        <v>45884</v>
+      </c>
+      <c r="F1013" s="7" t="inlineStr">
+        <is>
+          <t>월간</t>
+        </is>
+      </c>
     </row>
     <row r="1014" spans="1:6">
-      <c r="A1014" s="6"/>
-      <c r="B1014" s="7"/>
-      <c r="C1014" s="7"/>
-      <c r="D1014" s="7"/>
-      <c r="E1014" s="6"/>
-      <c r="F1014" s="7"/>
+      <c r="A1014" s="6">
+        <v>45839</v>
+      </c>
+      <c r="B1014" s="7" t="inlineStr">
+        <is>
+          <t>일본</t>
+        </is>
+      </c>
+      <c r="C1014" s="7" t="inlineStr">
+        <is>
+          <t>실업률</t>
+        </is>
+      </c>
+      <c r="D1014" s="7">
+        <v>2.4</v>
+      </c>
+      <c r="E1014" s="6">
+        <v>45915</v>
+      </c>
+      <c r="F1014" s="7" t="inlineStr">
+        <is>
+          <t>월간</t>
+        </is>
+      </c>
     </row>
     <row r="1015" spans="1:6">
-      <c r="A1015" s="6"/>
-      <c r="B1015" s="7"/>
-      <c r="C1015" s="7"/>
-      <c r="D1015" s="7"/>
-      <c r="E1015" s="6"/>
-      <c r="F1015" s="7"/>
+      <c r="A1015" s="6">
+        <v>45870</v>
+      </c>
+      <c r="B1015" s="7" t="inlineStr">
+        <is>
+          <t>일본</t>
+        </is>
+      </c>
+      <c r="C1015" s="7" t="inlineStr">
+        <is>
+          <t>실업률</t>
+        </is>
+      </c>
+      <c r="D1015" s="7">
+        <v>2.6</v>
+      </c>
+      <c r="E1015" s="6">
+        <v>45945</v>
+      </c>
+      <c r="F1015" s="7" t="inlineStr">
+        <is>
+          <t>월간</t>
+        </is>
+      </c>
     </row>
     <row r="1016" spans="1:6">
-      <c r="A1016" s="6"/>
-      <c r="B1016" s="7"/>
-      <c r="C1016" s="7"/>
-      <c r="D1016" s="7"/>
-      <c r="E1016" s="6"/>
-      <c r="F1016" s="7"/>
+      <c r="A1016" s="6">
+        <v>45901</v>
+      </c>
+      <c r="B1016" s="7" t="inlineStr">
+        <is>
+          <t>일본</t>
+        </is>
+      </c>
+      <c r="C1016" s="7" t="inlineStr">
+        <is>
+          <t>실업률</t>
+        </is>
+      </c>
+      <c r="D1016" s="7">
+        <v>2.6</v>
+      </c>
+      <c r="E1016" s="6">
+        <v>45978</v>
+      </c>
+      <c r="F1016" s="7" t="inlineStr">
+        <is>
+          <t>월간</t>
+        </is>
+      </c>
     </row>
     <row r="1017" spans="1:6">
-      <c r="A1017" s="6"/>
-      <c r="B1017" s="7"/>
-      <c r="C1017" s="7"/>
-      <c r="D1017" s="7"/>
-      <c r="E1017" s="6"/>
-      <c r="F1017" s="7"/>
+      <c r="A1017" s="6">
+        <v>45931</v>
+      </c>
+      <c r="B1017" s="7" t="inlineStr">
+        <is>
+          <t>일본</t>
+        </is>
+      </c>
+      <c r="C1017" s="7" t="inlineStr">
+        <is>
+          <t>실업률</t>
+        </is>
+      </c>
+      <c r="D1017" s="7">
+        <v>2.6</v>
+      </c>
+      <c r="E1017" s="6">
+        <v>46006</v>
+      </c>
+      <c r="F1017" s="7" t="inlineStr">
+        <is>
+          <t>월간</t>
+        </is>
+      </c>
     </row>
     <row r="1018" spans="1:6">
-      <c r="A1018" s="6"/>
-      <c r="B1018" s="7"/>
-      <c r="C1018" s="7"/>
-      <c r="D1018" s="7"/>
-      <c r="E1018" s="6"/>
-      <c r="F1018" s="7"/>
+      <c r="A1018" s="6">
+        <v>45962</v>
+      </c>
+      <c r="B1018" s="7" t="inlineStr">
+        <is>
+          <t>일본</t>
+        </is>
+      </c>
+      <c r="C1018" s="7" t="inlineStr">
+        <is>
+          <t>실업률</t>
+        </is>
+      </c>
+      <c r="D1018" s="7">
+        <v>2.6</v>
+      </c>
+      <c r="E1018" s="6">
+        <v>46037</v>
+      </c>
+      <c r="F1018" s="7" t="inlineStr">
+        <is>
+          <t>월간</t>
+        </is>
+      </c>
     </row>
     <row r="1019" spans="1:6">
-      <c r="A1019" s="6"/>
-      <c r="B1019" s="7"/>
-      <c r="C1019" s="7"/>
-      <c r="D1019" s="7"/>
-      <c r="E1019" s="6"/>
-      <c r="F1019" s="7"/>
+      <c r="A1019" s="6">
+        <v>45992</v>
+      </c>
+      <c r="B1019" s="7" t="inlineStr">
+        <is>
+          <t>일본</t>
+        </is>
+      </c>
+      <c r="C1019" s="7" t="inlineStr">
+        <is>
+          <t>실업률</t>
+        </is>
+      </c>
+      <c r="D1019" s="7">
+        <v>2.6</v>
+      </c>
+      <c r="E1019" s="6">
+        <v>46069</v>
+      </c>
+      <c r="F1019" s="7" t="inlineStr">
+        <is>
+          <t>월간</t>
+        </is>
+      </c>
     </row>
     <row r="1020" spans="1:6">
-      <c r="A1020" s="6"/>
-      <c r="B1020" s="7"/>
-      <c r="C1020" s="7"/>
-      <c r="D1020" s="7"/>
-      <c r="E1020" s="6"/>
-      <c r="F1020" s="7"/>
+      <c r="A1020" s="6">
+        <v>46023</v>
+      </c>
+      <c r="B1020" s="7" t="inlineStr">
+        <is>
+          <t>일본</t>
+        </is>
+      </c>
+      <c r="C1020" s="7" t="inlineStr">
+        <is>
+          <t>실업률</t>
+        </is>
+      </c>
+      <c r="D1020" s="7">
+        <v>2.7</v>
+      </c>
+      <c r="E1020" s="6">
+        <v>46097</v>
+      </c>
+      <c r="F1020" s="7" t="inlineStr">
+        <is>
+          <t>월간</t>
+        </is>
+      </c>
     </row>
     <row r="1021" spans="1:6">
-      <c r="A1021" s="6"/>
-      <c r="B1021" s="7"/>
-      <c r="C1021" s="7"/>
-      <c r="D1021" s="7"/>
-      <c r="E1021" s="6"/>
-      <c r="F1021" s="7"/>
+      <c r="A1021" s="6">
+        <v>46054</v>
+      </c>
+      <c r="B1021" s="7" t="inlineStr">
+        <is>
+          <t>일본</t>
+        </is>
+      </c>
+      <c r="C1021" s="7" t="inlineStr">
+        <is>
+          <t>실업률</t>
+        </is>
+      </c>
+      <c r="D1021" s="7">
+        <v>2.6</v>
+      </c>
+      <c r="E1021" s="6">
+        <v>46127</v>
+      </c>
+      <c r="F1021" s="7" t="inlineStr">
+        <is>
+          <t>월간</t>
+        </is>
+      </c>
     </row>
     <row r="1022" spans="1:6">
-      <c r="A1022" s="6"/>
-      <c r="B1022" s="7"/>
-      <c r="C1022" s="7"/>
-      <c r="D1022" s="7"/>
-      <c r="E1022" s="6"/>
-      <c r="F1022" s="7"/>
+      <c r="A1022" s="6">
+        <v>46082</v>
+      </c>
+      <c r="B1022" s="7" t="inlineStr">
+        <is>
+          <t>일본</t>
+        </is>
+      </c>
+      <c r="C1022" s="7" t="inlineStr">
+        <is>
+          <t>실업률</t>
+        </is>
+      </c>
+      <c r="D1022" s="7">
+        <v>2.7</v>
+      </c>
+      <c r="E1022" s="6">
+        <v>46157</v>
+      </c>
+      <c r="F1022" s="7" t="inlineStr">
+        <is>
+          <t>월간</t>
+        </is>
+      </c>
     </row>
     <row r="1023" spans="1:6">
-      <c r="A1023" s="6"/>
-      <c r="B1023" s="7"/>
-      <c r="C1023" s="7"/>
-      <c r="D1023" s="7"/>
-      <c r="E1023" s="6"/>
-      <c r="F1023" s="7"/>
+      <c r="A1023" s="6">
+        <v>46113</v>
+      </c>
+      <c r="B1023" s="7" t="inlineStr">
+        <is>
+          <t>일본</t>
+        </is>
+      </c>
+      <c r="C1023" s="7" t="inlineStr">
+        <is>
+          <t>실업률</t>
+        </is>
+      </c>
+      <c r="D1023" s="7">
+        <v>2.5</v>
+      </c>
+      <c r="E1023" s="6">
+        <v>46188</v>
+      </c>
+      <c r="F1023" s="7" t="inlineStr">
+        <is>
+          <t>월간</t>
+        </is>
+      </c>
     </row>
     <row r="1024" spans="1:6">
-      <c r="A1024" s="6"/>
-      <c r="B1024" s="7"/>
-      <c r="C1024" s="7"/>
-      <c r="D1024" s="7"/>
-      <c r="E1024" s="6"/>
-      <c r="F1024" s="7"/>
+      <c r="A1024" s="6">
+        <v>46143</v>
+      </c>
+      <c r="B1024" s="7" t="inlineStr">
+        <is>
+          <t>일본</t>
+        </is>
+      </c>
+      <c r="C1024" s="7" t="inlineStr">
+        <is>
+          <t>실업률</t>
+        </is>
+      </c>
+      <c r="D1024" s="7">
+        <v>2.5</v>
+      </c>
+      <c r="E1024" s="6">
+        <v>46219</v>
+      </c>
+      <c r="F1024" s="7" t="inlineStr">
+        <is>
+          <t>월간</t>
+        </is>
+      </c>
     </row>
     <row r="1025" spans="1:6">
-      <c r="A1025" s="6"/>
-      <c r="B1025" s="7"/>
-      <c r="C1025" s="7"/>
-      <c r="D1025" s="7"/>
-      <c r="E1025" s="6"/>
-      <c r="F1025" s="7"/>
+      <c r="A1025" s="6">
+        <v>46174</v>
+      </c>
+      <c r="B1025" s="7" t="inlineStr">
+        <is>
+          <t>일본</t>
+        </is>
+      </c>
+      <c r="C1025" s="7" t="inlineStr">
+        <is>
+          <t>실업률</t>
+        </is>
+      </c>
+      <c r="D1025" s="7">
+        <v>2.5</v>
+      </c>
+      <c r="E1025" s="6">
+        <v>46251</v>
+      </c>
+      <c r="F1025" s="7" t="inlineStr">
+        <is>
+          <t>월간</t>
+        </is>
+      </c>
     </row>
     <row r="1026" spans="1:6">
-      <c r="A1026" s="6"/>
-      <c r="B1026" s="7"/>
-      <c r="C1026" s="7"/>
-      <c r="D1026" s="7"/>
-      <c r="E1026" s="6"/>
-      <c r="F1026" s="7"/>
+      <c r="A1026" s="6">
+        <v>46204</v>
+      </c>
+      <c r="B1026" s="7" t="inlineStr">
+        <is>
+          <t>일본</t>
+        </is>
+      </c>
+      <c r="C1026" s="7" t="inlineStr">
+        <is>
+          <t>실업률</t>
+        </is>
+      </c>
+      <c r="D1026" s="7">
+        <v>2.4</v>
+      </c>
+      <c r="E1026" s="6">
+        <v>46280</v>
+      </c>
+      <c r="F1026" s="7" t="inlineStr">
+        <is>
+          <t>월간</t>
+        </is>
+      </c>
     </row>
     <row r="1027" spans="1:6">
-      <c r="A1027" s="6"/>
-      <c r="B1027" s="7"/>
-      <c r="C1027" s="7"/>
-      <c r="D1027" s="7"/>
+      <c r="A1027" s="6">
+        <v>44378</v>
+      </c>
+      <c r="B1027" s="7" t="inlineStr">
+        <is>
+          <t>일본</t>
+        </is>
+      </c>
+      <c r="C1027" s="7" t="inlineStr">
+        <is>
+          <t>실질GDP 성장률</t>
+        </is>
+      </c>
+      <c r="D1027" s="7">
+        <v>-0.19</v>
+      </c>
       <c r="E1027" s="6"/>
-      <c r="F1027" s="7"/>
+      <c r="F1027" s="7" t="inlineStr">
+        <is>
+          <t>분기</t>
+        </is>
+      </c>
     </row>
     <row r="1028" spans="1:6">
-      <c r="A1028" s="6"/>
-      <c r="B1028" s="7"/>
-      <c r="C1028" s="7"/>
-      <c r="D1028" s="7"/>
+      <c r="A1028" s="6">
+        <v>44470</v>
+      </c>
+      <c r="B1028" s="7" t="inlineStr">
+        <is>
+          <t>일본</t>
+        </is>
+      </c>
+      <c r="C1028" s="7" t="inlineStr">
+        <is>
+          <t>실질GDP 성장률</t>
+        </is>
+      </c>
+      <c r="D1028" s="7">
+        <v>1.18</v>
+      </c>
       <c r="E1028" s="6"/>
-      <c r="F1028" s="7"/>
+      <c r="F1028" s="7" t="inlineStr">
+        <is>
+          <t>분기</t>
+        </is>
+      </c>
     </row>
     <row r="1029" spans="1:6">
-      <c r="A1029" s="6"/>
-      <c r="B1029" s="7"/>
-      <c r="C1029" s="7"/>
-      <c r="D1029" s="7"/>
+      <c r="A1029" s="6">
+        <v>44562</v>
+      </c>
+      <c r="B1029" s="7" t="inlineStr">
+        <is>
+          <t>일본</t>
+        </is>
+      </c>
+      <c r="C1029" s="7" t="inlineStr">
+        <is>
+          <t>실질GDP 성장률</t>
+        </is>
+      </c>
+      <c r="D1029" s="7">
+        <v>-0.44</v>
+      </c>
       <c r="E1029" s="6"/>
-      <c r="F1029" s="7"/>
+      <c r="F1029" s="7" t="inlineStr">
+        <is>
+          <t>분기</t>
+        </is>
+      </c>
     </row>
     <row r="1030" spans="1:6">
-      <c r="A1030" s="6"/>
-      <c r="B1030" s="7"/>
-      <c r="C1030" s="7"/>
-      <c r="D1030" s="7"/>
+      <c r="A1030" s="6">
+        <v>44652</v>
+      </c>
+      <c r="B1030" s="7" t="inlineStr">
+        <is>
+          <t>일본</t>
+        </is>
+      </c>
+      <c r="C1030" s="7" t="inlineStr">
+        <is>
+          <t>실질GDP 성장률</t>
+        </is>
+      </c>
+      <c r="D1030" s="7">
+        <v>0.95</v>
+      </c>
       <c r="E1030" s="6"/>
-      <c r="F1030" s="7"/>
+      <c r="F1030" s="7" t="inlineStr">
+        <is>
+          <t>분기</t>
+        </is>
+      </c>
     </row>
     <row r="1031" spans="1:6">
-      <c r="A1031" s="6"/>
-      <c r="B1031" s="7"/>
-      <c r="C1031" s="7"/>
-      <c r="D1031" s="7"/>
+      <c r="A1031" s="6">
+        <v>44743</v>
+      </c>
+      <c r="B1031" s="7" t="inlineStr">
+        <is>
+          <t>일본</t>
+        </is>
+      </c>
+      <c r="C1031" s="7" t="inlineStr">
+        <is>
+          <t>실질GDP 성장률</t>
+        </is>
+      </c>
+      <c r="D1031" s="7">
+        <v>-0.27</v>
+      </c>
       <c r="E1031" s="6"/>
-      <c r="F1031" s="7"/>
+      <c r="F1031" s="7" t="inlineStr">
+        <is>
+          <t>분기</t>
+        </is>
+      </c>
     </row>
     <row r="1032" spans="1:6">
-      <c r="A1032" s="6"/>
-      <c r="B1032" s="7"/>
-      <c r="C1032" s="7"/>
-      <c r="D1032" s="7"/>
+      <c r="A1032" s="6">
+        <v>44835</v>
+      </c>
+      <c r="B1032" s="7" t="inlineStr">
+        <is>
+          <t>일본</t>
+        </is>
+      </c>
+      <c r="C1032" s="7" t="inlineStr">
+        <is>
+          <t>실질GDP 성장률</t>
+        </is>
+      </c>
+      <c r="D1032" s="7">
+        <v>0.5</v>
+      </c>
       <c r="E1032" s="6"/>
-      <c r="F1032" s="7"/>
+      <c r="F1032" s="7" t="inlineStr">
+        <is>
+          <t>분기</t>
+        </is>
+      </c>
     </row>
     <row r="1033" spans="1:6">
-      <c r="A1033" s="6"/>
-      <c r="B1033" s="7"/>
-      <c r="C1033" s="7"/>
-      <c r="D1033" s="7"/>
+      <c r="A1033" s="6">
+        <v>44927</v>
+      </c>
+      <c r="B1033" s="7" t="inlineStr">
+        <is>
+          <t>일본</t>
+        </is>
+      </c>
+      <c r="C1033" s="7" t="inlineStr">
+        <is>
+          <t>실질GDP 성장률</t>
+        </is>
+      </c>
+      <c r="D1033" s="7">
+        <v>0.87</v>
+      </c>
       <c r="E1033" s="6"/>
-      <c r="F1033" s="7"/>
+      <c r="F1033" s="7" t="inlineStr">
+        <is>
+          <t>분기</t>
+        </is>
+      </c>
     </row>
     <row r="1034" spans="1:6">
-      <c r="A1034" s="6"/>
-      <c r="B1034" s="7"/>
-      <c r="C1034" s="7"/>
-      <c r="D1034" s="7"/>
+      <c r="A1034" s="6">
+        <v>45017</v>
+      </c>
+      <c r="B1034" s="7" t="inlineStr">
+        <is>
+          <t>일본</t>
+        </is>
+      </c>
+      <c r="C1034" s="7" t="inlineStr">
+        <is>
+          <t>실질GDP 성장률</t>
+        </is>
+      </c>
+      <c r="D1034" s="7">
+        <v>0.07</v>
+      </c>
       <c r="E1034" s="6"/>
-      <c r="F1034" s="7"/>
+      <c r="F1034" s="7" t="inlineStr">
+        <is>
+          <t>분기</t>
+        </is>
+      </c>
     </row>
     <row r="1035" spans="1:6">
-      <c r="A1035" s="6"/>
-      <c r="B1035" s="7"/>
-      <c r="C1035" s="7"/>
-      <c r="D1035" s="7"/>
+      <c r="A1035" s="6">
+        <v>45108</v>
+      </c>
+      <c r="B1035" s="7" t="inlineStr">
+        <is>
+          <t>일본</t>
+        </is>
+      </c>
+      <c r="C1035" s="7" t="inlineStr">
+        <is>
+          <t>실질GDP 성장률</t>
+        </is>
+      </c>
+      <c r="D1035" s="7">
+        <v>-1.25</v>
+      </c>
       <c r="E1035" s="6"/>
-      <c r="F1035" s="7"/>
+      <c r="F1035" s="7" t="inlineStr">
+        <is>
+          <t>분기</t>
+        </is>
+      </c>
     </row>
     <row r="1036" spans="1:6">
-      <c r="A1036" s="6"/>
-      <c r="B1036" s="7"/>
-      <c r="C1036" s="7"/>
-      <c r="D1036" s="7"/>
+      <c r="A1036" s="6">
+        <v>45200</v>
+      </c>
+      <c r="B1036" s="7" t="inlineStr">
+        <is>
+          <t>일본</t>
+        </is>
+      </c>
+      <c r="C1036" s="7" t="inlineStr">
+        <is>
+          <t>실질GDP 성장률</t>
+        </is>
+      </c>
+      <c r="D1036" s="7">
+        <v>0.48</v>
+      </c>
       <c r="E1036" s="6"/>
-      <c r="F1036" s="7"/>
+      <c r="F1036" s="7" t="inlineStr">
+        <is>
+          <t>분기</t>
+        </is>
+      </c>
     </row>
     <row r="1037" spans="1:6">
-      <c r="A1037" s="6"/>
-      <c r="B1037" s="7"/>
-      <c r="C1037" s="7"/>
-      <c r="D1037" s="7"/>
+      <c r="A1037" s="6">
+        <v>45292</v>
+      </c>
+      <c r="B1037" s="7" t="inlineStr">
+        <is>
+          <t>일본</t>
+        </is>
+      </c>
+      <c r="C1037" s="7" t="inlineStr">
+        <is>
+          <t>실질GDP 성장률</t>
+        </is>
+      </c>
+      <c r="D1037" s="7">
+        <v>-0.09</v>
+      </c>
       <c r="E1037" s="6"/>
-      <c r="F1037" s="7"/>
+      <c r="F1037" s="7" t="inlineStr">
+        <is>
+          <t>분기</t>
+        </is>
+      </c>
     </row>
     <row r="1038" spans="1:6">
-      <c r="A1038" s="6"/>
-      <c r="B1038" s="7"/>
-      <c r="C1038" s="7"/>
-      <c r="D1038" s="7"/>
+      <c r="A1038" s="6">
+        <v>45383</v>
+      </c>
+      <c r="B1038" s="7" t="inlineStr">
+        <is>
+          <t>일본</t>
+        </is>
+      </c>
+      <c r="C1038" s="7" t="inlineStr">
+        <is>
+          <t>실질GDP 성장률</t>
+        </is>
+      </c>
+      <c r="D1038" s="7">
+        <v>-0.12</v>
+      </c>
       <c r="E1038" s="6"/>
-      <c r="F1038" s="7"/>
+      <c r="F1038" s="7" t="inlineStr">
+        <is>
+          <t>분기</t>
+        </is>
+      </c>
     </row>
     <row r="1039" spans="1:6">
-      <c r="A1039" s="6"/>
-      <c r="B1039" s="7"/>
-      <c r="C1039" s="7"/>
-      <c r="D1039" s="7"/>
+      <c r="A1039" s="6">
+        <v>45474</v>
+      </c>
+      <c r="B1039" s="7" t="inlineStr">
+        <is>
+          <t>일본</t>
+        </is>
+      </c>
+      <c r="C1039" s="7" t="inlineStr">
+        <is>
+          <t>실질GDP 성장률</t>
+        </is>
+      </c>
+      <c r="D1039" s="7">
+        <v>0.84</v>
+      </c>
       <c r="E1039" s="6"/>
-      <c r="F1039" s="7"/>
+      <c r="F1039" s="7" t="inlineStr">
+        <is>
+          <t>분기</t>
+        </is>
+      </c>
     </row>
     <row r="1040" spans="1:6">
-      <c r="A1040" s="6"/>
-      <c r="B1040" s="7"/>
-      <c r="C1040" s="7"/>
-      <c r="D1040" s="7"/>
+      <c r="A1040" s="6">
+        <v>45566</v>
+      </c>
+      <c r="B1040" s="7" t="inlineStr">
+        <is>
+          <t>일본</t>
+        </is>
+      </c>
+      <c r="C1040" s="7" t="inlineStr">
+        <is>
+          <t>실질GDP 성장률</t>
+        </is>
+      </c>
+      <c r="D1040" s="7">
+        <v>0.4</v>
+      </c>
       <c r="E1040" s="6"/>
-      <c r="F1040" s="7"/>
+      <c r="F1040" s="7" t="inlineStr">
+        <is>
+          <t>분기</t>
+        </is>
+      </c>
     </row>
     <row r="1041" spans="1:6">
-      <c r="A1041" s="6"/>
-      <c r="B1041" s="7"/>
-      <c r="C1041" s="7"/>
-      <c r="D1041" s="7"/>
+      <c r="A1041" s="6">
+        <v>45658</v>
+      </c>
+      <c r="B1041" s="7" t="inlineStr">
+        <is>
+          <t>일본</t>
+        </is>
+      </c>
+      <c r="C1041" s="7" t="inlineStr">
+        <is>
+          <t>실질GDP 성장률</t>
+        </is>
+      </c>
+      <c r="D1041" s="7">
+        <v>0.5</v>
+      </c>
       <c r="E1041" s="6"/>
-      <c r="F1041" s="7"/>
+      <c r="F1041" s="7" t="inlineStr">
+        <is>
+          <t>분기</t>
+        </is>
+      </c>
     </row>
     <row r="1042" spans="1:6">
-      <c r="A1042" s="6"/>
-      <c r="B1042" s="7"/>
-      <c r="C1042" s="7"/>
-      <c r="D1042" s="7"/>
+      <c r="A1042" s="6">
+        <v>45748</v>
+      </c>
+      <c r="B1042" s="7" t="inlineStr">
+        <is>
+          <t>일본</t>
+        </is>
+      </c>
+      <c r="C1042" s="7" t="inlineStr">
+        <is>
+          <t>실질GDP 성장률</t>
+        </is>
+      </c>
+      <c r="D1042" s="7">
+        <v>0.12</v>
+      </c>
       <c r="E1042" s="6"/>
-      <c r="F1042" s="7"/>
+      <c r="F1042" s="7" t="inlineStr">
+        <is>
+          <t>분기</t>
+        </is>
+      </c>
     </row>
     <row r="1043" spans="1:6">
-      <c r="A1043" s="6"/>
-      <c r="B1043" s="7"/>
-      <c r="C1043" s="7"/>
-      <c r="D1043" s="7"/>
+      <c r="A1043" s="6">
+        <v>45839</v>
+      </c>
+      <c r="B1043" s="7" t="inlineStr">
+        <is>
+          <t>일본</t>
+        </is>
+      </c>
+      <c r="C1043" s="7" t="inlineStr">
+        <is>
+          <t>실질GDP 성장률</t>
+        </is>
+      </c>
+      <c r="D1043" s="7">
+        <v>-0.37</v>
+      </c>
       <c r="E1043" s="6"/>
-      <c r="F1043" s="7"/>
+      <c r="F1043" s="7" t="inlineStr">
+        <is>
+          <t>분기</t>
+        </is>
+      </c>
     </row>
     <row r="1044" spans="1:6">
-      <c r="A1044" s="6"/>
-      <c r="B1044" s="7"/>
-      <c r="C1044" s="7"/>
-      <c r="D1044" s="7"/>
+      <c r="A1044" s="6">
+        <v>45931</v>
+      </c>
+      <c r="B1044" s="7" t="inlineStr">
+        <is>
+          <t>일본</t>
+        </is>
+      </c>
+      <c r="C1044" s="7" t="inlineStr">
+        <is>
+          <t>실질GDP 성장률</t>
+        </is>
+      </c>
+      <c r="D1044" s="7">
+        <v>0.26</v>
+      </c>
       <c r="E1044" s="6"/>
-      <c r="F1044" s="7"/>
+      <c r="F1044" s="7" t="inlineStr">
+        <is>
+          <t>분기</t>
+        </is>
+      </c>
     </row>
     <row r="1045" spans="1:6">
-      <c r="A1045" s="6"/>
-      <c r="B1045" s="7"/>
-      <c r="C1045" s="7"/>
-      <c r="D1045" s="7"/>
+      <c r="A1045" s="6">
+        <v>46023</v>
+      </c>
+      <c r="B1045" s="7" t="inlineStr">
+        <is>
+          <t>일본</t>
+        </is>
+      </c>
+      <c r="C1045" s="7" t="inlineStr">
+        <is>
+          <t>실질GDP 성장률</t>
+        </is>
+      </c>
+      <c r="D1045" s="7">
+        <v>0.48</v>
+      </c>
       <c r="E1045" s="6"/>
-      <c r="F1045" s="7"/>
+      <c r="F1045" s="7" t="inlineStr">
+        <is>
+          <t>분기</t>
+        </is>
+      </c>
     </row>
     <row r="1046" spans="1:6">
-      <c r="A1046" s="6"/>
-      <c r="B1046" s="7"/>
-      <c r="C1046" s="7"/>
-      <c r="D1046" s="7"/>
+      <c r="A1046" s="6">
+        <v>46113</v>
+      </c>
+      <c r="B1046" s="7" t="inlineStr">
+        <is>
+          <t>일본</t>
+        </is>
+      </c>
+      <c r="C1046" s="7" t="inlineStr">
+        <is>
+          <t>실질GDP 성장률</t>
+        </is>
+      </c>
+      <c r="D1046" s="7">
+        <v>0.36</v>
+      </c>
       <c r="E1046" s="6"/>
-      <c r="F1046" s="7"/>
+      <c r="F1046" s="7" t="inlineStr">
+        <is>
+          <t>분기</t>
+        </is>
+      </c>
     </row>
     <row r="1047" spans="1:6">
-      <c r="A1047" s="6"/>
-      <c r="B1047" s="7"/>
-      <c r="C1047" s="7"/>
-      <c r="D1047" s="7"/>
-      <c r="E1047" s="6"/>
-      <c r="F1047" s="7"/>
+      <c r="A1047" s="6">
+        <v>44440</v>
+      </c>
+      <c r="B1047" s="7" t="inlineStr">
+        <is>
+          <t>일본</t>
+        </is>
+      </c>
+      <c r="C1047" s="7" t="inlineStr">
+        <is>
+          <t>두바이유</t>
+        </is>
+      </c>
+      <c r="D1047" s="7">
+        <v>72.7582</v>
+      </c>
+      <c r="E1047" s="6">
+        <v>44483</v>
+      </c>
+      <c r="F1047" s="7" t="inlineStr">
+        <is>
+          <t>월간</t>
+        </is>
+      </c>
     </row>
     <row r="1048" spans="1:6">
-      <c r="A1048" s="6"/>
-      <c r="B1048" s="7"/>
-      <c r="C1048" s="7"/>
-      <c r="D1048" s="7"/>
-      <c r="E1048" s="6"/>
-      <c r="F1048" s="7"/>
+      <c r="A1048" s="6">
+        <v>44470</v>
+      </c>
+      <c r="B1048" s="7" t="inlineStr">
+        <is>
+          <t>일본</t>
+        </is>
+      </c>
+      <c r="C1048" s="7" t="inlineStr">
+        <is>
+          <t>두바이유</t>
+        </is>
+      </c>
+      <c r="D1048" s="7">
+        <v>81.4371</v>
+      </c>
+      <c r="E1048" s="6">
+        <v>44524</v>
+      </c>
+      <c r="F1048" s="7" t="inlineStr">
+        <is>
+          <t>월간</t>
+        </is>
+      </c>
     </row>
     <row r="1049" spans="1:6">
-      <c r="A1049" s="6"/>
-      <c r="B1049" s="7"/>
-      <c r="C1049" s="7"/>
-      <c r="D1049" s="7"/>
-      <c r="E1049" s="6"/>
-      <c r="F1049" s="7"/>
+      <c r="A1049" s="6">
+        <v>44501</v>
+      </c>
+      <c r="B1049" s="7" t="inlineStr">
+        <is>
+          <t>일본</t>
+        </is>
+      </c>
+      <c r="C1049" s="7" t="inlineStr">
+        <is>
+          <t>두바이유</t>
+        </is>
+      </c>
+      <c r="D1049" s="7">
+        <v>78.6577</v>
+      </c>
+      <c r="E1049" s="6">
+        <v>44536</v>
+      </c>
+      <c r="F1049" s="7" t="inlineStr">
+        <is>
+          <t>월간</t>
+        </is>
+      </c>
     </row>
     <row r="1050" spans="1:6">
-      <c r="A1050" s="6"/>
-      <c r="B1050" s="7"/>
-      <c r="C1050" s="7"/>
-      <c r="D1050" s="7"/>
-      <c r="E1050" s="6"/>
-      <c r="F1050" s="7"/>
+      <c r="A1050" s="6">
+        <v>44531</v>
+      </c>
+      <c r="B1050" s="7" t="inlineStr">
+        <is>
+          <t>일본</t>
+        </is>
+      </c>
+      <c r="C1050" s="7" t="inlineStr">
+        <is>
+          <t>두바이유</t>
+        </is>
+      </c>
+      <c r="D1050" s="7">
+        <v>72.8478</v>
+      </c>
+      <c r="E1050" s="6">
+        <v>44797</v>
+      </c>
+      <c r="F1050" s="7" t="inlineStr">
+        <is>
+          <t>월간</t>
+        </is>
+      </c>
     </row>
     <row r="1051" spans="1:6">
-      <c r="A1051" s="6"/>
-      <c r="B1051" s="7"/>
-      <c r="C1051" s="7"/>
-      <c r="D1051" s="7"/>
-      <c r="E1051" s="6"/>
-      <c r="F1051" s="7"/>
+      <c r="A1051" s="6">
+        <v>44562</v>
+      </c>
+      <c r="B1051" s="7" t="inlineStr">
+        <is>
+          <t>일본</t>
+        </is>
+      </c>
+      <c r="C1051" s="7" t="inlineStr">
+        <is>
+          <t>두바이유</t>
+        </is>
+      </c>
+      <c r="D1051" s="7">
+        <v>83.451</v>
+      </c>
+      <c r="E1051" s="6">
+        <v>44797</v>
+      </c>
+      <c r="F1051" s="7" t="inlineStr">
+        <is>
+          <t>월간</t>
+        </is>
+      </c>
     </row>
     <row r="1052" spans="1:6">
-      <c r="A1052" s="6"/>
-      <c r="B1052" s="7"/>
-      <c r="C1052" s="7"/>
-      <c r="D1052" s="7"/>
-      <c r="E1052" s="6"/>
-      <c r="F1052" s="7"/>
+      <c r="A1052" s="6">
+        <v>44593</v>
+      </c>
+      <c r="B1052" s="7" t="inlineStr">
+        <is>
+          <t>일본</t>
+        </is>
+      </c>
+      <c r="C1052" s="7" t="inlineStr">
+        <is>
+          <t>두바이유</t>
+        </is>
+      </c>
+      <c r="D1052" s="7">
+        <v>91.525</v>
+      </c>
+      <c r="E1052" s="6">
+        <v>44797</v>
+      </c>
+      <c r="F1052" s="7" t="inlineStr">
+        <is>
+          <t>월간</t>
+        </is>
+      </c>
     </row>
     <row r="1053" spans="1:6">
-      <c r="A1053" s="6"/>
-      <c r="B1053" s="7"/>
-      <c r="C1053" s="7"/>
-      <c r="D1053" s="7"/>
-      <c r="E1053" s="6"/>
-      <c r="F1053" s="7"/>
+      <c r="A1053" s="6">
+        <v>44621</v>
+      </c>
+      <c r="B1053" s="7" t="inlineStr">
+        <is>
+          <t>일본</t>
+        </is>
+      </c>
+      <c r="C1053" s="7" t="inlineStr">
+        <is>
+          <t>두바이유</t>
+        </is>
+      </c>
+      <c r="D1053" s="7">
+        <v>107.5878</v>
+      </c>
+      <c r="E1053" s="6">
+        <v>44797</v>
+      </c>
+      <c r="F1053" s="7" t="inlineStr">
+        <is>
+          <t>월간</t>
+        </is>
+      </c>
     </row>
     <row r="1054" spans="1:6">
-      <c r="A1054" s="6"/>
-      <c r="B1054" s="7"/>
-      <c r="C1054" s="7"/>
-      <c r="D1054" s="7"/>
-      <c r="E1054" s="6"/>
-      <c r="F1054" s="7"/>
+      <c r="A1054" s="6">
+        <v>44652</v>
+      </c>
+      <c r="B1054" s="7" t="inlineStr">
+        <is>
+          <t>일본</t>
+        </is>
+      </c>
+      <c r="C1054" s="7" t="inlineStr">
+        <is>
+          <t>두바이유</t>
+        </is>
+      </c>
+      <c r="D1054" s="7">
+        <v>102.7552</v>
+      </c>
+      <c r="E1054" s="6">
+        <v>44797</v>
+      </c>
+      <c r="F1054" s="7" t="inlineStr">
+        <is>
+          <t>월간</t>
+        </is>
+      </c>
     </row>
     <row r="1055" spans="1:6">
-      <c r="A1055" s="6"/>
-      <c r="B1055" s="7"/>
-      <c r="C1055" s="7"/>
-      <c r="D1055" s="7"/>
-      <c r="E1055" s="6"/>
-      <c r="F1055" s="7"/>
+      <c r="A1055" s="6">
+        <v>44682</v>
+      </c>
+      <c r="B1055" s="7" t="inlineStr">
+        <is>
+          <t>일본</t>
+        </is>
+      </c>
+      <c r="C1055" s="7" t="inlineStr">
+        <is>
+          <t>두바이유</t>
+        </is>
+      </c>
+      <c r="D1055" s="7">
+        <v>107.8614</v>
+      </c>
+      <c r="E1055" s="6">
+        <v>44797</v>
+      </c>
+      <c r="F1055" s="7" t="inlineStr">
+        <is>
+          <t>월간</t>
+        </is>
+      </c>
     </row>
     <row r="1056" spans="1:6">
-      <c r="A1056" s="6"/>
-      <c r="B1056" s="7"/>
-      <c r="C1056" s="7"/>
-      <c r="D1056" s="7"/>
-      <c r="E1056" s="6"/>
-      <c r="F1056" s="7"/>
+      <c r="A1056" s="6">
+        <v>44713</v>
+      </c>
+      <c r="B1056" s="7" t="inlineStr">
+        <is>
+          <t>일본</t>
+        </is>
+      </c>
+      <c r="C1056" s="7" t="inlineStr">
+        <is>
+          <t>두바이유</t>
+        </is>
+      </c>
+      <c r="D1056" s="7">
+        <v>111.8595</v>
+      </c>
+      <c r="E1056" s="6">
+        <v>44797</v>
+      </c>
+      <c r="F1056" s="7" t="inlineStr">
+        <is>
+          <t>월간</t>
+        </is>
+      </c>
     </row>
     <row r="1057" spans="1:6">
-      <c r="A1057" s="6"/>
-      <c r="B1057" s="7"/>
-      <c r="C1057" s="7"/>
-      <c r="D1057" s="7"/>
-      <c r="E1057" s="6"/>
-      <c r="F1057" s="7"/>
+      <c r="A1057" s="6">
+        <v>44743</v>
+      </c>
+      <c r="B1057" s="7" t="inlineStr">
+        <is>
+          <t>일본</t>
+        </is>
+      </c>
+      <c r="C1057" s="7" t="inlineStr">
+        <is>
+          <t>두바이유</t>
+        </is>
+      </c>
+      <c r="D1057" s="7">
+        <v>100.3186</v>
+      </c>
+      <c r="E1057" s="6">
+        <v>44797</v>
+      </c>
+      <c r="F1057" s="7" t="inlineStr">
+        <is>
+          <t>월간</t>
+        </is>
+      </c>
     </row>
     <row r="1058" spans="1:6">
-      <c r="A1058" s="6"/>
-      <c r="B1058" s="7"/>
-      <c r="C1058" s="7"/>
-      <c r="D1058" s="7"/>
-      <c r="E1058" s="6"/>
-      <c r="F1058" s="7"/>
+      <c r="A1058" s="6">
+        <v>44774</v>
+      </c>
+      <c r="B1058" s="7" t="inlineStr">
+        <is>
+          <t>일본</t>
+        </is>
+      </c>
+      <c r="C1058" s="7" t="inlineStr">
+        <is>
+          <t>두바이유</t>
+        </is>
+      </c>
+      <c r="D1058" s="7">
+        <v>95.693</v>
+      </c>
+      <c r="E1058" s="6">
+        <v>44833</v>
+      </c>
+      <c r="F1058" s="7" t="inlineStr">
+        <is>
+          <t>월간</t>
+        </is>
+      </c>
     </row>
     <row r="1059" spans="1:6">
-      <c r="A1059" s="6"/>
-      <c r="B1059" s="7"/>
-      <c r="C1059" s="7"/>
-      <c r="D1059" s="7"/>
-      <c r="E1059" s="6"/>
-      <c r="F1059" s="7"/>
+      <c r="A1059" s="6">
+        <v>44805</v>
+      </c>
+      <c r="B1059" s="7" t="inlineStr">
+        <is>
+          <t>일본</t>
+        </is>
+      </c>
+      <c r="C1059" s="7" t="inlineStr">
+        <is>
+          <t>두바이유</t>
+        </is>
+      </c>
+      <c r="D1059" s="7">
+        <v>89.7427</v>
+      </c>
+      <c r="E1059" s="6">
+        <v>44858</v>
+      </c>
+      <c r="F1059" s="7" t="inlineStr">
+        <is>
+          <t>월간</t>
+        </is>
+      </c>
     </row>
     <row r="1060" spans="1:6">
-      <c r="A1060" s="6"/>
-      <c r="B1060" s="7"/>
-      <c r="C1060" s="7"/>
-      <c r="D1060" s="7"/>
-      <c r="E1060" s="6"/>
-      <c r="F1060" s="7"/>
+      <c r="A1060" s="6">
+        <v>44835</v>
+      </c>
+      <c r="B1060" s="7" t="inlineStr">
+        <is>
+          <t>일본</t>
+        </is>
+      </c>
+      <c r="C1060" s="7" t="inlineStr">
+        <is>
+          <t>두바이유</t>
+        </is>
+      </c>
+      <c r="D1060" s="7">
+        <v>91.2148</v>
+      </c>
+      <c r="E1060" s="6">
+        <v>44887</v>
+      </c>
+      <c r="F1060" s="7" t="inlineStr">
+        <is>
+          <t>월간</t>
+        </is>
+      </c>
     </row>
     <row r="1061" spans="1:6">
-      <c r="A1061" s="6"/>
-      <c r="B1061" s="7"/>
-      <c r="C1061" s="7"/>
-      <c r="D1061" s="7"/>
-      <c r="E1061" s="6"/>
-      <c r="F1061" s="7"/>
+      <c r="A1061" s="6">
+        <v>44866</v>
+      </c>
+      <c r="B1061" s="7" t="inlineStr">
+        <is>
+          <t>일본</t>
+        </is>
+      </c>
+      <c r="C1061" s="7" t="inlineStr">
+        <is>
+          <t>두바이유</t>
+        </is>
+      </c>
+      <c r="D1061" s="7">
+        <v>84.5991</v>
+      </c>
+      <c r="E1061" s="6">
+        <v>44929</v>
+      </c>
+      <c r="F1061" s="7" t="inlineStr">
+        <is>
+          <t>월간</t>
+        </is>
+      </c>
     </row>
     <row r="1062" spans="1:6">
-      <c r="A1062" s="6"/>
-      <c r="B1062" s="7"/>
-      <c r="C1062" s="7"/>
-      <c r="D1062" s="7"/>
-      <c r="E1062" s="6"/>
-      <c r="F1062" s="7"/>
+      <c r="A1062" s="6">
+        <v>44896</v>
+      </c>
+      <c r="B1062" s="7" t="inlineStr">
+        <is>
+          <t>일본</t>
+        </is>
+      </c>
+      <c r="C1062" s="7" t="inlineStr">
+        <is>
+          <t>두바이유</t>
+        </is>
+      </c>
+      <c r="D1062" s="7">
+        <v>76.8559</v>
+      </c>
+      <c r="E1062" s="6">
+        <v>44966</v>
+      </c>
+      <c r="F1062" s="7" t="inlineStr">
+        <is>
+          <t>월간</t>
+        </is>
+      </c>
     </row>
     <row r="1063" spans="1:6">
-      <c r="A1063" s="6"/>
-      <c r="B1063" s="7"/>
-      <c r="C1063" s="7"/>
-      <c r="D1063" s="7"/>
-      <c r="E1063" s="6"/>
-      <c r="F1063" s="7"/>
+      <c r="A1063" s="6">
+        <v>44927</v>
+      </c>
+      <c r="B1063" s="7" t="inlineStr">
+        <is>
+          <t>일본</t>
+        </is>
+      </c>
+      <c r="C1063" s="7" t="inlineStr">
+        <is>
+          <t>두바이유</t>
+        </is>
+      </c>
+      <c r="D1063" s="7">
+        <v>80.905</v>
+      </c>
+      <c r="E1063" s="6">
+        <v>44966</v>
+      </c>
+      <c r="F1063" s="7" t="inlineStr">
+        <is>
+          <t>월간</t>
+        </is>
+      </c>
     </row>
     <row r="1064" spans="1:6">
-      <c r="A1064" s="6"/>
-      <c r="B1064" s="7"/>
-      <c r="C1064" s="7"/>
-      <c r="D1064" s="7"/>
-      <c r="E1064" s="6"/>
-      <c r="F1064" s="7"/>
+      <c r="A1064" s="6">
+        <v>44958</v>
+      </c>
+      <c r="B1064" s="7" t="inlineStr">
+        <is>
+          <t>일본</t>
+        </is>
+      </c>
+      <c r="C1064" s="7" t="inlineStr">
+        <is>
+          <t>두바이유</t>
+        </is>
+      </c>
+      <c r="D1064" s="7">
+        <v>81.275</v>
+      </c>
+      <c r="E1064" s="6">
+        <v>45006</v>
+      </c>
+      <c r="F1064" s="7" t="inlineStr">
+        <is>
+          <t>월간</t>
+        </is>
+      </c>
     </row>
     <row r="1065" spans="1:6">
-      <c r="A1065" s="6"/>
-      <c r="B1065" s="7"/>
-      <c r="C1065" s="7"/>
-      <c r="D1065" s="7"/>
-      <c r="E1065" s="6"/>
-      <c r="F1065" s="7"/>
+      <c r="A1065" s="6">
+        <v>44986</v>
+      </c>
+      <c r="B1065" s="7" t="inlineStr">
+        <is>
+          <t>일본</t>
+        </is>
+      </c>
+      <c r="C1065" s="7" t="inlineStr">
+        <is>
+          <t>두바이유</t>
+        </is>
+      </c>
+      <c r="D1065" s="7">
+        <v>78.2709</v>
+      </c>
+      <c r="E1065" s="6">
+        <v>45035</v>
+      </c>
+      <c r="F1065" s="7" t="inlineStr">
+        <is>
+          <t>월간</t>
+        </is>
+      </c>
     </row>
     <row r="1066" spans="1:6">
-      <c r="A1066" s="6"/>
-      <c r="B1066" s="7"/>
-      <c r="C1066" s="7"/>
-      <c r="D1066" s="7"/>
-      <c r="E1066" s="6"/>
-      <c r="F1066" s="7"/>
+      <c r="A1066" s="6">
+        <v>45017</v>
+      </c>
+      <c r="B1066" s="7" t="inlineStr">
+        <is>
+          <t>일본</t>
+        </is>
+      </c>
+      <c r="C1066" s="7" t="inlineStr">
+        <is>
+          <t>두바이유</t>
+        </is>
+      </c>
+      <c r="D1066" s="7">
+        <v>83.4085</v>
+      </c>
+      <c r="E1066" s="6">
+        <v>45058</v>
+      </c>
+      <c r="F1066" s="7" t="inlineStr">
+        <is>
+          <t>월간</t>
+        </is>
+      </c>
     </row>
     <row r="1067" spans="1:6">
-      <c r="A1067" s="6"/>
-      <c r="B1067" s="7"/>
-      <c r="C1067" s="7"/>
-      <c r="D1067" s="7"/>
-      <c r="E1067" s="6"/>
-      <c r="F1067" s="7"/>
+      <c r="A1067" s="6">
+        <v>45047</v>
+      </c>
+      <c r="B1067" s="7" t="inlineStr">
+        <is>
+          <t>일본</t>
+        </is>
+      </c>
+      <c r="C1067" s="7" t="inlineStr">
+        <is>
+          <t>두바이유</t>
+        </is>
+      </c>
+      <c r="D1067" s="7">
+        <v>74.7891</v>
+      </c>
+      <c r="E1067" s="6">
+        <v>45089</v>
+      </c>
+      <c r="F1067" s="7" t="inlineStr">
+        <is>
+          <t>월간</t>
+        </is>
+      </c>
     </row>
     <row r="1068" spans="1:6">
-      <c r="A1068" s="6"/>
-      <c r="B1068" s="7"/>
-      <c r="C1068" s="7"/>
-      <c r="D1068" s="7"/>
-      <c r="E1068" s="6"/>
-      <c r="F1068" s="7"/>
+      <c r="A1068" s="6">
+        <v>45078</v>
+      </c>
+      <c r="B1068" s="7" t="inlineStr">
+        <is>
+          <t>일본</t>
+        </is>
+      </c>
+      <c r="C1068" s="7" t="inlineStr">
+        <is>
+          <t>두바이유</t>
+        </is>
+      </c>
+      <c r="D1068" s="7">
+        <v>74.7295</v>
+      </c>
+      <c r="E1068" s="6">
+        <v>45133</v>
+      </c>
+      <c r="F1068" s="7" t="inlineStr">
+        <is>
+          <t>월간</t>
+        </is>
+      </c>
     </row>
     <row r="1069" spans="1:6">
-      <c r="A1069" s="6"/>
-      <c r="B1069" s="7"/>
-      <c r="C1069" s="7"/>
-      <c r="D1069" s="7"/>
-      <c r="E1069" s="6"/>
-      <c r="F1069" s="7"/>
+      <c r="A1069" s="6">
+        <v>45108</v>
+      </c>
+      <c r="B1069" s="7" t="inlineStr">
+        <is>
+          <t>일본</t>
+        </is>
+      </c>
+      <c r="C1069" s="7" t="inlineStr">
+        <is>
+          <t>두바이유</t>
+        </is>
+      </c>
+      <c r="D1069" s="7">
+        <v>80.6457</v>
+      </c>
+      <c r="E1069" s="6">
+        <v>45167</v>
+      </c>
+      <c r="F1069" s="7" t="inlineStr">
+        <is>
+          <t>월간</t>
+        </is>
+      </c>
     </row>
     <row r="1070" spans="1:6">
-      <c r="A1070" s="6"/>
-      <c r="B1070" s="7"/>
-      <c r="C1070" s="7"/>
-      <c r="D1070" s="7"/>
-      <c r="E1070" s="6"/>
-      <c r="F1070" s="7"/>
+      <c r="A1070" s="6">
+        <v>45139</v>
+      </c>
+      <c r="B1070" s="7" t="inlineStr">
+        <is>
+          <t>일본</t>
+        </is>
+      </c>
+      <c r="C1070" s="7" t="inlineStr">
+        <is>
+          <t>두바이유</t>
+        </is>
+      </c>
+      <c r="D1070" s="7">
+        <v>86.123</v>
+      </c>
+      <c r="E1070" s="6">
+        <v>45177</v>
+      </c>
+      <c r="F1070" s="7" t="inlineStr">
+        <is>
+          <t>월간</t>
+        </is>
+      </c>
     </row>
     <row r="1071" spans="1:6">
-      <c r="A1071" s="6"/>
-      <c r="B1071" s="7"/>
-      <c r="C1071" s="7"/>
-      <c r="D1071" s="7"/>
-      <c r="E1071" s="6"/>
-      <c r="F1071" s="7"/>
+      <c r="A1071" s="6">
+        <v>45170</v>
+      </c>
+      <c r="B1071" s="7" t="inlineStr">
+        <is>
+          <t>일본</t>
+        </is>
+      </c>
+      <c r="C1071" s="7" t="inlineStr">
+        <is>
+          <t>두바이유</t>
+        </is>
+      </c>
+      <c r="D1071" s="7">
+        <v>93.2386</v>
+      </c>
+      <c r="E1071" s="6">
+        <v>45215</v>
+      </c>
+      <c r="F1071" s="7" t="inlineStr">
+        <is>
+          <t>월간</t>
+        </is>
+      </c>
     </row>
     <row r="1072" spans="1:6">
-      <c r="A1072" s="6"/>
-      <c r="B1072" s="7"/>
-      <c r="C1072" s="7"/>
-      <c r="D1072" s="7"/>
-      <c r="E1072" s="6"/>
-      <c r="F1072" s="7"/>
+      <c r="A1072" s="6">
+        <v>45200</v>
+      </c>
+      <c r="B1072" s="7" t="inlineStr">
+        <is>
+          <t>일본</t>
+        </is>
+      </c>
+      <c r="C1072" s="7" t="inlineStr">
+        <is>
+          <t>두바이유</t>
+        </is>
+      </c>
+      <c r="D1072" s="7">
+        <v>88.7877</v>
+      </c>
+      <c r="E1072" s="6">
+        <v>45237</v>
+      </c>
+      <c r="F1072" s="7" t="inlineStr">
+        <is>
+          <t>월간</t>
+        </is>
+      </c>
     </row>
     <row r="1073" spans="1:6">
-      <c r="A1073" s="6"/>
-      <c r="B1073" s="7"/>
-      <c r="C1073" s="7"/>
-      <c r="D1073" s="7"/>
-      <c r="E1073" s="6"/>
-      <c r="F1073" s="7"/>
+      <c r="A1073" s="6">
+        <v>45231</v>
+      </c>
+      <c r="B1073" s="7" t="inlineStr">
+        <is>
+          <t>일본</t>
+        </is>
+      </c>
+      <c r="C1073" s="7" t="inlineStr">
+        <is>
+          <t>두바이유</t>
+        </is>
+      </c>
+      <c r="D1073" s="7">
+        <v>82.6409</v>
+      </c>
+      <c r="E1073" s="6">
+        <v>45268</v>
+      </c>
+      <c r="F1073" s="7" t="inlineStr">
+        <is>
+          <t>월간</t>
+        </is>
+      </c>
     </row>
     <row r="1074" spans="1:6">
-      <c r="A1074" s="6"/>
-      <c r="B1074" s="7"/>
-      <c r="C1074" s="7"/>
-      <c r="D1074" s="7"/>
-      <c r="E1074" s="6"/>
-      <c r="F1074" s="7"/>
+      <c r="A1074" s="6">
+        <v>45261</v>
+      </c>
+      <c r="B1074" s="7" t="inlineStr">
+        <is>
+          <t>일본</t>
+        </is>
+      </c>
+      <c r="C1074" s="7" t="inlineStr">
+        <is>
+          <t>두바이유</t>
+        </is>
+      </c>
+      <c r="D1074" s="7">
+        <v>77.5695</v>
+      </c>
+      <c r="E1074" s="6">
+        <v>45315</v>
+      </c>
+      <c r="F1074" s="7" t="inlineStr">
+        <is>
+          <t>월간</t>
+        </is>
+      </c>
     </row>
     <row r="1075" spans="1:6">
-      <c r="A1075" s="6"/>
-      <c r="B1075" s="7"/>
-      <c r="C1075" s="7"/>
-      <c r="D1075" s="7"/>
-      <c r="E1075" s="6"/>
-      <c r="F1075" s="7"/>
+      <c r="A1075" s="6">
+        <v>45292</v>
+      </c>
+      <c r="B1075" s="7" t="inlineStr">
+        <is>
+          <t>일본</t>
+        </is>
+      </c>
+      <c r="C1075" s="7" t="inlineStr">
+        <is>
+          <t>두바이유</t>
+        </is>
+      </c>
+      <c r="D1075" s="7">
+        <v>79.5822</v>
+      </c>
+      <c r="E1075" s="6">
+        <v>45334</v>
+      </c>
+      <c r="F1075" s="7" t="inlineStr">
+        <is>
+          <t>월간</t>
+        </is>
+      </c>
     </row>
     <row r="1076" spans="1:6">
-      <c r="A1076" s="6"/>
-      <c r="B1076" s="7"/>
-      <c r="C1076" s="7"/>
-      <c r="D1076" s="7"/>
-      <c r="E1076" s="6"/>
-      <c r="F1076" s="7"/>
+      <c r="A1076" s="6">
+        <v>45323</v>
+      </c>
+      <c r="B1076" s="7" t="inlineStr">
+        <is>
+          <t>일본</t>
+        </is>
+      </c>
+      <c r="C1076" s="7" t="inlineStr">
+        <is>
+          <t>두바이유</t>
+        </is>
+      </c>
+      <c r="D1076" s="7">
+        <v>82.809</v>
+      </c>
+      <c r="E1076" s="6">
+        <v>45359</v>
+      </c>
+      <c r="F1076" s="7" t="inlineStr">
+        <is>
+          <t>월간</t>
+        </is>
+      </c>
     </row>
     <row r="1077" spans="1:6">
-      <c r="A1077" s="6"/>
-      <c r="B1077" s="7"/>
-      <c r="C1077" s="7"/>
-      <c r="D1077" s="7"/>
-      <c r="E1077" s="6"/>
-      <c r="F1077" s="7"/>
+      <c r="A1077" s="6">
+        <v>45352</v>
+      </c>
+      <c r="B1077" s="7" t="inlineStr">
+        <is>
+          <t>일본</t>
+        </is>
+      </c>
+      <c r="C1077" s="7" t="inlineStr">
+        <is>
+          <t>두바이유</t>
+        </is>
+      </c>
+      <c r="D1077" s="7">
+        <v>86.6338</v>
+      </c>
+      <c r="E1077" s="6">
+        <v>45385</v>
+      </c>
+      <c r="F1077" s="7" t="inlineStr">
+        <is>
+          <t>월간</t>
+        </is>
+      </c>
     </row>
     <row r="1078" spans="1:6">
-      <c r="A1078" s="6"/>
-      <c r="B1078" s="7"/>
-      <c r="C1078" s="7"/>
-      <c r="D1078" s="7"/>
-      <c r="E1078" s="6"/>
-      <c r="F1078" s="7"/>
+      <c r="A1078" s="6">
+        <v>45383</v>
+      </c>
+      <c r="B1078" s="7" t="inlineStr">
+        <is>
+          <t>일본</t>
+        </is>
+      </c>
+      <c r="C1078" s="7" t="inlineStr">
+        <is>
+          <t>두바이유</t>
+        </is>
+      </c>
+      <c r="D1078" s="7">
+        <v>90.8695</v>
+      </c>
+      <c r="E1078" s="6">
+        <v>45418</v>
+      </c>
+      <c r="F1078" s="7" t="inlineStr">
+        <is>
+          <t>월간</t>
+        </is>
+      </c>
     </row>
     <row r="1079" spans="1:6">
-      <c r="A1079" s="6"/>
-      <c r="B1079" s="7"/>
-      <c r="C1079" s="7"/>
-      <c r="D1079" s="7"/>
-      <c r="E1079" s="6"/>
-      <c r="F1079" s="7"/>
+      <c r="A1079" s="6">
+        <v>45413</v>
+      </c>
+      <c r="B1079" s="7" t="inlineStr">
+        <is>
+          <t>일본</t>
+        </is>
+      </c>
+      <c r="C1079" s="7" t="inlineStr">
+        <is>
+          <t>두바이유</t>
+        </is>
+      </c>
+      <c r="D1079" s="7">
+        <v>84.6661</v>
+      </c>
+      <c r="E1079" s="6">
+        <v>45448</v>
+      </c>
+      <c r="F1079" s="7" t="inlineStr">
+        <is>
+          <t>월간</t>
+        </is>
+      </c>
     </row>
     <row r="1080" spans="1:6">
-      <c r="A1080" s="6"/>
-      <c r="B1080" s="7"/>
-      <c r="C1080" s="7"/>
-      <c r="D1080" s="7"/>
-      <c r="E1080" s="6"/>
-      <c r="F1080" s="7"/>
+      <c r="A1080" s="6">
+        <v>45444</v>
+      </c>
+      <c r="B1080" s="7" t="inlineStr">
+        <is>
+          <t>일본</t>
+        </is>
+      </c>
+      <c r="C1080" s="7" t="inlineStr">
+        <is>
+          <t>두바이유</t>
+        </is>
+      </c>
+      <c r="D1080" s="7">
+        <v>84.1125</v>
+      </c>
+      <c r="E1080" s="6">
+        <v>45476</v>
+      </c>
+      <c r="F1080" s="7" t="inlineStr">
+        <is>
+          <t>월간</t>
+        </is>
+      </c>
     </row>
     <row r="1081" spans="1:6">
-      <c r="A1081" s="6"/>
-      <c r="B1081" s="7"/>
-      <c r="C1081" s="7"/>
-      <c r="D1081" s="7"/>
-      <c r="E1081" s="6"/>
-      <c r="F1081" s="7"/>
+      <c r="A1081" s="6">
+        <v>45474</v>
+      </c>
+      <c r="B1081" s="7" t="inlineStr">
+        <is>
+          <t>일본</t>
+        </is>
+      </c>
+      <c r="C1081" s="7" t="inlineStr">
+        <is>
+          <t>두바이유</t>
+        </is>
+      </c>
+      <c r="D1081" s="7">
+        <v>85.2013</v>
+      </c>
+      <c r="E1081" s="6">
+        <v>45526</v>
+      </c>
+      <c r="F1081" s="7" t="inlineStr">
+        <is>
+          <t>월간</t>
+        </is>
+      </c>
     </row>
     <row r="1082" spans="1:6">
-      <c r="A1082" s="6"/>
-      <c r="B1082" s="7"/>
-      <c r="C1082" s="7"/>
-      <c r="D1082" s="7"/>
-      <c r="E1082" s="6"/>
-      <c r="F1082" s="7"/>
+      <c r="A1082" s="6">
+        <v>45505</v>
+      </c>
+      <c r="B1082" s="7" t="inlineStr">
+        <is>
+          <t>일본</t>
+        </is>
+      </c>
+      <c r="C1082" s="7" t="inlineStr">
+        <is>
+          <t>두바이유</t>
+        </is>
+      </c>
+      <c r="D1082" s="7">
+        <v>80.0891</v>
+      </c>
+      <c r="E1082" s="6">
+        <v>45541</v>
+      </c>
+      <c r="F1082" s="7" t="inlineStr">
+        <is>
+          <t>월간</t>
+        </is>
+      </c>
     </row>
     <row r="1083" spans="1:6">
-      <c r="A1083" s="6"/>
-      <c r="B1083" s="7"/>
-      <c r="C1083" s="7"/>
-      <c r="D1083" s="7"/>
-      <c r="E1083" s="6"/>
-      <c r="F1083" s="7"/>
+      <c r="A1083" s="6">
+        <v>45536</v>
+      </c>
+      <c r="B1083" s="7" t="inlineStr">
+        <is>
+          <t>일본</t>
+        </is>
+      </c>
+      <c r="C1083" s="7" t="inlineStr">
+        <is>
+          <t>두바이유</t>
+        </is>
+      </c>
+      <c r="D1083" s="7">
+        <v>73.76</v>
+      </c>
+      <c r="E1083" s="6">
+        <v>45572</v>
+      </c>
+      <c r="F1083" s="7" t="inlineStr">
+        <is>
+          <t>월간</t>
+        </is>
+      </c>
     </row>
     <row r="1084" spans="1:6">
-      <c r="A1084" s="6"/>
-      <c r="B1084" s="7"/>
-      <c r="C1084" s="7"/>
-      <c r="D1084" s="7"/>
-      <c r="E1084" s="6"/>
-      <c r="F1084" s="7"/>
+      <c r="A1084" s="6">
+        <v>45566</v>
+      </c>
+      <c r="B1084" s="7" t="inlineStr">
+        <is>
+          <t>일본</t>
+        </is>
+      </c>
+      <c r="C1084" s="7" t="inlineStr">
+        <is>
+          <t>두바이유</t>
+        </is>
+      </c>
+      <c r="D1084" s="7">
+        <v>76.07</v>
+      </c>
+      <c r="E1084" s="6">
+        <v>45603</v>
+      </c>
+      <c r="F1084" s="7" t="inlineStr">
+        <is>
+          <t>월간</t>
+        </is>
+      </c>
     </row>
     <row r="1085" spans="1:6">
-      <c r="A1085" s="6"/>
-      <c r="B1085" s="7"/>
-      <c r="C1085" s="7"/>
-      <c r="D1085" s="7"/>
-      <c r="E1085" s="6"/>
-      <c r="F1085" s="7"/>
+      <c r="A1085" s="6">
+        <v>45597</v>
+      </c>
+      <c r="B1085" s="7" t="inlineStr">
+        <is>
+          <t>일본</t>
+        </is>
+      </c>
+      <c r="C1085" s="7" t="inlineStr">
+        <is>
+          <t>두바이유</t>
+        </is>
+      </c>
+      <c r="D1085" s="7">
+        <v>74.0929</v>
+      </c>
+      <c r="E1085" s="6">
+        <v>45649</v>
+      </c>
+      <c r="F1085" s="7" t="inlineStr">
+        <is>
+          <t>월간</t>
+        </is>
+      </c>
     </row>
     <row r="1086" spans="1:6">
-      <c r="A1086" s="6"/>
-      <c r="B1086" s="7"/>
-      <c r="C1086" s="7"/>
-      <c r="D1086" s="7"/>
-      <c r="E1086" s="6"/>
-      <c r="F1086" s="7"/>
+      <c r="A1086" s="6">
+        <v>45627</v>
+      </c>
+      <c r="B1086" s="7" t="inlineStr">
+        <is>
+          <t>일본</t>
+        </is>
+      </c>
+      <c r="C1086" s="7" t="inlineStr">
+        <is>
+          <t>두바이유</t>
+        </is>
+      </c>
+      <c r="D1086" s="7">
+        <v>74.0027</v>
+      </c>
+      <c r="E1086" s="6">
+        <v>45684</v>
+      </c>
+      <c r="F1086" s="7" t="inlineStr">
+        <is>
+          <t>월간</t>
+        </is>
+      </c>
     </row>
     <row r="1087" spans="1:6">
-      <c r="A1087" s="6"/>
-      <c r="B1087" s="7"/>
-      <c r="C1087" s="7"/>
-      <c r="D1087" s="7"/>
-      <c r="E1087" s="6"/>
-      <c r="F1087" s="7"/>
+      <c r="A1087" s="6">
+        <v>45658</v>
+      </c>
+      <c r="B1087" s="7" t="inlineStr">
+        <is>
+          <t>일본</t>
+        </is>
+      </c>
+      <c r="C1087" s="7" t="inlineStr">
+        <is>
+          <t>두바이유</t>
+        </is>
+      </c>
+      <c r="D1087" s="7">
+        <v>80.8043</v>
+      </c>
+      <c r="E1087" s="6">
+        <v>45714</v>
+      </c>
+      <c r="F1087" s="7" t="inlineStr">
+        <is>
+          <t>월간</t>
+        </is>
+      </c>
     </row>
     <row r="1088" spans="1:6">
-      <c r="A1088" s="6"/>
-      <c r="B1088" s="7"/>
-      <c r="C1088" s="7"/>
-      <c r="D1088" s="7"/>
-      <c r="E1088" s="6"/>
-      <c r="F1088" s="7"/>
+      <c r="A1088" s="6">
+        <v>45689</v>
+      </c>
+      <c r="B1088" s="7" t="inlineStr">
+        <is>
+          <t>일본</t>
+        </is>
+      </c>
+      <c r="C1088" s="7" t="inlineStr">
+        <is>
+          <t>두바이유</t>
+        </is>
+      </c>
+      <c r="D1088" s="7">
+        <v>76.3215</v>
+      </c>
+      <c r="E1088" s="6">
+        <v>45727</v>
+      </c>
+      <c r="F1088" s="7" t="inlineStr">
+        <is>
+          <t>월간</t>
+        </is>
+      </c>
     </row>
     <row r="1089" spans="1:6">
-      <c r="A1089" s="6"/>
-      <c r="B1089" s="7"/>
-      <c r="C1089" s="7"/>
-      <c r="D1089" s="7"/>
-      <c r="E1089" s="6"/>
-      <c r="F1089" s="7"/>
+      <c r="A1089" s="6">
+        <v>45717</v>
+      </c>
+      <c r="B1089" s="7" t="inlineStr">
+        <is>
+          <t>일본</t>
+        </is>
+      </c>
+      <c r="C1089" s="7" t="inlineStr">
+        <is>
+          <t>두바이유</t>
+        </is>
+      </c>
+      <c r="D1089" s="7">
+        <v>72.9781</v>
+      </c>
+      <c r="E1089" s="6">
+        <v>45751</v>
+      </c>
+      <c r="F1089" s="7" t="inlineStr">
+        <is>
+          <t>월간</t>
+        </is>
+      </c>
     </row>
     <row r="1090" spans="1:6">
-      <c r="A1090" s="6"/>
-      <c r="B1090" s="7"/>
-      <c r="C1090" s="7"/>
-      <c r="D1090" s="7"/>
-      <c r="E1090" s="6"/>
-      <c r="F1090" s="7"/>
+      <c r="A1090" s="6">
+        <v>45748</v>
+      </c>
+      <c r="B1090" s="7" t="inlineStr">
+        <is>
+          <t>일본</t>
+        </is>
+      </c>
+      <c r="C1090" s="7" t="inlineStr">
+        <is>
+          <t>두바이유</t>
+        </is>
+      </c>
+      <c r="D1090" s="7">
+        <v>68.4895</v>
+      </c>
+      <c r="E1090" s="6">
+        <v>45786</v>
+      </c>
+      <c r="F1090" s="7" t="inlineStr">
+        <is>
+          <t>월간</t>
+        </is>
+      </c>
     </row>
     <row r="1091" spans="1:6">
-      <c r="A1091" s="6"/>
-      <c r="B1091" s="7"/>
-      <c r="C1091" s="7"/>
-      <c r="D1091" s="7"/>
-      <c r="E1091" s="6"/>
-      <c r="F1091" s="7"/>
+      <c r="A1091" s="6">
+        <v>45778</v>
+      </c>
+      <c r="B1091" s="7" t="inlineStr">
+        <is>
+          <t>일본</t>
+        </is>
+      </c>
+      <c r="C1091" s="7" t="inlineStr">
+        <is>
+          <t>두바이유</t>
+        </is>
+      </c>
+      <c r="D1091" s="7">
+        <v>63.6073</v>
+      </c>
+      <c r="E1091" s="6">
+        <v>45834</v>
+      </c>
+      <c r="F1091" s="7" t="inlineStr">
+        <is>
+          <t>월간</t>
+        </is>
+      </c>
     </row>
     <row r="1092" spans="1:6">
-      <c r="A1092" s="6"/>
-      <c r="B1092" s="7"/>
-      <c r="C1092" s="7"/>
-      <c r="D1092" s="7"/>
-      <c r="E1092" s="6"/>
-      <c r="F1092" s="7"/>
+      <c r="A1092" s="6">
+        <v>45809</v>
+      </c>
+      <c r="B1092" s="7" t="inlineStr">
+        <is>
+          <t>일본</t>
+        </is>
+      </c>
+      <c r="C1092" s="7" t="inlineStr">
+        <is>
+          <t>두바이유</t>
+        </is>
+      </c>
+      <c r="D1092" s="7">
+        <v>69.3629</v>
+      </c>
+      <c r="E1092" s="6">
+        <v>45852</v>
+      </c>
+      <c r="F1092" s="7" t="inlineStr">
+        <is>
+          <t>월간</t>
+        </is>
+      </c>
     </row>
     <row r="1093" spans="1:6">
-      <c r="A1093" s="6"/>
-      <c r="B1093" s="7"/>
-      <c r="C1093" s="7"/>
-      <c r="D1093" s="7"/>
-      <c r="E1093" s="6"/>
-      <c r="F1093" s="7"/>
+      <c r="A1093" s="6">
+        <v>45839</v>
+      </c>
+      <c r="B1093" s="7" t="inlineStr">
+        <is>
+          <t>일본</t>
+        </is>
+      </c>
+      <c r="C1093" s="7" t="inlineStr">
+        <is>
+          <t>두바이유</t>
+        </is>
+      </c>
+      <c r="D1093" s="7">
+        <v>71.043</v>
+      </c>
+      <c r="E1093" s="6">
+        <v>46044</v>
+      </c>
+      <c r="F1093" s="7" t="inlineStr">
+        <is>
+          <t>월간</t>
+        </is>
+      </c>
     </row>
     <row r="1094" spans="1:6">
-      <c r="A1094" s="6"/>
-      <c r="B1094" s="7"/>
-      <c r="C1094" s="7"/>
-      <c r="D1094" s="7"/>
-      <c r="E1094" s="6"/>
-      <c r="F1094" s="7"/>
+      <c r="A1094" s="6">
+        <v>45870</v>
+      </c>
+      <c r="B1094" s="7" t="inlineStr">
+        <is>
+          <t>일본</t>
+        </is>
+      </c>
+      <c r="C1094" s="7" t="inlineStr">
+        <is>
+          <t>두바이유</t>
+        </is>
+      </c>
+      <c r="D1094" s="7">
+        <v>69.3881</v>
+      </c>
+      <c r="E1094" s="6">
+        <v>46044</v>
+      </c>
+      <c r="F1094" s="7" t="inlineStr">
+        <is>
+          <t>월간</t>
+        </is>
+      </c>
     </row>
     <row r="1095" spans="1:6">
-      <c r="A1095" s="6"/>
-      <c r="B1095" s="7"/>
-      <c r="C1095" s="7"/>
-      <c r="D1095" s="7"/>
-      <c r="E1095" s="6"/>
-      <c r="F1095" s="7"/>
+      <c r="A1095" s="6">
+        <v>45901</v>
+      </c>
+      <c r="B1095" s="7" t="inlineStr">
+        <is>
+          <t>일본</t>
+        </is>
+      </c>
+      <c r="C1095" s="7" t="inlineStr">
+        <is>
+          <t>두바이유</t>
+        </is>
+      </c>
+      <c r="D1095" s="7">
+        <v>69.9191</v>
+      </c>
+      <c r="E1095" s="6">
+        <v>46044</v>
+      </c>
+      <c r="F1095" s="7" t="inlineStr">
+        <is>
+          <t>월간</t>
+        </is>
+      </c>
     </row>
     <row r="1096" spans="1:6">
-      <c r="A1096" s="6"/>
-      <c r="B1096" s="7"/>
-      <c r="C1096" s="7"/>
-      <c r="D1096" s="7"/>
-      <c r="E1096" s="6"/>
-      <c r="F1096" s="7"/>
+      <c r="A1096" s="6">
+        <v>45931</v>
+      </c>
+      <c r="B1096" s="7" t="inlineStr">
+        <is>
+          <t>일본</t>
+        </is>
+      </c>
+      <c r="C1096" s="7" t="inlineStr">
+        <is>
+          <t>두바이유</t>
+        </is>
+      </c>
+      <c r="D1096" s="7">
+        <v>64.5987</v>
+      </c>
+      <c r="E1096" s="6">
+        <v>46044</v>
+      </c>
+      <c r="F1096" s="7" t="inlineStr">
+        <is>
+          <t>월간</t>
+        </is>
+      </c>
     </row>
     <row r="1097" spans="1:6">
-      <c r="A1097" s="6"/>
-      <c r="B1097" s="7"/>
-      <c r="C1097" s="7"/>
-      <c r="D1097" s="7"/>
-      <c r="E1097" s="6"/>
-      <c r="F1097" s="7"/>
+      <c r="A1097" s="6">
+        <v>45962</v>
+      </c>
+      <c r="B1097" s="7" t="inlineStr">
+        <is>
+          <t>일본</t>
+        </is>
+      </c>
+      <c r="C1097" s="7" t="inlineStr">
+        <is>
+          <t>두바이유</t>
+        </is>
+      </c>
+      <c r="D1097" s="7">
+        <v>64.3555</v>
+      </c>
+      <c r="E1097" s="6">
+        <v>46044</v>
+      </c>
+      <c r="F1097" s="7" t="inlineStr">
+        <is>
+          <t>월간</t>
+        </is>
+      </c>
     </row>
     <row r="1098" spans="1:6">
-      <c r="A1098" s="6"/>
-      <c r="B1098" s="7"/>
-      <c r="C1098" s="7"/>
-      <c r="D1098" s="7"/>
-      <c r="E1098" s="6"/>
-      <c r="F1098" s="7"/>
+      <c r="A1098" s="6">
+        <v>45992</v>
+      </c>
+      <c r="B1098" s="7" t="inlineStr">
+        <is>
+          <t>일본</t>
+        </is>
+      </c>
+      <c r="C1098" s="7" t="inlineStr">
+        <is>
+          <t>두바이유</t>
+        </is>
+      </c>
+      <c r="D1098" s="7">
+        <v>61.83</v>
+      </c>
+      <c r="E1098" s="6">
+        <v>46044</v>
+      </c>
+      <c r="F1098" s="7" t="inlineStr">
+        <is>
+          <t>월간</t>
+        </is>
+      </c>
     </row>
     <row r="1099" spans="1:6">
-      <c r="A1099" s="6"/>
-      <c r="B1099" s="7"/>
-      <c r="C1099" s="7"/>
-      <c r="D1099" s="7"/>
-      <c r="E1099" s="6"/>
-      <c r="F1099" s="7"/>
+      <c r="A1099" s="6">
+        <v>46023</v>
+      </c>
+      <c r="B1099" s="7" t="inlineStr">
+        <is>
+          <t>일본</t>
+        </is>
+      </c>
+      <c r="C1099" s="7" t="inlineStr">
+        <is>
+          <t>두바이유</t>
+        </is>
+      </c>
+      <c r="D1099" s="7">
+        <v>62.7282</v>
+      </c>
+      <c r="E1099" s="6">
+        <v>46065</v>
+      </c>
+      <c r="F1099" s="7" t="inlineStr">
+        <is>
+          <t>월간</t>
+        </is>
+      </c>
     </row>
     <row r="1100" spans="1:6">
-      <c r="A1100" s="6"/>
-      <c r="B1100" s="7"/>
-      <c r="C1100" s="7"/>
-      <c r="D1100" s="7"/>
-      <c r="E1100" s="6"/>
-      <c r="F1100" s="7"/>
+      <c r="A1100" s="6">
+        <v>46054</v>
+      </c>
+      <c r="B1100" s="7" t="inlineStr">
+        <is>
+          <t>일본</t>
+        </is>
+      </c>
+      <c r="C1100" s="7" t="inlineStr">
+        <is>
+          <t>두바이유</t>
+        </is>
+      </c>
+      <c r="D1100" s="7">
+        <v>68.5085</v>
+      </c>
+      <c r="E1100" s="6">
+        <v>46105</v>
+      </c>
+      <c r="F1100" s="7" t="inlineStr">
+        <is>
+          <t>월간</t>
+        </is>
+      </c>
     </row>
     <row r="1101" spans="1:6">
-      <c r="A1101" s="6"/>
-      <c r="B1101" s="7"/>
-      <c r="C1101" s="7"/>
-      <c r="D1101" s="7"/>
-      <c r="E1101" s="6"/>
-      <c r="F1101" s="7"/>
+      <c r="A1101" s="6">
+        <v>46082</v>
+      </c>
+      <c r="B1101" s="7" t="inlineStr">
+        <is>
+          <t>일본</t>
+        </is>
+      </c>
+      <c r="C1101" s="7" t="inlineStr">
+        <is>
+          <t>두바이유</t>
+        </is>
+      </c>
+      <c r="D1101" s="7">
+        <v>126.7064</v>
+      </c>
+      <c r="E1101" s="6">
+        <v>46127</v>
+      </c>
+      <c r="F1101" s="7" t="inlineStr">
+        <is>
+          <t>월간</t>
+        </is>
+      </c>
     </row>
     <row r="1102" spans="1:6">
-      <c r="A1102" s="6"/>
-      <c r="B1102" s="7"/>
-      <c r="C1102" s="7"/>
-      <c r="D1102" s="7"/>
-      <c r="E1102" s="6"/>
-      <c r="F1102" s="7"/>
+      <c r="A1102" s="6">
+        <v>46113</v>
+      </c>
+      <c r="B1102" s="7" t="inlineStr">
+        <is>
+          <t>일본</t>
+        </is>
+      </c>
+      <c r="C1102" s="7" t="inlineStr">
+        <is>
+          <t>두바이유</t>
+        </is>
+      </c>
+      <c r="D1102" s="7">
+        <v>105.2991</v>
+      </c>
+      <c r="E1102" s="6">
+        <v>46178</v>
+      </c>
+      <c r="F1102" s="7" t="inlineStr">
+        <is>
+          <t>월간</t>
+        </is>
+      </c>
     </row>
     <row r="1103" spans="1:6">
-      <c r="A1103" s="6"/>
-      <c r="B1103" s="7"/>
-      <c r="C1103" s="7"/>
-      <c r="D1103" s="7"/>
-      <c r="E1103" s="6"/>
-      <c r="F1103" s="7"/>
+      <c r="A1103" s="6">
+        <v>46143</v>
+      </c>
+      <c r="B1103" s="7" t="inlineStr">
+        <is>
+          <t>일본</t>
+        </is>
+      </c>
+      <c r="C1103" s="7" t="inlineStr">
+        <is>
+          <t>두바이유</t>
+        </is>
+      </c>
+      <c r="D1103" s="7">
+        <v>100.3643</v>
+      </c>
+      <c r="E1103" s="6">
+        <v>46178</v>
+      </c>
+      <c r="F1103" s="7" t="inlineStr">
+        <is>
+          <t>월간</t>
+        </is>
+      </c>
     </row>
     <row r="1104" spans="1:6">
-      <c r="A1104" s="6"/>
-      <c r="B1104" s="7"/>
-      <c r="C1104" s="7"/>
-      <c r="D1104" s="7"/>
-      <c r="E1104" s="6"/>
-      <c r="F1104" s="7"/>
+      <c r="A1104" s="6">
+        <v>46174</v>
+      </c>
+      <c r="B1104" s="7" t="inlineStr">
+        <is>
+          <t>일본</t>
+        </is>
+      </c>
+      <c r="C1104" s="7" t="inlineStr">
+        <is>
+          <t>두바이유</t>
+        </is>
+      </c>
+      <c r="D1104" s="7">
+        <v>79.5395</v>
+      </c>
+      <c r="E1104" s="6">
+        <v>46216</v>
+      </c>
+      <c r="F1104" s="7" t="inlineStr">
+        <is>
+          <t>월간</t>
+        </is>
+      </c>
     </row>
     <row r="1105" spans="1:6">
-      <c r="A1105" s="6"/>
-      <c r="B1105" s="7"/>
-      <c r="C1105" s="7"/>
-      <c r="D1105" s="7"/>
-      <c r="E1105" s="6"/>
-      <c r="F1105" s="7"/>
+      <c r="A1105" s="6">
+        <v>46204</v>
+      </c>
+      <c r="B1105" s="7" t="inlineStr">
+        <is>
+          <t>일본</t>
+        </is>
+      </c>
+      <c r="C1105" s="7" t="inlineStr">
+        <is>
+          <t>두바이유</t>
+        </is>
+      </c>
+      <c r="D1105" s="7">
+        <v>77.1318</v>
+      </c>
+      <c r="E1105" s="6">
+        <v>46251</v>
+      </c>
+      <c r="F1105" s="7" t="inlineStr">
+        <is>
+          <t>월간</t>
+        </is>
+      </c>
     </row>
     <row r="1106" spans="1:6">
-      <c r="A1106" s="6"/>
-      <c r="B1106" s="7"/>
-      <c r="C1106" s="7"/>
-      <c r="D1106" s="7"/>
-      <c r="E1106" s="6"/>
-      <c r="F1106" s="7"/>
+      <c r="A1106" s="6">
+        <v>44440</v>
+      </c>
+      <c r="B1106" s="7" t="inlineStr">
+        <is>
+          <t>일본</t>
+        </is>
+      </c>
+      <c r="C1106" s="7" t="inlineStr">
+        <is>
+          <t>정책금리</t>
+        </is>
+      </c>
+      <c r="D1106" s="7">
+        <v>-0.1</v>
+      </c>
+      <c r="E1106" s="6">
+        <v>44440</v>
+      </c>
+      <c r="F1106" s="7" t="inlineStr">
+        <is>
+          <t>수시</t>
+        </is>
+      </c>
     </row>
     <row r="1107" spans="1:6">
-      <c r="A1107" s="6"/>
-      <c r="B1107" s="7"/>
-      <c r="C1107" s="7"/>
-      <c r="D1107" s="7"/>
-      <c r="E1107" s="6"/>
-      <c r="F1107" s="7"/>
+      <c r="A1107" s="6">
+        <v>45370</v>
+      </c>
+      <c r="B1107" s="7" t="inlineStr">
+        <is>
+          <t>일본</t>
+        </is>
+      </c>
+      <c r="C1107" s="7" t="inlineStr">
+        <is>
+          <t>정책금리</t>
+        </is>
+      </c>
+      <c r="D1107" s="7">
+        <v>0.1</v>
+      </c>
+      <c r="E1107" s="6">
+        <v>45370</v>
+      </c>
+      <c r="F1107" s="7" t="inlineStr">
+        <is>
+          <t>수시</t>
+        </is>
+      </c>
     </row>
     <row r="1108" spans="1:6">
-      <c r="A1108" s="6"/>
-      <c r="B1108" s="7"/>
-      <c r="C1108" s="7"/>
-      <c r="D1108" s="7"/>
-      <c r="E1108" s="6"/>
-      <c r="F1108" s="7"/>
+      <c r="A1108" s="6">
+        <v>45504</v>
+      </c>
+      <c r="B1108" s="7" t="inlineStr">
+        <is>
+          <t>일본</t>
+        </is>
+      </c>
+      <c r="C1108" s="7" t="inlineStr">
+        <is>
+          <t>정책금리</t>
+        </is>
+      </c>
+      <c r="D1108" s="7">
+        <v>0.25</v>
+      </c>
+      <c r="E1108" s="6">
+        <v>45504</v>
+      </c>
+      <c r="F1108" s="7" t="inlineStr">
+        <is>
+          <t>수시</t>
+        </is>
+      </c>
     </row>
     <row r="1109" spans="1:6">
-      <c r="A1109" s="6"/>
-      <c r="B1109" s="7"/>
-      <c r="C1109" s="7"/>
-      <c r="D1109" s="7"/>
-      <c r="E1109" s="6"/>
-      <c r="F1109" s="7"/>
+      <c r="A1109" s="6">
+        <v>45681</v>
+      </c>
+      <c r="B1109" s="7" t="inlineStr">
+        <is>
+          <t>일본</t>
+        </is>
+      </c>
+      <c r="C1109" s="7" t="inlineStr">
+        <is>
+          <t>정책금리</t>
+        </is>
+      </c>
+      <c r="D1109" s="7">
+        <v>0.5</v>
+      </c>
+      <c r="E1109" s="6">
+        <v>45681</v>
+      </c>
+      <c r="F1109" s="7" t="inlineStr">
+        <is>
+          <t>수시</t>
+        </is>
+      </c>
     </row>
     <row r="1110" spans="1:6">
-      <c r="A1110" s="6"/>
-      <c r="B1110" s="7"/>
-      <c r="C1110" s="7"/>
-      <c r="D1110" s="7"/>
-      <c r="E1110" s="6"/>
-      <c r="F1110" s="7"/>
+      <c r="A1110" s="6">
+        <v>46010</v>
+      </c>
+      <c r="B1110" s="7" t="inlineStr">
+        <is>
+          <t>일본</t>
+        </is>
+      </c>
+      <c r="C1110" s="7" t="inlineStr">
+        <is>
+          <t>정책금리</t>
+        </is>
+      </c>
+      <c r="D1110" s="7">
+        <v>0.75</v>
+      </c>
+      <c r="E1110" s="6">
+        <v>46010</v>
+      </c>
+      <c r="F1110" s="7" t="inlineStr">
+        <is>
+          <t>수시</t>
+        </is>
+      </c>
     </row>
     <row r="1111" spans="1:6">
-      <c r="A1111" s="6"/>
-      <c r="B1111" s="7"/>
-      <c r="C1111" s="7"/>
-      <c r="D1111" s="7"/>
-      <c r="E1111" s="6"/>
-      <c r="F1111" s="7"/>
+      <c r="A1111" s="6">
+        <v>46189</v>
+      </c>
+      <c r="B1111" s="7" t="inlineStr">
+        <is>
+          <t>일본</t>
+        </is>
+      </c>
+      <c r="C1111" s="7" t="inlineStr">
+        <is>
+          <t>정책금리</t>
+        </is>
+      </c>
+      <c r="D1111" s="7">
+        <v>1.0</v>
+      </c>
+      <c r="E1111" s="6">
+        <v>46189</v>
+      </c>
+      <c r="F1111" s="7" t="inlineStr">
+        <is>
+          <t>수시</t>
+        </is>
+      </c>
     </row>
     <row r="1112" spans="1:6">
-      <c r="A1112" s="6"/>
-      <c r="B1112" s="7"/>
-      <c r="C1112" s="7"/>
-      <c r="D1112" s="7"/>
-      <c r="E1112" s="6"/>
-      <c r="F1112" s="7"/>
+      <c r="A1112" s="6">
+        <v>44440</v>
+      </c>
+      <c r="B1112" s="7" t="inlineStr">
+        <is>
+          <t>일본</t>
+        </is>
+      </c>
+      <c r="C1112" s="7" t="inlineStr">
+        <is>
+          <t>국채10년</t>
+        </is>
+      </c>
+      <c r="D1112" s="7">
+        <v>0.065</v>
+      </c>
+      <c r="E1112" s="6">
+        <v>44482</v>
+      </c>
+      <c r="F1112" s="7" t="inlineStr">
+        <is>
+          <t>월간</t>
+        </is>
+      </c>
     </row>
     <row r="1113" spans="1:6">
-      <c r="A1113" s="6"/>
-      <c r="B1113" s="7"/>
-      <c r="C1113" s="7"/>
-      <c r="D1113" s="7"/>
-      <c r="E1113" s="6"/>
-      <c r="F1113" s="7"/>
+      <c r="A1113" s="6">
+        <v>44470</v>
+      </c>
+      <c r="B1113" s="7" t="inlineStr">
+        <is>
+          <t>일본</t>
+        </is>
+      </c>
+      <c r="C1113" s="7" t="inlineStr">
+        <is>
+          <t>국채10년</t>
+        </is>
+      </c>
+      <c r="D1113" s="7">
+        <v>0.095</v>
+      </c>
+      <c r="E1113" s="6">
+        <v>44511</v>
+      </c>
+      <c r="F1113" s="7" t="inlineStr">
+        <is>
+          <t>월간</t>
+        </is>
+      </c>
     </row>
     <row r="1114" spans="1:6">
-      <c r="A1114" s="6"/>
-      <c r="B1114" s="7"/>
-      <c r="C1114" s="7"/>
-      <c r="D1114" s="7"/>
-      <c r="E1114" s="6"/>
-      <c r="F1114" s="7"/>
+      <c r="A1114" s="6">
+        <v>44501</v>
+      </c>
+      <c r="B1114" s="7" t="inlineStr">
+        <is>
+          <t>일본</t>
+        </is>
+      </c>
+      <c r="C1114" s="7" t="inlineStr">
+        <is>
+          <t>국채10년</t>
+        </is>
+      </c>
+      <c r="D1114" s="7">
+        <v>0.05</v>
+      </c>
+      <c r="E1114" s="6">
+        <v>44540</v>
+      </c>
+      <c r="F1114" s="7" t="inlineStr">
+        <is>
+          <t>월간</t>
+        </is>
+      </c>
     </row>
     <row r="1115" spans="1:6">
-      <c r="A1115" s="6"/>
-      <c r="B1115" s="7"/>
-      <c r="C1115" s="7"/>
-      <c r="D1115" s="7"/>
-      <c r="E1115" s="6"/>
-      <c r="F1115" s="7"/>
+      <c r="A1115" s="6">
+        <v>44531</v>
+      </c>
+      <c r="B1115" s="7" t="inlineStr">
+        <is>
+          <t>일본</t>
+        </is>
+      </c>
+      <c r="C1115" s="7" t="inlineStr">
+        <is>
+          <t>국채10년</t>
+        </is>
+      </c>
+      <c r="D1115" s="7">
+        <v>0.07</v>
+      </c>
+      <c r="E1115" s="6">
+        <v>44579</v>
+      </c>
+      <c r="F1115" s="7" t="inlineStr">
+        <is>
+          <t>월간</t>
+        </is>
+      </c>
     </row>
     <row r="1116" spans="1:6">
-      <c r="A1116" s="6"/>
-      <c r="B1116" s="7"/>
-      <c r="C1116" s="7"/>
-      <c r="D1116" s="7"/>
-      <c r="E1116" s="6"/>
-      <c r="F1116" s="7"/>
+      <c r="A1116" s="6">
+        <v>44562</v>
+      </c>
+      <c r="B1116" s="7" t="inlineStr">
+        <is>
+          <t>일본</t>
+        </is>
+      </c>
+      <c r="C1116" s="7" t="inlineStr">
+        <is>
+          <t>국채10년</t>
+        </is>
+      </c>
+      <c r="D1116" s="7">
+        <v>0.17</v>
+      </c>
+      <c r="E1116" s="6">
+        <v>44603</v>
+      </c>
+      <c r="F1116" s="7" t="inlineStr">
+        <is>
+          <t>월간</t>
+        </is>
+      </c>
     </row>
     <row r="1117" spans="1:6">
-      <c r="A1117" s="6"/>
-      <c r="B1117" s="7"/>
-      <c r="C1117" s="7"/>
-      <c r="D1117" s="7"/>
-      <c r="E1117" s="6"/>
-      <c r="F1117" s="7"/>
+      <c r="A1117" s="6">
+        <v>44593</v>
+      </c>
+      <c r="B1117" s="7" t="inlineStr">
+        <is>
+          <t>일본</t>
+        </is>
+      </c>
+      <c r="C1117" s="7" t="inlineStr">
+        <is>
+          <t>국채10년</t>
+        </is>
+      </c>
+      <c r="D1117" s="7">
+        <v>0.18</v>
+      </c>
+      <c r="E1117" s="6">
+        <v>44630</v>
+      </c>
+      <c r="F1117" s="7" t="inlineStr">
+        <is>
+          <t>월간</t>
+        </is>
+      </c>
     </row>
     <row r="1118" spans="1:6">
-      <c r="A1118" s="6"/>
-      <c r="B1118" s="7"/>
-      <c r="C1118" s="7"/>
-      <c r="D1118" s="7"/>
-      <c r="E1118" s="6"/>
-      <c r="F1118" s="7"/>
+      <c r="A1118" s="6">
+        <v>44621</v>
+      </c>
+      <c r="B1118" s="7" t="inlineStr">
+        <is>
+          <t>일본</t>
+        </is>
+      </c>
+      <c r="C1118" s="7" t="inlineStr">
+        <is>
+          <t>국채10년</t>
+        </is>
+      </c>
+      <c r="D1118" s="7">
+        <v>0.21</v>
+      </c>
+      <c r="E1118" s="6">
+        <v>44665</v>
+      </c>
+      <c r="F1118" s="7" t="inlineStr">
+        <is>
+          <t>월간</t>
+        </is>
+      </c>
     </row>
     <row r="1119" spans="1:6">
-      <c r="A1119" s="6"/>
-      <c r="B1119" s="7"/>
-      <c r="C1119" s="7"/>
-      <c r="D1119" s="7"/>
-      <c r="E1119" s="6"/>
-      <c r="F1119" s="7"/>
+      <c r="A1119" s="6">
+        <v>44652</v>
+      </c>
+      <c r="B1119" s="7" t="inlineStr">
+        <is>
+          <t>일본</t>
+        </is>
+      </c>
+      <c r="C1119" s="7" t="inlineStr">
+        <is>
+          <t>국채10년</t>
+        </is>
+      </c>
+      <c r="D1119" s="7">
+        <v>0.215</v>
+      </c>
+      <c r="E1119" s="6">
+        <v>44692</v>
+      </c>
+      <c r="F1119" s="7" t="inlineStr">
+        <is>
+          <t>월간</t>
+        </is>
+      </c>
     </row>
     <row r="1120" spans="1:6">
-      <c r="A1120" s="6"/>
-      <c r="B1120" s="7"/>
-      <c r="C1120" s="7"/>
-      <c r="D1120" s="7"/>
-      <c r="E1120" s="6"/>
-      <c r="F1120" s="7"/>
+      <c r="A1120" s="6">
+        <v>44682</v>
+      </c>
+      <c r="B1120" s="7" t="inlineStr">
+        <is>
+          <t>일본</t>
+        </is>
+      </c>
+      <c r="C1120" s="7" t="inlineStr">
+        <is>
+          <t>국채10년</t>
+        </is>
+      </c>
+      <c r="D1120" s="7">
+        <v>0.235</v>
+      </c>
+      <c r="E1120" s="6">
+        <v>44726</v>
+      </c>
+      <c r="F1120" s="7" t="inlineStr">
+        <is>
+          <t>월간</t>
+        </is>
+      </c>
     </row>
     <row r="1121" spans="1:6">
-      <c r="A1121" s="6"/>
-      <c r="B1121" s="7"/>
-      <c r="C1121" s="7"/>
-      <c r="D1121" s="7"/>
-      <c r="E1121" s="6"/>
-      <c r="F1121" s="7"/>
+      <c r="A1121" s="6">
+        <v>44713</v>
+      </c>
+      <c r="B1121" s="7" t="inlineStr">
+        <is>
+          <t>일본</t>
+        </is>
+      </c>
+      <c r="C1121" s="7" t="inlineStr">
+        <is>
+          <t>국채10년</t>
+        </is>
+      </c>
+      <c r="D1121" s="7">
+        <v>0.225</v>
+      </c>
+      <c r="E1121" s="6">
+        <v>44755</v>
+      </c>
+      <c r="F1121" s="7" t="inlineStr">
+        <is>
+          <t>월간</t>
+        </is>
+      </c>
     </row>
     <row r="1122" spans="1:6">
-      <c r="A1122" s="6"/>
-      <c r="B1122" s="7"/>
-      <c r="C1122" s="7"/>
-      <c r="D1122" s="7"/>
-      <c r="E1122" s="6"/>
-      <c r="F1122" s="7"/>
+      <c r="A1122" s="6">
+        <v>44743</v>
+      </c>
+      <c r="B1122" s="7" t="inlineStr">
+        <is>
+          <t>일본</t>
+        </is>
+      </c>
+      <c r="C1122" s="7" t="inlineStr">
+        <is>
+          <t>국채10년</t>
+        </is>
+      </c>
+      <c r="D1122" s="7">
+        <v>0.18</v>
+      </c>
+      <c r="E1122" s="6">
+        <v>44783</v>
+      </c>
+      <c r="F1122" s="7" t="inlineStr">
+        <is>
+          <t>월간</t>
+        </is>
+      </c>
     </row>
     <row r="1123" spans="1:6">
-      <c r="A1123" s="6"/>
-      <c r="B1123" s="7"/>
-      <c r="C1123" s="7"/>
-      <c r="D1123" s="7"/>
-      <c r="E1123" s="6"/>
-      <c r="F1123" s="7"/>
+      <c r="A1123" s="6">
+        <v>44774</v>
+      </c>
+      <c r="B1123" s="7" t="inlineStr">
+        <is>
+          <t>일본</t>
+        </is>
+      </c>
+      <c r="C1123" s="7" t="inlineStr">
+        <is>
+          <t>국채10년</t>
+        </is>
+      </c>
+      <c r="D1123" s="7">
+        <v>0.22</v>
+      </c>
+      <c r="E1123" s="6">
+        <v>44818</v>
+      </c>
+      <c r="F1123" s="7" t="inlineStr">
+        <is>
+          <t>월간</t>
+        </is>
+      </c>
     </row>
     <row r="1124" spans="1:6">
-      <c r="A1124" s="6"/>
-      <c r="B1124" s="7"/>
-      <c r="C1124" s="7"/>
-      <c r="D1124" s="7"/>
-      <c r="E1124" s="6"/>
-      <c r="F1124" s="7"/>
+      <c r="A1124" s="6">
+        <v>44805</v>
+      </c>
+      <c r="B1124" s="7" t="inlineStr">
+        <is>
+          <t>일본</t>
+        </is>
+      </c>
+      <c r="C1124" s="7" t="inlineStr">
+        <is>
+          <t>국채10년</t>
+        </is>
+      </c>
+      <c r="D1124" s="7">
+        <v>0.24</v>
+      </c>
+      <c r="E1124" s="6">
+        <v>44876</v>
+      </c>
+      <c r="F1124" s="7" t="inlineStr">
+        <is>
+          <t>월간</t>
+        </is>
+      </c>
     </row>
     <row r="1125" spans="1:6">
-      <c r="A1125" s="6"/>
-      <c r="B1125" s="7"/>
-      <c r="C1125" s="7"/>
-      <c r="D1125" s="7"/>
-      <c r="E1125" s="6"/>
-      <c r="F1125" s="7"/>
+      <c r="A1125" s="6">
+        <v>44835</v>
+      </c>
+      <c r="B1125" s="7" t="inlineStr">
+        <is>
+          <t>일본</t>
+        </is>
+      </c>
+      <c r="C1125" s="7" t="inlineStr">
+        <is>
+          <t>국채10년</t>
+        </is>
+      </c>
+      <c r="D1125" s="7">
+        <v>0.245</v>
+      </c>
+      <c r="E1125" s="6">
+        <v>44876</v>
+      </c>
+      <c r="F1125" s="7" t="inlineStr">
+        <is>
+          <t>월간</t>
+        </is>
+      </c>
     </row>
     <row r="1126" spans="1:6">
-      <c r="A1126" s="6"/>
-      <c r="B1126" s="7"/>
-      <c r="C1126" s="7"/>
-      <c r="D1126" s="7"/>
-      <c r="E1126" s="6"/>
-      <c r="F1126" s="7"/>
+      <c r="A1126" s="6">
+        <v>44866</v>
+      </c>
+      <c r="B1126" s="7" t="inlineStr">
+        <is>
+          <t>일본</t>
+        </is>
+      </c>
+      <c r="C1126" s="7" t="inlineStr">
+        <is>
+          <t>국채10년</t>
+        </is>
+      </c>
+      <c r="D1126" s="7">
+        <v>0.25</v>
+      </c>
+      <c r="E1126" s="6">
+        <v>44905</v>
+      </c>
+      <c r="F1126" s="7" t="inlineStr">
+        <is>
+          <t>월간</t>
+        </is>
+      </c>
     </row>
     <row r="1127" spans="1:6">
-      <c r="A1127" s="6"/>
-      <c r="B1127" s="7"/>
-      <c r="C1127" s="7"/>
-      <c r="D1127" s="7"/>
-      <c r="E1127" s="6"/>
-      <c r="F1127" s="7"/>
+      <c r="A1127" s="6">
+        <v>44896</v>
+      </c>
+      <c r="B1127" s="7" t="inlineStr">
+        <is>
+          <t>일본</t>
+        </is>
+      </c>
+      <c r="C1127" s="7" t="inlineStr">
+        <is>
+          <t>국채10년</t>
+        </is>
+      </c>
+      <c r="D1127" s="7">
+        <v>0.41</v>
+      </c>
+      <c r="E1127" s="6">
+        <v>44937</v>
+      </c>
+      <c r="F1127" s="7" t="inlineStr">
+        <is>
+          <t>월간</t>
+        </is>
+      </c>
     </row>
     <row r="1128" spans="1:6">
-      <c r="A1128" s="6"/>
-      <c r="B1128" s="7"/>
-      <c r="C1128" s="7"/>
-      <c r="D1128" s="7"/>
-      <c r="E1128" s="6"/>
-      <c r="F1128" s="7"/>
+      <c r="A1128" s="6">
+        <v>44927</v>
+      </c>
+      <c r="B1128" s="7" t="inlineStr">
+        <is>
+          <t>일본</t>
+        </is>
+      </c>
+      <c r="C1128" s="7" t="inlineStr">
+        <is>
+          <t>국채10년</t>
+        </is>
+      </c>
+      <c r="D1128" s="7">
+        <v>0.49</v>
+      </c>
+      <c r="E1128" s="6">
+        <v>44970</v>
+      </c>
+      <c r="F1128" s="7" t="inlineStr">
+        <is>
+          <t>월간</t>
+        </is>
+      </c>
     </row>
     <row r="1129" spans="1:6">
-      <c r="A1129" s="6"/>
-      <c r="B1129" s="7"/>
-      <c r="C1129" s="7"/>
-      <c r="D1129" s="7"/>
-      <c r="E1129" s="6"/>
-      <c r="F1129" s="7"/>
+      <c r="A1129" s="6">
+        <v>44958</v>
+      </c>
+      <c r="B1129" s="7" t="inlineStr">
+        <is>
+          <t>일본</t>
+        </is>
+      </c>
+      <c r="C1129" s="7" t="inlineStr">
+        <is>
+          <t>국채10년</t>
+        </is>
+      </c>
+      <c r="D1129" s="7">
+        <v>0.5</v>
+      </c>
+      <c r="E1129" s="6">
+        <v>44994</v>
+      </c>
+      <c r="F1129" s="7" t="inlineStr">
+        <is>
+          <t>월간</t>
+        </is>
+      </c>
     </row>
     <row r="1130" spans="1:6">
-      <c r="A1130" s="6"/>
-      <c r="B1130" s="7"/>
-      <c r="C1130" s="7"/>
-      <c r="D1130" s="7"/>
-      <c r="E1130" s="6"/>
-      <c r="F1130" s="7"/>
+      <c r="A1130" s="6">
+        <v>44986</v>
+      </c>
+      <c r="B1130" s="7" t="inlineStr">
+        <is>
+          <t>일본</t>
+        </is>
+      </c>
+      <c r="C1130" s="7" t="inlineStr">
+        <is>
+          <t>국채10년</t>
+        </is>
+      </c>
+      <c r="D1130" s="7">
+        <v>0.32</v>
+      </c>
+      <c r="E1130" s="6">
+        <v>45023</v>
+      </c>
+      <c r="F1130" s="7" t="inlineStr">
+        <is>
+          <t>월간</t>
+        </is>
+      </c>
     </row>
     <row r="1131" spans="1:6">
-      <c r="A1131" s="6"/>
-      <c r="B1131" s="7"/>
-      <c r="C1131" s="7"/>
-      <c r="D1131" s="7"/>
-      <c r="E1131" s="6"/>
-      <c r="F1131" s="7"/>
+      <c r="A1131" s="6">
+        <v>45017</v>
+      </c>
+      <c r="B1131" s="7" t="inlineStr">
+        <is>
+          <t>일본</t>
+        </is>
+      </c>
+      <c r="C1131" s="7" t="inlineStr">
+        <is>
+          <t>국채10년</t>
+        </is>
+      </c>
+      <c r="D1131" s="7">
+        <v>0.385</v>
+      </c>
+      <c r="E1131" s="6">
+        <v>45056</v>
+      </c>
+      <c r="F1131" s="7" t="inlineStr">
+        <is>
+          <t>월간</t>
+        </is>
+      </c>
     </row>
     <row r="1132" spans="1:6">
-      <c r="A1132" s="6"/>
-      <c r="B1132" s="7"/>
-      <c r="C1132" s="7"/>
-      <c r="D1132" s="7"/>
-      <c r="E1132" s="6"/>
-      <c r="F1132" s="7"/>
+      <c r="A1132" s="6">
+        <v>45047</v>
+      </c>
+      <c r="B1132" s="7" t="inlineStr">
+        <is>
+          <t>일본</t>
+        </is>
+      </c>
+      <c r="C1132" s="7" t="inlineStr">
+        <is>
+          <t>국채10년</t>
+        </is>
+      </c>
+      <c r="D1132" s="7">
+        <v>0.43</v>
+      </c>
+      <c r="E1132" s="6">
+        <v>45090</v>
+      </c>
+      <c r="F1132" s="7" t="inlineStr">
+        <is>
+          <t>월간</t>
+        </is>
+      </c>
     </row>
     <row r="1133" spans="1:6">
-      <c r="A1133" s="6"/>
-      <c r="B1133" s="7"/>
-      <c r="C1133" s="7"/>
-      <c r="D1133" s="7"/>
-      <c r="E1133" s="6"/>
-      <c r="F1133" s="7"/>
+      <c r="A1133" s="6">
+        <v>45078</v>
+      </c>
+      <c r="B1133" s="7" t="inlineStr">
+        <is>
+          <t>일본</t>
+        </is>
+      </c>
+      <c r="C1133" s="7" t="inlineStr">
+        <is>
+          <t>국채10년</t>
+        </is>
+      </c>
+      <c r="D1133" s="7">
+        <v>0.395</v>
+      </c>
+      <c r="E1133" s="6">
+        <v>45114</v>
+      </c>
+      <c r="F1133" s="7" t="inlineStr">
+        <is>
+          <t>월간</t>
+        </is>
+      </c>
     </row>
     <row r="1134" spans="1:6">
-      <c r="A1134" s="6"/>
-      <c r="B1134" s="7"/>
-      <c r="C1134" s="7"/>
-      <c r="D1134" s="7"/>
-      <c r="E1134" s="6"/>
-      <c r="F1134" s="7"/>
+      <c r="A1134" s="6">
+        <v>45108</v>
+      </c>
+      <c r="B1134" s="7" t="inlineStr">
+        <is>
+          <t>일본</t>
+        </is>
+      </c>
+      <c r="C1134" s="7" t="inlineStr">
+        <is>
+          <t>국채10년</t>
+        </is>
+      </c>
+      <c r="D1134" s="7">
+        <v>0.595</v>
+      </c>
+      <c r="E1134" s="6">
+        <v>45148</v>
+      </c>
+      <c r="F1134" s="7" t="inlineStr">
+        <is>
+          <t>월간</t>
+        </is>
+      </c>
     </row>
     <row r="1135" spans="1:6">
-      <c r="A1135" s="6"/>
-      <c r="B1135" s="7"/>
-      <c r="C1135" s="7"/>
-      <c r="D1135" s="7"/>
-      <c r="E1135" s="6"/>
-      <c r="F1135" s="7"/>
+      <c r="A1135" s="6">
+        <v>45139</v>
+      </c>
+      <c r="B1135" s="7" t="inlineStr">
+        <is>
+          <t>일본</t>
+        </is>
+      </c>
+      <c r="C1135" s="7" t="inlineStr">
+        <is>
+          <t>국채10년</t>
+        </is>
+      </c>
+      <c r="D1135" s="7">
+        <v>0.64</v>
+      </c>
+      <c r="E1135" s="6">
+        <v>45178</v>
+      </c>
+      <c r="F1135" s="7" t="inlineStr">
+        <is>
+          <t>월간</t>
+        </is>
+      </c>
     </row>
     <row r="1136" spans="1:6">
-      <c r="A1136" s="6"/>
-      <c r="B1136" s="7"/>
-      <c r="C1136" s="7"/>
-      <c r="D1136" s="7"/>
-      <c r="E1136" s="6"/>
-      <c r="F1136" s="7"/>
+      <c r="A1136" s="6">
+        <v>45170</v>
+      </c>
+      <c r="B1136" s="7" t="inlineStr">
+        <is>
+          <t>일본</t>
+        </is>
+      </c>
+      <c r="C1136" s="7" t="inlineStr">
+        <is>
+          <t>국채10년</t>
+        </is>
+      </c>
+      <c r="D1136" s="7">
+        <v>0.765</v>
+      </c>
+      <c r="E1136" s="6">
+        <v>45206</v>
+      </c>
+      <c r="F1136" s="7" t="inlineStr">
+        <is>
+          <t>월간</t>
+        </is>
+      </c>
     </row>
     <row r="1137" spans="1:6">
-      <c r="A1137" s="6"/>
-      <c r="B1137" s="7"/>
-      <c r="C1137" s="7"/>
-      <c r="D1137" s="7"/>
-      <c r="E1137" s="6"/>
-      <c r="F1137" s="7"/>
+      <c r="A1137" s="6">
+        <v>45200</v>
+      </c>
+      <c r="B1137" s="7" t="inlineStr">
+        <is>
+          <t>일본</t>
+        </is>
+      </c>
+      <c r="C1137" s="7" t="inlineStr">
+        <is>
+          <t>국채10년</t>
+        </is>
+      </c>
+      <c r="D1137" s="7">
+        <v>0.95</v>
+      </c>
+      <c r="E1137" s="6">
+        <v>45240</v>
+      </c>
+      <c r="F1137" s="7" t="inlineStr">
+        <is>
+          <t>월간</t>
+        </is>
+      </c>
     </row>
     <row r="1138" spans="1:6">
-      <c r="A1138" s="6"/>
-      <c r="B1138" s="7"/>
-      <c r="C1138" s="7"/>
-      <c r="D1138" s="7"/>
-      <c r="E1138" s="6"/>
-      <c r="F1138" s="7"/>
+      <c r="A1138" s="6">
+        <v>45231</v>
+      </c>
+      <c r="B1138" s="7" t="inlineStr">
+        <is>
+          <t>일본</t>
+        </is>
+      </c>
+      <c r="C1138" s="7" t="inlineStr">
+        <is>
+          <t>국채10년</t>
+        </is>
+      </c>
+      <c r="D1138" s="7">
+        <v>0.66</v>
+      </c>
+      <c r="E1138" s="6">
+        <v>45269</v>
+      </c>
+      <c r="F1138" s="7" t="inlineStr">
+        <is>
+          <t>월간</t>
+        </is>
+      </c>
     </row>
     <row r="1139" spans="1:6">
-      <c r="A1139" s="6"/>
-      <c r="B1139" s="7"/>
-      <c r="C1139" s="7"/>
-      <c r="D1139" s="7"/>
-      <c r="E1139" s="6"/>
-      <c r="F1139" s="7"/>
+      <c r="A1139" s="6">
+        <v>45261</v>
+      </c>
+      <c r="B1139" s="7" t="inlineStr">
+        <is>
+          <t>일본</t>
+        </is>
+      </c>
+      <c r="C1139" s="7" t="inlineStr">
+        <is>
+          <t>국채10년</t>
+        </is>
+      </c>
+      <c r="D1139" s="7">
+        <v>0.62</v>
+      </c>
+      <c r="E1139" s="6">
+        <v>45302</v>
+      </c>
+      <c r="F1139" s="7" t="inlineStr">
+        <is>
+          <t>월간</t>
+        </is>
+      </c>
     </row>
     <row r="1140" spans="1:6">
-      <c r="A1140" s="6"/>
-      <c r="B1140" s="7"/>
-      <c r="C1140" s="7"/>
-      <c r="D1140" s="7"/>
-      <c r="E1140" s="6"/>
-      <c r="F1140" s="7"/>
+      <c r="A1140" s="6">
+        <v>45292</v>
+      </c>
+      <c r="B1140" s="7" t="inlineStr">
+        <is>
+          <t>일본</t>
+        </is>
+      </c>
+      <c r="C1140" s="7" t="inlineStr">
+        <is>
+          <t>국채10년</t>
+        </is>
+      </c>
+      <c r="D1140" s="7">
+        <v>0.73</v>
+      </c>
+      <c r="E1140" s="6">
+        <v>45392</v>
+      </c>
+      <c r="F1140" s="7" t="inlineStr">
+        <is>
+          <t>월간</t>
+        </is>
+      </c>
     </row>
     <row r="1141" spans="1:6">
-      <c r="A1141" s="6"/>
-      <c r="B1141" s="7"/>
-      <c r="C1141" s="7"/>
-      <c r="D1141" s="7"/>
-      <c r="E1141" s="6"/>
-      <c r="F1141" s="7"/>
+      <c r="A1141" s="6">
+        <v>45323</v>
+      </c>
+      <c r="B1141" s="7" t="inlineStr">
+        <is>
+          <t>일본</t>
+        </is>
+      </c>
+      <c r="C1141" s="7" t="inlineStr">
+        <is>
+          <t>국채10년</t>
+        </is>
+      </c>
+      <c r="D1141" s="7">
+        <v>0.71</v>
+      </c>
+      <c r="E1141" s="6">
+        <v>45392</v>
+      </c>
+      <c r="F1141" s="7" t="inlineStr">
+        <is>
+          <t>월간</t>
+        </is>
+      </c>
     </row>
     <row r="1142" spans="1:6">
-      <c r="A1142" s="6"/>
-      <c r="B1142" s="7"/>
-      <c r="C1142" s="7"/>
-      <c r="D1142" s="7"/>
-      <c r="E1142" s="6"/>
-      <c r="F1142" s="7"/>
+      <c r="A1142" s="6">
+        <v>45352</v>
+      </c>
+      <c r="B1142" s="7" t="inlineStr">
+        <is>
+          <t>일본</t>
+        </is>
+      </c>
+      <c r="C1142" s="7" t="inlineStr">
+        <is>
+          <t>국채10년</t>
+        </is>
+      </c>
+      <c r="D1142" s="7">
+        <v>0.725</v>
+      </c>
+      <c r="E1142" s="6">
+        <v>45392</v>
+      </c>
+      <c r="F1142" s="7" t="inlineStr">
+        <is>
+          <t>월간</t>
+        </is>
+      </c>
     </row>
     <row r="1143" spans="1:6">
-      <c r="A1143" s="6"/>
-      <c r="B1143" s="7"/>
-      <c r="C1143" s="7"/>
-      <c r="D1143" s="7"/>
-      <c r="E1143" s="6"/>
-      <c r="F1143" s="7"/>
+      <c r="A1143" s="6">
+        <v>45383</v>
+      </c>
+      <c r="B1143" s="7" t="inlineStr">
+        <is>
+          <t>일본</t>
+        </is>
+      </c>
+      <c r="C1143" s="7" t="inlineStr">
+        <is>
+          <t>국채10년</t>
+        </is>
+      </c>
+      <c r="D1143" s="7">
+        <v>0.87</v>
+      </c>
+      <c r="E1143" s="6">
+        <v>45427</v>
+      </c>
+      <c r="F1143" s="7" t="inlineStr">
+        <is>
+          <t>월간</t>
+        </is>
+      </c>
     </row>
     <row r="1144" spans="1:6">
-      <c r="A1144" s="6"/>
-      <c r="B1144" s="7"/>
-      <c r="C1144" s="7"/>
-      <c r="D1144" s="7"/>
-      <c r="E1144" s="6"/>
-      <c r="F1144" s="7"/>
+      <c r="A1144" s="6">
+        <v>45413</v>
+      </c>
+      <c r="B1144" s="7" t="inlineStr">
+        <is>
+          <t>일본</t>
+        </is>
+      </c>
+      <c r="C1144" s="7" t="inlineStr">
+        <is>
+          <t>국채10년</t>
+        </is>
+      </c>
+      <c r="D1144" s="7">
+        <v>1.07</v>
+      </c>
+      <c r="E1144" s="6">
+        <v>45460</v>
+      </c>
+      <c r="F1144" s="7" t="inlineStr">
+        <is>
+          <t>월간</t>
+        </is>
+      </c>
     </row>
     <row r="1145" spans="1:6">
-      <c r="A1145" s="6"/>
-      <c r="B1145" s="7"/>
-      <c r="C1145" s="7"/>
-      <c r="D1145" s="7"/>
-      <c r="E1145" s="6"/>
-      <c r="F1145" s="7"/>
+      <c r="A1145" s="6">
+        <v>45444</v>
+      </c>
+      <c r="B1145" s="7" t="inlineStr">
+        <is>
+          <t>일본</t>
+        </is>
+      </c>
+      <c r="C1145" s="7" t="inlineStr">
+        <is>
+          <t>국채10년</t>
+        </is>
+      </c>
+      <c r="D1145" s="7">
+        <v>1.05</v>
+      </c>
+      <c r="E1145" s="6">
+        <v>45488</v>
+      </c>
+      <c r="F1145" s="7" t="inlineStr">
+        <is>
+          <t>월간</t>
+        </is>
+      </c>
     </row>
     <row r="1146" spans="1:6">
-      <c r="A1146" s="6"/>
-      <c r="B1146" s="7"/>
-      <c r="C1146" s="7"/>
-      <c r="D1146" s="7"/>
-      <c r="E1146" s="6"/>
-      <c r="F1146" s="7"/>
+      <c r="A1146" s="6">
+        <v>45474</v>
+      </c>
+      <c r="B1146" s="7" t="inlineStr">
+        <is>
+          <t>일본</t>
+        </is>
+      </c>
+      <c r="C1146" s="7" t="inlineStr">
+        <is>
+          <t>국채10년</t>
+        </is>
+      </c>
+      <c r="D1146" s="7">
+        <v>1.045</v>
+      </c>
+      <c r="E1146" s="6">
+        <v>45551</v>
+      </c>
+      <c r="F1146" s="7" t="inlineStr">
+        <is>
+          <t>월간</t>
+        </is>
+      </c>
     </row>
     <row r="1147" spans="1:6">
-      <c r="A1147" s="6"/>
-      <c r="B1147" s="7"/>
-      <c r="C1147" s="7"/>
-      <c r="D1147" s="7"/>
-      <c r="E1147" s="6"/>
-      <c r="F1147" s="7"/>
+      <c r="A1147" s="6">
+        <v>45505</v>
+      </c>
+      <c r="B1147" s="7" t="inlineStr">
+        <is>
+          <t>일본</t>
+        </is>
+      </c>
+      <c r="C1147" s="7" t="inlineStr">
+        <is>
+          <t>국채10년</t>
+        </is>
+      </c>
+      <c r="D1147" s="7">
+        <v>0.89</v>
+      </c>
+      <c r="E1147" s="6">
+        <v>45551</v>
+      </c>
+      <c r="F1147" s="7" t="inlineStr">
+        <is>
+          <t>월간</t>
+        </is>
+      </c>
     </row>
     <row r="1148" spans="1:6">
-      <c r="A1148" s="6"/>
-      <c r="B1148" s="7"/>
-      <c r="C1148" s="7"/>
-      <c r="D1148" s="7"/>
-      <c r="E1148" s="6"/>
-      <c r="F1148" s="7"/>
+      <c r="A1148" s="6">
+        <v>45536</v>
+      </c>
+      <c r="B1148" s="7" t="inlineStr">
+        <is>
+          <t>일본</t>
+        </is>
+      </c>
+      <c r="C1148" s="7" t="inlineStr">
+        <is>
+          <t>국채10년</t>
+        </is>
+      </c>
+      <c r="D1148" s="7">
+        <v>0.855</v>
+      </c>
+      <c r="E1148" s="6">
+        <v>45580</v>
+      </c>
+      <c r="F1148" s="7" t="inlineStr">
+        <is>
+          <t>월간</t>
+        </is>
+      </c>
     </row>
     <row r="1149" spans="1:6">
-      <c r="A1149" s="6"/>
-      <c r="B1149" s="7"/>
-      <c r="C1149" s="7"/>
-      <c r="D1149" s="7"/>
-      <c r="E1149" s="6"/>
-      <c r="F1149" s="7"/>
+      <c r="A1149" s="6">
+        <v>45566</v>
+      </c>
+      <c r="B1149" s="7" t="inlineStr">
+        <is>
+          <t>일본</t>
+        </is>
+      </c>
+      <c r="C1149" s="7" t="inlineStr">
+        <is>
+          <t>국채10년</t>
+        </is>
+      </c>
+      <c r="D1149" s="7">
+        <v>0.935</v>
+      </c>
+      <c r="E1149" s="6">
+        <v>45611</v>
+      </c>
+      <c r="F1149" s="7" t="inlineStr">
+        <is>
+          <t>월간</t>
+        </is>
+      </c>
     </row>
     <row r="1150" spans="1:6">
-      <c r="A1150" s="6"/>
-      <c r="B1150" s="7"/>
-      <c r="C1150" s="7"/>
-      <c r="D1150" s="7"/>
-      <c r="E1150" s="6"/>
-      <c r="F1150" s="7"/>
+      <c r="A1150" s="6">
+        <v>45597</v>
+      </c>
+      <c r="B1150" s="7" t="inlineStr">
+        <is>
+          <t>일본</t>
+        </is>
+      </c>
+      <c r="C1150" s="7" t="inlineStr">
+        <is>
+          <t>국채10년</t>
+        </is>
+      </c>
+      <c r="D1150" s="7">
+        <v>1.05</v>
+      </c>
+      <c r="E1150" s="6">
+        <v>45642</v>
+      </c>
+      <c r="F1150" s="7" t="inlineStr">
+        <is>
+          <t>월간</t>
+        </is>
+      </c>
     </row>
     <row r="1151" spans="1:6">
-      <c r="A1151" s="6"/>
-      <c r="B1151" s="7"/>
-      <c r="C1151" s="7"/>
-      <c r="D1151" s="7"/>
-      <c r="E1151" s="6"/>
-      <c r="F1151" s="7"/>
+      <c r="A1151" s="6">
+        <v>45627</v>
+      </c>
+      <c r="B1151" s="7" t="inlineStr">
+        <is>
+          <t>일본</t>
+        </is>
+      </c>
+      <c r="C1151" s="7" t="inlineStr">
+        <is>
+          <t>국채10년</t>
+        </is>
+      </c>
+      <c r="D1151" s="7">
+        <v>1.09</v>
+      </c>
+      <c r="E1151" s="6">
+        <v>45672</v>
+      </c>
+      <c r="F1151" s="7" t="inlineStr">
+        <is>
+          <t>월간</t>
+        </is>
+      </c>
     </row>
     <row r="1152" spans="1:6">
-      <c r="A1152" s="6"/>
-      <c r="B1152" s="7"/>
-      <c r="C1152" s="7"/>
-      <c r="D1152" s="7"/>
-      <c r="E1152" s="6"/>
-      <c r="F1152" s="7"/>
+      <c r="A1152" s="6">
+        <v>45658</v>
+      </c>
+      <c r="B1152" s="7" t="inlineStr">
+        <is>
+          <t>일본</t>
+        </is>
+      </c>
+      <c r="C1152" s="7" t="inlineStr">
+        <is>
+          <t>국채10년</t>
+        </is>
+      </c>
+      <c r="D1152" s="7">
+        <v>1.245</v>
+      </c>
+      <c r="E1152" s="6">
+        <v>45705</v>
+      </c>
+      <c r="F1152" s="7" t="inlineStr">
+        <is>
+          <t>월간</t>
+        </is>
+      </c>
     </row>
     <row r="1153" spans="1:6">
-      <c r="A1153" s="6"/>
-      <c r="B1153" s="7"/>
-      <c r="C1153" s="7"/>
-      <c r="D1153" s="7"/>
-      <c r="E1153" s="6"/>
-      <c r="F1153" s="7"/>
+      <c r="A1153" s="6">
+        <v>45689</v>
+      </c>
+      <c r="B1153" s="7" t="inlineStr">
+        <is>
+          <t>일본</t>
+        </is>
+      </c>
+      <c r="C1153" s="7" t="inlineStr">
+        <is>
+          <t>국채10년</t>
+        </is>
+      </c>
+      <c r="D1153" s="7">
+        <v>1.37</v>
+      </c>
+      <c r="E1153" s="6">
+        <v>45733</v>
+      </c>
+      <c r="F1153" s="7" t="inlineStr">
+        <is>
+          <t>월간</t>
+        </is>
+      </c>
     </row>
     <row r="1154" spans="1:6">
-      <c r="A1154" s="6"/>
-      <c r="B1154" s="7"/>
-      <c r="C1154" s="7"/>
-      <c r="D1154" s="7"/>
-      <c r="E1154" s="6"/>
-      <c r="F1154" s="7"/>
+      <c r="A1154" s="6">
+        <v>45717</v>
+      </c>
+      <c r="B1154" s="7" t="inlineStr">
+        <is>
+          <t>일본</t>
+        </is>
+      </c>
+      <c r="C1154" s="7" t="inlineStr">
+        <is>
+          <t>국채10년</t>
+        </is>
+      </c>
+      <c r="D1154" s="7">
+        <v>1.485</v>
+      </c>
+      <c r="E1154" s="6">
+        <v>45762</v>
+      </c>
+      <c r="F1154" s="7" t="inlineStr">
+        <is>
+          <t>월간</t>
+        </is>
+      </c>
     </row>
     <row r="1155" spans="1:6">
-      <c r="A1155" s="6"/>
-      <c r="B1155" s="7"/>
-      <c r="C1155" s="7"/>
-      <c r="D1155" s="7"/>
-      <c r="E1155" s="6"/>
-      <c r="F1155" s="7"/>
+      <c r="A1155" s="6">
+        <v>45748</v>
+      </c>
+      <c r="B1155" s="7" t="inlineStr">
+        <is>
+          <t>일본</t>
+        </is>
+      </c>
+      <c r="C1155" s="7" t="inlineStr">
+        <is>
+          <t>국채10년</t>
+        </is>
+      </c>
+      <c r="D1155" s="7">
+        <v>1.31</v>
+      </c>
+      <c r="E1155" s="6">
+        <v>45792</v>
+      </c>
+      <c r="F1155" s="7" t="inlineStr">
+        <is>
+          <t>월간</t>
+        </is>
+      </c>
     </row>
     <row r="1156" spans="1:6">
-      <c r="A1156" s="6"/>
-      <c r="B1156" s="7"/>
-      <c r="C1156" s="7"/>
-      <c r="D1156" s="7"/>
-      <c r="E1156" s="6"/>
-      <c r="F1156" s="7"/>
+      <c r="A1156" s="6">
+        <v>45778</v>
+      </c>
+      <c r="B1156" s="7" t="inlineStr">
+        <is>
+          <t>일본</t>
+        </is>
+      </c>
+      <c r="C1156" s="7" t="inlineStr">
+        <is>
+          <t>국채10년</t>
+        </is>
+      </c>
+      <c r="D1156" s="7">
+        <v>1.5</v>
+      </c>
+      <c r="E1156" s="6">
+        <v>45824</v>
+      </c>
+      <c r="F1156" s="7" t="inlineStr">
+        <is>
+          <t>월간</t>
+        </is>
+      </c>
     </row>
     <row r="1157" spans="1:6">
-      <c r="A1157" s="6"/>
-      <c r="B1157" s="7"/>
-      <c r="C1157" s="7"/>
-      <c r="D1157" s="7"/>
-      <c r="E1157" s="6"/>
-      <c r="F1157" s="7"/>
+      <c r="A1157" s="6">
+        <v>45809</v>
+      </c>
+      <c r="B1157" s="7" t="inlineStr">
+        <is>
+          <t>일본</t>
+        </is>
+      </c>
+      <c r="C1157" s="7" t="inlineStr">
+        <is>
+          <t>국채10년</t>
+        </is>
+      </c>
+      <c r="D1157" s="7">
+        <v>1.42</v>
+      </c>
+      <c r="E1157" s="6">
+        <v>45853</v>
+      </c>
+      <c r="F1157" s="7" t="inlineStr">
+        <is>
+          <t>월간</t>
+        </is>
+      </c>
     </row>
     <row r="1158" spans="1:6">
-      <c r="A1158" s="6"/>
-      <c r="B1158" s="7"/>
-      <c r="C1158" s="7"/>
-      <c r="D1158" s="7"/>
-      <c r="E1158" s="6"/>
-      <c r="F1158" s="7"/>
+      <c r="A1158" s="6">
+        <v>45839</v>
+      </c>
+      <c r="B1158" s="7" t="inlineStr">
+        <is>
+          <t>일본</t>
+        </is>
+      </c>
+      <c r="C1158" s="7" t="inlineStr">
+        <is>
+          <t>국채10년</t>
+        </is>
+      </c>
+      <c r="D1158" s="7">
+        <v>1.545</v>
+      </c>
+      <c r="E1158" s="6">
+        <v>45884</v>
+      </c>
+      <c r="F1158" s="7" t="inlineStr">
+        <is>
+          <t>월간</t>
+        </is>
+      </c>
     </row>
     <row r="1159" spans="1:6">
-      <c r="A1159" s="6"/>
-      <c r="B1159" s="7"/>
-      <c r="C1159" s="7"/>
-      <c r="D1159" s="7"/>
-      <c r="E1159" s="6"/>
-      <c r="F1159" s="7"/>
+      <c r="A1159" s="6">
+        <v>45870</v>
+      </c>
+      <c r="B1159" s="7" t="inlineStr">
+        <is>
+          <t>일본</t>
+        </is>
+      </c>
+      <c r="C1159" s="7" t="inlineStr">
+        <is>
+          <t>국채10년</t>
+        </is>
+      </c>
+      <c r="D1159" s="7">
+        <v>1.6</v>
+      </c>
+      <c r="E1159" s="6">
+        <v>45915</v>
+      </c>
+      <c r="F1159" s="7" t="inlineStr">
+        <is>
+          <t>월간</t>
+        </is>
+      </c>
     </row>
     <row r="1160" spans="1:6">
-      <c r="A1160" s="6"/>
-      <c r="B1160" s="7"/>
-      <c r="C1160" s="7"/>
-      <c r="D1160" s="7"/>
-      <c r="E1160" s="6"/>
-      <c r="F1160" s="7"/>
+      <c r="A1160" s="6">
+        <v>45901</v>
+      </c>
+      <c r="B1160" s="7" t="inlineStr">
+        <is>
+          <t>일본</t>
+        </is>
+      </c>
+      <c r="C1160" s="7" t="inlineStr">
+        <is>
+          <t>국채10년</t>
+        </is>
+      </c>
+      <c r="D1160" s="7">
+        <v>1.645</v>
+      </c>
+      <c r="E1160" s="6">
+        <v>45945</v>
+      </c>
+      <c r="F1160" s="7" t="inlineStr">
+        <is>
+          <t>월간</t>
+        </is>
+      </c>
     </row>
     <row r="1161" spans="1:6">
-      <c r="A1161" s="6"/>
-      <c r="B1161" s="7"/>
-      <c r="C1161" s="7"/>
-      <c r="D1161" s="7"/>
-      <c r="E1161" s="6"/>
-      <c r="F1161" s="7"/>
+      <c r="A1161" s="6">
+        <v>45931</v>
+      </c>
+      <c r="B1161" s="7" t="inlineStr">
+        <is>
+          <t>일본</t>
+        </is>
+      </c>
+      <c r="C1161" s="7" t="inlineStr">
+        <is>
+          <t>국채10년</t>
+        </is>
+      </c>
+      <c r="D1161" s="7">
+        <v>1.655</v>
+      </c>
+      <c r="E1161" s="6">
+        <v>45978</v>
+      </c>
+      <c r="F1161" s="7" t="inlineStr">
+        <is>
+          <t>월간</t>
+        </is>
+      </c>
     </row>
     <row r="1162" spans="1:6">
-      <c r="A1162" s="6"/>
-      <c r="B1162" s="7"/>
-      <c r="C1162" s="7"/>
-      <c r="D1162" s="7"/>
-      <c r="E1162" s="6"/>
-      <c r="F1162" s="7"/>
+      <c r="A1162" s="6">
+        <v>45962</v>
+      </c>
+      <c r="B1162" s="7" t="inlineStr">
+        <is>
+          <t>일본</t>
+        </is>
+      </c>
+      <c r="C1162" s="7" t="inlineStr">
+        <is>
+          <t>국채10년</t>
+        </is>
+      </c>
+      <c r="D1162" s="7">
+        <v>1.805</v>
+      </c>
+      <c r="E1162" s="6">
+        <v>46006</v>
+      </c>
+      <c r="F1162" s="7" t="inlineStr">
+        <is>
+          <t>월간</t>
+        </is>
+      </c>
     </row>
     <row r="1163" spans="1:6">
-      <c r="A1163" s="6"/>
-      <c r="B1163" s="7"/>
-      <c r="C1163" s="7"/>
-      <c r="D1163" s="7"/>
-      <c r="E1163" s="6"/>
-      <c r="F1163" s="7"/>
+      <c r="A1163" s="6">
+        <v>45992</v>
+      </c>
+      <c r="B1163" s="7" t="inlineStr">
+        <is>
+          <t>일본</t>
+        </is>
+      </c>
+      <c r="C1163" s="7" t="inlineStr">
+        <is>
+          <t>국채10년</t>
+        </is>
+      </c>
+      <c r="D1163" s="7">
+        <v>2.06</v>
+      </c>
+      <c r="E1163" s="6">
+        <v>46037</v>
+      </c>
+      <c r="F1163" s="7" t="inlineStr">
+        <is>
+          <t>월간</t>
+        </is>
+      </c>
     </row>
     <row r="1164" spans="1:6">
-      <c r="A1164" s="6"/>
-      <c r="B1164" s="7"/>
-      <c r="C1164" s="7"/>
-      <c r="D1164" s="7"/>
-      <c r="E1164" s="6"/>
-      <c r="F1164" s="7"/>
+      <c r="A1164" s="6">
+        <v>46023</v>
+      </c>
+      <c r="B1164" s="7" t="inlineStr">
+        <is>
+          <t>일본</t>
+        </is>
+      </c>
+      <c r="C1164" s="7" t="inlineStr">
+        <is>
+          <t>국채10년</t>
+        </is>
+      </c>
+      <c r="D1164" s="7">
+        <v>2.24</v>
+      </c>
+      <c r="E1164" s="6">
+        <v>46069</v>
+      </c>
+      <c r="F1164" s="7" t="inlineStr">
+        <is>
+          <t>월간</t>
+        </is>
+      </c>
     </row>
     <row r="1165" spans="1:6">
-      <c r="A1165" s="6"/>
-      <c r="B1165" s="7"/>
-      <c r="C1165" s="7"/>
-      <c r="D1165" s="7"/>
-      <c r="E1165" s="6"/>
-      <c r="F1165" s="7"/>
+      <c r="A1165" s="6">
+        <v>46054</v>
+      </c>
+      <c r="B1165" s="7" t="inlineStr">
+        <is>
+          <t>일본</t>
+        </is>
+      </c>
+      <c r="C1165" s="7" t="inlineStr">
+        <is>
+          <t>국채10년</t>
+        </is>
+      </c>
+      <c r="D1165" s="7">
+        <v>2.11</v>
+      </c>
+      <c r="E1165" s="6">
+        <v>46097</v>
+      </c>
+      <c r="F1165" s="7" t="inlineStr">
+        <is>
+          <t>월간</t>
+        </is>
+      </c>
     </row>
     <row r="1166" spans="1:6">
-      <c r="A1166" s="6"/>
-      <c r="B1166" s="7"/>
-      <c r="C1166" s="7"/>
-      <c r="D1166" s="7"/>
-      <c r="E1166" s="6"/>
-      <c r="F1166" s="7"/>
+      <c r="A1166" s="6">
+        <v>46082</v>
+      </c>
+      <c r="B1166" s="7" t="inlineStr">
+        <is>
+          <t>일본</t>
+        </is>
+      </c>
+      <c r="C1166" s="7" t="inlineStr">
+        <is>
+          <t>국채10년</t>
+        </is>
+      </c>
+      <c r="D1166" s="7">
+        <v>2.345</v>
+      </c>
+      <c r="E1166" s="6">
+        <v>46127</v>
+      </c>
+      <c r="F1166" s="7" t="inlineStr">
+        <is>
+          <t>월간</t>
+        </is>
+      </c>
     </row>
     <row r="1167" spans="1:6">
-      <c r="A1167" s="6"/>
-      <c r="B1167" s="7"/>
-      <c r="C1167" s="7"/>
-      <c r="D1167" s="7"/>
-      <c r="E1167" s="6"/>
-      <c r="F1167" s="7"/>
+      <c r="A1167" s="6">
+        <v>46113</v>
+      </c>
+      <c r="B1167" s="7" t="inlineStr">
+        <is>
+          <t>일본</t>
+        </is>
+      </c>
+      <c r="C1167" s="7" t="inlineStr">
+        <is>
+          <t>국채10년</t>
+        </is>
+      </c>
+      <c r="D1167" s="7">
+        <v>2.515</v>
+      </c>
+      <c r="E1167" s="6">
+        <v>46157</v>
+      </c>
+      <c r="F1167" s="7" t="inlineStr">
+        <is>
+          <t>월간</t>
+        </is>
+      </c>
     </row>
     <row r="1168" spans="1:6">
-      <c r="A1168" s="6"/>
-      <c r="B1168" s="7"/>
-      <c r="C1168" s="7"/>
-      <c r="D1168" s="7"/>
-      <c r="E1168" s="6"/>
-      <c r="F1168" s="7"/>
+      <c r="A1168" s="6">
+        <v>46143</v>
+      </c>
+      <c r="B1168" s="7" t="inlineStr">
+        <is>
+          <t>일본</t>
+        </is>
+      </c>
+      <c r="C1168" s="7" t="inlineStr">
+        <is>
+          <t>국채10년</t>
+        </is>
+      </c>
+      <c r="D1168" s="7">
+        <v>2.65</v>
+      </c>
+      <c r="E1168" s="6">
+        <v>46188</v>
+      </c>
+      <c r="F1168" s="7" t="inlineStr">
+        <is>
+          <t>월간</t>
+        </is>
+      </c>
     </row>
     <row r="1169" spans="1:6">
-      <c r="A1169" s="6"/>
-      <c r="B1169" s="7"/>
-      <c r="C1169" s="7"/>
-      <c r="D1169" s="7"/>
-      <c r="E1169" s="6"/>
-      <c r="F1169" s="7"/>
+      <c r="A1169" s="6">
+        <v>46174</v>
+      </c>
+      <c r="B1169" s="7" t="inlineStr">
+        <is>
+          <t>일본</t>
+        </is>
+      </c>
+      <c r="C1169" s="7" t="inlineStr">
+        <is>
+          <t>국채10년</t>
+        </is>
+      </c>
+      <c r="D1169" s="7">
+        <v>2.67</v>
+      </c>
+      <c r="E1169" s="6">
+        <v>46219</v>
+      </c>
+      <c r="F1169" s="7" t="inlineStr">
+        <is>
+          <t>월간</t>
+        </is>
+      </c>
     </row>
     <row r="1170" spans="1:6">
-      <c r="A1170" s="6"/>
-      <c r="B1170" s="7"/>
-      <c r="C1170" s="7"/>
-      <c r="D1170" s="7"/>
-      <c r="E1170" s="6"/>
-      <c r="F1170" s="7"/>
+      <c r="A1170" s="6">
+        <v>46204</v>
+      </c>
+      <c r="B1170" s="7" t="inlineStr">
+        <is>
+          <t>일본</t>
+        </is>
+      </c>
+      <c r="C1170" s="7" t="inlineStr">
+        <is>
+          <t>국채10년</t>
+        </is>
+      </c>
+      <c r="D1170" s="7">
+        <v>2.79</v>
+      </c>
+      <c r="E1170" s="6">
+        <v>46280</v>
+      </c>
+      <c r="F1170" s="7" t="inlineStr">
+        <is>
+          <t>월간</t>
+        </is>
+      </c>
     </row>
     <row r="1171" spans="1:6">
-      <c r="A1171" s="6"/>
-      <c r="B1171" s="7"/>
-      <c r="C1171" s="7"/>
-      <c r="D1171" s="7"/>
-      <c r="E1171" s="6"/>
-      <c r="F1171" s="7"/>
+      <c r="A1171" s="6">
+        <v>46235</v>
+      </c>
+      <c r="B1171" s="7" t="inlineStr">
+        <is>
+          <t>일본</t>
+        </is>
+      </c>
+      <c r="C1171" s="7" t="inlineStr">
+        <is>
+          <t>국채10년</t>
+        </is>
+      </c>
+      <c r="D1171" s="7">
+        <v>2.94</v>
+      </c>
+      <c r="E1171" s="6">
+        <v>46280</v>
+      </c>
+      <c r="F1171" s="7" t="inlineStr">
+        <is>
+          <t>월간</t>
+        </is>
+      </c>
     </row>
     <row r="1172" spans="1:6">
       <c r="A1172" s="6"/>
@@ -55955,8 +61475,10 @@
       <c r="F11" s="8" t="s">
         <v>79</v>
       </c>
-      <c r="G11" s="9" t="s">
-        <v>80</v>
+      <c r="G11" s="8" t="inlineStr">
+        <is>
+          <t>ESTAT: 0004052037/tab3/cat0001/area00000 (전년동월비, e-Stat 제공값)</t>
+        </is>
       </c>
       <c r="H11" s="8"/>
     </row>
@@ -55979,8 +61501,10 @@
       <c r="F12" s="8" t="s">
         <v>79</v>
       </c>
-      <c r="G12" s="9" t="s">
-        <v>80</v>
+      <c r="G12" s="8" t="inlineStr">
+        <is>
+          <t>ESTAT: 0004052037/tab3/cat0161/area00000 (전년동월비, e-Stat 제공값)</t>
+        </is>
       </c>
       <c r="H12" s="8" t="s">
         <v>81</v>
@@ -56005,8 +61529,10 @@
       <c r="F13" s="8" t="s">
         <v>82</v>
       </c>
-      <c r="G13" s="9" t="s">
-        <v>80</v>
+      <c r="G13" s="8" t="inlineStr">
+        <is>
+          <t>FRED: LRUNTTTTJPM156S</t>
+        </is>
       </c>
       <c r="H13" s="8"/>
     </row>
@@ -56029,8 +61555,10 @@
       <c r="F14" s="8" t="s">
         <v>84</v>
       </c>
-      <c r="G14" s="9" t="s">
-        <v>85</v>
+      <c r="G14" s="8" t="inlineStr">
+        <is>
+          <t>FRED: JPNRGDPEXP (전기비 계산)</t>
+        </is>
       </c>
       <c r="H14" s="8"/>
     </row>
@@ -56077,8 +61605,10 @@
       <c r="F16" s="8" t="s">
         <v>90</v>
       </c>
-      <c r="G16" s="9" t="s">
-        <v>91</v>
+      <c r="G16" s="8" t="inlineStr">
+        <is>
+          <t>BOJ 공표자료 (수동 확정: 2021-09-01=-0.10%, 2024-03-19=0.10%, 2024-07-31=0.25%, 2025-01-24=0.50%, 2025-12-19=0.75%, 2026-06-16=1.00%)</t>
+        </is>
       </c>
       <c r="H16" s="8" t="s">
         <v>92</v>

--- a/매크로_트래커_로우데이터.xlsx
+++ b/매크로_트래커_로우데이터.xlsx
@@ -824,7 +824,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:B22"/>
+  <dimension ref="A1:B23"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="17"/>
   <cols>
     <col min="1" max="1" width="16" customWidth="1"/>
@@ -966,22 +966,34 @@
       </c>
     </row>
     <row r="20" spans="1:2">
-      <c r="A20" s="3" t="s">
+      <c r="A20" s="3" t="inlineStr">
+        <is>
+          <t>FRED 발표일</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
+          <t>OECD·IMF 경유 FRED 시리즈는 FRED 반영일이 실제 발표일보다 늦어 발표일을 기록하지 않음</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" spans="1:2">
+      <c r="A21" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="B20" s="2" t="s">
+      <c r="B21" s="2" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="21" spans="1:2">
-      <c r="A21" s="3"/>
-      <c r="B21" s="2"/>
-    </row>
     <row r="22" spans="1:2">
-      <c r="A22" s="3" t="s">
+      <c r="A22" s="3"/>
+      <c r="B22" s="2"/>
+    </row>
+    <row r="23" spans="1:2">
+      <c r="A23" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="B22" s="2" t="s">
+      <c r="B23" s="2" t="s">
         <v>32</v>
       </c>
     </row>
@@ -18964,9 +18976,7 @@
       <c r="D716" s="7">
         <v>72.7582</v>
       </c>
-      <c r="E716" s="6">
-        <v>44483</v>
-      </c>
+      <c r="E716" s="6"/>
       <c r="F716" s="7" t="inlineStr">
         <is>
           <t>월간</t>
@@ -18990,9 +19000,7 @@
       <c r="D717" s="7">
         <v>81.4371</v>
       </c>
-      <c r="E717" s="6">
-        <v>44524</v>
-      </c>
+      <c r="E717" s="6"/>
       <c r="F717" s="7" t="inlineStr">
         <is>
           <t>월간</t>
@@ -19016,9 +19024,7 @@
       <c r="D718" s="7">
         <v>78.6577</v>
       </c>
-      <c r="E718" s="6">
-        <v>44536</v>
-      </c>
+      <c r="E718" s="6"/>
       <c r="F718" s="7" t="inlineStr">
         <is>
           <t>월간</t>
@@ -19042,9 +19048,7 @@
       <c r="D719" s="7">
         <v>72.8478</v>
       </c>
-      <c r="E719" s="6">
-        <v>44797</v>
-      </c>
+      <c r="E719" s="6"/>
       <c r="F719" s="7" t="inlineStr">
         <is>
           <t>월간</t>
@@ -19068,9 +19072,7 @@
       <c r="D720" s="7">
         <v>83.451</v>
       </c>
-      <c r="E720" s="6">
-        <v>44797</v>
-      </c>
+      <c r="E720" s="6"/>
       <c r="F720" s="7" t="inlineStr">
         <is>
           <t>월간</t>
@@ -19094,9 +19096,7 @@
       <c r="D721" s="7">
         <v>91.525</v>
       </c>
-      <c r="E721" s="6">
-        <v>44797</v>
-      </c>
+      <c r="E721" s="6"/>
       <c r="F721" s="7" t="inlineStr">
         <is>
           <t>월간</t>
@@ -19120,9 +19120,7 @@
       <c r="D722" s="7">
         <v>107.5878</v>
       </c>
-      <c r="E722" s="6">
-        <v>44797</v>
-      </c>
+      <c r="E722" s="6"/>
       <c r="F722" s="7" t="inlineStr">
         <is>
           <t>월간</t>
@@ -19146,9 +19144,7 @@
       <c r="D723" s="7">
         <v>102.7552</v>
       </c>
-      <c r="E723" s="6">
-        <v>44797</v>
-      </c>
+      <c r="E723" s="6"/>
       <c r="F723" s="7" t="inlineStr">
         <is>
           <t>월간</t>
@@ -19172,9 +19168,7 @@
       <c r="D724" s="7">
         <v>107.8614</v>
       </c>
-      <c r="E724" s="6">
-        <v>44797</v>
-      </c>
+      <c r="E724" s="6"/>
       <c r="F724" s="7" t="inlineStr">
         <is>
           <t>월간</t>
@@ -19198,9 +19192,7 @@
       <c r="D725" s="7">
         <v>111.8595</v>
       </c>
-      <c r="E725" s="6">
-        <v>44797</v>
-      </c>
+      <c r="E725" s="6"/>
       <c r="F725" s="7" t="inlineStr">
         <is>
           <t>월간</t>
@@ -19224,9 +19216,7 @@
       <c r="D726" s="7">
         <v>100.3186</v>
       </c>
-      <c r="E726" s="6">
-        <v>44797</v>
-      </c>
+      <c r="E726" s="6"/>
       <c r="F726" s="7" t="inlineStr">
         <is>
           <t>월간</t>
@@ -19250,9 +19240,7 @@
       <c r="D727" s="7">
         <v>95.693</v>
       </c>
-      <c r="E727" s="6">
-        <v>44833</v>
-      </c>
+      <c r="E727" s="6"/>
       <c r="F727" s="7" t="inlineStr">
         <is>
           <t>월간</t>
@@ -19276,9 +19264,7 @@
       <c r="D728" s="7">
         <v>89.7427</v>
       </c>
-      <c r="E728" s="6">
-        <v>44858</v>
-      </c>
+      <c r="E728" s="6"/>
       <c r="F728" s="7" t="inlineStr">
         <is>
           <t>월간</t>
@@ -19302,9 +19288,7 @@
       <c r="D729" s="7">
         <v>91.2148</v>
       </c>
-      <c r="E729" s="6">
-        <v>44887</v>
-      </c>
+      <c r="E729" s="6"/>
       <c r="F729" s="7" t="inlineStr">
         <is>
           <t>월간</t>
@@ -19328,9 +19312,7 @@
       <c r="D730" s="7">
         <v>84.5991</v>
       </c>
-      <c r="E730" s="6">
-        <v>44929</v>
-      </c>
+      <c r="E730" s="6"/>
       <c r="F730" s="7" t="inlineStr">
         <is>
           <t>월간</t>
@@ -19354,9 +19336,7 @@
       <c r="D731" s="7">
         <v>76.8559</v>
       </c>
-      <c r="E731" s="6">
-        <v>44966</v>
-      </c>
+      <c r="E731" s="6"/>
       <c r="F731" s="7" t="inlineStr">
         <is>
           <t>월간</t>
@@ -19380,9 +19360,7 @@
       <c r="D732" s="7">
         <v>80.905</v>
       </c>
-      <c r="E732" s="6">
-        <v>44966</v>
-      </c>
+      <c r="E732" s="6"/>
       <c r="F732" s="7" t="inlineStr">
         <is>
           <t>월간</t>
@@ -19406,9 +19384,7 @@
       <c r="D733" s="7">
         <v>81.275</v>
       </c>
-      <c r="E733" s="6">
-        <v>45006</v>
-      </c>
+      <c r="E733" s="6"/>
       <c r="F733" s="7" t="inlineStr">
         <is>
           <t>월간</t>
@@ -19432,9 +19408,7 @@
       <c r="D734" s="7">
         <v>78.2709</v>
       </c>
-      <c r="E734" s="6">
-        <v>45035</v>
-      </c>
+      <c r="E734" s="6"/>
       <c r="F734" s="7" t="inlineStr">
         <is>
           <t>월간</t>
@@ -19458,9 +19432,7 @@
       <c r="D735" s="7">
         <v>83.4085</v>
       </c>
-      <c r="E735" s="6">
-        <v>45058</v>
-      </c>
+      <c r="E735" s="6"/>
       <c r="F735" s="7" t="inlineStr">
         <is>
           <t>월간</t>
@@ -19484,9 +19456,7 @@
       <c r="D736" s="7">
         <v>74.7891</v>
       </c>
-      <c r="E736" s="6">
-        <v>45089</v>
-      </c>
+      <c r="E736" s="6"/>
       <c r="F736" s="7" t="inlineStr">
         <is>
           <t>월간</t>
@@ -19510,9 +19480,7 @@
       <c r="D737" s="7">
         <v>74.7295</v>
       </c>
-      <c r="E737" s="6">
-        <v>45133</v>
-      </c>
+      <c r="E737" s="6"/>
       <c r="F737" s="7" t="inlineStr">
         <is>
           <t>월간</t>
@@ -19536,9 +19504,7 @@
       <c r="D738" s="7">
         <v>80.6457</v>
       </c>
-      <c r="E738" s="6">
-        <v>45167</v>
-      </c>
+      <c r="E738" s="6"/>
       <c r="F738" s="7" t="inlineStr">
         <is>
           <t>월간</t>
@@ -19562,9 +19528,7 @@
       <c r="D739" s="7">
         <v>86.123</v>
       </c>
-      <c r="E739" s="6">
-        <v>45177</v>
-      </c>
+      <c r="E739" s="6"/>
       <c r="F739" s="7" t="inlineStr">
         <is>
           <t>월간</t>
@@ -19588,9 +19552,7 @@
       <c r="D740" s="7">
         <v>93.2386</v>
       </c>
-      <c r="E740" s="6">
-        <v>45215</v>
-      </c>
+      <c r="E740" s="6"/>
       <c r="F740" s="7" t="inlineStr">
         <is>
           <t>월간</t>
@@ -19614,9 +19576,7 @@
       <c r="D741" s="7">
         <v>88.7877</v>
       </c>
-      <c r="E741" s="6">
-        <v>45237</v>
-      </c>
+      <c r="E741" s="6"/>
       <c r="F741" s="7" t="inlineStr">
         <is>
           <t>월간</t>
@@ -19640,9 +19600,7 @@
       <c r="D742" s="7">
         <v>82.6409</v>
       </c>
-      <c r="E742" s="6">
-        <v>45268</v>
-      </c>
+      <c r="E742" s="6"/>
       <c r="F742" s="7" t="inlineStr">
         <is>
           <t>월간</t>
@@ -19666,9 +19624,7 @@
       <c r="D743" s="7">
         <v>77.5695</v>
       </c>
-      <c r="E743" s="6">
-        <v>45315</v>
-      </c>
+      <c r="E743" s="6"/>
       <c r="F743" s="7" t="inlineStr">
         <is>
           <t>월간</t>
@@ -19692,9 +19648,7 @@
       <c r="D744" s="7">
         <v>79.5822</v>
       </c>
-      <c r="E744" s="6">
-        <v>45334</v>
-      </c>
+      <c r="E744" s="6"/>
       <c r="F744" s="7" t="inlineStr">
         <is>
           <t>월간</t>
@@ -19718,9 +19672,7 @@
       <c r="D745" s="7">
         <v>82.809</v>
       </c>
-      <c r="E745" s="6">
-        <v>45359</v>
-      </c>
+      <c r="E745" s="6"/>
       <c r="F745" s="7" t="inlineStr">
         <is>
           <t>월간</t>
@@ -19744,9 +19696,7 @@
       <c r="D746" s="7">
         <v>86.6338</v>
       </c>
-      <c r="E746" s="6">
-        <v>45385</v>
-      </c>
+      <c r="E746" s="6"/>
       <c r="F746" s="7" t="inlineStr">
         <is>
           <t>월간</t>
@@ -19770,9 +19720,7 @@
       <c r="D747" s="7">
         <v>90.8695</v>
       </c>
-      <c r="E747" s="6">
-        <v>45418</v>
-      </c>
+      <c r="E747" s="6"/>
       <c r="F747" s="7" t="inlineStr">
         <is>
           <t>월간</t>
@@ -19796,9 +19744,7 @@
       <c r="D748" s="7">
         <v>84.6661</v>
       </c>
-      <c r="E748" s="6">
-        <v>45448</v>
-      </c>
+      <c r="E748" s="6"/>
       <c r="F748" s="7" t="inlineStr">
         <is>
           <t>월간</t>
@@ -19822,9 +19768,7 @@
       <c r="D749" s="7">
         <v>84.1125</v>
       </c>
-      <c r="E749" s="6">
-        <v>45476</v>
-      </c>
+      <c r="E749" s="6"/>
       <c r="F749" s="7" t="inlineStr">
         <is>
           <t>월간</t>
@@ -19848,9 +19792,7 @@
       <c r="D750" s="7">
         <v>85.2013</v>
       </c>
-      <c r="E750" s="6">
-        <v>45526</v>
-      </c>
+      <c r="E750" s="6"/>
       <c r="F750" s="7" t="inlineStr">
         <is>
           <t>월간</t>
@@ -19874,9 +19816,7 @@
       <c r="D751" s="7">
         <v>80.0891</v>
       </c>
-      <c r="E751" s="6">
-        <v>45541</v>
-      </c>
+      <c r="E751" s="6"/>
       <c r="F751" s="7" t="inlineStr">
         <is>
           <t>월간</t>
@@ -19900,9 +19840,7 @@
       <c r="D752" s="7">
         <v>73.76</v>
       </c>
-      <c r="E752" s="6">
-        <v>45572</v>
-      </c>
+      <c r="E752" s="6"/>
       <c r="F752" s="7" t="inlineStr">
         <is>
           <t>월간</t>
@@ -19926,9 +19864,7 @@
       <c r="D753" s="7">
         <v>76.07</v>
       </c>
-      <c r="E753" s="6">
-        <v>45603</v>
-      </c>
+      <c r="E753" s="6"/>
       <c r="F753" s="7" t="inlineStr">
         <is>
           <t>월간</t>
@@ -19952,9 +19888,7 @@
       <c r="D754" s="7">
         <v>74.0929</v>
       </c>
-      <c r="E754" s="6">
-        <v>45649</v>
-      </c>
+      <c r="E754" s="6"/>
       <c r="F754" s="7" t="inlineStr">
         <is>
           <t>월간</t>
@@ -19978,9 +19912,7 @@
       <c r="D755" s="7">
         <v>74.0027</v>
       </c>
-      <c r="E755" s="6">
-        <v>45684</v>
-      </c>
+      <c r="E755" s="6"/>
       <c r="F755" s="7" t="inlineStr">
         <is>
           <t>월간</t>
@@ -20004,9 +19936,7 @@
       <c r="D756" s="7">
         <v>80.8043</v>
       </c>
-      <c r="E756" s="6">
-        <v>45714</v>
-      </c>
+      <c r="E756" s="6"/>
       <c r="F756" s="7" t="inlineStr">
         <is>
           <t>월간</t>
@@ -20030,9 +19960,7 @@
       <c r="D757" s="7">
         <v>76.3215</v>
       </c>
-      <c r="E757" s="6">
-        <v>45727</v>
-      </c>
+      <c r="E757" s="6"/>
       <c r="F757" s="7" t="inlineStr">
         <is>
           <t>월간</t>
@@ -20056,9 +19984,7 @@
       <c r="D758" s="7">
         <v>72.9781</v>
       </c>
-      <c r="E758" s="6">
-        <v>45751</v>
-      </c>
+      <c r="E758" s="6"/>
       <c r="F758" s="7" t="inlineStr">
         <is>
           <t>월간</t>
@@ -20082,9 +20008,7 @@
       <c r="D759" s="7">
         <v>68.4895</v>
       </c>
-      <c r="E759" s="6">
-        <v>45786</v>
-      </c>
+      <c r="E759" s="6"/>
       <c r="F759" s="7" t="inlineStr">
         <is>
           <t>월간</t>
@@ -20108,9 +20032,7 @@
       <c r="D760" s="7">
         <v>63.6073</v>
       </c>
-      <c r="E760" s="6">
-        <v>45834</v>
-      </c>
+      <c r="E760" s="6"/>
       <c r="F760" s="7" t="inlineStr">
         <is>
           <t>월간</t>
@@ -20134,9 +20056,7 @@
       <c r="D761" s="7">
         <v>69.3629</v>
       </c>
-      <c r="E761" s="6">
-        <v>45852</v>
-      </c>
+      <c r="E761" s="6"/>
       <c r="F761" s="7" t="inlineStr">
         <is>
           <t>월간</t>
@@ -20160,9 +20080,7 @@
       <c r="D762" s="7">
         <v>71.043</v>
       </c>
-      <c r="E762" s="6">
-        <v>46044</v>
-      </c>
+      <c r="E762" s="6"/>
       <c r="F762" s="7" t="inlineStr">
         <is>
           <t>월간</t>
@@ -20186,9 +20104,7 @@
       <c r="D763" s="7">
         <v>69.3881</v>
       </c>
-      <c r="E763" s="6">
-        <v>46044</v>
-      </c>
+      <c r="E763" s="6"/>
       <c r="F763" s="7" t="inlineStr">
         <is>
           <t>월간</t>
@@ -20212,9 +20128,7 @@
       <c r="D764" s="7">
         <v>69.9191</v>
       </c>
-      <c r="E764" s="6">
-        <v>46044</v>
-      </c>
+      <c r="E764" s="6"/>
       <c r="F764" s="7" t="inlineStr">
         <is>
           <t>월간</t>
@@ -20238,9 +20152,7 @@
       <c r="D765" s="7">
         <v>64.5987</v>
       </c>
-      <c r="E765" s="6">
-        <v>46044</v>
-      </c>
+      <c r="E765" s="6"/>
       <c r="F765" s="7" t="inlineStr">
         <is>
           <t>월간</t>
@@ -20264,9 +20176,7 @@
       <c r="D766" s="7">
         <v>64.3555</v>
       </c>
-      <c r="E766" s="6">
-        <v>46044</v>
-      </c>
+      <c r="E766" s="6"/>
       <c r="F766" s="7" t="inlineStr">
         <is>
           <t>월간</t>
@@ -20290,9 +20200,7 @@
       <c r="D767" s="7">
         <v>61.83</v>
       </c>
-      <c r="E767" s="6">
-        <v>46044</v>
-      </c>
+      <c r="E767" s="6"/>
       <c r="F767" s="7" t="inlineStr">
         <is>
           <t>월간</t>
@@ -20316,9 +20224,7 @@
       <c r="D768" s="7">
         <v>62.7282</v>
       </c>
-      <c r="E768" s="6">
-        <v>46065</v>
-      </c>
+      <c r="E768" s="6"/>
       <c r="F768" s="7" t="inlineStr">
         <is>
           <t>월간</t>
@@ -20342,9 +20248,7 @@
       <c r="D769" s="7">
         <v>68.5085</v>
       </c>
-      <c r="E769" s="6">
-        <v>46105</v>
-      </c>
+      <c r="E769" s="6"/>
       <c r="F769" s="7" t="inlineStr">
         <is>
           <t>월간</t>
@@ -20368,9 +20272,7 @@
       <c r="D770" s="7">
         <v>126.7064</v>
       </c>
-      <c r="E770" s="6">
-        <v>46127</v>
-      </c>
+      <c r="E770" s="6"/>
       <c r="F770" s="7" t="inlineStr">
         <is>
           <t>월간</t>
@@ -20394,9 +20296,7 @@
       <c r="D771" s="7">
         <v>105.2991</v>
       </c>
-      <c r="E771" s="6">
-        <v>46178</v>
-      </c>
+      <c r="E771" s="6"/>
       <c r="F771" s="7" t="inlineStr">
         <is>
           <t>월간</t>
@@ -20420,9 +20320,7 @@
       <c r="D772" s="7">
         <v>100.3643</v>
       </c>
-      <c r="E772" s="6">
-        <v>46178</v>
-      </c>
+      <c r="E772" s="6"/>
       <c r="F772" s="7" t="inlineStr">
         <is>
           <t>월간</t>
@@ -20446,9 +20344,7 @@
       <c r="D773" s="7">
         <v>79.5395</v>
       </c>
-      <c r="E773" s="6">
-        <v>46216</v>
-      </c>
+      <c r="E773" s="6"/>
       <c r="F773" s="7" t="inlineStr">
         <is>
           <t>월간</t>
@@ -20472,9 +20368,7 @@
       <c r="D774" s="7">
         <v>77.1318</v>
       </c>
-      <c r="E774" s="6">
-        <v>46251</v>
-      </c>
+      <c r="E774" s="6"/>
       <c r="F774" s="7" t="inlineStr">
         <is>
           <t>월간</t>
@@ -20888,9 +20782,7 @@
       <c r="D790" s="7">
         <v>2.061</v>
       </c>
-      <c r="E790" s="6">
-        <v>44482</v>
-      </c>
+      <c r="E790" s="6"/>
       <c r="F790" s="7" t="inlineStr">
         <is>
           <t>월간</t>
@@ -20914,9 +20806,7 @@
       <c r="D791" s="7">
         <v>2.399</v>
       </c>
-      <c r="E791" s="6">
-        <v>44511</v>
-      </c>
+      <c r="E791" s="6"/>
       <c r="F791" s="7" t="inlineStr">
         <is>
           <t>월간</t>
@@ -20940,9 +20830,7 @@
       <c r="D792" s="7">
         <v>2.355</v>
       </c>
-      <c r="E792" s="6">
-        <v>44540</v>
-      </c>
+      <c r="E792" s="6"/>
       <c r="F792" s="7" t="inlineStr">
         <is>
           <t>월간</t>
@@ -20966,9 +20854,7 @@
       <c r="D793" s="7">
         <v>2.187</v>
       </c>
-      <c r="E793" s="6">
-        <v>44579</v>
-      </c>
+      <c r="E793" s="6"/>
       <c r="F793" s="7" t="inlineStr">
         <is>
           <t>월간</t>
@@ -20992,9 +20878,7 @@
       <c r="D794" s="7">
         <v>2.492</v>
       </c>
-      <c r="E794" s="6">
-        <v>44630</v>
-      </c>
+      <c r="E794" s="6"/>
       <c r="F794" s="7" t="inlineStr">
         <is>
           <t>월간</t>
@@ -21018,9 +20902,7 @@
       <c r="D795" s="7">
         <v>2.69</v>
       </c>
-      <c r="E795" s="6">
-        <v>44630</v>
-      </c>
+      <c r="E795" s="6"/>
       <c r="F795" s="7" t="inlineStr">
         <is>
           <t>월간</t>
@@ -21044,9 +20926,7 @@
       <c r="D796" s="7">
         <v>2.784</v>
       </c>
-      <c r="E796" s="6">
-        <v>44665</v>
-      </c>
+      <c r="E796" s="6"/>
       <c r="F796" s="7" t="inlineStr">
         <is>
           <t>월간</t>
@@ -21070,9 +20950,7 @@
       <c r="D797" s="7">
         <v>3.219</v>
       </c>
-      <c r="E797" s="6">
-        <v>44692</v>
-      </c>
+      <c r="E797" s="6"/>
       <c r="F797" s="7" t="inlineStr">
         <is>
           <t>월간</t>
@@ -21096,9 +20974,7 @@
       <c r="D798" s="7">
         <v>3.295</v>
       </c>
-      <c r="E798" s="6">
-        <v>44726</v>
-      </c>
+      <c r="E798" s="6"/>
       <c r="F798" s="7" t="inlineStr">
         <is>
           <t>월간</t>
@@ -21122,9 +20998,7 @@
       <c r="D799" s="7">
         <v>3.64</v>
       </c>
-      <c r="E799" s="6">
-        <v>44755</v>
-      </c>
+      <c r="E799" s="6"/>
       <c r="F799" s="7" t="inlineStr">
         <is>
           <t>월간</t>
@@ -21148,9 +21022,7 @@
       <c r="D800" s="7">
         <v>3.3</v>
       </c>
-      <c r="E800" s="6">
-        <v>44783</v>
-      </c>
+      <c r="E800" s="6"/>
       <c r="F800" s="7" t="inlineStr">
         <is>
           <t>월간</t>
@@ -21174,9 +21046,7 @@
       <c r="D801" s="7">
         <v>3.322</v>
       </c>
-      <c r="E801" s="6">
-        <v>44818</v>
-      </c>
+      <c r="E801" s="6"/>
       <c r="F801" s="7" t="inlineStr">
         <is>
           <t>월간</t>
@@ -21200,9 +21070,7 @@
       <c r="D802" s="7">
         <v>3.897</v>
       </c>
-      <c r="E802" s="6">
-        <v>44876</v>
-      </c>
+      <c r="E802" s="6"/>
       <c r="F802" s="7" t="inlineStr">
         <is>
           <t>월간</t>
@@ -21226,9 +21094,7 @@
       <c r="D803" s="7">
         <v>4.267</v>
       </c>
-      <c r="E803" s="6">
-        <v>44876</v>
-      </c>
+      <c r="E803" s="6"/>
       <c r="F803" s="7" t="inlineStr">
         <is>
           <t>월간</t>
@@ -21252,9 +21118,7 @@
       <c r="D804" s="7">
         <v>3.915</v>
       </c>
-      <c r="E804" s="6">
-        <v>44905</v>
-      </c>
+      <c r="E804" s="6"/>
       <c r="F804" s="7" t="inlineStr">
         <is>
           <t>월간</t>
@@ -21278,9 +21142,7 @@
       <c r="D805" s="7">
         <v>3.541</v>
       </c>
-      <c r="E805" s="6">
-        <v>44937</v>
-      </c>
+      <c r="E805" s="6"/>
       <c r="F805" s="7" t="inlineStr">
         <is>
           <t>월간</t>
@@ -21304,9 +21166,7 @@
       <c r="D806" s="7">
         <v>3.411</v>
       </c>
-      <c r="E806" s="6">
-        <v>44970</v>
-      </c>
+      <c r="E806" s="6"/>
       <c r="F806" s="7" t="inlineStr">
         <is>
           <t>월간</t>
@@ -21330,9 +21190,7 @@
       <c r="D807" s="7">
         <v>3.45</v>
       </c>
-      <c r="E807" s="6">
-        <v>44994</v>
-      </c>
+      <c r="E807" s="6"/>
       <c r="F807" s="7" t="inlineStr">
         <is>
           <t>월간</t>
@@ -21356,9 +21214,7 @@
       <c r="D808" s="7">
         <v>3.448</v>
       </c>
-      <c r="E808" s="6">
-        <v>45023</v>
-      </c>
+      <c r="E808" s="6"/>
       <c r="F808" s="7" t="inlineStr">
         <is>
           <t>월간</t>
@@ -21382,9 +21238,7 @@
       <c r="D809" s="7">
         <v>3.319</v>
       </c>
-      <c r="E809" s="6">
-        <v>45056</v>
-      </c>
+      <c r="E809" s="6"/>
       <c r="F809" s="7" t="inlineStr">
         <is>
           <t>월간</t>
@@ -21408,9 +21262,7 @@
       <c r="D810" s="7">
         <v>3.402</v>
       </c>
-      <c r="E810" s="6">
-        <v>45090</v>
-      </c>
+      <c r="E810" s="6"/>
       <c r="F810" s="7" t="inlineStr">
         <is>
           <t>월간</t>
@@ -21434,9 +21286,7 @@
       <c r="D811" s="7">
         <v>3.611</v>
       </c>
-      <c r="E811" s="6">
-        <v>45114</v>
-      </c>
+      <c r="E811" s="6"/>
       <c r="F811" s="7" t="inlineStr">
         <is>
           <t>월간</t>
@@ -21460,9 +21310,7 @@
       <c r="D812" s="7">
         <v>3.681</v>
       </c>
-      <c r="E812" s="6">
-        <v>45148</v>
-      </c>
+      <c r="E812" s="6"/>
       <c r="F812" s="7" t="inlineStr">
         <is>
           <t>월간</t>
@@ -21486,9 +21334,7 @@
       <c r="D813" s="7">
         <v>3.86</v>
       </c>
-      <c r="E813" s="6">
-        <v>45178</v>
-      </c>
+      <c r="E813" s="6"/>
       <c r="F813" s="7" t="inlineStr">
         <is>
           <t>월간</t>
@@ -21512,9 +21358,7 @@
       <c r="D814" s="7">
         <v>3.949</v>
       </c>
-      <c r="E814" s="6">
-        <v>45206</v>
-      </c>
+      <c r="E814" s="6"/>
       <c r="F814" s="7" t="inlineStr">
         <is>
           <t>월간</t>
@@ -21538,9 +21382,7 @@
       <c r="D815" s="7">
         <v>4.272</v>
       </c>
-      <c r="E815" s="6">
-        <v>45240</v>
-      </c>
+      <c r="E815" s="6"/>
       <c r="F815" s="7" t="inlineStr">
         <is>
           <t>월간</t>
@@ -21564,9 +21406,7 @@
       <c r="D816" s="7">
         <v>3.89</v>
       </c>
-      <c r="E816" s="6">
-        <v>45269</v>
-      </c>
+      <c r="E816" s="6"/>
       <c r="F816" s="7" t="inlineStr">
         <is>
           <t>월간</t>
@@ -21590,9 +21430,7 @@
       <c r="D817" s="7">
         <v>3.415</v>
       </c>
-      <c r="E817" s="6">
-        <v>45302</v>
-      </c>
+      <c r="E817" s="6"/>
       <c r="F817" s="7" t="inlineStr">
         <is>
           <t>월간</t>
@@ -21616,9 +21454,7 @@
       <c r="D818" s="7">
         <v>3.353</v>
       </c>
-      <c r="E818" s="6">
-        <v>45392</v>
-      </c>
+      <c r="E818" s="6"/>
       <c r="F818" s="7" t="inlineStr">
         <is>
           <t>월간</t>
@@ -21642,9 +21478,7 @@
       <c r="D819" s="7">
         <v>3.429</v>
       </c>
-      <c r="E819" s="6">
-        <v>45392</v>
-      </c>
+      <c r="E819" s="6"/>
       <c r="F819" s="7" t="inlineStr">
         <is>
           <t>월간</t>
@@ -21668,9 +21502,7 @@
       <c r="D820" s="7">
         <v>3.39</v>
       </c>
-      <c r="E820" s="6">
-        <v>45392</v>
-      </c>
+      <c r="E820" s="6"/>
       <c r="F820" s="7" t="inlineStr">
         <is>
           <t>월간</t>
@@ -21694,9 +21526,7 @@
       <c r="D821" s="7">
         <v>3.567</v>
       </c>
-      <c r="E821" s="6">
-        <v>45427</v>
-      </c>
+      <c r="E821" s="6"/>
       <c r="F821" s="7" t="inlineStr">
         <is>
           <t>월간</t>
@@ -21720,9 +21550,7 @@
       <c r="D822" s="7">
         <v>3.527</v>
       </c>
-      <c r="E822" s="6">
-        <v>45460</v>
-      </c>
+      <c r="E822" s="6"/>
       <c r="F822" s="7" t="inlineStr">
         <is>
           <t>월간</t>
@@ -21746,9 +21574,7 @@
       <c r="D823" s="7">
         <v>3.337</v>
       </c>
-      <c r="E823" s="6">
-        <v>45488</v>
-      </c>
+      <c r="E823" s="6"/>
       <c r="F823" s="7" t="inlineStr">
         <is>
           <t>월간</t>
@@ -21772,9 +21598,7 @@
       <c r="D824" s="7">
         <v>3.171</v>
       </c>
-      <c r="E824" s="6">
-        <v>45551</v>
-      </c>
+      <c r="E824" s="6"/>
       <c r="F824" s="7" t="inlineStr">
         <is>
           <t>월간</t>
@@ -21798,9 +21622,7 @@
       <c r="D825" s="7">
         <v>2.999</v>
       </c>
-      <c r="E825" s="6">
-        <v>45551</v>
-      </c>
+      <c r="E825" s="6"/>
       <c r="F825" s="7" t="inlineStr">
         <is>
           <t>월간</t>
@@ -21824,9 +21646,7 @@
       <c r="D826" s="7">
         <v>3.011</v>
       </c>
-      <c r="E826" s="6">
-        <v>45580</v>
-      </c>
+      <c r="E826" s="6"/>
       <c r="F826" s="7" t="inlineStr">
         <is>
           <t>월간</t>
@@ -21850,9 +21670,7 @@
       <c r="D827" s="7">
         <v>3.07</v>
       </c>
-      <c r="E827" s="6">
-        <v>45611</v>
-      </c>
+      <c r="E827" s="6"/>
       <c r="F827" s="7" t="inlineStr">
         <is>
           <t>월간</t>
@@ -21876,9 +21694,7 @@
       <c r="D828" s="7">
         <v>3.006</v>
       </c>
-      <c r="E828" s="6">
-        <v>45642</v>
-      </c>
+      <c r="E828" s="6"/>
       <c r="F828" s="7" t="inlineStr">
         <is>
           <t>월간</t>
@@ -21902,9 +21718,7 @@
       <c r="D829" s="7">
         <v>2.771</v>
       </c>
-      <c r="E829" s="6">
-        <v>45672</v>
-      </c>
+      <c r="E829" s="6"/>
       <c r="F829" s="7" t="inlineStr">
         <is>
           <t>월간</t>
@@ -21928,9 +21742,7 @@
       <c r="D830" s="7">
         <v>2.821</v>
       </c>
-      <c r="E830" s="6">
-        <v>45705</v>
-      </c>
+      <c r="E830" s="6"/>
       <c r="F830" s="7" t="inlineStr">
         <is>
           <t>월간</t>
@@ -21954,9 +21766,7 @@
       <c r="D831" s="7">
         <v>2.83</v>
       </c>
-      <c r="E831" s="6">
-        <v>45733</v>
-      </c>
+      <c r="E831" s="6"/>
       <c r="F831" s="7" t="inlineStr">
         <is>
           <t>월간</t>
@@ -21980,9 +21790,7 @@
       <c r="D832" s="7">
         <v>2.795</v>
       </c>
-      <c r="E832" s="6">
-        <v>45762</v>
-      </c>
+      <c r="E832" s="6"/>
       <c r="F832" s="7" t="inlineStr">
         <is>
           <t>월간</t>
@@ -22006,9 +21814,7 @@
       <c r="D833" s="7">
         <v>2.658</v>
       </c>
-      <c r="E833" s="6">
-        <v>45792</v>
-      </c>
+      <c r="E833" s="6"/>
       <c r="F833" s="7" t="inlineStr">
         <is>
           <t>월간</t>
@@ -22032,9 +21838,7 @@
       <c r="D834" s="7">
         <v>2.71</v>
       </c>
-      <c r="E834" s="6">
-        <v>45824</v>
-      </c>
+      <c r="E834" s="6"/>
       <c r="F834" s="7" t="inlineStr">
         <is>
           <t>월간</t>
@@ -22058,9 +21862,7 @@
       <c r="D835" s="7">
         <v>2.842</v>
       </c>
-      <c r="E835" s="6">
-        <v>45853</v>
-      </c>
+      <c r="E835" s="6"/>
       <c r="F835" s="7" t="inlineStr">
         <is>
           <t>월간</t>
@@ -22084,9 +21886,7 @@
       <c r="D836" s="7">
         <v>2.84</v>
       </c>
-      <c r="E836" s="6">
-        <v>45884</v>
-      </c>
+      <c r="E836" s="6"/>
       <c r="F836" s="7" t="inlineStr">
         <is>
           <t>월간</t>
@@ -22110,9 +21910,7 @@
       <c r="D837" s="7">
         <v>2.815</v>
       </c>
-      <c r="E837" s="6">
-        <v>45915</v>
-      </c>
+      <c r="E837" s="6"/>
       <c r="F837" s="7" t="inlineStr">
         <is>
           <t>월간</t>
@@ -22136,9 +21934,7 @@
       <c r="D838" s="7">
         <v>2.849</v>
       </c>
-      <c r="E838" s="6">
-        <v>45945</v>
-      </c>
+      <c r="E838" s="6"/>
       <c r="F838" s="7" t="inlineStr">
         <is>
           <t>월간</t>
@@ -22162,9 +21958,7 @@
       <c r="D839" s="7">
         <v>2.933</v>
       </c>
-      <c r="E839" s="6">
-        <v>45978</v>
-      </c>
+      <c r="E839" s="6"/>
       <c r="F839" s="7" t="inlineStr">
         <is>
           <t>월간</t>
@@ -22188,9 +21982,7 @@
       <c r="D840" s="7">
         <v>3.248</v>
       </c>
-      <c r="E840" s="6">
-        <v>46006</v>
-      </c>
+      <c r="E840" s="6"/>
       <c r="F840" s="7" t="inlineStr">
         <is>
           <t>월간</t>
@@ -22214,9 +22006,7 @@
       <c r="D841" s="7">
         <v>3.366</v>
       </c>
-      <c r="E841" s="6">
-        <v>46037</v>
-      </c>
+      <c r="E841" s="6"/>
       <c r="F841" s="7" t="inlineStr">
         <is>
           <t>월간</t>
@@ -22240,9 +22030,7 @@
       <c r="D842" s="7">
         <v>3.485</v>
       </c>
-      <c r="E842" s="6">
-        <v>46069</v>
-      </c>
+      <c r="E842" s="6"/>
       <c r="F842" s="7" t="inlineStr">
         <is>
           <t>월간</t>
@@ -22266,9 +22054,7 @@
       <c r="D843" s="7">
         <v>3.612</v>
       </c>
-      <c r="E843" s="6">
-        <v>46097</v>
-      </c>
+      <c r="E843" s="6"/>
       <c r="F843" s="7" t="inlineStr">
         <is>
           <t>월간</t>
@@ -22292,9 +22078,7 @@
       <c r="D844" s="7">
         <v>3.728</v>
       </c>
-      <c r="E844" s="6">
-        <v>46127</v>
-      </c>
+      <c r="E844" s="6"/>
       <c r="F844" s="7" t="inlineStr">
         <is>
           <t>월간</t>
@@ -22318,9 +22102,7 @@
       <c r="D845" s="7">
         <v>3.737</v>
       </c>
-      <c r="E845" s="6">
-        <v>46157</v>
-      </c>
+      <c r="E845" s="6"/>
       <c r="F845" s="7" t="inlineStr">
         <is>
           <t>월간</t>
@@ -22344,9 +22126,7 @@
       <c r="D846" s="7">
         <v>4.075</v>
       </c>
-      <c r="E846" s="6">
-        <v>46188</v>
-      </c>
+      <c r="E846" s="6"/>
       <c r="F846" s="7" t="inlineStr">
         <is>
           <t>월간</t>
@@ -22370,9 +22150,7 @@
       <c r="D847" s="7">
         <v>4.181</v>
       </c>
-      <c r="E847" s="6">
-        <v>46219</v>
-      </c>
+      <c r="E847" s="6"/>
       <c r="F847" s="7" t="inlineStr">
         <is>
           <t>월간</t>
@@ -22396,9 +22174,7 @@
       <c r="D848" s="7">
         <v>4.286</v>
       </c>
-      <c r="E848" s="6">
-        <v>46280</v>
-      </c>
+      <c r="E848" s="6"/>
       <c r="F848" s="7" t="inlineStr">
         <is>
           <t>월간</t>
@@ -22407,24 +22183,22 @@
     </row>
     <row r="849" spans="1:6">
       <c r="A849" s="6">
-        <v>46235</v>
+        <v>44440</v>
       </c>
       <c r="B849" s="7" t="inlineStr">
         <is>
-          <t>한국</t>
+          <t>일본</t>
         </is>
       </c>
       <c r="C849" s="7" t="inlineStr">
         <is>
-          <t>국채10년</t>
+          <t>CPI 헤드라인</t>
         </is>
       </c>
       <c r="D849" s="7">
-        <v>4.286</v>
-      </c>
-      <c r="E849" s="6">
-        <v>46280</v>
-      </c>
+        <v>0.2</v>
+      </c>
+      <c r="E849" s="6"/>
       <c r="F849" s="7" t="inlineStr">
         <is>
           <t>월간</t>
@@ -22433,7 +22207,7 @@
     </row>
     <row r="850" spans="1:6">
       <c r="A850" s="6">
-        <v>44440</v>
+        <v>44470</v>
       </c>
       <c r="B850" s="7" t="inlineStr">
         <is>
@@ -22446,7 +22220,7 @@
         </is>
       </c>
       <c r="D850" s="7">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="E850" s="6"/>
       <c r="F850" s="7" t="inlineStr">
@@ -22457,7 +22231,7 @@
     </row>
     <row r="851" spans="1:6">
       <c r="A851" s="6">
-        <v>44470</v>
+        <v>44501</v>
       </c>
       <c r="B851" s="7" t="inlineStr">
         <is>
@@ -22470,7 +22244,7 @@
         </is>
       </c>
       <c r="D851" s="7">
-        <v>0.1</v>
+        <v>0.6</v>
       </c>
       <c r="E851" s="6"/>
       <c r="F851" s="7" t="inlineStr">
@@ -22481,7 +22255,7 @@
     </row>
     <row r="852" spans="1:6">
       <c r="A852" s="6">
-        <v>44501</v>
+        <v>44531</v>
       </c>
       <c r="B852" s="7" t="inlineStr">
         <is>
@@ -22494,7 +22268,7 @@
         </is>
       </c>
       <c r="D852" s="7">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="E852" s="6"/>
       <c r="F852" s="7" t="inlineStr">
@@ -22505,7 +22279,7 @@
     </row>
     <row r="853" spans="1:6">
       <c r="A853" s="6">
-        <v>44531</v>
+        <v>44562</v>
       </c>
       <c r="B853" s="7" t="inlineStr">
         <is>
@@ -22518,7 +22292,7 @@
         </is>
       </c>
       <c r="D853" s="7">
-        <v>0.8</v>
+        <v>0.5</v>
       </c>
       <c r="E853" s="6"/>
       <c r="F853" s="7" t="inlineStr">
@@ -22529,7 +22303,7 @@
     </row>
     <row r="854" spans="1:6">
       <c r="A854" s="6">
-        <v>44562</v>
+        <v>44593</v>
       </c>
       <c r="B854" s="7" t="inlineStr">
         <is>
@@ -22542,7 +22316,7 @@
         </is>
       </c>
       <c r="D854" s="7">
-        <v>0.5</v>
+        <v>0.9</v>
       </c>
       <c r="E854" s="6"/>
       <c r="F854" s="7" t="inlineStr">
@@ -22553,7 +22327,7 @@
     </row>
     <row r="855" spans="1:6">
       <c r="A855" s="6">
-        <v>44593</v>
+        <v>44621</v>
       </c>
       <c r="B855" s="7" t="inlineStr">
         <is>
@@ -22566,7 +22340,7 @@
         </is>
       </c>
       <c r="D855" s="7">
-        <v>0.9</v>
+        <v>1.2</v>
       </c>
       <c r="E855" s="6"/>
       <c r="F855" s="7" t="inlineStr">
@@ -22577,7 +22351,7 @@
     </row>
     <row r="856" spans="1:6">
       <c r="A856" s="6">
-        <v>44621</v>
+        <v>44652</v>
       </c>
       <c r="B856" s="7" t="inlineStr">
         <is>
@@ -22590,7 +22364,7 @@
         </is>
       </c>
       <c r="D856" s="7">
-        <v>1.2</v>
+        <v>2.5</v>
       </c>
       <c r="E856" s="6"/>
       <c r="F856" s="7" t="inlineStr">
@@ -22601,7 +22375,7 @@
     </row>
     <row r="857" spans="1:6">
       <c r="A857" s="6">
-        <v>44652</v>
+        <v>44682</v>
       </c>
       <c r="B857" s="7" t="inlineStr">
         <is>
@@ -22625,7 +22399,7 @@
     </row>
     <row r="858" spans="1:6">
       <c r="A858" s="6">
-        <v>44682</v>
+        <v>44713</v>
       </c>
       <c r="B858" s="7" t="inlineStr">
         <is>
@@ -22638,7 +22412,7 @@
         </is>
       </c>
       <c r="D858" s="7">
-        <v>2.5</v>
+        <v>2.4</v>
       </c>
       <c r="E858" s="6"/>
       <c r="F858" s="7" t="inlineStr">
@@ -22649,7 +22423,7 @@
     </row>
     <row r="859" spans="1:6">
       <c r="A859" s="6">
-        <v>44713</v>
+        <v>44743</v>
       </c>
       <c r="B859" s="7" t="inlineStr">
         <is>
@@ -22662,7 +22436,7 @@
         </is>
       </c>
       <c r="D859" s="7">
-        <v>2.4</v>
+        <v>2.6</v>
       </c>
       <c r="E859" s="6"/>
       <c r="F859" s="7" t="inlineStr">
@@ -22673,7 +22447,7 @@
     </row>
     <row r="860" spans="1:6">
       <c r="A860" s="6">
-        <v>44743</v>
+        <v>44774</v>
       </c>
       <c r="B860" s="7" t="inlineStr">
         <is>
@@ -22686,7 +22460,7 @@
         </is>
       </c>
       <c r="D860" s="7">
-        <v>2.6</v>
+        <v>3.0</v>
       </c>
       <c r="E860" s="6"/>
       <c r="F860" s="7" t="inlineStr">
@@ -22697,7 +22471,7 @@
     </row>
     <row r="861" spans="1:6">
       <c r="A861" s="6">
-        <v>44774</v>
+        <v>44805</v>
       </c>
       <c r="B861" s="7" t="inlineStr">
         <is>
@@ -22721,7 +22495,7 @@
     </row>
     <row r="862" spans="1:6">
       <c r="A862" s="6">
-        <v>44805</v>
+        <v>44835</v>
       </c>
       <c r="B862" s="7" t="inlineStr">
         <is>
@@ -22734,7 +22508,7 @@
         </is>
       </c>
       <c r="D862" s="7">
-        <v>3.0</v>
+        <v>3.7</v>
       </c>
       <c r="E862" s="6"/>
       <c r="F862" s="7" t="inlineStr">
@@ -22745,7 +22519,7 @@
     </row>
     <row r="863" spans="1:6">
       <c r="A863" s="6">
-        <v>44835</v>
+        <v>44866</v>
       </c>
       <c r="B863" s="7" t="inlineStr">
         <is>
@@ -22758,7 +22532,7 @@
         </is>
       </c>
       <c r="D863" s="7">
-        <v>3.7</v>
+        <v>3.8</v>
       </c>
       <c r="E863" s="6"/>
       <c r="F863" s="7" t="inlineStr">
@@ -22769,7 +22543,7 @@
     </row>
     <row r="864" spans="1:6">
       <c r="A864" s="6">
-        <v>44866</v>
+        <v>44896</v>
       </c>
       <c r="B864" s="7" t="inlineStr">
         <is>
@@ -22782,7 +22556,7 @@
         </is>
       </c>
       <c r="D864" s="7">
-        <v>3.8</v>
+        <v>4.0</v>
       </c>
       <c r="E864" s="6"/>
       <c r="F864" s="7" t="inlineStr">
@@ -22793,7 +22567,7 @@
     </row>
     <row r="865" spans="1:6">
       <c r="A865" s="6">
-        <v>44896</v>
+        <v>44927</v>
       </c>
       <c r="B865" s="7" t="inlineStr">
         <is>
@@ -22806,7 +22580,7 @@
         </is>
       </c>
       <c r="D865" s="7">
-        <v>4.0</v>
+        <v>4.3</v>
       </c>
       <c r="E865" s="6"/>
       <c r="F865" s="7" t="inlineStr">
@@ -22817,7 +22591,7 @@
     </row>
     <row r="866" spans="1:6">
       <c r="A866" s="6">
-        <v>44927</v>
+        <v>44958</v>
       </c>
       <c r="B866" s="7" t="inlineStr">
         <is>
@@ -22830,7 +22604,7 @@
         </is>
       </c>
       <c r="D866" s="7">
-        <v>4.3</v>
+        <v>3.3</v>
       </c>
       <c r="E866" s="6"/>
       <c r="F866" s="7" t="inlineStr">
@@ -22841,7 +22615,7 @@
     </row>
     <row r="867" spans="1:6">
       <c r="A867" s="6">
-        <v>44958</v>
+        <v>44986</v>
       </c>
       <c r="B867" s="7" t="inlineStr">
         <is>
@@ -22854,7 +22628,7 @@
         </is>
       </c>
       <c r="D867" s="7">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="E867" s="6"/>
       <c r="F867" s="7" t="inlineStr">
@@ -22865,7 +22639,7 @@
     </row>
     <row r="868" spans="1:6">
       <c r="A868" s="6">
-        <v>44986</v>
+        <v>45017</v>
       </c>
       <c r="B868" s="7" t="inlineStr">
         <is>
@@ -22878,7 +22652,7 @@
         </is>
       </c>
       <c r="D868" s="7">
-        <v>3.2</v>
+        <v>3.5</v>
       </c>
       <c r="E868" s="6"/>
       <c r="F868" s="7" t="inlineStr">
@@ -22889,7 +22663,7 @@
     </row>
     <row r="869" spans="1:6">
       <c r="A869" s="6">
-        <v>45017</v>
+        <v>45047</v>
       </c>
       <c r="B869" s="7" t="inlineStr">
         <is>
@@ -22902,7 +22676,7 @@
         </is>
       </c>
       <c r="D869" s="7">
-        <v>3.5</v>
+        <v>3.2</v>
       </c>
       <c r="E869" s="6"/>
       <c r="F869" s="7" t="inlineStr">
@@ -22913,7 +22687,7 @@
     </row>
     <row r="870" spans="1:6">
       <c r="A870" s="6">
-        <v>45047</v>
+        <v>45078</v>
       </c>
       <c r="B870" s="7" t="inlineStr">
         <is>
@@ -22926,7 +22700,7 @@
         </is>
       </c>
       <c r="D870" s="7">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="E870" s="6"/>
       <c r="F870" s="7" t="inlineStr">
@@ -22937,7 +22711,7 @@
     </row>
     <row r="871" spans="1:6">
       <c r="A871" s="6">
-        <v>45078</v>
+        <v>45108</v>
       </c>
       <c r="B871" s="7" t="inlineStr">
         <is>
@@ -22961,7 +22735,7 @@
     </row>
     <row r="872" spans="1:6">
       <c r="A872" s="6">
-        <v>45108</v>
+        <v>45139</v>
       </c>
       <c r="B872" s="7" t="inlineStr">
         <is>
@@ -22974,7 +22748,7 @@
         </is>
       </c>
       <c r="D872" s="7">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="E872" s="6"/>
       <c r="F872" s="7" t="inlineStr">
@@ -22985,7 +22759,7 @@
     </row>
     <row r="873" spans="1:6">
       <c r="A873" s="6">
-        <v>45139</v>
+        <v>45170</v>
       </c>
       <c r="B873" s="7" t="inlineStr">
         <is>
@@ -22998,7 +22772,7 @@
         </is>
       </c>
       <c r="D873" s="7">
-        <v>3.2</v>
+        <v>3.0</v>
       </c>
       <c r="E873" s="6"/>
       <c r="F873" s="7" t="inlineStr">
@@ -23009,7 +22783,7 @@
     </row>
     <row r="874" spans="1:6">
       <c r="A874" s="6">
-        <v>45170</v>
+        <v>45200</v>
       </c>
       <c r="B874" s="7" t="inlineStr">
         <is>
@@ -23022,7 +22796,7 @@
         </is>
       </c>
       <c r="D874" s="7">
-        <v>3.0</v>
+        <v>3.3</v>
       </c>
       <c r="E874" s="6"/>
       <c r="F874" s="7" t="inlineStr">
@@ -23033,7 +22807,7 @@
     </row>
     <row r="875" spans="1:6">
       <c r="A875" s="6">
-        <v>45200</v>
+        <v>45231</v>
       </c>
       <c r="B875" s="7" t="inlineStr">
         <is>
@@ -23046,7 +22820,7 @@
         </is>
       </c>
       <c r="D875" s="7">
-        <v>3.3</v>
+        <v>2.8</v>
       </c>
       <c r="E875" s="6"/>
       <c r="F875" s="7" t="inlineStr">
@@ -23057,7 +22831,7 @@
     </row>
     <row r="876" spans="1:6">
       <c r="A876" s="6">
-        <v>45231</v>
+        <v>45261</v>
       </c>
       <c r="B876" s="7" t="inlineStr">
         <is>
@@ -23070,7 +22844,7 @@
         </is>
       </c>
       <c r="D876" s="7">
-        <v>2.8</v>
+        <v>2.6</v>
       </c>
       <c r="E876" s="6"/>
       <c r="F876" s="7" t="inlineStr">
@@ -23081,7 +22855,7 @@
     </row>
     <row r="877" spans="1:6">
       <c r="A877" s="6">
-        <v>45261</v>
+        <v>45292</v>
       </c>
       <c r="B877" s="7" t="inlineStr">
         <is>
@@ -23094,7 +22868,7 @@
         </is>
       </c>
       <c r="D877" s="7">
-        <v>2.6</v>
+        <v>2.2</v>
       </c>
       <c r="E877" s="6"/>
       <c r="F877" s="7" t="inlineStr">
@@ -23105,7 +22879,7 @@
     </row>
     <row r="878" spans="1:6">
       <c r="A878" s="6">
-        <v>45292</v>
+        <v>45323</v>
       </c>
       <c r="B878" s="7" t="inlineStr">
         <is>
@@ -23118,7 +22892,7 @@
         </is>
       </c>
       <c r="D878" s="7">
-        <v>2.2</v>
+        <v>2.8</v>
       </c>
       <c r="E878" s="6"/>
       <c r="F878" s="7" t="inlineStr">
@@ -23129,7 +22903,7 @@
     </row>
     <row r="879" spans="1:6">
       <c r="A879" s="6">
-        <v>45323</v>
+        <v>45352</v>
       </c>
       <c r="B879" s="7" t="inlineStr">
         <is>
@@ -23142,7 +22916,7 @@
         </is>
       </c>
       <c r="D879" s="7">
-        <v>2.8</v>
+        <v>2.7</v>
       </c>
       <c r="E879" s="6"/>
       <c r="F879" s="7" t="inlineStr">
@@ -23153,7 +22927,7 @@
     </row>
     <row r="880" spans="1:6">
       <c r="A880" s="6">
-        <v>45352</v>
+        <v>45383</v>
       </c>
       <c r="B880" s="7" t="inlineStr">
         <is>
@@ -23166,7 +22940,7 @@
         </is>
       </c>
       <c r="D880" s="7">
-        <v>2.7</v>
+        <v>2.5</v>
       </c>
       <c r="E880" s="6"/>
       <c r="F880" s="7" t="inlineStr">
@@ -23177,7 +22951,7 @@
     </row>
     <row r="881" spans="1:6">
       <c r="A881" s="6">
-        <v>45383</v>
+        <v>45413</v>
       </c>
       <c r="B881" s="7" t="inlineStr">
         <is>
@@ -23190,7 +22964,7 @@
         </is>
       </c>
       <c r="D881" s="7">
-        <v>2.5</v>
+        <v>2.8</v>
       </c>
       <c r="E881" s="6"/>
       <c r="F881" s="7" t="inlineStr">
@@ -23201,7 +22975,7 @@
     </row>
     <row r="882" spans="1:6">
       <c r="A882" s="6">
-        <v>45413</v>
+        <v>45444</v>
       </c>
       <c r="B882" s="7" t="inlineStr">
         <is>
@@ -23225,7 +22999,7 @@
     </row>
     <row r="883" spans="1:6">
       <c r="A883" s="6">
-        <v>45444</v>
+        <v>45474</v>
       </c>
       <c r="B883" s="7" t="inlineStr">
         <is>
@@ -23249,7 +23023,7 @@
     </row>
     <row r="884" spans="1:6">
       <c r="A884" s="6">
-        <v>45474</v>
+        <v>45505</v>
       </c>
       <c r="B884" s="7" t="inlineStr">
         <is>
@@ -23262,7 +23036,7 @@
         </is>
       </c>
       <c r="D884" s="7">
-        <v>2.8</v>
+        <v>3.0</v>
       </c>
       <c r="E884" s="6"/>
       <c r="F884" s="7" t="inlineStr">
@@ -23273,7 +23047,7 @@
     </row>
     <row r="885" spans="1:6">
       <c r="A885" s="6">
-        <v>45505</v>
+        <v>45536</v>
       </c>
       <c r="B885" s="7" t="inlineStr">
         <is>
@@ -23286,7 +23060,7 @@
         </is>
       </c>
       <c r="D885" s="7">
-        <v>3.0</v>
+        <v>2.5</v>
       </c>
       <c r="E885" s="6"/>
       <c r="F885" s="7" t="inlineStr">
@@ -23297,7 +23071,7 @@
     </row>
     <row r="886" spans="1:6">
       <c r="A886" s="6">
-        <v>45536</v>
+        <v>45566</v>
       </c>
       <c r="B886" s="7" t="inlineStr">
         <is>
@@ -23310,7 +23084,7 @@
         </is>
       </c>
       <c r="D886" s="7">
-        <v>2.5</v>
+        <v>2.3</v>
       </c>
       <c r="E886" s="6"/>
       <c r="F886" s="7" t="inlineStr">
@@ -23321,7 +23095,7 @@
     </row>
     <row r="887" spans="1:6">
       <c r="A887" s="6">
-        <v>45566</v>
+        <v>45597</v>
       </c>
       <c r="B887" s="7" t="inlineStr">
         <is>
@@ -23334,7 +23108,7 @@
         </is>
       </c>
       <c r="D887" s="7">
-        <v>2.3</v>
+        <v>2.9</v>
       </c>
       <c r="E887" s="6"/>
       <c r="F887" s="7" t="inlineStr">
@@ -23345,7 +23119,7 @@
     </row>
     <row r="888" spans="1:6">
       <c r="A888" s="6">
-        <v>45597</v>
+        <v>45627</v>
       </c>
       <c r="B888" s="7" t="inlineStr">
         <is>
@@ -23358,7 +23132,7 @@
         </is>
       </c>
       <c r="D888" s="7">
-        <v>2.9</v>
+        <v>3.6</v>
       </c>
       <c r="E888" s="6"/>
       <c r="F888" s="7" t="inlineStr">
@@ -23369,7 +23143,7 @@
     </row>
     <row r="889" spans="1:6">
       <c r="A889" s="6">
-        <v>45627</v>
+        <v>45658</v>
       </c>
       <c r="B889" s="7" t="inlineStr">
         <is>
@@ -23382,7 +23156,7 @@
         </is>
       </c>
       <c r="D889" s="7">
-        <v>3.6</v>
+        <v>4.0</v>
       </c>
       <c r="E889" s="6"/>
       <c r="F889" s="7" t="inlineStr">
@@ -23393,7 +23167,7 @@
     </row>
     <row r="890" spans="1:6">
       <c r="A890" s="6">
-        <v>45658</v>
+        <v>45689</v>
       </c>
       <c r="B890" s="7" t="inlineStr">
         <is>
@@ -23406,7 +23180,7 @@
         </is>
       </c>
       <c r="D890" s="7">
-        <v>4.0</v>
+        <v>3.7</v>
       </c>
       <c r="E890" s="6"/>
       <c r="F890" s="7" t="inlineStr">
@@ -23417,7 +23191,7 @@
     </row>
     <row r="891" spans="1:6">
       <c r="A891" s="6">
-        <v>45689</v>
+        <v>45717</v>
       </c>
       <c r="B891" s="7" t="inlineStr">
         <is>
@@ -23430,7 +23204,7 @@
         </is>
       </c>
       <c r="D891" s="7">
-        <v>3.7</v>
+        <v>3.6</v>
       </c>
       <c r="E891" s="6"/>
       <c r="F891" s="7" t="inlineStr">
@@ -23441,7 +23215,7 @@
     </row>
     <row r="892" spans="1:6">
       <c r="A892" s="6">
-        <v>45717</v>
+        <v>45748</v>
       </c>
       <c r="B892" s="7" t="inlineStr">
         <is>
@@ -23465,7 +23239,7 @@
     </row>
     <row r="893" spans="1:6">
       <c r="A893" s="6">
-        <v>45748</v>
+        <v>45778</v>
       </c>
       <c r="B893" s="7" t="inlineStr">
         <is>
@@ -23478,7 +23252,7 @@
         </is>
       </c>
       <c r="D893" s="7">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="E893" s="6"/>
       <c r="F893" s="7" t="inlineStr">
@@ -23489,7 +23263,7 @@
     </row>
     <row r="894" spans="1:6">
       <c r="A894" s="6">
-        <v>45778</v>
+        <v>45809</v>
       </c>
       <c r="B894" s="7" t="inlineStr">
         <is>
@@ -23502,7 +23276,7 @@
         </is>
       </c>
       <c r="D894" s="7">
-        <v>3.5</v>
+        <v>3.3</v>
       </c>
       <c r="E894" s="6"/>
       <c r="F894" s="7" t="inlineStr">
@@ -23513,7 +23287,7 @@
     </row>
     <row r="895" spans="1:6">
       <c r="A895" s="6">
-        <v>45809</v>
+        <v>45839</v>
       </c>
       <c r="B895" s="7" t="inlineStr">
         <is>
@@ -23526,7 +23300,7 @@
         </is>
       </c>
       <c r="D895" s="7">
-        <v>3.3</v>
+        <v>3.1</v>
       </c>
       <c r="E895" s="6"/>
       <c r="F895" s="7" t="inlineStr">
@@ -23537,7 +23311,7 @@
     </row>
     <row r="896" spans="1:6">
       <c r="A896" s="6">
-        <v>45839</v>
+        <v>45870</v>
       </c>
       <c r="B896" s="7" t="inlineStr">
         <is>
@@ -23550,7 +23324,7 @@
         </is>
       </c>
       <c r="D896" s="7">
-        <v>3.1</v>
+        <v>2.7</v>
       </c>
       <c r="E896" s="6"/>
       <c r="F896" s="7" t="inlineStr">
@@ -23561,7 +23335,7 @@
     </row>
     <row r="897" spans="1:6">
       <c r="A897" s="6">
-        <v>45870</v>
+        <v>45901</v>
       </c>
       <c r="B897" s="7" t="inlineStr">
         <is>
@@ -23574,7 +23348,7 @@
         </is>
       </c>
       <c r="D897" s="7">
-        <v>2.7</v>
+        <v>2.9</v>
       </c>
       <c r="E897" s="6"/>
       <c r="F897" s="7" t="inlineStr">
@@ -23585,7 +23359,7 @@
     </row>
     <row r="898" spans="1:6">
       <c r="A898" s="6">
-        <v>45901</v>
+        <v>45931</v>
       </c>
       <c r="B898" s="7" t="inlineStr">
         <is>
@@ -23598,7 +23372,7 @@
         </is>
       </c>
       <c r="D898" s="7">
-        <v>2.9</v>
+        <v>3.0</v>
       </c>
       <c r="E898" s="6"/>
       <c r="F898" s="7" t="inlineStr">
@@ -23609,7 +23383,7 @@
     </row>
     <row r="899" spans="1:6">
       <c r="A899" s="6">
-        <v>45931</v>
+        <v>45962</v>
       </c>
       <c r="B899" s="7" t="inlineStr">
         <is>
@@ -23622,7 +23396,7 @@
         </is>
       </c>
       <c r="D899" s="7">
-        <v>3.0</v>
+        <v>2.9</v>
       </c>
       <c r="E899" s="6"/>
       <c r="F899" s="7" t="inlineStr">
@@ -23633,7 +23407,7 @@
     </row>
     <row r="900" spans="1:6">
       <c r="A900" s="6">
-        <v>45962</v>
+        <v>45992</v>
       </c>
       <c r="B900" s="7" t="inlineStr">
         <is>
@@ -23646,7 +23420,7 @@
         </is>
       </c>
       <c r="D900" s="7">
-        <v>2.9</v>
+        <v>2.1</v>
       </c>
       <c r="E900" s="6"/>
       <c r="F900" s="7" t="inlineStr">
@@ -23657,7 +23431,7 @@
     </row>
     <row r="901" spans="1:6">
       <c r="A901" s="6">
-        <v>45992</v>
+        <v>46023</v>
       </c>
       <c r="B901" s="7" t="inlineStr">
         <is>
@@ -23670,7 +23444,7 @@
         </is>
       </c>
       <c r="D901" s="7">
-        <v>2.1</v>
+        <v>1.5</v>
       </c>
       <c r="E901" s="6"/>
       <c r="F901" s="7" t="inlineStr">
@@ -23681,7 +23455,7 @@
     </row>
     <row r="902" spans="1:6">
       <c r="A902" s="6">
-        <v>46023</v>
+        <v>46054</v>
       </c>
       <c r="B902" s="7" t="inlineStr">
         <is>
@@ -23694,7 +23468,7 @@
         </is>
       </c>
       <c r="D902" s="7">
-        <v>1.5</v>
+        <v>1.3</v>
       </c>
       <c r="E902" s="6"/>
       <c r="F902" s="7" t="inlineStr">
@@ -23705,7 +23479,7 @@
     </row>
     <row r="903" spans="1:6">
       <c r="A903" s="6">
-        <v>46054</v>
+        <v>46082</v>
       </c>
       <c r="B903" s="7" t="inlineStr">
         <is>
@@ -23718,7 +23492,7 @@
         </is>
       </c>
       <c r="D903" s="7">
-        <v>1.3</v>
+        <v>1.5</v>
       </c>
       <c r="E903" s="6"/>
       <c r="F903" s="7" t="inlineStr">
@@ -23729,7 +23503,7 @@
     </row>
     <row r="904" spans="1:6">
       <c r="A904" s="6">
-        <v>46082</v>
+        <v>46113</v>
       </c>
       <c r="B904" s="7" t="inlineStr">
         <is>
@@ -23742,7 +23516,7 @@
         </is>
       </c>
       <c r="D904" s="7">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="E904" s="6"/>
       <c r="F904" s="7" t="inlineStr">
@@ -23753,7 +23527,7 @@
     </row>
     <row r="905" spans="1:6">
       <c r="A905" s="6">
-        <v>46113</v>
+        <v>46143</v>
       </c>
       <c r="B905" s="7" t="inlineStr">
         <is>
@@ -23766,7 +23540,7 @@
         </is>
       </c>
       <c r="D905" s="7">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
       <c r="E905" s="6"/>
       <c r="F905" s="7" t="inlineStr">
@@ -23777,7 +23551,7 @@
     </row>
     <row r="906" spans="1:6">
       <c r="A906" s="6">
-        <v>46143</v>
+        <v>46174</v>
       </c>
       <c r="B906" s="7" t="inlineStr">
         <is>
@@ -23790,7 +23564,7 @@
         </is>
       </c>
       <c r="D906" s="7">
-        <v>1.5</v>
+        <v>1.6</v>
       </c>
       <c r="E906" s="6"/>
       <c r="F906" s="7" t="inlineStr">
@@ -23801,7 +23575,7 @@
     </row>
     <row r="907" spans="1:6">
       <c r="A907" s="6">
-        <v>46174</v>
+        <v>46204</v>
       </c>
       <c r="B907" s="7" t="inlineStr">
         <is>
@@ -23814,7 +23588,7 @@
         </is>
       </c>
       <c r="D907" s="7">
-        <v>1.6</v>
+        <v>1.9</v>
       </c>
       <c r="E907" s="6"/>
       <c r="F907" s="7" t="inlineStr">
@@ -23825,7 +23599,7 @@
     </row>
     <row r="908" spans="1:6">
       <c r="A908" s="6">
-        <v>46204</v>
+        <v>44440</v>
       </c>
       <c r="B908" s="7" t="inlineStr">
         <is>
@@ -23834,11 +23608,11 @@
       </c>
       <c r="C908" s="7" t="inlineStr">
         <is>
-          <t>CPI 헤드라인</t>
+          <t>CPI 근원</t>
         </is>
       </c>
       <c r="D908" s="7">
-        <v>1.9</v>
+        <v>0.1</v>
       </c>
       <c r="E908" s="6"/>
       <c r="F908" s="7" t="inlineStr">
@@ -23849,7 +23623,7 @@
     </row>
     <row r="909" spans="1:6">
       <c r="A909" s="6">
-        <v>44440</v>
+        <v>44470</v>
       </c>
       <c r="B909" s="7" t="inlineStr">
         <is>
@@ -23873,7 +23647,7 @@
     </row>
     <row r="910" spans="1:6">
       <c r="A910" s="6">
-        <v>44470</v>
+        <v>44501</v>
       </c>
       <c r="B910" s="7" t="inlineStr">
         <is>
@@ -23886,7 +23660,7 @@
         </is>
       </c>
       <c r="D910" s="7">
-        <v>0.1</v>
+        <v>0.5</v>
       </c>
       <c r="E910" s="6"/>
       <c r="F910" s="7" t="inlineStr">
@@ -23897,7 +23671,7 @@
     </row>
     <row r="911" spans="1:6">
       <c r="A911" s="6">
-        <v>44501</v>
+        <v>44531</v>
       </c>
       <c r="B911" s="7" t="inlineStr">
         <is>
@@ -23921,7 +23695,7 @@
     </row>
     <row r="912" spans="1:6">
       <c r="A912" s="6">
-        <v>44531</v>
+        <v>44562</v>
       </c>
       <c r="B912" s="7" t="inlineStr">
         <is>
@@ -23934,7 +23708,7 @@
         </is>
       </c>
       <c r="D912" s="7">
-        <v>0.5</v>
+        <v>0.2</v>
       </c>
       <c r="E912" s="6"/>
       <c r="F912" s="7" t="inlineStr">
@@ -23945,7 +23719,7 @@
     </row>
     <row r="913" spans="1:6">
       <c r="A913" s="6">
-        <v>44562</v>
+        <v>44593</v>
       </c>
       <c r="B913" s="7" t="inlineStr">
         <is>
@@ -23958,7 +23732,7 @@
         </is>
       </c>
       <c r="D913" s="7">
-        <v>0.2</v>
+        <v>0.6</v>
       </c>
       <c r="E913" s="6"/>
       <c r="F913" s="7" t="inlineStr">
@@ -23969,7 +23743,7 @@
     </row>
     <row r="914" spans="1:6">
       <c r="A914" s="6">
-        <v>44593</v>
+        <v>44621</v>
       </c>
       <c r="B914" s="7" t="inlineStr">
         <is>
@@ -23982,7 +23756,7 @@
         </is>
       </c>
       <c r="D914" s="7">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="E914" s="6"/>
       <c r="F914" s="7" t="inlineStr">
@@ -23993,7 +23767,7 @@
     </row>
     <row r="915" spans="1:6">
       <c r="A915" s="6">
-        <v>44621</v>
+        <v>44652</v>
       </c>
       <c r="B915" s="7" t="inlineStr">
         <is>
@@ -24006,7 +23780,7 @@
         </is>
       </c>
       <c r="D915" s="7">
-        <v>0.8</v>
+        <v>2.1</v>
       </c>
       <c r="E915" s="6"/>
       <c r="F915" s="7" t="inlineStr">
@@ -24017,7 +23791,7 @@
     </row>
     <row r="916" spans="1:6">
       <c r="A916" s="6">
-        <v>44652</v>
+        <v>44682</v>
       </c>
       <c r="B916" s="7" t="inlineStr">
         <is>
@@ -24041,7 +23815,7 @@
     </row>
     <row r="917" spans="1:6">
       <c r="A917" s="6">
-        <v>44682</v>
+        <v>44713</v>
       </c>
       <c r="B917" s="7" t="inlineStr">
         <is>
@@ -24054,7 +23828,7 @@
         </is>
       </c>
       <c r="D917" s="7">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="E917" s="6"/>
       <c r="F917" s="7" t="inlineStr">
@@ -24065,7 +23839,7 @@
     </row>
     <row r="918" spans="1:6">
       <c r="A918" s="6">
-        <v>44713</v>
+        <v>44743</v>
       </c>
       <c r="B918" s="7" t="inlineStr">
         <is>
@@ -24078,7 +23852,7 @@
         </is>
       </c>
       <c r="D918" s="7">
-        <v>2.2</v>
+        <v>2.4</v>
       </c>
       <c r="E918" s="6"/>
       <c r="F918" s="7" t="inlineStr">
@@ -24089,7 +23863,7 @@
     </row>
     <row r="919" spans="1:6">
       <c r="A919" s="6">
-        <v>44743</v>
+        <v>44774</v>
       </c>
       <c r="B919" s="7" t="inlineStr">
         <is>
@@ -24102,7 +23876,7 @@
         </is>
       </c>
       <c r="D919" s="7">
-        <v>2.4</v>
+        <v>2.8</v>
       </c>
       <c r="E919" s="6"/>
       <c r="F919" s="7" t="inlineStr">
@@ -24113,7 +23887,7 @@
     </row>
     <row r="920" spans="1:6">
       <c r="A920" s="6">
-        <v>44774</v>
+        <v>44805</v>
       </c>
       <c r="B920" s="7" t="inlineStr">
         <is>
@@ -24126,7 +23900,7 @@
         </is>
       </c>
       <c r="D920" s="7">
-        <v>2.8</v>
+        <v>3.0</v>
       </c>
       <c r="E920" s="6"/>
       <c r="F920" s="7" t="inlineStr">
@@ -24137,7 +23911,7 @@
     </row>
     <row r="921" spans="1:6">
       <c r="A921" s="6">
-        <v>44805</v>
+        <v>44835</v>
       </c>
       <c r="B921" s="7" t="inlineStr">
         <is>
@@ -24150,7 +23924,7 @@
         </is>
       </c>
       <c r="D921" s="7">
-        <v>3.0</v>
+        <v>3.6</v>
       </c>
       <c r="E921" s="6"/>
       <c r="F921" s="7" t="inlineStr">
@@ -24161,7 +23935,7 @@
     </row>
     <row r="922" spans="1:6">
       <c r="A922" s="6">
-        <v>44835</v>
+        <v>44866</v>
       </c>
       <c r="B922" s="7" t="inlineStr">
         <is>
@@ -24174,7 +23948,7 @@
         </is>
       </c>
       <c r="D922" s="7">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="E922" s="6"/>
       <c r="F922" s="7" t="inlineStr">
@@ -24185,7 +23959,7 @@
     </row>
     <row r="923" spans="1:6">
       <c r="A923" s="6">
-        <v>44866</v>
+        <v>44896</v>
       </c>
       <c r="B923" s="7" t="inlineStr">
         <is>
@@ -24198,7 +23972,7 @@
         </is>
       </c>
       <c r="D923" s="7">
-        <v>3.7</v>
+        <v>4.0</v>
       </c>
       <c r="E923" s="6"/>
       <c r="F923" s="7" t="inlineStr">
@@ -24209,7 +23983,7 @@
     </row>
     <row r="924" spans="1:6">
       <c r="A924" s="6">
-        <v>44896</v>
+        <v>44927</v>
       </c>
       <c r="B924" s="7" t="inlineStr">
         <is>
@@ -24222,7 +23996,7 @@
         </is>
       </c>
       <c r="D924" s="7">
-        <v>4.0</v>
+        <v>4.2</v>
       </c>
       <c r="E924" s="6"/>
       <c r="F924" s="7" t="inlineStr">
@@ -24233,7 +24007,7 @@
     </row>
     <row r="925" spans="1:6">
       <c r="A925" s="6">
-        <v>44927</v>
+        <v>44958</v>
       </c>
       <c r="B925" s="7" t="inlineStr">
         <is>
@@ -24246,7 +24020,7 @@
         </is>
       </c>
       <c r="D925" s="7">
-        <v>4.2</v>
+        <v>3.1</v>
       </c>
       <c r="E925" s="6"/>
       <c r="F925" s="7" t="inlineStr">
@@ -24257,7 +24031,7 @@
     </row>
     <row r="926" spans="1:6">
       <c r="A926" s="6">
-        <v>44958</v>
+        <v>44986</v>
       </c>
       <c r="B926" s="7" t="inlineStr">
         <is>
@@ -24281,7 +24055,7 @@
     </row>
     <row r="927" spans="1:6">
       <c r="A927" s="6">
-        <v>44986</v>
+        <v>45017</v>
       </c>
       <c r="B927" s="7" t="inlineStr">
         <is>
@@ -24294,7 +24068,7 @@
         </is>
       </c>
       <c r="D927" s="7">
-        <v>3.1</v>
+        <v>3.4</v>
       </c>
       <c r="E927" s="6"/>
       <c r="F927" s="7" t="inlineStr">
@@ -24305,7 +24079,7 @@
     </row>
     <row r="928" spans="1:6">
       <c r="A928" s="6">
-        <v>45017</v>
+        <v>45047</v>
       </c>
       <c r="B928" s="7" t="inlineStr">
         <is>
@@ -24318,7 +24092,7 @@
         </is>
       </c>
       <c r="D928" s="7">
-        <v>3.4</v>
+        <v>3.2</v>
       </c>
       <c r="E928" s="6"/>
       <c r="F928" s="7" t="inlineStr">
@@ -24329,7 +24103,7 @@
     </row>
     <row r="929" spans="1:6">
       <c r="A929" s="6">
-        <v>45047</v>
+        <v>45078</v>
       </c>
       <c r="B929" s="7" t="inlineStr">
         <is>
@@ -24342,7 +24116,7 @@
         </is>
       </c>
       <c r="D929" s="7">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="E929" s="6"/>
       <c r="F929" s="7" t="inlineStr">
@@ -24353,7 +24127,7 @@
     </row>
     <row r="930" spans="1:6">
       <c r="A930" s="6">
-        <v>45078</v>
+        <v>45108</v>
       </c>
       <c r="B930" s="7" t="inlineStr">
         <is>
@@ -24366,7 +24140,7 @@
         </is>
       </c>
       <c r="D930" s="7">
-        <v>3.3</v>
+        <v>3.1</v>
       </c>
       <c r="E930" s="6"/>
       <c r="F930" s="7" t="inlineStr">
@@ -24377,7 +24151,7 @@
     </row>
     <row r="931" spans="1:6">
       <c r="A931" s="6">
-        <v>45108</v>
+        <v>45139</v>
       </c>
       <c r="B931" s="7" t="inlineStr">
         <is>
@@ -24401,7 +24175,7 @@
     </row>
     <row r="932" spans="1:6">
       <c r="A932" s="6">
-        <v>45139</v>
+        <v>45170</v>
       </c>
       <c r="B932" s="7" t="inlineStr">
         <is>
@@ -24414,7 +24188,7 @@
         </is>
       </c>
       <c r="D932" s="7">
-        <v>3.1</v>
+        <v>2.8</v>
       </c>
       <c r="E932" s="6"/>
       <c r="F932" s="7" t="inlineStr">
@@ -24425,7 +24199,7 @@
     </row>
     <row r="933" spans="1:6">
       <c r="A933" s="6">
-        <v>45170</v>
+        <v>45200</v>
       </c>
       <c r="B933" s="7" t="inlineStr">
         <is>
@@ -24438,7 +24212,7 @@
         </is>
       </c>
       <c r="D933" s="7">
-        <v>2.8</v>
+        <v>2.9</v>
       </c>
       <c r="E933" s="6"/>
       <c r="F933" s="7" t="inlineStr">
@@ -24449,7 +24223,7 @@
     </row>
     <row r="934" spans="1:6">
       <c r="A934" s="6">
-        <v>45200</v>
+        <v>45231</v>
       </c>
       <c r="B934" s="7" t="inlineStr">
         <is>
@@ -24462,7 +24236,7 @@
         </is>
       </c>
       <c r="D934" s="7">
-        <v>2.9</v>
+        <v>2.5</v>
       </c>
       <c r="E934" s="6"/>
       <c r="F934" s="7" t="inlineStr">
@@ -24473,7 +24247,7 @@
     </row>
     <row r="935" spans="1:6">
       <c r="A935" s="6">
-        <v>45231</v>
+        <v>45261</v>
       </c>
       <c r="B935" s="7" t="inlineStr">
         <is>
@@ -24486,7 +24260,7 @@
         </is>
       </c>
       <c r="D935" s="7">
-        <v>2.5</v>
+        <v>2.3</v>
       </c>
       <c r="E935" s="6"/>
       <c r="F935" s="7" t="inlineStr">
@@ -24497,7 +24271,7 @@
     </row>
     <row r="936" spans="1:6">
       <c r="A936" s="6">
-        <v>45261</v>
+        <v>45292</v>
       </c>
       <c r="B936" s="7" t="inlineStr">
         <is>
@@ -24510,7 +24284,7 @@
         </is>
       </c>
       <c r="D936" s="7">
-        <v>2.3</v>
+        <v>2.0</v>
       </c>
       <c r="E936" s="6"/>
       <c r="F936" s="7" t="inlineStr">
@@ -24521,7 +24295,7 @@
     </row>
     <row r="937" spans="1:6">
       <c r="A937" s="6">
-        <v>45292</v>
+        <v>45323</v>
       </c>
       <c r="B937" s="7" t="inlineStr">
         <is>
@@ -24534,7 +24308,7 @@
         </is>
       </c>
       <c r="D937" s="7">
-        <v>2.0</v>
+        <v>2.8</v>
       </c>
       <c r="E937" s="6"/>
       <c r="F937" s="7" t="inlineStr">
@@ -24545,7 +24319,7 @@
     </row>
     <row r="938" spans="1:6">
       <c r="A938" s="6">
-        <v>45323</v>
+        <v>45352</v>
       </c>
       <c r="B938" s="7" t="inlineStr">
         <is>
@@ -24558,7 +24332,7 @@
         </is>
       </c>
       <c r="D938" s="7">
-        <v>2.8</v>
+        <v>2.6</v>
       </c>
       <c r="E938" s="6"/>
       <c r="F938" s="7" t="inlineStr">
@@ -24569,7 +24343,7 @@
     </row>
     <row r="939" spans="1:6">
       <c r="A939" s="6">
-        <v>45352</v>
+        <v>45383</v>
       </c>
       <c r="B939" s="7" t="inlineStr">
         <is>
@@ -24582,7 +24356,7 @@
         </is>
       </c>
       <c r="D939" s="7">
-        <v>2.6</v>
+        <v>2.2</v>
       </c>
       <c r="E939" s="6"/>
       <c r="F939" s="7" t="inlineStr">
@@ -24593,7 +24367,7 @@
     </row>
     <row r="940" spans="1:6">
       <c r="A940" s="6">
-        <v>45383</v>
+        <v>45413</v>
       </c>
       <c r="B940" s="7" t="inlineStr">
         <is>
@@ -24606,7 +24380,7 @@
         </is>
       </c>
       <c r="D940" s="7">
-        <v>2.2</v>
+        <v>2.5</v>
       </c>
       <c r="E940" s="6"/>
       <c r="F940" s="7" t="inlineStr">
@@ -24617,7 +24391,7 @@
     </row>
     <row r="941" spans="1:6">
       <c r="A941" s="6">
-        <v>45413</v>
+        <v>45444</v>
       </c>
       <c r="B941" s="7" t="inlineStr">
         <is>
@@ -24630,7 +24404,7 @@
         </is>
       </c>
       <c r="D941" s="7">
-        <v>2.5</v>
+        <v>2.6</v>
       </c>
       <c r="E941" s="6"/>
       <c r="F941" s="7" t="inlineStr">
@@ -24641,7 +24415,7 @@
     </row>
     <row r="942" spans="1:6">
       <c r="A942" s="6">
-        <v>45444</v>
+        <v>45474</v>
       </c>
       <c r="B942" s="7" t="inlineStr">
         <is>
@@ -24654,7 +24428,7 @@
         </is>
       </c>
       <c r="D942" s="7">
-        <v>2.6</v>
+        <v>2.7</v>
       </c>
       <c r="E942" s="6"/>
       <c r="F942" s="7" t="inlineStr">
@@ -24665,7 +24439,7 @@
     </row>
     <row r="943" spans="1:6">
       <c r="A943" s="6">
-        <v>45474</v>
+        <v>45505</v>
       </c>
       <c r="B943" s="7" t="inlineStr">
         <is>
@@ -24678,7 +24452,7 @@
         </is>
       </c>
       <c r="D943" s="7">
-        <v>2.7</v>
+        <v>2.8</v>
       </c>
       <c r="E943" s="6"/>
       <c r="F943" s="7" t="inlineStr">
@@ -24689,7 +24463,7 @@
     </row>
     <row r="944" spans="1:6">
       <c r="A944" s="6">
-        <v>45505</v>
+        <v>45536</v>
       </c>
       <c r="B944" s="7" t="inlineStr">
         <is>
@@ -24702,7 +24476,7 @@
         </is>
       </c>
       <c r="D944" s="7">
-        <v>2.8</v>
+        <v>2.4</v>
       </c>
       <c r="E944" s="6"/>
       <c r="F944" s="7" t="inlineStr">
@@ -24713,7 +24487,7 @@
     </row>
     <row r="945" spans="1:6">
       <c r="A945" s="6">
-        <v>45536</v>
+        <v>45566</v>
       </c>
       <c r="B945" s="7" t="inlineStr">
         <is>
@@ -24726,7 +24500,7 @@
         </is>
       </c>
       <c r="D945" s="7">
-        <v>2.4</v>
+        <v>2.3</v>
       </c>
       <c r="E945" s="6"/>
       <c r="F945" s="7" t="inlineStr">
@@ -24737,7 +24511,7 @@
     </row>
     <row r="946" spans="1:6">
       <c r="A946" s="6">
-        <v>45566</v>
+        <v>45597</v>
       </c>
       <c r="B946" s="7" t="inlineStr">
         <is>
@@ -24750,7 +24524,7 @@
         </is>
       </c>
       <c r="D946" s="7">
-        <v>2.3</v>
+        <v>2.7</v>
       </c>
       <c r="E946" s="6"/>
       <c r="F946" s="7" t="inlineStr">
@@ -24761,7 +24535,7 @@
     </row>
     <row r="947" spans="1:6">
       <c r="A947" s="6">
-        <v>45597</v>
+        <v>45627</v>
       </c>
       <c r="B947" s="7" t="inlineStr">
         <is>
@@ -24774,7 +24548,7 @@
         </is>
       </c>
       <c r="D947" s="7">
-        <v>2.7</v>
+        <v>3.0</v>
       </c>
       <c r="E947" s="6"/>
       <c r="F947" s="7" t="inlineStr">
@@ -24785,7 +24559,7 @@
     </row>
     <row r="948" spans="1:6">
       <c r="A948" s="6">
-        <v>45627</v>
+        <v>45658</v>
       </c>
       <c r="B948" s="7" t="inlineStr">
         <is>
@@ -24798,7 +24572,7 @@
         </is>
       </c>
       <c r="D948" s="7">
-        <v>3.0</v>
+        <v>3.2</v>
       </c>
       <c r="E948" s="6"/>
       <c r="F948" s="7" t="inlineStr">
@@ -24809,7 +24583,7 @@
     </row>
     <row r="949" spans="1:6">
       <c r="A949" s="6">
-        <v>45658</v>
+        <v>45689</v>
       </c>
       <c r="B949" s="7" t="inlineStr">
         <is>
@@ -24822,7 +24596,7 @@
         </is>
       </c>
       <c r="D949" s="7">
-        <v>3.2</v>
+        <v>3.0</v>
       </c>
       <c r="E949" s="6"/>
       <c r="F949" s="7" t="inlineStr">
@@ -24833,7 +24607,7 @@
     </row>
     <row r="950" spans="1:6">
       <c r="A950" s="6">
-        <v>45689</v>
+        <v>45717</v>
       </c>
       <c r="B950" s="7" t="inlineStr">
         <is>
@@ -24846,7 +24620,7 @@
         </is>
       </c>
       <c r="D950" s="7">
-        <v>3.0</v>
+        <v>3.2</v>
       </c>
       <c r="E950" s="6"/>
       <c r="F950" s="7" t="inlineStr">
@@ -24857,7 +24631,7 @@
     </row>
     <row r="951" spans="1:6">
       <c r="A951" s="6">
-        <v>45717</v>
+        <v>45748</v>
       </c>
       <c r="B951" s="7" t="inlineStr">
         <is>
@@ -24870,7 +24644,7 @@
         </is>
       </c>
       <c r="D951" s="7">
-        <v>3.2</v>
+        <v>3.5</v>
       </c>
       <c r="E951" s="6"/>
       <c r="F951" s="7" t="inlineStr">
@@ -24881,7 +24655,7 @@
     </row>
     <row r="952" spans="1:6">
       <c r="A952" s="6">
-        <v>45748</v>
+        <v>45778</v>
       </c>
       <c r="B952" s="7" t="inlineStr">
         <is>
@@ -24894,7 +24668,7 @@
         </is>
       </c>
       <c r="D952" s="7">
-        <v>3.5</v>
+        <v>3.7</v>
       </c>
       <c r="E952" s="6"/>
       <c r="F952" s="7" t="inlineStr">
@@ -24905,7 +24679,7 @@
     </row>
     <row r="953" spans="1:6">
       <c r="A953" s="6">
-        <v>45778</v>
+        <v>45809</v>
       </c>
       <c r="B953" s="7" t="inlineStr">
         <is>
@@ -24918,7 +24692,7 @@
         </is>
       </c>
       <c r="D953" s="7">
-        <v>3.7</v>
+        <v>3.3</v>
       </c>
       <c r="E953" s="6"/>
       <c r="F953" s="7" t="inlineStr">
@@ -24929,7 +24703,7 @@
     </row>
     <row r="954" spans="1:6">
       <c r="A954" s="6">
-        <v>45809</v>
+        <v>45839</v>
       </c>
       <c r="B954" s="7" t="inlineStr">
         <is>
@@ -24942,7 +24716,7 @@
         </is>
       </c>
       <c r="D954" s="7">
-        <v>3.3</v>
+        <v>3.1</v>
       </c>
       <c r="E954" s="6"/>
       <c r="F954" s="7" t="inlineStr">
@@ -24953,7 +24727,7 @@
     </row>
     <row r="955" spans="1:6">
       <c r="A955" s="6">
-        <v>45839</v>
+        <v>45870</v>
       </c>
       <c r="B955" s="7" t="inlineStr">
         <is>
@@ -24966,7 +24740,7 @@
         </is>
       </c>
       <c r="D955" s="7">
-        <v>3.1</v>
+        <v>2.7</v>
       </c>
       <c r="E955" s="6"/>
       <c r="F955" s="7" t="inlineStr">
@@ -24977,7 +24751,7 @@
     </row>
     <row r="956" spans="1:6">
       <c r="A956" s="6">
-        <v>45870</v>
+        <v>45901</v>
       </c>
       <c r="B956" s="7" t="inlineStr">
         <is>
@@ -24990,7 +24764,7 @@
         </is>
       </c>
       <c r="D956" s="7">
-        <v>2.7</v>
+        <v>2.9</v>
       </c>
       <c r="E956" s="6"/>
       <c r="F956" s="7" t="inlineStr">
@@ -25001,7 +24775,7 @@
     </row>
     <row r="957" spans="1:6">
       <c r="A957" s="6">
-        <v>45901</v>
+        <v>45931</v>
       </c>
       <c r="B957" s="7" t="inlineStr">
         <is>
@@ -25014,7 +24788,7 @@
         </is>
       </c>
       <c r="D957" s="7">
-        <v>2.9</v>
+        <v>3.0</v>
       </c>
       <c r="E957" s="6"/>
       <c r="F957" s="7" t="inlineStr">
@@ -25025,7 +24799,7 @@
     </row>
     <row r="958" spans="1:6">
       <c r="A958" s="6">
-        <v>45931</v>
+        <v>45962</v>
       </c>
       <c r="B958" s="7" t="inlineStr">
         <is>
@@ -25049,7 +24823,7 @@
     </row>
     <row r="959" spans="1:6">
       <c r="A959" s="6">
-        <v>45962</v>
+        <v>45992</v>
       </c>
       <c r="B959" s="7" t="inlineStr">
         <is>
@@ -25062,7 +24836,7 @@
         </is>
       </c>
       <c r="D959" s="7">
-        <v>3.0</v>
+        <v>2.4</v>
       </c>
       <c r="E959" s="6"/>
       <c r="F959" s="7" t="inlineStr">
@@ -25073,7 +24847,7 @@
     </row>
     <row r="960" spans="1:6">
       <c r="A960" s="6">
-        <v>45992</v>
+        <v>46023</v>
       </c>
       <c r="B960" s="7" t="inlineStr">
         <is>
@@ -25086,7 +24860,7 @@
         </is>
       </c>
       <c r="D960" s="7">
-        <v>2.4</v>
+        <v>1.9</v>
       </c>
       <c r="E960" s="6"/>
       <c r="F960" s="7" t="inlineStr">
@@ -25097,7 +24871,7 @@
     </row>
     <row r="961" spans="1:6">
       <c r="A961" s="6">
-        <v>46023</v>
+        <v>46054</v>
       </c>
       <c r="B961" s="7" t="inlineStr">
         <is>
@@ -25110,7 +24884,7 @@
         </is>
       </c>
       <c r="D961" s="7">
-        <v>1.9</v>
+        <v>1.5</v>
       </c>
       <c r="E961" s="6"/>
       <c r="F961" s="7" t="inlineStr">
@@ -25121,7 +24895,7 @@
     </row>
     <row r="962" spans="1:6">
       <c r="A962" s="6">
-        <v>46054</v>
+        <v>46082</v>
       </c>
       <c r="B962" s="7" t="inlineStr">
         <is>
@@ -25134,7 +24908,7 @@
         </is>
       </c>
       <c r="D962" s="7">
-        <v>1.5</v>
+        <v>1.7</v>
       </c>
       <c r="E962" s="6"/>
       <c r="F962" s="7" t="inlineStr">
@@ -25145,7 +24919,7 @@
     </row>
     <row r="963" spans="1:6">
       <c r="A963" s="6">
-        <v>46082</v>
+        <v>46113</v>
       </c>
       <c r="B963" s="7" t="inlineStr">
         <is>
@@ -25158,7 +24932,7 @@
         </is>
       </c>
       <c r="D963" s="7">
-        <v>1.7</v>
+        <v>1.4</v>
       </c>
       <c r="E963" s="6"/>
       <c r="F963" s="7" t="inlineStr">
@@ -25169,7 +24943,7 @@
     </row>
     <row r="964" spans="1:6">
       <c r="A964" s="6">
-        <v>46113</v>
+        <v>46143</v>
       </c>
       <c r="B964" s="7" t="inlineStr">
         <is>
@@ -25193,7 +24967,7 @@
     </row>
     <row r="965" spans="1:6">
       <c r="A965" s="6">
-        <v>46143</v>
+        <v>46174</v>
       </c>
       <c r="B965" s="7" t="inlineStr">
         <is>
@@ -25206,7 +24980,7 @@
         </is>
       </c>
       <c r="D965" s="7">
-        <v>1.4</v>
+        <v>1.6</v>
       </c>
       <c r="E965" s="6"/>
       <c r="F965" s="7" t="inlineStr">
@@ -25217,7 +24991,7 @@
     </row>
     <row r="966" spans="1:6">
       <c r="A966" s="6">
-        <v>46174</v>
+        <v>46204</v>
       </c>
       <c r="B966" s="7" t="inlineStr">
         <is>
@@ -25230,7 +25004,7 @@
         </is>
       </c>
       <c r="D966" s="7">
-        <v>1.6</v>
+        <v>1.8</v>
       </c>
       <c r="E966" s="6"/>
       <c r="F966" s="7" t="inlineStr">
@@ -25241,7 +25015,7 @@
     </row>
     <row r="967" spans="1:6">
       <c r="A967" s="6">
-        <v>46204</v>
+        <v>44440</v>
       </c>
       <c r="B967" s="7" t="inlineStr">
         <is>
@@ -25250,11 +25024,11 @@
       </c>
       <c r="C967" s="7" t="inlineStr">
         <is>
-          <t>CPI 근원</t>
+          <t>실업률</t>
         </is>
       </c>
       <c r="D967" s="7">
-        <v>1.8</v>
+        <v>2.7</v>
       </c>
       <c r="E967" s="6"/>
       <c r="F967" s="7" t="inlineStr">
@@ -25265,7 +25039,7 @@
     </row>
     <row r="968" spans="1:6">
       <c r="A968" s="6">
-        <v>44440</v>
+        <v>44470</v>
       </c>
       <c r="B968" s="7" t="inlineStr">
         <is>
@@ -25280,9 +25054,7 @@
       <c r="D968" s="7">
         <v>2.7</v>
       </c>
-      <c r="E968" s="6">
-        <v>44511</v>
-      </c>
+      <c r="E968" s="6"/>
       <c r="F968" s="7" t="inlineStr">
         <is>
           <t>월간</t>
@@ -25291,7 +25063,7 @@
     </row>
     <row r="969" spans="1:6">
       <c r="A969" s="6">
-        <v>44470</v>
+        <v>44501</v>
       </c>
       <c r="B969" s="7" t="inlineStr">
         <is>
@@ -25304,11 +25076,9 @@
         </is>
       </c>
       <c r="D969" s="7">
-        <v>2.7</v>
-      </c>
-      <c r="E969" s="6">
-        <v>44540</v>
-      </c>
+        <v>2.8</v>
+      </c>
+      <c r="E969" s="6"/>
       <c r="F969" s="7" t="inlineStr">
         <is>
           <t>월간</t>
@@ -25317,7 +25087,7 @@
     </row>
     <row r="970" spans="1:6">
       <c r="A970" s="6">
-        <v>44501</v>
+        <v>44531</v>
       </c>
       <c r="B970" s="7" t="inlineStr">
         <is>
@@ -25330,11 +25100,9 @@
         </is>
       </c>
       <c r="D970" s="7">
-        <v>2.8</v>
-      </c>
-      <c r="E970" s="6">
-        <v>44579</v>
-      </c>
+        <v>2.7</v>
+      </c>
+      <c r="E970" s="6"/>
       <c r="F970" s="7" t="inlineStr">
         <is>
           <t>월간</t>
@@ -25343,7 +25111,7 @@
     </row>
     <row r="971" spans="1:6">
       <c r="A971" s="6">
-        <v>44531</v>
+        <v>44562</v>
       </c>
       <c r="B971" s="7" t="inlineStr">
         <is>
@@ -25356,11 +25124,9 @@
         </is>
       </c>
       <c r="D971" s="7">
-        <v>2.7</v>
-      </c>
-      <c r="E971" s="6">
-        <v>44603</v>
-      </c>
+        <v>2.8</v>
+      </c>
+      <c r="E971" s="6"/>
       <c r="F971" s="7" t="inlineStr">
         <is>
           <t>월간</t>
@@ -25369,7 +25135,7 @@
     </row>
     <row r="972" spans="1:6">
       <c r="A972" s="6">
-        <v>44562</v>
+        <v>44593</v>
       </c>
       <c r="B972" s="7" t="inlineStr">
         <is>
@@ -25382,11 +25148,9 @@
         </is>
       </c>
       <c r="D972" s="7">
-        <v>2.8</v>
-      </c>
-      <c r="E972" s="6">
-        <v>44630</v>
-      </c>
+        <v>2.7</v>
+      </c>
+      <c r="E972" s="6"/>
       <c r="F972" s="7" t="inlineStr">
         <is>
           <t>월간</t>
@@ -25395,7 +25159,7 @@
     </row>
     <row r="973" spans="1:6">
       <c r="A973" s="6">
-        <v>44593</v>
+        <v>44621</v>
       </c>
       <c r="B973" s="7" t="inlineStr">
         <is>
@@ -25408,11 +25172,9 @@
         </is>
       </c>
       <c r="D973" s="7">
-        <v>2.7</v>
-      </c>
-      <c r="E973" s="6">
-        <v>44665</v>
-      </c>
+        <v>2.6</v>
+      </c>
+      <c r="E973" s="6"/>
       <c r="F973" s="7" t="inlineStr">
         <is>
           <t>월간</t>
@@ -25421,7 +25183,7 @@
     </row>
     <row r="974" spans="1:6">
       <c r="A974" s="6">
-        <v>44621</v>
+        <v>44652</v>
       </c>
       <c r="B974" s="7" t="inlineStr">
         <is>
@@ -25436,9 +25198,7 @@
       <c r="D974" s="7">
         <v>2.6</v>
       </c>
-      <c r="E974" s="6">
-        <v>44692</v>
-      </c>
+      <c r="E974" s="6"/>
       <c r="F974" s="7" t="inlineStr">
         <is>
           <t>월간</t>
@@ -25447,7 +25207,7 @@
     </row>
     <row r="975" spans="1:6">
       <c r="A975" s="6">
-        <v>44652</v>
+        <v>44682</v>
       </c>
       <c r="B975" s="7" t="inlineStr">
         <is>
@@ -25462,9 +25222,7 @@
       <c r="D975" s="7">
         <v>2.6</v>
       </c>
-      <c r="E975" s="6">
-        <v>44726</v>
-      </c>
+      <c r="E975" s="6"/>
       <c r="F975" s="7" t="inlineStr">
         <is>
           <t>월간</t>
@@ -25473,7 +25231,7 @@
     </row>
     <row r="976" spans="1:6">
       <c r="A976" s="6">
-        <v>44682</v>
+        <v>44713</v>
       </c>
       <c r="B976" s="7" t="inlineStr">
         <is>
@@ -25488,9 +25246,7 @@
       <c r="D976" s="7">
         <v>2.6</v>
       </c>
-      <c r="E976" s="6">
-        <v>44755</v>
-      </c>
+      <c r="E976" s="6"/>
       <c r="F976" s="7" t="inlineStr">
         <is>
           <t>월간</t>
@@ -25499,7 +25255,7 @@
     </row>
     <row r="977" spans="1:6">
       <c r="A977" s="6">
-        <v>44713</v>
+        <v>44743</v>
       </c>
       <c r="B977" s="7" t="inlineStr">
         <is>
@@ -25512,11 +25268,9 @@
         </is>
       </c>
       <c r="D977" s="7">
-        <v>2.6</v>
-      </c>
-      <c r="E977" s="6">
-        <v>44783</v>
-      </c>
+        <v>2.5</v>
+      </c>
+      <c r="E977" s="6"/>
       <c r="F977" s="7" t="inlineStr">
         <is>
           <t>월간</t>
@@ -25525,7 +25279,7 @@
     </row>
     <row r="978" spans="1:6">
       <c r="A978" s="6">
-        <v>44743</v>
+        <v>44774</v>
       </c>
       <c r="B978" s="7" t="inlineStr">
         <is>
@@ -25540,9 +25294,7 @@
       <c r="D978" s="7">
         <v>2.5</v>
       </c>
-      <c r="E978" s="6">
-        <v>44818</v>
-      </c>
+      <c r="E978" s="6"/>
       <c r="F978" s="7" t="inlineStr">
         <is>
           <t>월간</t>
@@ -25551,7 +25303,7 @@
     </row>
     <row r="979" spans="1:6">
       <c r="A979" s="6">
-        <v>44774</v>
+        <v>44805</v>
       </c>
       <c r="B979" s="7" t="inlineStr">
         <is>
@@ -25564,11 +25316,9 @@
         </is>
       </c>
       <c r="D979" s="7">
-        <v>2.5</v>
-      </c>
-      <c r="E979" s="6">
-        <v>44876</v>
-      </c>
+        <v>2.6</v>
+      </c>
+      <c r="E979" s="6"/>
       <c r="F979" s="7" t="inlineStr">
         <is>
           <t>월간</t>
@@ -25577,7 +25327,7 @@
     </row>
     <row r="980" spans="1:6">
       <c r="A980" s="6">
-        <v>44805</v>
+        <v>44835</v>
       </c>
       <c r="B980" s="7" t="inlineStr">
         <is>
@@ -25592,9 +25342,7 @@
       <c r="D980" s="7">
         <v>2.6</v>
       </c>
-      <c r="E980" s="6">
-        <v>44876</v>
-      </c>
+      <c r="E980" s="6"/>
       <c r="F980" s="7" t="inlineStr">
         <is>
           <t>월간</t>
@@ -25603,7 +25351,7 @@
     </row>
     <row r="981" spans="1:6">
       <c r="A981" s="6">
-        <v>44835</v>
+        <v>44866</v>
       </c>
       <c r="B981" s="7" t="inlineStr">
         <is>
@@ -25616,11 +25364,9 @@
         </is>
       </c>
       <c r="D981" s="7">
-        <v>2.6</v>
-      </c>
-      <c r="E981" s="6">
-        <v>44905</v>
-      </c>
+        <v>2.5</v>
+      </c>
+      <c r="E981" s="6"/>
       <c r="F981" s="7" t="inlineStr">
         <is>
           <t>월간</t>
@@ -25629,7 +25375,7 @@
     </row>
     <row r="982" spans="1:6">
       <c r="A982" s="6">
-        <v>44866</v>
+        <v>44896</v>
       </c>
       <c r="B982" s="7" t="inlineStr">
         <is>
@@ -25644,9 +25390,7 @@
       <c r="D982" s="7">
         <v>2.5</v>
       </c>
-      <c r="E982" s="6">
-        <v>44937</v>
-      </c>
+      <c r="E982" s="6"/>
       <c r="F982" s="7" t="inlineStr">
         <is>
           <t>월간</t>
@@ -25655,7 +25399,7 @@
     </row>
     <row r="983" spans="1:6">
       <c r="A983" s="6">
-        <v>44896</v>
+        <v>44927</v>
       </c>
       <c r="B983" s="7" t="inlineStr">
         <is>
@@ -25670,9 +25414,7 @@
       <c r="D983" s="7">
         <v>2.5</v>
       </c>
-      <c r="E983" s="6">
-        <v>44970</v>
-      </c>
+      <c r="E983" s="6"/>
       <c r="F983" s="7" t="inlineStr">
         <is>
           <t>월간</t>
@@ -25681,7 +25423,7 @@
     </row>
     <row r="984" spans="1:6">
       <c r="A984" s="6">
-        <v>44927</v>
+        <v>44958</v>
       </c>
       <c r="B984" s="7" t="inlineStr">
         <is>
@@ -25694,11 +25436,9 @@
         </is>
       </c>
       <c r="D984" s="7">
-        <v>2.5</v>
-      </c>
-      <c r="E984" s="6">
-        <v>44994</v>
-      </c>
+        <v>2.6</v>
+      </c>
+      <c r="E984" s="6"/>
       <c r="F984" s="7" t="inlineStr">
         <is>
           <t>월간</t>
@@ -25707,7 +25447,7 @@
     </row>
     <row r="985" spans="1:6">
       <c r="A985" s="6">
-        <v>44958</v>
+        <v>44986</v>
       </c>
       <c r="B985" s="7" t="inlineStr">
         <is>
@@ -25720,11 +25460,9 @@
         </is>
       </c>
       <c r="D985" s="7">
-        <v>2.6</v>
-      </c>
-      <c r="E985" s="6">
-        <v>45023</v>
-      </c>
+        <v>2.7</v>
+      </c>
+      <c r="E985" s="6"/>
       <c r="F985" s="7" t="inlineStr">
         <is>
           <t>월간</t>
@@ -25733,7 +25471,7 @@
     </row>
     <row r="986" spans="1:6">
       <c r="A986" s="6">
-        <v>44986</v>
+        <v>45017</v>
       </c>
       <c r="B986" s="7" t="inlineStr">
         <is>
@@ -25746,11 +25484,9 @@
         </is>
       </c>
       <c r="D986" s="7">
-        <v>2.7</v>
-      </c>
-      <c r="E986" s="6">
-        <v>45056</v>
-      </c>
+        <v>2.6</v>
+      </c>
+      <c r="E986" s="6"/>
       <c r="F986" s="7" t="inlineStr">
         <is>
           <t>월간</t>
@@ -25759,7 +25495,7 @@
     </row>
     <row r="987" spans="1:6">
       <c r="A987" s="6">
-        <v>45017</v>
+        <v>45047</v>
       </c>
       <c r="B987" s="7" t="inlineStr">
         <is>
@@ -25772,11 +25508,9 @@
         </is>
       </c>
       <c r="D987" s="7">
-        <v>2.6</v>
-      </c>
-      <c r="E987" s="6">
-        <v>45090</v>
-      </c>
+        <v>2.5</v>
+      </c>
+      <c r="E987" s="6"/>
       <c r="F987" s="7" t="inlineStr">
         <is>
           <t>월간</t>
@@ -25785,7 +25519,7 @@
     </row>
     <row r="988" spans="1:6">
       <c r="A988" s="6">
-        <v>45047</v>
+        <v>45078</v>
       </c>
       <c r="B988" s="7" t="inlineStr">
         <is>
@@ -25800,9 +25534,7 @@
       <c r="D988" s="7">
         <v>2.5</v>
       </c>
-      <c r="E988" s="6">
-        <v>45114</v>
-      </c>
+      <c r="E988" s="6"/>
       <c r="F988" s="7" t="inlineStr">
         <is>
           <t>월간</t>
@@ -25811,7 +25543,7 @@
     </row>
     <row r="989" spans="1:6">
       <c r="A989" s="6">
-        <v>45078</v>
+        <v>45108</v>
       </c>
       <c r="B989" s="7" t="inlineStr">
         <is>
@@ -25824,11 +25556,9 @@
         </is>
       </c>
       <c r="D989" s="7">
-        <v>2.5</v>
-      </c>
-      <c r="E989" s="6">
-        <v>45148</v>
-      </c>
+        <v>2.6</v>
+      </c>
+      <c r="E989" s="6"/>
       <c r="F989" s="7" t="inlineStr">
         <is>
           <t>월간</t>
@@ -25837,7 +25567,7 @@
     </row>
     <row r="990" spans="1:6">
       <c r="A990" s="6">
-        <v>45108</v>
+        <v>45139</v>
       </c>
       <c r="B990" s="7" t="inlineStr">
         <is>
@@ -25852,9 +25582,7 @@
       <c r="D990" s="7">
         <v>2.6</v>
       </c>
-      <c r="E990" s="6">
-        <v>45178</v>
-      </c>
+      <c r="E990" s="6"/>
       <c r="F990" s="7" t="inlineStr">
         <is>
           <t>월간</t>
@@ -25863,7 +25591,7 @@
     </row>
     <row r="991" spans="1:6">
       <c r="A991" s="6">
-        <v>45139</v>
+        <v>45170</v>
       </c>
       <c r="B991" s="7" t="inlineStr">
         <is>
@@ -25878,9 +25606,7 @@
       <c r="D991" s="7">
         <v>2.6</v>
       </c>
-      <c r="E991" s="6">
-        <v>45206</v>
-      </c>
+      <c r="E991" s="6"/>
       <c r="F991" s="7" t="inlineStr">
         <is>
           <t>월간</t>
@@ -25889,7 +25615,7 @@
     </row>
     <row r="992" spans="1:6">
       <c r="A992" s="6">
-        <v>45170</v>
+        <v>45200</v>
       </c>
       <c r="B992" s="7" t="inlineStr">
         <is>
@@ -25902,11 +25628,9 @@
         </is>
       </c>
       <c r="D992" s="7">
-        <v>2.6</v>
-      </c>
-      <c r="E992" s="6">
-        <v>45240</v>
-      </c>
+        <v>2.5</v>
+      </c>
+      <c r="E992" s="6"/>
       <c r="F992" s="7" t="inlineStr">
         <is>
           <t>월간</t>
@@ -25915,7 +25639,7 @@
     </row>
     <row r="993" spans="1:6">
       <c r="A993" s="6">
-        <v>45200</v>
+        <v>45231</v>
       </c>
       <c r="B993" s="7" t="inlineStr">
         <is>
@@ -25928,11 +25652,9 @@
         </is>
       </c>
       <c r="D993" s="7">
-        <v>2.5</v>
-      </c>
-      <c r="E993" s="6">
-        <v>45269</v>
-      </c>
+        <v>2.6</v>
+      </c>
+      <c r="E993" s="6"/>
       <c r="F993" s="7" t="inlineStr">
         <is>
           <t>월간</t>
@@ -25941,7 +25663,7 @@
     </row>
     <row r="994" spans="1:6">
       <c r="A994" s="6">
-        <v>45231</v>
+        <v>45261</v>
       </c>
       <c r="B994" s="7" t="inlineStr">
         <is>
@@ -25954,11 +25676,9 @@
         </is>
       </c>
       <c r="D994" s="7">
-        <v>2.6</v>
-      </c>
-      <c r="E994" s="6">
-        <v>45302</v>
-      </c>
+        <v>2.5</v>
+      </c>
+      <c r="E994" s="6"/>
       <c r="F994" s="7" t="inlineStr">
         <is>
           <t>월간</t>
@@ -25967,7 +25687,7 @@
     </row>
     <row r="995" spans="1:6">
       <c r="A995" s="6">
-        <v>45261</v>
+        <v>45292</v>
       </c>
       <c r="B995" s="7" t="inlineStr">
         <is>
@@ -25982,9 +25702,7 @@
       <c r="D995" s="7">
         <v>2.5</v>
       </c>
-      <c r="E995" s="6">
-        <v>45392</v>
-      </c>
+      <c r="E995" s="6"/>
       <c r="F995" s="7" t="inlineStr">
         <is>
           <t>월간</t>
@@ -25993,7 +25711,7 @@
     </row>
     <row r="996" spans="1:6">
       <c r="A996" s="6">
-        <v>45292</v>
+        <v>45323</v>
       </c>
       <c r="B996" s="7" t="inlineStr">
         <is>
@@ -26006,11 +25724,9 @@
         </is>
       </c>
       <c r="D996" s="7">
-        <v>2.5</v>
-      </c>
-      <c r="E996" s="6">
-        <v>45392</v>
-      </c>
+        <v>2.6</v>
+      </c>
+      <c r="E996" s="6"/>
       <c r="F996" s="7" t="inlineStr">
         <is>
           <t>월간</t>
@@ -26019,7 +25735,7 @@
     </row>
     <row r="997" spans="1:6">
       <c r="A997" s="6">
-        <v>45323</v>
+        <v>45352</v>
       </c>
       <c r="B997" s="7" t="inlineStr">
         <is>
@@ -26034,9 +25750,7 @@
       <c r="D997" s="7">
         <v>2.6</v>
       </c>
-      <c r="E997" s="6">
-        <v>45392</v>
-      </c>
+      <c r="E997" s="6"/>
       <c r="F997" s="7" t="inlineStr">
         <is>
           <t>월간</t>
@@ -26045,7 +25759,7 @@
     </row>
     <row r="998" spans="1:6">
       <c r="A998" s="6">
-        <v>45352</v>
+        <v>45383</v>
       </c>
       <c r="B998" s="7" t="inlineStr">
         <is>
@@ -26060,9 +25774,7 @@
       <c r="D998" s="7">
         <v>2.6</v>
       </c>
-      <c r="E998" s="6">
-        <v>45427</v>
-      </c>
+      <c r="E998" s="6"/>
       <c r="F998" s="7" t="inlineStr">
         <is>
           <t>월간</t>
@@ -26071,7 +25783,7 @@
     </row>
     <row r="999" spans="1:6">
       <c r="A999" s="6">
-        <v>45383</v>
+        <v>45413</v>
       </c>
       <c r="B999" s="7" t="inlineStr">
         <is>
@@ -26086,9 +25798,7 @@
       <c r="D999" s="7">
         <v>2.6</v>
       </c>
-      <c r="E999" s="6">
-        <v>45460</v>
-      </c>
+      <c r="E999" s="6"/>
       <c r="F999" s="7" t="inlineStr">
         <is>
           <t>월간</t>
@@ -26097,7 +25807,7 @@
     </row>
     <row r="1000" spans="1:6">
       <c r="A1000" s="6">
-        <v>45413</v>
+        <v>45444</v>
       </c>
       <c r="B1000" s="7" t="inlineStr">
         <is>
@@ -26110,11 +25820,9 @@
         </is>
       </c>
       <c r="D1000" s="7">
-        <v>2.6</v>
-      </c>
-      <c r="E1000" s="6">
-        <v>45488</v>
-      </c>
+        <v>2.5</v>
+      </c>
+      <c r="E1000" s="6"/>
       <c r="F1000" s="7" t="inlineStr">
         <is>
           <t>월간</t>
@@ -26123,7 +25831,7 @@
     </row>
     <row r="1001" spans="1:6">
       <c r="A1001" s="6">
-        <v>45444</v>
+        <v>45474</v>
       </c>
       <c r="B1001" s="7" t="inlineStr">
         <is>
@@ -26136,11 +25844,9 @@
         </is>
       </c>
       <c r="D1001" s="7">
-        <v>2.5</v>
-      </c>
-      <c r="E1001" s="6">
-        <v>45519</v>
-      </c>
+        <v>2.7</v>
+      </c>
+      <c r="E1001" s="6"/>
       <c r="F1001" s="7" t="inlineStr">
         <is>
           <t>월간</t>
@@ -26149,7 +25855,7 @@
     </row>
     <row r="1002" spans="1:6">
       <c r="A1002" s="6">
-        <v>45474</v>
+        <v>45505</v>
       </c>
       <c r="B1002" s="7" t="inlineStr">
         <is>
@@ -26162,11 +25868,9 @@
         </is>
       </c>
       <c r="D1002" s="7">
-        <v>2.7</v>
-      </c>
-      <c r="E1002" s="6">
-        <v>45551</v>
-      </c>
+        <v>2.5</v>
+      </c>
+      <c r="E1002" s="6"/>
       <c r="F1002" s="7" t="inlineStr">
         <is>
           <t>월간</t>
@@ -26175,7 +25879,7 @@
     </row>
     <row r="1003" spans="1:6">
       <c r="A1003" s="6">
-        <v>45505</v>
+        <v>45536</v>
       </c>
       <c r="B1003" s="7" t="inlineStr">
         <is>
@@ -26188,11 +25892,9 @@
         </is>
       </c>
       <c r="D1003" s="7">
-        <v>2.5</v>
-      </c>
-      <c r="E1003" s="6">
-        <v>45580</v>
-      </c>
+        <v>2.4</v>
+      </c>
+      <c r="E1003" s="6"/>
       <c r="F1003" s="7" t="inlineStr">
         <is>
           <t>월간</t>
@@ -26201,7 +25903,7 @@
     </row>
     <row r="1004" spans="1:6">
       <c r="A1004" s="6">
-        <v>45536</v>
+        <v>45566</v>
       </c>
       <c r="B1004" s="7" t="inlineStr">
         <is>
@@ -26214,11 +25916,9 @@
         </is>
       </c>
       <c r="D1004" s="7">
-        <v>2.4</v>
-      </c>
-      <c r="E1004" s="6">
-        <v>45611</v>
-      </c>
+        <v>2.5</v>
+      </c>
+      <c r="E1004" s="6"/>
       <c r="F1004" s="7" t="inlineStr">
         <is>
           <t>월간</t>
@@ -26227,7 +25927,7 @@
     </row>
     <row r="1005" spans="1:6">
       <c r="A1005" s="6">
-        <v>45566</v>
+        <v>45597</v>
       </c>
       <c r="B1005" s="7" t="inlineStr">
         <is>
@@ -26242,9 +25942,7 @@
       <c r="D1005" s="7">
         <v>2.5</v>
       </c>
-      <c r="E1005" s="6">
-        <v>45642</v>
-      </c>
+      <c r="E1005" s="6"/>
       <c r="F1005" s="7" t="inlineStr">
         <is>
           <t>월간</t>
@@ -26253,7 +25951,7 @@
     </row>
     <row r="1006" spans="1:6">
       <c r="A1006" s="6">
-        <v>45597</v>
+        <v>45627</v>
       </c>
       <c r="B1006" s="7" t="inlineStr">
         <is>
@@ -26268,9 +25966,7 @@
       <c r="D1006" s="7">
         <v>2.5</v>
       </c>
-      <c r="E1006" s="6">
-        <v>45672</v>
-      </c>
+      <c r="E1006" s="6"/>
       <c r="F1006" s="7" t="inlineStr">
         <is>
           <t>월간</t>
@@ -26279,7 +25975,7 @@
     </row>
     <row r="1007" spans="1:6">
       <c r="A1007" s="6">
-        <v>45627</v>
+        <v>45658</v>
       </c>
       <c r="B1007" s="7" t="inlineStr">
         <is>
@@ -26294,9 +25990,7 @@
       <c r="D1007" s="7">
         <v>2.5</v>
       </c>
-      <c r="E1007" s="6">
-        <v>45705</v>
-      </c>
+      <c r="E1007" s="6"/>
       <c r="F1007" s="7" t="inlineStr">
         <is>
           <t>월간</t>
@@ -26305,7 +25999,7 @@
     </row>
     <row r="1008" spans="1:6">
       <c r="A1008" s="6">
-        <v>45658</v>
+        <v>45689</v>
       </c>
       <c r="B1008" s="7" t="inlineStr">
         <is>
@@ -26318,11 +26012,9 @@
         </is>
       </c>
       <c r="D1008" s="7">
-        <v>2.5</v>
-      </c>
-      <c r="E1008" s="6">
-        <v>45733</v>
-      </c>
+        <v>2.4</v>
+      </c>
+      <c r="E1008" s="6"/>
       <c r="F1008" s="7" t="inlineStr">
         <is>
           <t>월간</t>
@@ -26331,7 +26023,7 @@
     </row>
     <row r="1009" spans="1:6">
       <c r="A1009" s="6">
-        <v>45689</v>
+        <v>45717</v>
       </c>
       <c r="B1009" s="7" t="inlineStr">
         <is>
@@ -26344,11 +26036,9 @@
         </is>
       </c>
       <c r="D1009" s="7">
-        <v>2.4</v>
-      </c>
-      <c r="E1009" s="6">
-        <v>45762</v>
-      </c>
+        <v>2.5</v>
+      </c>
+      <c r="E1009" s="6"/>
       <c r="F1009" s="7" t="inlineStr">
         <is>
           <t>월간</t>
@@ -26357,7 +26047,7 @@
     </row>
     <row r="1010" spans="1:6">
       <c r="A1010" s="6">
-        <v>45717</v>
+        <v>45748</v>
       </c>
       <c r="B1010" s="7" t="inlineStr">
         <is>
@@ -26372,9 +26062,7 @@
       <c r="D1010" s="7">
         <v>2.5</v>
       </c>
-      <c r="E1010" s="6">
-        <v>45792</v>
-      </c>
+      <c r="E1010" s="6"/>
       <c r="F1010" s="7" t="inlineStr">
         <is>
           <t>월간</t>
@@ -26383,7 +26071,7 @@
     </row>
     <row r="1011" spans="1:6">
       <c r="A1011" s="6">
-        <v>45748</v>
+        <v>45778</v>
       </c>
       <c r="B1011" s="7" t="inlineStr">
         <is>
@@ -26398,9 +26086,7 @@
       <c r="D1011" s="7">
         <v>2.5</v>
       </c>
-      <c r="E1011" s="6">
-        <v>45824</v>
-      </c>
+      <c r="E1011" s="6"/>
       <c r="F1011" s="7" t="inlineStr">
         <is>
           <t>월간</t>
@@ -26409,7 +26095,7 @@
     </row>
     <row r="1012" spans="1:6">
       <c r="A1012" s="6">
-        <v>45778</v>
+        <v>45809</v>
       </c>
       <c r="B1012" s="7" t="inlineStr">
         <is>
@@ -26424,9 +26110,7 @@
       <c r="D1012" s="7">
         <v>2.5</v>
       </c>
-      <c r="E1012" s="6">
-        <v>45853</v>
-      </c>
+      <c r="E1012" s="6"/>
       <c r="F1012" s="7" t="inlineStr">
         <is>
           <t>월간</t>
@@ -26435,7 +26119,7 @@
     </row>
     <row r="1013" spans="1:6">
       <c r="A1013" s="6">
-        <v>45809</v>
+        <v>45839</v>
       </c>
       <c r="B1013" s="7" t="inlineStr">
         <is>
@@ -26448,11 +26132,9 @@
         </is>
       </c>
       <c r="D1013" s="7">
-        <v>2.5</v>
-      </c>
-      <c r="E1013" s="6">
-        <v>45884</v>
-      </c>
+        <v>2.4</v>
+      </c>
+      <c r="E1013" s="6"/>
       <c r="F1013" s="7" t="inlineStr">
         <is>
           <t>월간</t>
@@ -26461,7 +26143,7 @@
     </row>
     <row r="1014" spans="1:6">
       <c r="A1014" s="6">
-        <v>45839</v>
+        <v>45870</v>
       </c>
       <c r="B1014" s="7" t="inlineStr">
         <is>
@@ -26474,11 +26156,9 @@
         </is>
       </c>
       <c r="D1014" s="7">
-        <v>2.4</v>
-      </c>
-      <c r="E1014" s="6">
-        <v>45915</v>
-      </c>
+        <v>2.6</v>
+      </c>
+      <c r="E1014" s="6"/>
       <c r="F1014" s="7" t="inlineStr">
         <is>
           <t>월간</t>
@@ -26487,7 +26167,7 @@
     </row>
     <row r="1015" spans="1:6">
       <c r="A1015" s="6">
-        <v>45870</v>
+        <v>45901</v>
       </c>
       <c r="B1015" s="7" t="inlineStr">
         <is>
@@ -26502,9 +26182,7 @@
       <c r="D1015" s="7">
         <v>2.6</v>
       </c>
-      <c r="E1015" s="6">
-        <v>45945</v>
-      </c>
+      <c r="E1015" s="6"/>
       <c r="F1015" s="7" t="inlineStr">
         <is>
           <t>월간</t>
@@ -26513,7 +26191,7 @@
     </row>
     <row r="1016" spans="1:6">
       <c r="A1016" s="6">
-        <v>45901</v>
+        <v>45931</v>
       </c>
       <c r="B1016" s="7" t="inlineStr">
         <is>
@@ -26528,9 +26206,7 @@
       <c r="D1016" s="7">
         <v>2.6</v>
       </c>
-      <c r="E1016" s="6">
-        <v>45978</v>
-      </c>
+      <c r="E1016" s="6"/>
       <c r="F1016" s="7" t="inlineStr">
         <is>
           <t>월간</t>
@@ -26539,7 +26215,7 @@
     </row>
     <row r="1017" spans="1:6">
       <c r="A1017" s="6">
-        <v>45931</v>
+        <v>45962</v>
       </c>
       <c r="B1017" s="7" t="inlineStr">
         <is>
@@ -26554,9 +26230,7 @@
       <c r="D1017" s="7">
         <v>2.6</v>
       </c>
-      <c r="E1017" s="6">
-        <v>46006</v>
-      </c>
+      <c r="E1017" s="6"/>
       <c r="F1017" s="7" t="inlineStr">
         <is>
           <t>월간</t>
@@ -26565,7 +26239,7 @@
     </row>
     <row r="1018" spans="1:6">
       <c r="A1018" s="6">
-        <v>45962</v>
+        <v>45992</v>
       </c>
       <c r="B1018" s="7" t="inlineStr">
         <is>
@@ -26580,9 +26254,7 @@
       <c r="D1018" s="7">
         <v>2.6</v>
       </c>
-      <c r="E1018" s="6">
-        <v>46037</v>
-      </c>
+      <c r="E1018" s="6"/>
       <c r="F1018" s="7" t="inlineStr">
         <is>
           <t>월간</t>
@@ -26591,7 +26263,7 @@
     </row>
     <row r="1019" spans="1:6">
       <c r="A1019" s="6">
-        <v>45992</v>
+        <v>46023</v>
       </c>
       <c r="B1019" s="7" t="inlineStr">
         <is>
@@ -26604,11 +26276,9 @@
         </is>
       </c>
       <c r="D1019" s="7">
-        <v>2.6</v>
-      </c>
-      <c r="E1019" s="6">
-        <v>46069</v>
-      </c>
+        <v>2.7</v>
+      </c>
+      <c r="E1019" s="6"/>
       <c r="F1019" s="7" t="inlineStr">
         <is>
           <t>월간</t>
@@ -26617,7 +26287,7 @@
     </row>
     <row r="1020" spans="1:6">
       <c r="A1020" s="6">
-        <v>46023</v>
+        <v>46054</v>
       </c>
       <c r="B1020" s="7" t="inlineStr">
         <is>
@@ -26630,11 +26300,9 @@
         </is>
       </c>
       <c r="D1020" s="7">
-        <v>2.7</v>
-      </c>
-      <c r="E1020" s="6">
-        <v>46097</v>
-      </c>
+        <v>2.6</v>
+      </c>
+      <c r="E1020" s="6"/>
       <c r="F1020" s="7" t="inlineStr">
         <is>
           <t>월간</t>
@@ -26643,7 +26311,7 @@
     </row>
     <row r="1021" spans="1:6">
       <c r="A1021" s="6">
-        <v>46054</v>
+        <v>46082</v>
       </c>
       <c r="B1021" s="7" t="inlineStr">
         <is>
@@ -26656,11 +26324,9 @@
         </is>
       </c>
       <c r="D1021" s="7">
-        <v>2.6</v>
-      </c>
-      <c r="E1021" s="6">
-        <v>46127</v>
-      </c>
+        <v>2.7</v>
+      </c>
+      <c r="E1021" s="6"/>
       <c r="F1021" s="7" t="inlineStr">
         <is>
           <t>월간</t>
@@ -26669,7 +26335,7 @@
     </row>
     <row r="1022" spans="1:6">
       <c r="A1022" s="6">
-        <v>46082</v>
+        <v>46113</v>
       </c>
       <c r="B1022" s="7" t="inlineStr">
         <is>
@@ -26682,11 +26348,9 @@
         </is>
       </c>
       <c r="D1022" s="7">
-        <v>2.7</v>
-      </c>
-      <c r="E1022" s="6">
-        <v>46157</v>
-      </c>
+        <v>2.5</v>
+      </c>
+      <c r="E1022" s="6"/>
       <c r="F1022" s="7" t="inlineStr">
         <is>
           <t>월간</t>
@@ -26695,7 +26359,7 @@
     </row>
     <row r="1023" spans="1:6">
       <c r="A1023" s="6">
-        <v>46113</v>
+        <v>46143</v>
       </c>
       <c r="B1023" s="7" t="inlineStr">
         <is>
@@ -26710,9 +26374,7 @@
       <c r="D1023" s="7">
         <v>2.5</v>
       </c>
-      <c r="E1023" s="6">
-        <v>46188</v>
-      </c>
+      <c r="E1023" s="6"/>
       <c r="F1023" s="7" t="inlineStr">
         <is>
           <t>월간</t>
@@ -26721,7 +26383,7 @@
     </row>
     <row r="1024" spans="1:6">
       <c r="A1024" s="6">
-        <v>46143</v>
+        <v>46174</v>
       </c>
       <c r="B1024" s="7" t="inlineStr">
         <is>
@@ -26736,9 +26398,7 @@
       <c r="D1024" s="7">
         <v>2.5</v>
       </c>
-      <c r="E1024" s="6">
-        <v>46219</v>
-      </c>
+      <c r="E1024" s="6"/>
       <c r="F1024" s="7" t="inlineStr">
         <is>
           <t>월간</t>
@@ -26747,7 +26407,7 @@
     </row>
     <row r="1025" spans="1:6">
       <c r="A1025" s="6">
-        <v>46174</v>
+        <v>46204</v>
       </c>
       <c r="B1025" s="7" t="inlineStr">
         <is>
@@ -26760,11 +26420,9 @@
         </is>
       </c>
       <c r="D1025" s="7">
-        <v>2.5</v>
-      </c>
-      <c r="E1025" s="6">
-        <v>46251</v>
-      </c>
+        <v>2.4</v>
+      </c>
+      <c r="E1025" s="6"/>
       <c r="F1025" s="7" t="inlineStr">
         <is>
           <t>월간</t>
@@ -26773,7 +26431,7 @@
     </row>
     <row r="1026" spans="1:6">
       <c r="A1026" s="6">
-        <v>46204</v>
+        <v>44378</v>
       </c>
       <c r="B1026" s="7" t="inlineStr">
         <is>
@@ -26782,24 +26440,22 @@
       </c>
       <c r="C1026" s="7" t="inlineStr">
         <is>
-          <t>실업률</t>
+          <t>실질GDP 성장률</t>
         </is>
       </c>
       <c r="D1026" s="7">
-        <v>2.4</v>
-      </c>
-      <c r="E1026" s="6">
-        <v>46280</v>
-      </c>
+        <v>-0.19</v>
+      </c>
+      <c r="E1026" s="6"/>
       <c r="F1026" s="7" t="inlineStr">
         <is>
-          <t>월간</t>
+          <t>분기</t>
         </is>
       </c>
     </row>
     <row r="1027" spans="1:6">
       <c r="A1027" s="6">
-        <v>44378</v>
+        <v>44470</v>
       </c>
       <c r="B1027" s="7" t="inlineStr">
         <is>
@@ -26812,7 +26468,7 @@
         </is>
       </c>
       <c r="D1027" s="7">
-        <v>-0.19</v>
+        <v>1.18</v>
       </c>
       <c r="E1027" s="6"/>
       <c r="F1027" s="7" t="inlineStr">
@@ -26823,7 +26479,7 @@
     </row>
     <row r="1028" spans="1:6">
       <c r="A1028" s="6">
-        <v>44470</v>
+        <v>44562</v>
       </c>
       <c r="B1028" s="7" t="inlineStr">
         <is>
@@ -26836,7 +26492,7 @@
         </is>
       </c>
       <c r="D1028" s="7">
-        <v>1.18</v>
+        <v>-0.44</v>
       </c>
       <c r="E1028" s="6"/>
       <c r="F1028" s="7" t="inlineStr">
@@ -26847,7 +26503,7 @@
     </row>
     <row r="1029" spans="1:6">
       <c r="A1029" s="6">
-        <v>44562</v>
+        <v>44652</v>
       </c>
       <c r="B1029" s="7" t="inlineStr">
         <is>
@@ -26860,7 +26516,7 @@
         </is>
       </c>
       <c r="D1029" s="7">
-        <v>-0.44</v>
+        <v>0.95</v>
       </c>
       <c r="E1029" s="6"/>
       <c r="F1029" s="7" t="inlineStr">
@@ -26871,7 +26527,7 @@
     </row>
     <row r="1030" spans="1:6">
       <c r="A1030" s="6">
-        <v>44652</v>
+        <v>44743</v>
       </c>
       <c r="B1030" s="7" t="inlineStr">
         <is>
@@ -26884,7 +26540,7 @@
         </is>
       </c>
       <c r="D1030" s="7">
-        <v>0.95</v>
+        <v>-0.27</v>
       </c>
       <c r="E1030" s="6"/>
       <c r="F1030" s="7" t="inlineStr">
@@ -26895,7 +26551,7 @@
     </row>
     <row r="1031" spans="1:6">
       <c r="A1031" s="6">
-        <v>44743</v>
+        <v>44835</v>
       </c>
       <c r="B1031" s="7" t="inlineStr">
         <is>
@@ -26908,7 +26564,7 @@
         </is>
       </c>
       <c r="D1031" s="7">
-        <v>-0.27</v>
+        <v>0.5</v>
       </c>
       <c r="E1031" s="6"/>
       <c r="F1031" s="7" t="inlineStr">
@@ -26919,7 +26575,7 @@
     </row>
     <row r="1032" spans="1:6">
       <c r="A1032" s="6">
-        <v>44835</v>
+        <v>44927</v>
       </c>
       <c r="B1032" s="7" t="inlineStr">
         <is>
@@ -26932,7 +26588,7 @@
         </is>
       </c>
       <c r="D1032" s="7">
-        <v>0.5</v>
+        <v>0.87</v>
       </c>
       <c r="E1032" s="6"/>
       <c r="F1032" s="7" t="inlineStr">
@@ -26943,7 +26599,7 @@
     </row>
     <row r="1033" spans="1:6">
       <c r="A1033" s="6">
-        <v>44927</v>
+        <v>45017</v>
       </c>
       <c r="B1033" s="7" t="inlineStr">
         <is>
@@ -26956,7 +26612,7 @@
         </is>
       </c>
       <c r="D1033" s="7">
-        <v>0.87</v>
+        <v>0.07</v>
       </c>
       <c r="E1033" s="6"/>
       <c r="F1033" s="7" t="inlineStr">
@@ -26967,7 +26623,7 @@
     </row>
     <row r="1034" spans="1:6">
       <c r="A1034" s="6">
-        <v>45017</v>
+        <v>45108</v>
       </c>
       <c r="B1034" s="7" t="inlineStr">
         <is>
@@ -26980,7 +26636,7 @@
         </is>
       </c>
       <c r="D1034" s="7">
-        <v>0.07</v>
+        <v>-1.25</v>
       </c>
       <c r="E1034" s="6"/>
       <c r="F1034" s="7" t="inlineStr">
@@ -26991,7 +26647,7 @@
     </row>
     <row r="1035" spans="1:6">
       <c r="A1035" s="6">
-        <v>45108</v>
+        <v>45200</v>
       </c>
       <c r="B1035" s="7" t="inlineStr">
         <is>
@@ -27004,7 +26660,7 @@
         </is>
       </c>
       <c r="D1035" s="7">
-        <v>-1.25</v>
+        <v>0.48</v>
       </c>
       <c r="E1035" s="6"/>
       <c r="F1035" s="7" t="inlineStr">
@@ -27015,7 +26671,7 @@
     </row>
     <row r="1036" spans="1:6">
       <c r="A1036" s="6">
-        <v>45200</v>
+        <v>45292</v>
       </c>
       <c r="B1036" s="7" t="inlineStr">
         <is>
@@ -27028,7 +26684,7 @@
         </is>
       </c>
       <c r="D1036" s="7">
-        <v>0.48</v>
+        <v>-0.09</v>
       </c>
       <c r="E1036" s="6"/>
       <c r="F1036" s="7" t="inlineStr">
@@ -27039,7 +26695,7 @@
     </row>
     <row r="1037" spans="1:6">
       <c r="A1037" s="6">
-        <v>45292</v>
+        <v>45383</v>
       </c>
       <c r="B1037" s="7" t="inlineStr">
         <is>
@@ -27052,7 +26708,7 @@
         </is>
       </c>
       <c r="D1037" s="7">
-        <v>-0.09</v>
+        <v>-0.12</v>
       </c>
       <c r="E1037" s="6"/>
       <c r="F1037" s="7" t="inlineStr">
@@ -27063,7 +26719,7 @@
     </row>
     <row r="1038" spans="1:6">
       <c r="A1038" s="6">
-        <v>45383</v>
+        <v>45474</v>
       </c>
       <c r="B1038" s="7" t="inlineStr">
         <is>
@@ -27076,7 +26732,7 @@
         </is>
       </c>
       <c r="D1038" s="7">
-        <v>-0.12</v>
+        <v>0.84</v>
       </c>
       <c r="E1038" s="6"/>
       <c r="F1038" s="7" t="inlineStr">
@@ -27087,7 +26743,7 @@
     </row>
     <row r="1039" spans="1:6">
       <c r="A1039" s="6">
-        <v>45474</v>
+        <v>45566</v>
       </c>
       <c r="B1039" s="7" t="inlineStr">
         <is>
@@ -27100,7 +26756,7 @@
         </is>
       </c>
       <c r="D1039" s="7">
-        <v>0.84</v>
+        <v>0.4</v>
       </c>
       <c r="E1039" s="6"/>
       <c r="F1039" s="7" t="inlineStr">
@@ -27111,7 +26767,7 @@
     </row>
     <row r="1040" spans="1:6">
       <c r="A1040" s="6">
-        <v>45566</v>
+        <v>45658</v>
       </c>
       <c r="B1040" s="7" t="inlineStr">
         <is>
@@ -27124,7 +26780,7 @@
         </is>
       </c>
       <c r="D1040" s="7">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
       <c r="E1040" s="6"/>
       <c r="F1040" s="7" t="inlineStr">
@@ -27135,7 +26791,7 @@
     </row>
     <row r="1041" spans="1:6">
       <c r="A1041" s="6">
-        <v>45658</v>
+        <v>45748</v>
       </c>
       <c r="B1041" s="7" t="inlineStr">
         <is>
@@ -27148,7 +26804,7 @@
         </is>
       </c>
       <c r="D1041" s="7">
-        <v>0.5</v>
+        <v>0.12</v>
       </c>
       <c r="E1041" s="6"/>
       <c r="F1041" s="7" t="inlineStr">
@@ -27159,7 +26815,7 @@
     </row>
     <row r="1042" spans="1:6">
       <c r="A1042" s="6">
-        <v>45748</v>
+        <v>45839</v>
       </c>
       <c r="B1042" s="7" t="inlineStr">
         <is>
@@ -27172,7 +26828,7 @@
         </is>
       </c>
       <c r="D1042" s="7">
-        <v>0.12</v>
+        <v>-0.37</v>
       </c>
       <c r="E1042" s="6"/>
       <c r="F1042" s="7" t="inlineStr">
@@ -27183,7 +26839,7 @@
     </row>
     <row r="1043" spans="1:6">
       <c r="A1043" s="6">
-        <v>45839</v>
+        <v>45931</v>
       </c>
       <c r="B1043" s="7" t="inlineStr">
         <is>
@@ -27196,7 +26852,7 @@
         </is>
       </c>
       <c r="D1043" s="7">
-        <v>-0.37</v>
+        <v>0.26</v>
       </c>
       <c r="E1043" s="6"/>
       <c r="F1043" s="7" t="inlineStr">
@@ -27207,7 +26863,7 @@
     </row>
     <row r="1044" spans="1:6">
       <c r="A1044" s="6">
-        <v>45931</v>
+        <v>46023</v>
       </c>
       <c r="B1044" s="7" t="inlineStr">
         <is>
@@ -27220,7 +26876,7 @@
         </is>
       </c>
       <c r="D1044" s="7">
-        <v>0.26</v>
+        <v>0.48</v>
       </c>
       <c r="E1044" s="6"/>
       <c r="F1044" s="7" t="inlineStr">
@@ -27231,7 +26887,7 @@
     </row>
     <row r="1045" spans="1:6">
       <c r="A1045" s="6">
-        <v>46023</v>
+        <v>46113</v>
       </c>
       <c r="B1045" s="7" t="inlineStr">
         <is>
@@ -27244,7 +26900,7 @@
         </is>
       </c>
       <c r="D1045" s="7">
-        <v>0.48</v>
+        <v>0.36</v>
       </c>
       <c r="E1045" s="6"/>
       <c r="F1045" s="7" t="inlineStr">
@@ -27255,7 +26911,7 @@
     </row>
     <row r="1046" spans="1:6">
       <c r="A1046" s="6">
-        <v>46113</v>
+        <v>44440</v>
       </c>
       <c r="B1046" s="7" t="inlineStr">
         <is>
@@ -27264,22 +26920,22 @@
       </c>
       <c r="C1046" s="7" t="inlineStr">
         <is>
-          <t>실질GDP 성장률</t>
+          <t>두바이유</t>
         </is>
       </c>
       <c r="D1046" s="7">
-        <v>0.36</v>
+        <v>72.7582</v>
       </c>
       <c r="E1046" s="6"/>
       <c r="F1046" s="7" t="inlineStr">
         <is>
-          <t>분기</t>
+          <t>월간</t>
         </is>
       </c>
     </row>
     <row r="1047" spans="1:6">
       <c r="A1047" s="6">
-        <v>44440</v>
+        <v>44470</v>
       </c>
       <c r="B1047" s="7" t="inlineStr">
         <is>
@@ -27292,11 +26948,9 @@
         </is>
       </c>
       <c r="D1047" s="7">
-        <v>72.7582</v>
-      </c>
-      <c r="E1047" s="6">
-        <v>44483</v>
-      </c>
+        <v>81.4371</v>
+      </c>
+      <c r="E1047" s="6"/>
       <c r="F1047" s="7" t="inlineStr">
         <is>
           <t>월간</t>
@@ -27305,7 +26959,7 @@
     </row>
     <row r="1048" spans="1:6">
       <c r="A1048" s="6">
-        <v>44470</v>
+        <v>44501</v>
       </c>
       <c r="B1048" s="7" t="inlineStr">
         <is>
@@ -27318,11 +26972,9 @@
         </is>
       </c>
       <c r="D1048" s="7">
-        <v>81.4371</v>
-      </c>
-      <c r="E1048" s="6">
-        <v>44524</v>
-      </c>
+        <v>78.6577</v>
+      </c>
+      <c r="E1048" s="6"/>
       <c r="F1048" s="7" t="inlineStr">
         <is>
           <t>월간</t>
@@ -27331,7 +26983,7 @@
     </row>
     <row r="1049" spans="1:6">
       <c r="A1049" s="6">
-        <v>44501</v>
+        <v>44531</v>
       </c>
       <c r="B1049" s="7" t="inlineStr">
         <is>
@@ -27344,11 +26996,9 @@
         </is>
       </c>
       <c r="D1049" s="7">
-        <v>78.6577</v>
-      </c>
-      <c r="E1049" s="6">
-        <v>44536</v>
-      </c>
+        <v>72.8478</v>
+      </c>
+      <c r="E1049" s="6"/>
       <c r="F1049" s="7" t="inlineStr">
         <is>
           <t>월간</t>
@@ -27357,7 +27007,7 @@
     </row>
     <row r="1050" spans="1:6">
       <c r="A1050" s="6">
-        <v>44531</v>
+        <v>44562</v>
       </c>
       <c r="B1050" s="7" t="inlineStr">
         <is>
@@ -27370,11 +27020,9 @@
         </is>
       </c>
       <c r="D1050" s="7">
-        <v>72.8478</v>
-      </c>
-      <c r="E1050" s="6">
-        <v>44797</v>
-      </c>
+        <v>83.451</v>
+      </c>
+      <c r="E1050" s="6"/>
       <c r="F1050" s="7" t="inlineStr">
         <is>
           <t>월간</t>
@@ -27383,7 +27031,7 @@
     </row>
     <row r="1051" spans="1:6">
       <c r="A1051" s="6">
-        <v>44562</v>
+        <v>44593</v>
       </c>
       <c r="B1051" s="7" t="inlineStr">
         <is>
@@ -27396,11 +27044,9 @@
         </is>
       </c>
       <c r="D1051" s="7">
-        <v>83.451</v>
-      </c>
-      <c r="E1051" s="6">
-        <v>44797</v>
-      </c>
+        <v>91.525</v>
+      </c>
+      <c r="E1051" s="6"/>
       <c r="F1051" s="7" t="inlineStr">
         <is>
           <t>월간</t>
@@ -27409,7 +27055,7 @@
     </row>
     <row r="1052" spans="1:6">
       <c r="A1052" s="6">
-        <v>44593</v>
+        <v>44621</v>
       </c>
       <c r="B1052" s="7" t="inlineStr">
         <is>
@@ -27422,11 +27068,9 @@
         </is>
       </c>
       <c r="D1052" s="7">
-        <v>91.525</v>
-      </c>
-      <c r="E1052" s="6">
-        <v>44797</v>
-      </c>
+        <v>107.5878</v>
+      </c>
+      <c r="E1052" s="6"/>
       <c r="F1052" s="7" t="inlineStr">
         <is>
           <t>월간</t>
@@ -27435,7 +27079,7 @@
     </row>
     <row r="1053" spans="1:6">
       <c r="A1053" s="6">
-        <v>44621</v>
+        <v>44652</v>
       </c>
       <c r="B1053" s="7" t="inlineStr">
         <is>
@@ -27448,11 +27092,9 @@
         </is>
       </c>
       <c r="D1053" s="7">
-        <v>107.5878</v>
-      </c>
-      <c r="E1053" s="6">
-        <v>44797</v>
-      </c>
+        <v>102.7552</v>
+      </c>
+      <c r="E1053" s="6"/>
       <c r="F1053" s="7" t="inlineStr">
         <is>
           <t>월간</t>
@@ -27461,7 +27103,7 @@
     </row>
     <row r="1054" spans="1:6">
       <c r="A1054" s="6">
-        <v>44652</v>
+        <v>44682</v>
       </c>
       <c r="B1054" s="7" t="inlineStr">
         <is>
@@ -27474,11 +27116,9 @@
         </is>
       </c>
       <c r="D1054" s="7">
-        <v>102.7552</v>
-      </c>
-      <c r="E1054" s="6">
-        <v>44797</v>
-      </c>
+        <v>107.8614</v>
+      </c>
+      <c r="E1054" s="6"/>
       <c r="F1054" s="7" t="inlineStr">
         <is>
           <t>월간</t>
@@ -27487,7 +27127,7 @@
     </row>
     <row r="1055" spans="1:6">
       <c r="A1055" s="6">
-        <v>44682</v>
+        <v>44713</v>
       </c>
       <c r="B1055" s="7" t="inlineStr">
         <is>
@@ -27500,11 +27140,9 @@
         </is>
       </c>
       <c r="D1055" s="7">
-        <v>107.8614</v>
-      </c>
-      <c r="E1055" s="6">
-        <v>44797</v>
-      </c>
+        <v>111.8595</v>
+      </c>
+      <c r="E1055" s="6"/>
       <c r="F1055" s="7" t="inlineStr">
         <is>
           <t>월간</t>
@@ -27513,7 +27151,7 @@
     </row>
     <row r="1056" spans="1:6">
       <c r="A1056" s="6">
-        <v>44713</v>
+        <v>44743</v>
       </c>
       <c r="B1056" s="7" t="inlineStr">
         <is>
@@ -27526,11 +27164,9 @@
         </is>
       </c>
       <c r="D1056" s="7">
-        <v>111.8595</v>
-      </c>
-      <c r="E1056" s="6">
-        <v>44797</v>
-      </c>
+        <v>100.3186</v>
+      </c>
+      <c r="E1056" s="6"/>
       <c r="F1056" s="7" t="inlineStr">
         <is>
           <t>월간</t>
@@ -27539,7 +27175,7 @@
     </row>
     <row r="1057" spans="1:6">
       <c r="A1057" s="6">
-        <v>44743</v>
+        <v>44774</v>
       </c>
       <c r="B1057" s="7" t="inlineStr">
         <is>
@@ -27552,11 +27188,9 @@
         </is>
       </c>
       <c r="D1057" s="7">
-        <v>100.3186</v>
-      </c>
-      <c r="E1057" s="6">
-        <v>44797</v>
-      </c>
+        <v>95.693</v>
+      </c>
+      <c r="E1057" s="6"/>
       <c r="F1057" s="7" t="inlineStr">
         <is>
           <t>월간</t>
@@ -27565,7 +27199,7 @@
     </row>
     <row r="1058" spans="1:6">
       <c r="A1058" s="6">
-        <v>44774</v>
+        <v>44805</v>
       </c>
       <c r="B1058" s="7" t="inlineStr">
         <is>
@@ -27578,11 +27212,9 @@
         </is>
       </c>
       <c r="D1058" s="7">
-        <v>95.693</v>
-      </c>
-      <c r="E1058" s="6">
-        <v>44833</v>
-      </c>
+        <v>89.7427</v>
+      </c>
+      <c r="E1058" s="6"/>
       <c r="F1058" s="7" t="inlineStr">
         <is>
           <t>월간</t>
@@ -27591,7 +27223,7 @@
     </row>
     <row r="1059" spans="1:6">
       <c r="A1059" s="6">
-        <v>44805</v>
+        <v>44835</v>
       </c>
       <c r="B1059" s="7" t="inlineStr">
         <is>
@@ -27604,11 +27236,9 @@
         </is>
       </c>
       <c r="D1059" s="7">
-        <v>89.7427</v>
-      </c>
-      <c r="E1059" s="6">
-        <v>44858</v>
-      </c>
+        <v>91.2148</v>
+      </c>
+      <c r="E1059" s="6"/>
       <c r="F1059" s="7" t="inlineStr">
         <is>
           <t>월간</t>
@@ -27617,7 +27247,7 @@
     </row>
     <row r="1060" spans="1:6">
       <c r="A1060" s="6">
-        <v>44835</v>
+        <v>44866</v>
       </c>
       <c r="B1060" s="7" t="inlineStr">
         <is>
@@ -27630,11 +27260,9 @@
         </is>
       </c>
       <c r="D1060" s="7">
-        <v>91.2148</v>
-      </c>
-      <c r="E1060" s="6">
-        <v>44887</v>
-      </c>
+        <v>84.5991</v>
+      </c>
+      <c r="E1060" s="6"/>
       <c r="F1060" s="7" t="inlineStr">
         <is>
           <t>월간</t>
@@ -27643,7 +27271,7 @@
     </row>
     <row r="1061" spans="1:6">
       <c r="A1061" s="6">
-        <v>44866</v>
+        <v>44896</v>
       </c>
       <c r="B1061" s="7" t="inlineStr">
         <is>
@@ -27656,11 +27284,9 @@
         </is>
       </c>
       <c r="D1061" s="7">
-        <v>84.5991</v>
-      </c>
-      <c r="E1061" s="6">
-        <v>44929</v>
-      </c>
+        <v>76.8559</v>
+      </c>
+      <c r="E1061" s="6"/>
       <c r="F1061" s="7" t="inlineStr">
         <is>
           <t>월간</t>
@@ -27669,7 +27295,7 @@
     </row>
     <row r="1062" spans="1:6">
       <c r="A1062" s="6">
-        <v>44896</v>
+        <v>44927</v>
       </c>
       <c r="B1062" s="7" t="inlineStr">
         <is>
@@ -27682,11 +27308,9 @@
         </is>
       </c>
       <c r="D1062" s="7">
-        <v>76.8559</v>
-      </c>
-      <c r="E1062" s="6">
-        <v>44966</v>
-      </c>
+        <v>80.905</v>
+      </c>
+      <c r="E1062" s="6"/>
       <c r="F1062" s="7" t="inlineStr">
         <is>
           <t>월간</t>
@@ -27695,7 +27319,7 @@
     </row>
     <row r="1063" spans="1:6">
       <c r="A1063" s="6">
-        <v>44927</v>
+        <v>44958</v>
       </c>
       <c r="B1063" s="7" t="inlineStr">
         <is>
@@ -27708,11 +27332,9 @@
         </is>
       </c>
       <c r="D1063" s="7">
-        <v>80.905</v>
-      </c>
-      <c r="E1063" s="6">
-        <v>44966</v>
-      </c>
+        <v>81.275</v>
+      </c>
+      <c r="E1063" s="6"/>
       <c r="F1063" s="7" t="inlineStr">
         <is>
           <t>월간</t>
@@ -27721,7 +27343,7 @@
     </row>
     <row r="1064" spans="1:6">
       <c r="A1064" s="6">
-        <v>44958</v>
+        <v>44986</v>
       </c>
       <c r="B1064" s="7" t="inlineStr">
         <is>
@@ -27734,11 +27356,9 @@
         </is>
       </c>
       <c r="D1064" s="7">
-        <v>81.275</v>
-      </c>
-      <c r="E1064" s="6">
-        <v>45006</v>
-      </c>
+        <v>78.2709</v>
+      </c>
+      <c r="E1064" s="6"/>
       <c r="F1064" s="7" t="inlineStr">
         <is>
           <t>월간</t>
@@ -27747,7 +27367,7 @@
     </row>
     <row r="1065" spans="1:6">
       <c r="A1065" s="6">
-        <v>44986</v>
+        <v>45017</v>
       </c>
       <c r="B1065" s="7" t="inlineStr">
         <is>
@@ -27760,11 +27380,9 @@
         </is>
       </c>
       <c r="D1065" s="7">
-        <v>78.2709</v>
-      </c>
-      <c r="E1065" s="6">
-        <v>45035</v>
-      </c>
+        <v>83.4085</v>
+      </c>
+      <c r="E1065" s="6"/>
       <c r="F1065" s="7" t="inlineStr">
         <is>
           <t>월간</t>
@@ -27773,7 +27391,7 @@
     </row>
     <row r="1066" spans="1:6">
       <c r="A1066" s="6">
-        <v>45017</v>
+        <v>45047</v>
       </c>
       <c r="B1066" s="7" t="inlineStr">
         <is>
@@ -27786,11 +27404,9 @@
         </is>
       </c>
       <c r="D1066" s="7">
-        <v>83.4085</v>
-      </c>
-      <c r="E1066" s="6">
-        <v>45058</v>
-      </c>
+        <v>74.7891</v>
+      </c>
+      <c r="E1066" s="6"/>
       <c r="F1066" s="7" t="inlineStr">
         <is>
           <t>월간</t>
@@ -27799,7 +27415,7 @@
     </row>
     <row r="1067" spans="1:6">
       <c r="A1067" s="6">
-        <v>45047</v>
+        <v>45078</v>
       </c>
       <c r="B1067" s="7" t="inlineStr">
         <is>
@@ -27812,11 +27428,9 @@
         </is>
       </c>
       <c r="D1067" s="7">
-        <v>74.7891</v>
-      </c>
-      <c r="E1067" s="6">
-        <v>45089</v>
-      </c>
+        <v>74.7295</v>
+      </c>
+      <c r="E1067" s="6"/>
       <c r="F1067" s="7" t="inlineStr">
         <is>
           <t>월간</t>
@@ -27825,7 +27439,7 @@
     </row>
     <row r="1068" spans="1:6">
       <c r="A1068" s="6">
-        <v>45078</v>
+        <v>45108</v>
       </c>
       <c r="B1068" s="7" t="inlineStr">
         <is>
@@ -27838,11 +27452,9 @@
         </is>
       </c>
       <c r="D1068" s="7">
-        <v>74.7295</v>
-      </c>
-      <c r="E1068" s="6">
-        <v>45133</v>
-      </c>
+        <v>80.6457</v>
+      </c>
+      <c r="E1068" s="6"/>
       <c r="F1068" s="7" t="inlineStr">
         <is>
           <t>월간</t>
@@ -27851,7 +27463,7 @@
     </row>
     <row r="1069" spans="1:6">
       <c r="A1069" s="6">
-        <v>45108</v>
+        <v>45139</v>
       </c>
       <c r="B1069" s="7" t="inlineStr">
         <is>
@@ -27864,11 +27476,9 @@
         </is>
       </c>
       <c r="D1069" s="7">
-        <v>80.6457</v>
-      </c>
-      <c r="E1069" s="6">
-        <v>45167</v>
-      </c>
+        <v>86.123</v>
+      </c>
+      <c r="E1069" s="6"/>
       <c r="F1069" s="7" t="inlineStr">
         <is>
           <t>월간</t>
@@ -27877,7 +27487,7 @@
     </row>
     <row r="1070" spans="1:6">
       <c r="A1070" s="6">
-        <v>45139</v>
+        <v>45170</v>
       </c>
       <c r="B1070" s="7" t="inlineStr">
         <is>
@@ -27890,11 +27500,9 @@
         </is>
       </c>
       <c r="D1070" s="7">
-        <v>86.123</v>
-      </c>
-      <c r="E1070" s="6">
-        <v>45177</v>
-      </c>
+        <v>93.2386</v>
+      </c>
+      <c r="E1070" s="6"/>
       <c r="F1070" s="7" t="inlineStr">
         <is>
           <t>월간</t>
@@ -27903,7 +27511,7 @@
     </row>
     <row r="1071" spans="1:6">
       <c r="A1071" s="6">
-        <v>45170</v>
+        <v>45200</v>
       </c>
       <c r="B1071" s="7" t="inlineStr">
         <is>
@@ -27916,11 +27524,9 @@
         </is>
       </c>
       <c r="D1071" s="7">
-        <v>93.2386</v>
-      </c>
-      <c r="E1071" s="6">
-        <v>45215</v>
-      </c>
+        <v>88.7877</v>
+      </c>
+      <c r="E1071" s="6"/>
       <c r="F1071" s="7" t="inlineStr">
         <is>
           <t>월간</t>
@@ -27929,7 +27535,7 @@
     </row>
     <row r="1072" spans="1:6">
       <c r="A1072" s="6">
-        <v>45200</v>
+        <v>45231</v>
       </c>
       <c r="B1072" s="7" t="inlineStr">
         <is>
@@ -27942,11 +27548,9 @@
         </is>
       </c>
       <c r="D1072" s="7">
-        <v>88.7877</v>
-      </c>
-      <c r="E1072" s="6">
-        <v>45237</v>
-      </c>
+        <v>82.6409</v>
+      </c>
+      <c r="E1072" s="6"/>
       <c r="F1072" s="7" t="inlineStr">
         <is>
           <t>월간</t>
@@ -27955,7 +27559,7 @@
     </row>
     <row r="1073" spans="1:6">
       <c r="A1073" s="6">
-        <v>45231</v>
+        <v>45261</v>
       </c>
       <c r="B1073" s="7" t="inlineStr">
         <is>
@@ -27968,11 +27572,9 @@
         </is>
       </c>
       <c r="D1073" s="7">
-        <v>82.6409</v>
-      </c>
-      <c r="E1073" s="6">
-        <v>45268</v>
-      </c>
+        <v>77.5695</v>
+      </c>
+      <c r="E1073" s="6"/>
       <c r="F1073" s="7" t="inlineStr">
         <is>
           <t>월간</t>
@@ -27981,7 +27583,7 @@
     </row>
     <row r="1074" spans="1:6">
       <c r="A1074" s="6">
-        <v>45261</v>
+        <v>45292</v>
       </c>
       <c r="B1074" s="7" t="inlineStr">
         <is>
@@ -27994,11 +27596,9 @@
         </is>
       </c>
       <c r="D1074" s="7">
-        <v>77.5695</v>
-      </c>
-      <c r="E1074" s="6">
-        <v>45315</v>
-      </c>
+        <v>79.5822</v>
+      </c>
+      <c r="E1074" s="6"/>
       <c r="F1074" s="7" t="inlineStr">
         <is>
           <t>월간</t>
@@ -28007,7 +27607,7 @@
     </row>
     <row r="1075" spans="1:6">
       <c r="A1075" s="6">
-        <v>45292</v>
+        <v>45323</v>
       </c>
       <c r="B1075" s="7" t="inlineStr">
         <is>
@@ -28020,11 +27620,9 @@
         </is>
       </c>
       <c r="D1075" s="7">
-        <v>79.5822</v>
-      </c>
-      <c r="E1075" s="6">
-        <v>45334</v>
-      </c>
+        <v>82.809</v>
+      </c>
+      <c r="E1075" s="6"/>
       <c r="F1075" s="7" t="inlineStr">
         <is>
           <t>월간</t>
@@ -28033,7 +27631,7 @@
     </row>
     <row r="1076" spans="1:6">
       <c r="A1076" s="6">
-        <v>45323</v>
+        <v>45352</v>
       </c>
       <c r="B1076" s="7" t="inlineStr">
         <is>
@@ -28046,11 +27644,9 @@
         </is>
       </c>
       <c r="D1076" s="7">
-        <v>82.809</v>
-      </c>
-      <c r="E1076" s="6">
-        <v>45359</v>
-      </c>
+        <v>86.6338</v>
+      </c>
+      <c r="E1076" s="6"/>
       <c r="F1076" s="7" t="inlineStr">
         <is>
           <t>월간</t>
@@ -28059,7 +27655,7 @@
     </row>
     <row r="1077" spans="1:6">
       <c r="A1077" s="6">
-        <v>45352</v>
+        <v>45383</v>
       </c>
       <c r="B1077" s="7" t="inlineStr">
         <is>
@@ -28072,11 +27668,9 @@
         </is>
       </c>
       <c r="D1077" s="7">
-        <v>86.6338</v>
-      </c>
-      <c r="E1077" s="6">
-        <v>45385</v>
-      </c>
+        <v>90.8695</v>
+      </c>
+      <c r="E1077" s="6"/>
       <c r="F1077" s="7" t="inlineStr">
         <is>
           <t>월간</t>
@@ -28085,7 +27679,7 @@
     </row>
     <row r="1078" spans="1:6">
       <c r="A1078" s="6">
-        <v>45383</v>
+        <v>45413</v>
       </c>
       <c r="B1078" s="7" t="inlineStr">
         <is>
@@ -28098,11 +27692,9 @@
         </is>
       </c>
       <c r="D1078" s="7">
-        <v>90.8695</v>
-      </c>
-      <c r="E1078" s="6">
-        <v>45418</v>
-      </c>
+        <v>84.6661</v>
+      </c>
+      <c r="E1078" s="6"/>
       <c r="F1078" s="7" t="inlineStr">
         <is>
           <t>월간</t>
@@ -28111,7 +27703,7 @@
     </row>
     <row r="1079" spans="1:6">
       <c r="A1079" s="6">
-        <v>45413</v>
+        <v>45444</v>
       </c>
       <c r="B1079" s="7" t="inlineStr">
         <is>
@@ -28124,11 +27716,9 @@
         </is>
       </c>
       <c r="D1079" s="7">
-        <v>84.6661</v>
-      </c>
-      <c r="E1079" s="6">
-        <v>45448</v>
-      </c>
+        <v>84.1125</v>
+      </c>
+      <c r="E1079" s="6"/>
       <c r="F1079" s="7" t="inlineStr">
         <is>
           <t>월간</t>
@@ -28137,7 +27727,7 @@
     </row>
     <row r="1080" spans="1:6">
       <c r="A1080" s="6">
-        <v>45444</v>
+        <v>45474</v>
       </c>
       <c r="B1080" s="7" t="inlineStr">
         <is>
@@ -28150,11 +27740,9 @@
         </is>
       </c>
       <c r="D1080" s="7">
-        <v>84.1125</v>
-      </c>
-      <c r="E1080" s="6">
-        <v>45476</v>
-      </c>
+        <v>85.2013</v>
+      </c>
+      <c r="E1080" s="6"/>
       <c r="F1080" s="7" t="inlineStr">
         <is>
           <t>월간</t>
@@ -28163,7 +27751,7 @@
     </row>
     <row r="1081" spans="1:6">
       <c r="A1081" s="6">
-        <v>45474</v>
+        <v>45505</v>
       </c>
       <c r="B1081" s="7" t="inlineStr">
         <is>
@@ -28176,11 +27764,9 @@
         </is>
       </c>
       <c r="D1081" s="7">
-        <v>85.2013</v>
-      </c>
-      <c r="E1081" s="6">
-        <v>45526</v>
-      </c>
+        <v>80.0891</v>
+      </c>
+      <c r="E1081" s="6"/>
       <c r="F1081" s="7" t="inlineStr">
         <is>
           <t>월간</t>
@@ -28189,7 +27775,7 @@
     </row>
     <row r="1082" spans="1:6">
       <c r="A1082" s="6">
-        <v>45505</v>
+        <v>45536</v>
       </c>
       <c r="B1082" s="7" t="inlineStr">
         <is>
@@ -28202,11 +27788,9 @@
         </is>
       </c>
       <c r="D1082" s="7">
-        <v>80.0891</v>
-      </c>
-      <c r="E1082" s="6">
-        <v>45541</v>
-      </c>
+        <v>73.76</v>
+      </c>
+      <c r="E1082" s="6"/>
       <c r="F1082" s="7" t="inlineStr">
         <is>
           <t>월간</t>
@@ -28215,7 +27799,7 @@
     </row>
     <row r="1083" spans="1:6">
       <c r="A1083" s="6">
-        <v>45536</v>
+        <v>45566</v>
       </c>
       <c r="B1083" s="7" t="inlineStr">
         <is>
@@ -28228,11 +27812,9 @@
         </is>
       </c>
       <c r="D1083" s="7">
-        <v>73.76</v>
-      </c>
-      <c r="E1083" s="6">
-        <v>45572</v>
-      </c>
+        <v>76.07</v>
+      </c>
+      <c r="E1083" s="6"/>
       <c r="F1083" s="7" t="inlineStr">
         <is>
           <t>월간</t>
@@ -28241,7 +27823,7 @@
     </row>
     <row r="1084" spans="1:6">
       <c r="A1084" s="6">
-        <v>45566</v>
+        <v>45597</v>
       </c>
       <c r="B1084" s="7" t="inlineStr">
         <is>
@@ -28254,11 +27836,9 @@
         </is>
       </c>
       <c r="D1084" s="7">
-        <v>76.07</v>
-      </c>
-      <c r="E1084" s="6">
-        <v>45603</v>
-      </c>
+        <v>74.0929</v>
+      </c>
+      <c r="E1084" s="6"/>
       <c r="F1084" s="7" t="inlineStr">
         <is>
           <t>월간</t>
@@ -28267,7 +27847,7 @@
     </row>
     <row r="1085" spans="1:6">
       <c r="A1085" s="6">
-        <v>45597</v>
+        <v>45627</v>
       </c>
       <c r="B1085" s="7" t="inlineStr">
         <is>
@@ -28280,11 +27860,9 @@
         </is>
       </c>
       <c r="D1085" s="7">
-        <v>74.0929</v>
-      </c>
-      <c r="E1085" s="6">
-        <v>45649</v>
-      </c>
+        <v>74.0027</v>
+      </c>
+      <c r="E1085" s="6"/>
       <c r="F1085" s="7" t="inlineStr">
         <is>
           <t>월간</t>
@@ -28293,7 +27871,7 @@
     </row>
     <row r="1086" spans="1:6">
       <c r="A1086" s="6">
-        <v>45627</v>
+        <v>45658</v>
       </c>
       <c r="B1086" s="7" t="inlineStr">
         <is>
@@ -28306,11 +27884,9 @@
         </is>
       </c>
       <c r="D1086" s="7">
-        <v>74.0027</v>
-      </c>
-      <c r="E1086" s="6">
-        <v>45684</v>
-      </c>
+        <v>80.8043</v>
+      </c>
+      <c r="E1086" s="6"/>
       <c r="F1086" s="7" t="inlineStr">
         <is>
           <t>월간</t>
@@ -28319,7 +27895,7 @@
     </row>
     <row r="1087" spans="1:6">
       <c r="A1087" s="6">
-        <v>45658</v>
+        <v>45689</v>
       </c>
       <c r="B1087" s="7" t="inlineStr">
         <is>
@@ -28332,11 +27908,9 @@
         </is>
       </c>
       <c r="D1087" s="7">
-        <v>80.8043</v>
-      </c>
-      <c r="E1087" s="6">
-        <v>45714</v>
-      </c>
+        <v>76.3215</v>
+      </c>
+      <c r="E1087" s="6"/>
       <c r="F1087" s="7" t="inlineStr">
         <is>
           <t>월간</t>
@@ -28345,7 +27919,7 @@
     </row>
     <row r="1088" spans="1:6">
       <c r="A1088" s="6">
-        <v>45689</v>
+        <v>45717</v>
       </c>
       <c r="B1088" s="7" t="inlineStr">
         <is>
@@ -28358,11 +27932,9 @@
         </is>
       </c>
       <c r="D1088" s="7">
-        <v>76.3215</v>
-      </c>
-      <c r="E1088" s="6">
-        <v>45727</v>
-      </c>
+        <v>72.9781</v>
+      </c>
+      <c r="E1088" s="6"/>
       <c r="F1088" s="7" t="inlineStr">
         <is>
           <t>월간</t>
@@ -28371,7 +27943,7 @@
     </row>
     <row r="1089" spans="1:6">
       <c r="A1089" s="6">
-        <v>45717</v>
+        <v>45748</v>
       </c>
       <c r="B1089" s="7" t="inlineStr">
         <is>
@@ -28384,11 +27956,9 @@
         </is>
       </c>
       <c r="D1089" s="7">
-        <v>72.9781</v>
-      </c>
-      <c r="E1089" s="6">
-        <v>45751</v>
-      </c>
+        <v>68.4895</v>
+      </c>
+      <c r="E1089" s="6"/>
       <c r="F1089" s="7" t="inlineStr">
         <is>
           <t>월간</t>
@@ -28397,7 +27967,7 @@
     </row>
     <row r="1090" spans="1:6">
       <c r="A1090" s="6">
-        <v>45748</v>
+        <v>45778</v>
       </c>
       <c r="B1090" s="7" t="inlineStr">
         <is>
@@ -28410,11 +27980,9 @@
         </is>
       </c>
       <c r="D1090" s="7">
-        <v>68.4895</v>
-      </c>
-      <c r="E1090" s="6">
-        <v>45786</v>
-      </c>
+        <v>63.6073</v>
+      </c>
+      <c r="E1090" s="6"/>
       <c r="F1090" s="7" t="inlineStr">
         <is>
           <t>월간</t>
@@ -28423,7 +27991,7 @@
     </row>
     <row r="1091" spans="1:6">
       <c r="A1091" s="6">
-        <v>45778</v>
+        <v>45809</v>
       </c>
       <c r="B1091" s="7" t="inlineStr">
         <is>
@@ -28436,11 +28004,9 @@
         </is>
       </c>
       <c r="D1091" s="7">
-        <v>63.6073</v>
-      </c>
-      <c r="E1091" s="6">
-        <v>45834</v>
-      </c>
+        <v>69.3629</v>
+      </c>
+      <c r="E1091" s="6"/>
       <c r="F1091" s="7" t="inlineStr">
         <is>
           <t>월간</t>
@@ -28449,7 +28015,7 @@
     </row>
     <row r="1092" spans="1:6">
       <c r="A1092" s="6">
-        <v>45809</v>
+        <v>45839</v>
       </c>
       <c r="B1092" s="7" t="inlineStr">
         <is>
@@ -28462,11 +28028,9 @@
         </is>
       </c>
       <c r="D1092" s="7">
-        <v>69.3629</v>
-      </c>
-      <c r="E1092" s="6">
-        <v>45852</v>
-      </c>
+        <v>71.043</v>
+      </c>
+      <c r="E1092" s="6"/>
       <c r="F1092" s="7" t="inlineStr">
         <is>
           <t>월간</t>
@@ -28475,7 +28039,7 @@
     </row>
     <row r="1093" spans="1:6">
       <c r="A1093" s="6">
-        <v>45839</v>
+        <v>45870</v>
       </c>
       <c r="B1093" s="7" t="inlineStr">
         <is>
@@ -28488,11 +28052,9 @@
         </is>
       </c>
       <c r="D1093" s="7">
-        <v>71.043</v>
-      </c>
-      <c r="E1093" s="6">
-        <v>46044</v>
-      </c>
+        <v>69.3881</v>
+      </c>
+      <c r="E1093" s="6"/>
       <c r="F1093" s="7" t="inlineStr">
         <is>
           <t>월간</t>
@@ -28501,7 +28063,7 @@
     </row>
     <row r="1094" spans="1:6">
       <c r="A1094" s="6">
-        <v>45870</v>
+        <v>45901</v>
       </c>
       <c r="B1094" s="7" t="inlineStr">
         <is>
@@ -28514,11 +28076,9 @@
         </is>
       </c>
       <c r="D1094" s="7">
-        <v>69.3881</v>
-      </c>
-      <c r="E1094" s="6">
-        <v>46044</v>
-      </c>
+        <v>69.9191</v>
+      </c>
+      <c r="E1094" s="6"/>
       <c r="F1094" s="7" t="inlineStr">
         <is>
           <t>월간</t>
@@ -28527,7 +28087,7 @@
     </row>
     <row r="1095" spans="1:6">
       <c r="A1095" s="6">
-        <v>45901</v>
+        <v>45931</v>
       </c>
       <c r="B1095" s="7" t="inlineStr">
         <is>
@@ -28540,11 +28100,9 @@
         </is>
       </c>
       <c r="D1095" s="7">
-        <v>69.9191</v>
-      </c>
-      <c r="E1095" s="6">
-        <v>46044</v>
-      </c>
+        <v>64.5987</v>
+      </c>
+      <c r="E1095" s="6"/>
       <c r="F1095" s="7" t="inlineStr">
         <is>
           <t>월간</t>
@@ -28553,7 +28111,7 @@
     </row>
     <row r="1096" spans="1:6">
       <c r="A1096" s="6">
-        <v>45931</v>
+        <v>45962</v>
       </c>
       <c r="B1096" s="7" t="inlineStr">
         <is>
@@ -28566,11 +28124,9 @@
         </is>
       </c>
       <c r="D1096" s="7">
-        <v>64.5987</v>
-      </c>
-      <c r="E1096" s="6">
-        <v>46044</v>
-      </c>
+        <v>64.3555</v>
+      </c>
+      <c r="E1096" s="6"/>
       <c r="F1096" s="7" t="inlineStr">
         <is>
           <t>월간</t>
@@ -28579,7 +28135,7 @@
     </row>
     <row r="1097" spans="1:6">
       <c r="A1097" s="6">
-        <v>45962</v>
+        <v>45992</v>
       </c>
       <c r="B1097" s="7" t="inlineStr">
         <is>
@@ -28592,11 +28148,9 @@
         </is>
       </c>
       <c r="D1097" s="7">
-        <v>64.3555</v>
-      </c>
-      <c r="E1097" s="6">
-        <v>46044</v>
-      </c>
+        <v>61.83</v>
+      </c>
+      <c r="E1097" s="6"/>
       <c r="F1097" s="7" t="inlineStr">
         <is>
           <t>월간</t>
@@ -28605,7 +28159,7 @@
     </row>
     <row r="1098" spans="1:6">
       <c r="A1098" s="6">
-        <v>45992</v>
+        <v>46023</v>
       </c>
       <c r="B1098" s="7" t="inlineStr">
         <is>
@@ -28618,11 +28172,9 @@
         </is>
       </c>
       <c r="D1098" s="7">
-        <v>61.83</v>
-      </c>
-      <c r="E1098" s="6">
-        <v>46044</v>
-      </c>
+        <v>62.7282</v>
+      </c>
+      <c r="E1098" s="6"/>
       <c r="F1098" s="7" t="inlineStr">
         <is>
           <t>월간</t>
@@ -28631,7 +28183,7 @@
     </row>
     <row r="1099" spans="1:6">
       <c r="A1099" s="6">
-        <v>46023</v>
+        <v>46054</v>
       </c>
       <c r="B1099" s="7" t="inlineStr">
         <is>
@@ -28644,11 +28196,9 @@
         </is>
       </c>
       <c r="D1099" s="7">
-        <v>62.7282</v>
-      </c>
-      <c r="E1099" s="6">
-        <v>46065</v>
-      </c>
+        <v>68.5085</v>
+      </c>
+      <c r="E1099" s="6"/>
       <c r="F1099" s="7" t="inlineStr">
         <is>
           <t>월간</t>
@@ -28657,7 +28207,7 @@
     </row>
     <row r="1100" spans="1:6">
       <c r="A1100" s="6">
-        <v>46054</v>
+        <v>46082</v>
       </c>
       <c r="B1100" s="7" t="inlineStr">
         <is>
@@ -28670,11 +28220,9 @@
         </is>
       </c>
       <c r="D1100" s="7">
-        <v>68.5085</v>
-      </c>
-      <c r="E1100" s="6">
-        <v>46105</v>
-      </c>
+        <v>126.7064</v>
+      </c>
+      <c r="E1100" s="6"/>
       <c r="F1100" s="7" t="inlineStr">
         <is>
           <t>월간</t>
@@ -28683,7 +28231,7 @@
     </row>
     <row r="1101" spans="1:6">
       <c r="A1101" s="6">
-        <v>46082</v>
+        <v>46113</v>
       </c>
       <c r="B1101" s="7" t="inlineStr">
         <is>
@@ -28696,11 +28244,9 @@
         </is>
       </c>
       <c r="D1101" s="7">
-        <v>126.7064</v>
-      </c>
-      <c r="E1101" s="6">
-        <v>46127</v>
-      </c>
+        <v>105.2991</v>
+      </c>
+      <c r="E1101" s="6"/>
       <c r="F1101" s="7" t="inlineStr">
         <is>
           <t>월간</t>
@@ -28709,7 +28255,7 @@
     </row>
     <row r="1102" spans="1:6">
       <c r="A1102" s="6">
-        <v>46113</v>
+        <v>46143</v>
       </c>
       <c r="B1102" s="7" t="inlineStr">
         <is>
@@ -28722,11 +28268,9 @@
         </is>
       </c>
       <c r="D1102" s="7">
-        <v>105.2991</v>
-      </c>
-      <c r="E1102" s="6">
-        <v>46178</v>
-      </c>
+        <v>100.3643</v>
+      </c>
+      <c r="E1102" s="6"/>
       <c r="F1102" s="7" t="inlineStr">
         <is>
           <t>월간</t>
@@ -28735,7 +28279,7 @@
     </row>
     <row r="1103" spans="1:6">
       <c r="A1103" s="6">
-        <v>46143</v>
+        <v>46174</v>
       </c>
       <c r="B1103" s="7" t="inlineStr">
         <is>
@@ -28748,11 +28292,9 @@
         </is>
       </c>
       <c r="D1103" s="7">
-        <v>100.3643</v>
-      </c>
-      <c r="E1103" s="6">
-        <v>46178</v>
-      </c>
+        <v>79.5395</v>
+      </c>
+      <c r="E1103" s="6"/>
       <c r="F1103" s="7" t="inlineStr">
         <is>
           <t>월간</t>
@@ -28761,7 +28303,7 @@
     </row>
     <row r="1104" spans="1:6">
       <c r="A1104" s="6">
-        <v>46174</v>
+        <v>46204</v>
       </c>
       <c r="B1104" s="7" t="inlineStr">
         <is>
@@ -28774,11 +28316,9 @@
         </is>
       </c>
       <c r="D1104" s="7">
-        <v>79.5395</v>
-      </c>
-      <c r="E1104" s="6">
-        <v>46216</v>
-      </c>
+        <v>77.1318</v>
+      </c>
+      <c r="E1104" s="6"/>
       <c r="F1104" s="7" t="inlineStr">
         <is>
           <t>월간</t>
@@ -28787,7 +28327,7 @@
     </row>
     <row r="1105" spans="1:6">
       <c r="A1105" s="6">
-        <v>46204</v>
+        <v>44440</v>
       </c>
       <c r="B1105" s="7" t="inlineStr">
         <is>
@@ -28796,24 +28336,24 @@
       </c>
       <c r="C1105" s="7" t="inlineStr">
         <is>
-          <t>두바이유</t>
+          <t>정책금리</t>
         </is>
       </c>
       <c r="D1105" s="7">
-        <v>77.1318</v>
+        <v>-0.1</v>
       </c>
       <c r="E1105" s="6">
-        <v>46251</v>
+        <v>44440</v>
       </c>
       <c r="F1105" s="7" t="inlineStr">
         <is>
-          <t>월간</t>
+          <t>수시</t>
         </is>
       </c>
     </row>
     <row r="1106" spans="1:6">
       <c r="A1106" s="6">
-        <v>44440</v>
+        <v>45370</v>
       </c>
       <c r="B1106" s="7" t="inlineStr">
         <is>
@@ -28826,10 +28366,10 @@
         </is>
       </c>
       <c r="D1106" s="7">
-        <v>-0.1</v>
+        <v>0.1</v>
       </c>
       <c r="E1106" s="6">
-        <v>44440</v>
+        <v>45370</v>
       </c>
       <c r="F1106" s="7" t="inlineStr">
         <is>
@@ -28839,7 +28379,7 @@
     </row>
     <row r="1107" spans="1:6">
       <c r="A1107" s="6">
-        <v>45370</v>
+        <v>45504</v>
       </c>
       <c r="B1107" s="7" t="inlineStr">
         <is>
@@ -28852,10 +28392,10 @@
         </is>
       </c>
       <c r="D1107" s="7">
-        <v>0.1</v>
+        <v>0.25</v>
       </c>
       <c r="E1107" s="6">
-        <v>45370</v>
+        <v>45504</v>
       </c>
       <c r="F1107" s="7" t="inlineStr">
         <is>
@@ -28865,7 +28405,7 @@
     </row>
     <row r="1108" spans="1:6">
       <c r="A1108" s="6">
-        <v>45504</v>
+        <v>45681</v>
       </c>
       <c r="B1108" s="7" t="inlineStr">
         <is>
@@ -28878,10 +28418,10 @@
         </is>
       </c>
       <c r="D1108" s="7">
-        <v>0.25</v>
+        <v>0.5</v>
       </c>
       <c r="E1108" s="6">
-        <v>45504</v>
+        <v>45681</v>
       </c>
       <c r="F1108" s="7" t="inlineStr">
         <is>
@@ -28891,7 +28431,7 @@
     </row>
     <row r="1109" spans="1:6">
       <c r="A1109" s="6">
-        <v>45681</v>
+        <v>46010</v>
       </c>
       <c r="B1109" s="7" t="inlineStr">
         <is>
@@ -28904,10 +28444,10 @@
         </is>
       </c>
       <c r="D1109" s="7">
-        <v>0.5</v>
+        <v>0.75</v>
       </c>
       <c r="E1109" s="6">
-        <v>45681</v>
+        <v>46010</v>
       </c>
       <c r="F1109" s="7" t="inlineStr">
         <is>
@@ -28917,7 +28457,7 @@
     </row>
     <row r="1110" spans="1:6">
       <c r="A1110" s="6">
-        <v>46010</v>
+        <v>46189</v>
       </c>
       <c r="B1110" s="7" t="inlineStr">
         <is>
@@ -28930,10 +28470,10 @@
         </is>
       </c>
       <c r="D1110" s="7">
-        <v>0.75</v>
+        <v>1.0</v>
       </c>
       <c r="E1110" s="6">
-        <v>46010</v>
+        <v>46189</v>
       </c>
       <c r="F1110" s="7" t="inlineStr">
         <is>
@@ -28943,7 +28483,7 @@
     </row>
     <row r="1111" spans="1:6">
       <c r="A1111" s="6">
-        <v>46189</v>
+        <v>44440</v>
       </c>
       <c r="B1111" s="7" t="inlineStr">
         <is>
@@ -28952,24 +28492,22 @@
       </c>
       <c r="C1111" s="7" t="inlineStr">
         <is>
-          <t>정책금리</t>
+          <t>국채10년</t>
         </is>
       </c>
       <c r="D1111" s="7">
-        <v>1.0</v>
-      </c>
-      <c r="E1111" s="6">
-        <v>46189</v>
-      </c>
+        <v>0.065</v>
+      </c>
+      <c r="E1111" s="6"/>
       <c r="F1111" s="7" t="inlineStr">
         <is>
-          <t>수시</t>
+          <t>월간</t>
         </is>
       </c>
     </row>
     <row r="1112" spans="1:6">
       <c r="A1112" s="6">
-        <v>44440</v>
+        <v>44470</v>
       </c>
       <c r="B1112" s="7" t="inlineStr">
         <is>
@@ -28982,11 +28520,9 @@
         </is>
       </c>
       <c r="D1112" s="7">
-        <v>0.065</v>
-      </c>
-      <c r="E1112" s="6">
-        <v>44482</v>
-      </c>
+        <v>0.095</v>
+      </c>
+      <c r="E1112" s="6"/>
       <c r="F1112" s="7" t="inlineStr">
         <is>
           <t>월간</t>
@@ -28995,7 +28531,7 @@
     </row>
     <row r="1113" spans="1:6">
       <c r="A1113" s="6">
-        <v>44470</v>
+        <v>44501</v>
       </c>
       <c r="B1113" s="7" t="inlineStr">
         <is>
@@ -29008,11 +28544,9 @@
         </is>
       </c>
       <c r="D1113" s="7">
-        <v>0.095</v>
-      </c>
-      <c r="E1113" s="6">
-        <v>44511</v>
-      </c>
+        <v>0.05</v>
+      </c>
+      <c r="E1113" s="6"/>
       <c r="F1113" s="7" t="inlineStr">
         <is>
           <t>월간</t>
@@ -29021,7 +28555,7 @@
     </row>
     <row r="1114" spans="1:6">
       <c r="A1114" s="6">
-        <v>44501</v>
+        <v>44531</v>
       </c>
       <c r="B1114" s="7" t="inlineStr">
         <is>
@@ -29034,11 +28568,9 @@
         </is>
       </c>
       <c r="D1114" s="7">
-        <v>0.05</v>
-      </c>
-      <c r="E1114" s="6">
-        <v>44540</v>
-      </c>
+        <v>0.07</v>
+      </c>
+      <c r="E1114" s="6"/>
       <c r="F1114" s="7" t="inlineStr">
         <is>
           <t>월간</t>
@@ -29047,7 +28579,7 @@
     </row>
     <row r="1115" spans="1:6">
       <c r="A1115" s="6">
-        <v>44531</v>
+        <v>44562</v>
       </c>
       <c r="B1115" s="7" t="inlineStr">
         <is>
@@ -29060,11 +28592,9 @@
         </is>
       </c>
       <c r="D1115" s="7">
-        <v>0.07</v>
-      </c>
-      <c r="E1115" s="6">
-        <v>44579</v>
-      </c>
+        <v>0.17</v>
+      </c>
+      <c r="E1115" s="6"/>
       <c r="F1115" s="7" t="inlineStr">
         <is>
           <t>월간</t>
@@ -29073,7 +28603,7 @@
     </row>
     <row r="1116" spans="1:6">
       <c r="A1116" s="6">
-        <v>44562</v>
+        <v>44593</v>
       </c>
       <c r="B1116" s="7" t="inlineStr">
         <is>
@@ -29086,11 +28616,9 @@
         </is>
       </c>
       <c r="D1116" s="7">
-        <v>0.17</v>
-      </c>
-      <c r="E1116" s="6">
-        <v>44603</v>
-      </c>
+        <v>0.18</v>
+      </c>
+      <c r="E1116" s="6"/>
       <c r="F1116" s="7" t="inlineStr">
         <is>
           <t>월간</t>
@@ -29099,7 +28627,7 @@
     </row>
     <row r="1117" spans="1:6">
       <c r="A1117" s="6">
-        <v>44593</v>
+        <v>44621</v>
       </c>
       <c r="B1117" s="7" t="inlineStr">
         <is>
@@ -29112,11 +28640,9 @@
         </is>
       </c>
       <c r="D1117" s="7">
-        <v>0.18</v>
-      </c>
-      <c r="E1117" s="6">
-        <v>44630</v>
-      </c>
+        <v>0.21</v>
+      </c>
+      <c r="E1117" s="6"/>
       <c r="F1117" s="7" t="inlineStr">
         <is>
           <t>월간</t>
@@ -29125,7 +28651,7 @@
     </row>
     <row r="1118" spans="1:6">
       <c r="A1118" s="6">
-        <v>44621</v>
+        <v>44652</v>
       </c>
       <c r="B1118" s="7" t="inlineStr">
         <is>
@@ -29138,11 +28664,9 @@
         </is>
       </c>
       <c r="D1118" s="7">
-        <v>0.21</v>
-      </c>
-      <c r="E1118" s="6">
-        <v>44665</v>
-      </c>
+        <v>0.215</v>
+      </c>
+      <c r="E1118" s="6"/>
       <c r="F1118" s="7" t="inlineStr">
         <is>
           <t>월간</t>
@@ -29151,7 +28675,7 @@
     </row>
     <row r="1119" spans="1:6">
       <c r="A1119" s="6">
-        <v>44652</v>
+        <v>44682</v>
       </c>
       <c r="B1119" s="7" t="inlineStr">
         <is>
@@ -29164,11 +28688,9 @@
         </is>
       </c>
       <c r="D1119" s="7">
-        <v>0.215</v>
-      </c>
-      <c r="E1119" s="6">
-        <v>44692</v>
-      </c>
+        <v>0.235</v>
+      </c>
+      <c r="E1119" s="6"/>
       <c r="F1119" s="7" t="inlineStr">
         <is>
           <t>월간</t>
@@ -29177,7 +28699,7 @@
     </row>
     <row r="1120" spans="1:6">
       <c r="A1120" s="6">
-        <v>44682</v>
+        <v>44713</v>
       </c>
       <c r="B1120" s="7" t="inlineStr">
         <is>
@@ -29190,11 +28712,9 @@
         </is>
       </c>
       <c r="D1120" s="7">
-        <v>0.235</v>
-      </c>
-      <c r="E1120" s="6">
-        <v>44726</v>
-      </c>
+        <v>0.225</v>
+      </c>
+      <c r="E1120" s="6"/>
       <c r="F1120" s="7" t="inlineStr">
         <is>
           <t>월간</t>
@@ -29203,7 +28723,7 @@
     </row>
     <row r="1121" spans="1:6">
       <c r="A1121" s="6">
-        <v>44713</v>
+        <v>44743</v>
       </c>
       <c r="B1121" s="7" t="inlineStr">
         <is>
@@ -29216,11 +28736,9 @@
         </is>
       </c>
       <c r="D1121" s="7">
-        <v>0.225</v>
-      </c>
-      <c r="E1121" s="6">
-        <v>44755</v>
-      </c>
+        <v>0.18</v>
+      </c>
+      <c r="E1121" s="6"/>
       <c r="F1121" s="7" t="inlineStr">
         <is>
           <t>월간</t>
@@ -29229,7 +28747,7 @@
     </row>
     <row r="1122" spans="1:6">
       <c r="A1122" s="6">
-        <v>44743</v>
+        <v>44774</v>
       </c>
       <c r="B1122" s="7" t="inlineStr">
         <is>
@@ -29242,11 +28760,9 @@
         </is>
       </c>
       <c r="D1122" s="7">
-        <v>0.18</v>
-      </c>
-      <c r="E1122" s="6">
-        <v>44783</v>
-      </c>
+        <v>0.22</v>
+      </c>
+      <c r="E1122" s="6"/>
       <c r="F1122" s="7" t="inlineStr">
         <is>
           <t>월간</t>
@@ -29255,7 +28771,7 @@
     </row>
     <row r="1123" spans="1:6">
       <c r="A1123" s="6">
-        <v>44774</v>
+        <v>44805</v>
       </c>
       <c r="B1123" s="7" t="inlineStr">
         <is>
@@ -29268,11 +28784,9 @@
         </is>
       </c>
       <c r="D1123" s="7">
-        <v>0.22</v>
-      </c>
-      <c r="E1123" s="6">
-        <v>44818</v>
-      </c>
+        <v>0.24</v>
+      </c>
+      <c r="E1123" s="6"/>
       <c r="F1123" s="7" t="inlineStr">
         <is>
           <t>월간</t>
@@ -29281,7 +28795,7 @@
     </row>
     <row r="1124" spans="1:6">
       <c r="A1124" s="6">
-        <v>44805</v>
+        <v>44835</v>
       </c>
       <c r="B1124" s="7" t="inlineStr">
         <is>
@@ -29294,11 +28808,9 @@
         </is>
       </c>
       <c r="D1124" s="7">
-        <v>0.24</v>
-      </c>
-      <c r="E1124" s="6">
-        <v>44876</v>
-      </c>
+        <v>0.245</v>
+      </c>
+      <c r="E1124" s="6"/>
       <c r="F1124" s="7" t="inlineStr">
         <is>
           <t>월간</t>
@@ -29307,7 +28819,7 @@
     </row>
     <row r="1125" spans="1:6">
       <c r="A1125" s="6">
-        <v>44835</v>
+        <v>44866</v>
       </c>
       <c r="B1125" s="7" t="inlineStr">
         <is>
@@ -29320,11 +28832,9 @@
         </is>
       </c>
       <c r="D1125" s="7">
-        <v>0.245</v>
-      </c>
-      <c r="E1125" s="6">
-        <v>44876</v>
-      </c>
+        <v>0.25</v>
+      </c>
+      <c r="E1125" s="6"/>
       <c r="F1125" s="7" t="inlineStr">
         <is>
           <t>월간</t>
@@ -29333,7 +28843,7 @@
     </row>
     <row r="1126" spans="1:6">
       <c r="A1126" s="6">
-        <v>44866</v>
+        <v>44896</v>
       </c>
       <c r="B1126" s="7" t="inlineStr">
         <is>
@@ -29346,11 +28856,9 @@
         </is>
       </c>
       <c r="D1126" s="7">
-        <v>0.25</v>
-      </c>
-      <c r="E1126" s="6">
-        <v>44905</v>
-      </c>
+        <v>0.41</v>
+      </c>
+      <c r="E1126" s="6"/>
       <c r="F1126" s="7" t="inlineStr">
         <is>
           <t>월간</t>
@@ -29359,7 +28867,7 @@
     </row>
     <row r="1127" spans="1:6">
       <c r="A1127" s="6">
-        <v>44896</v>
+        <v>44927</v>
       </c>
       <c r="B1127" s="7" t="inlineStr">
         <is>
@@ -29372,11 +28880,9 @@
         </is>
       </c>
       <c r="D1127" s="7">
-        <v>0.41</v>
-      </c>
-      <c r="E1127" s="6">
-        <v>44937</v>
-      </c>
+        <v>0.49</v>
+      </c>
+      <c r="E1127" s="6"/>
       <c r="F1127" s="7" t="inlineStr">
         <is>
           <t>월간</t>
@@ -29385,7 +28891,7 @@
     </row>
     <row r="1128" spans="1:6">
       <c r="A1128" s="6">
-        <v>44927</v>
+        <v>44958</v>
       </c>
       <c r="B1128" s="7" t="inlineStr">
         <is>
@@ -29398,11 +28904,9 @@
         </is>
       </c>
       <c r="D1128" s="7">
-        <v>0.49</v>
-      </c>
-      <c r="E1128" s="6">
-        <v>44970</v>
-      </c>
+        <v>0.5</v>
+      </c>
+      <c r="E1128" s="6"/>
       <c r="F1128" s="7" t="inlineStr">
         <is>
           <t>월간</t>
@@ -29411,7 +28915,7 @@
     </row>
     <row r="1129" spans="1:6">
       <c r="A1129" s="6">
-        <v>44958</v>
+        <v>44986</v>
       </c>
       <c r="B1129" s="7" t="inlineStr">
         <is>
@@ -29424,11 +28928,9 @@
         </is>
       </c>
       <c r="D1129" s="7">
-        <v>0.5</v>
-      </c>
-      <c r="E1129" s="6">
-        <v>44994</v>
-      </c>
+        <v>0.32</v>
+      </c>
+      <c r="E1129" s="6"/>
       <c r="F1129" s="7" t="inlineStr">
         <is>
           <t>월간</t>
@@ -29437,7 +28939,7 @@
     </row>
     <row r="1130" spans="1:6">
       <c r="A1130" s="6">
-        <v>44986</v>
+        <v>45017</v>
       </c>
       <c r="B1130" s="7" t="inlineStr">
         <is>
@@ -29450,11 +28952,9 @@
         </is>
       </c>
       <c r="D1130" s="7">
-        <v>0.32</v>
-      </c>
-      <c r="E1130" s="6">
-        <v>45023</v>
-      </c>
+        <v>0.385</v>
+      </c>
+      <c r="E1130" s="6"/>
       <c r="F1130" s="7" t="inlineStr">
         <is>
           <t>월간</t>
@@ -29463,7 +28963,7 @@
     </row>
     <row r="1131" spans="1:6">
       <c r="A1131" s="6">
-        <v>45017</v>
+        <v>45047</v>
       </c>
       <c r="B1131" s="7" t="inlineStr">
         <is>
@@ -29476,11 +28976,9 @@
         </is>
       </c>
       <c r="D1131" s="7">
-        <v>0.385</v>
-      </c>
-      <c r="E1131" s="6">
-        <v>45056</v>
-      </c>
+        <v>0.43</v>
+      </c>
+      <c r="E1131" s="6"/>
       <c r="F1131" s="7" t="inlineStr">
         <is>
           <t>월간</t>
@@ -29489,7 +28987,7 @@
     </row>
     <row r="1132" spans="1:6">
       <c r="A1132" s="6">
-        <v>45047</v>
+        <v>45078</v>
       </c>
       <c r="B1132" s="7" t="inlineStr">
         <is>
@@ -29502,11 +29000,9 @@
         </is>
       </c>
       <c r="D1132" s="7">
-        <v>0.43</v>
-      </c>
-      <c r="E1132" s="6">
-        <v>45090</v>
-      </c>
+        <v>0.395</v>
+      </c>
+      <c r="E1132" s="6"/>
       <c r="F1132" s="7" t="inlineStr">
         <is>
           <t>월간</t>
@@ -29515,7 +29011,7 @@
     </row>
     <row r="1133" spans="1:6">
       <c r="A1133" s="6">
-        <v>45078</v>
+        <v>45108</v>
       </c>
       <c r="B1133" s="7" t="inlineStr">
         <is>
@@ -29528,11 +29024,9 @@
         </is>
       </c>
       <c r="D1133" s="7">
-        <v>0.395</v>
-      </c>
-      <c r="E1133" s="6">
-        <v>45114</v>
-      </c>
+        <v>0.595</v>
+      </c>
+      <c r="E1133" s="6"/>
       <c r="F1133" s="7" t="inlineStr">
         <is>
           <t>월간</t>
@@ -29541,7 +29035,7 @@
     </row>
     <row r="1134" spans="1:6">
       <c r="A1134" s="6">
-        <v>45108</v>
+        <v>45139</v>
       </c>
       <c r="B1134" s="7" t="inlineStr">
         <is>
@@ -29554,11 +29048,9 @@
         </is>
       </c>
       <c r="D1134" s="7">
-        <v>0.595</v>
-      </c>
-      <c r="E1134" s="6">
-        <v>45148</v>
-      </c>
+        <v>0.64</v>
+      </c>
+      <c r="E1134" s="6"/>
       <c r="F1134" s="7" t="inlineStr">
         <is>
           <t>월간</t>
@@ -29567,7 +29059,7 @@
     </row>
     <row r="1135" spans="1:6">
       <c r="A1135" s="6">
-        <v>45139</v>
+        <v>45170</v>
       </c>
       <c r="B1135" s="7" t="inlineStr">
         <is>
@@ -29580,11 +29072,9 @@
         </is>
       </c>
       <c r="D1135" s="7">
-        <v>0.64</v>
-      </c>
-      <c r="E1135" s="6">
-        <v>45178</v>
-      </c>
+        <v>0.765</v>
+      </c>
+      <c r="E1135" s="6"/>
       <c r="F1135" s="7" t="inlineStr">
         <is>
           <t>월간</t>
@@ -29593,7 +29083,7 @@
     </row>
     <row r="1136" spans="1:6">
       <c r="A1136" s="6">
-        <v>45170</v>
+        <v>45200</v>
       </c>
       <c r="B1136" s="7" t="inlineStr">
         <is>
@@ -29606,11 +29096,9 @@
         </is>
       </c>
       <c r="D1136" s="7">
-        <v>0.765</v>
-      </c>
-      <c r="E1136" s="6">
-        <v>45206</v>
-      </c>
+        <v>0.95</v>
+      </c>
+      <c r="E1136" s="6"/>
       <c r="F1136" s="7" t="inlineStr">
         <is>
           <t>월간</t>
@@ -29619,7 +29107,7 @@
     </row>
     <row r="1137" spans="1:6">
       <c r="A1137" s="6">
-        <v>45200</v>
+        <v>45231</v>
       </c>
       <c r="B1137" s="7" t="inlineStr">
         <is>
@@ -29632,11 +29120,9 @@
         </is>
       </c>
       <c r="D1137" s="7">
-        <v>0.95</v>
-      </c>
-      <c r="E1137" s="6">
-        <v>45240</v>
-      </c>
+        <v>0.66</v>
+      </c>
+      <c r="E1137" s="6"/>
       <c r="F1137" s="7" t="inlineStr">
         <is>
           <t>월간</t>
@@ -29645,7 +29131,7 @@
     </row>
     <row r="1138" spans="1:6">
       <c r="A1138" s="6">
-        <v>45231</v>
+        <v>45261</v>
       </c>
       <c r="B1138" s="7" t="inlineStr">
         <is>
@@ -29658,11 +29144,9 @@
         </is>
       </c>
       <c r="D1138" s="7">
-        <v>0.66</v>
-      </c>
-      <c r="E1138" s="6">
-        <v>45269</v>
-      </c>
+        <v>0.62</v>
+      </c>
+      <c r="E1138" s="6"/>
       <c r="F1138" s="7" t="inlineStr">
         <is>
           <t>월간</t>
@@ -29671,7 +29155,7 @@
     </row>
     <row r="1139" spans="1:6">
       <c r="A1139" s="6">
-        <v>45261</v>
+        <v>45292</v>
       </c>
       <c r="B1139" s="7" t="inlineStr">
         <is>
@@ -29684,11 +29168,9 @@
         </is>
       </c>
       <c r="D1139" s="7">
-        <v>0.62</v>
-      </c>
-      <c r="E1139" s="6">
-        <v>45302</v>
-      </c>
+        <v>0.73</v>
+      </c>
+      <c r="E1139" s="6"/>
       <c r="F1139" s="7" t="inlineStr">
         <is>
           <t>월간</t>
@@ -29697,7 +29179,7 @@
     </row>
     <row r="1140" spans="1:6">
       <c r="A1140" s="6">
-        <v>45292</v>
+        <v>45323</v>
       </c>
       <c r="B1140" s="7" t="inlineStr">
         <is>
@@ -29710,11 +29192,9 @@
         </is>
       </c>
       <c r="D1140" s="7">
-        <v>0.73</v>
-      </c>
-      <c r="E1140" s="6">
-        <v>45392</v>
-      </c>
+        <v>0.71</v>
+      </c>
+      <c r="E1140" s="6"/>
       <c r="F1140" s="7" t="inlineStr">
         <is>
           <t>월간</t>
@@ -29723,7 +29203,7 @@
     </row>
     <row r="1141" spans="1:6">
       <c r="A1141" s="6">
-        <v>45323</v>
+        <v>45352</v>
       </c>
       <c r="B1141" s="7" t="inlineStr">
         <is>
@@ -29736,11 +29216,9 @@
         </is>
       </c>
       <c r="D1141" s="7">
-        <v>0.71</v>
-      </c>
-      <c r="E1141" s="6">
-        <v>45392</v>
-      </c>
+        <v>0.725</v>
+      </c>
+      <c r="E1141" s="6"/>
       <c r="F1141" s="7" t="inlineStr">
         <is>
           <t>월간</t>
@@ -29749,7 +29227,7 @@
     </row>
     <row r="1142" spans="1:6">
       <c r="A1142" s="6">
-        <v>45352</v>
+        <v>45383</v>
       </c>
       <c r="B1142" s="7" t="inlineStr">
         <is>
@@ -29762,11 +29240,9 @@
         </is>
       </c>
       <c r="D1142" s="7">
-        <v>0.725</v>
-      </c>
-      <c r="E1142" s="6">
-        <v>45392</v>
-      </c>
+        <v>0.87</v>
+      </c>
+      <c r="E1142" s="6"/>
       <c r="F1142" s="7" t="inlineStr">
         <is>
           <t>월간</t>
@@ -29775,7 +29251,7 @@
     </row>
     <row r="1143" spans="1:6">
       <c r="A1143" s="6">
-        <v>45383</v>
+        <v>45413</v>
       </c>
       <c r="B1143" s="7" t="inlineStr">
         <is>
@@ -29788,11 +29264,9 @@
         </is>
       </c>
       <c r="D1143" s="7">
-        <v>0.87</v>
-      </c>
-      <c r="E1143" s="6">
-        <v>45427</v>
-      </c>
+        <v>1.07</v>
+      </c>
+      <c r="E1143" s="6"/>
       <c r="F1143" s="7" t="inlineStr">
         <is>
           <t>월간</t>
@@ -29801,7 +29275,7 @@
     </row>
     <row r="1144" spans="1:6">
       <c r="A1144" s="6">
-        <v>45413</v>
+        <v>45444</v>
       </c>
       <c r="B1144" s="7" t="inlineStr">
         <is>
@@ -29814,11 +29288,9 @@
         </is>
       </c>
       <c r="D1144" s="7">
-        <v>1.07</v>
-      </c>
-      <c r="E1144" s="6">
-        <v>45460</v>
-      </c>
+        <v>1.05</v>
+      </c>
+      <c r="E1144" s="6"/>
       <c r="F1144" s="7" t="inlineStr">
         <is>
           <t>월간</t>
@@ -29827,7 +29299,7 @@
     </row>
     <row r="1145" spans="1:6">
       <c r="A1145" s="6">
-        <v>45444</v>
+        <v>45474</v>
       </c>
       <c r="B1145" s="7" t="inlineStr">
         <is>
@@ -29840,11 +29312,9 @@
         </is>
       </c>
       <c r="D1145" s="7">
-        <v>1.05</v>
-      </c>
-      <c r="E1145" s="6">
-        <v>45488</v>
-      </c>
+        <v>1.045</v>
+      </c>
+      <c r="E1145" s="6"/>
       <c r="F1145" s="7" t="inlineStr">
         <is>
           <t>월간</t>
@@ -29853,7 +29323,7 @@
     </row>
     <row r="1146" spans="1:6">
       <c r="A1146" s="6">
-        <v>45474</v>
+        <v>45505</v>
       </c>
       <c r="B1146" s="7" t="inlineStr">
         <is>
@@ -29866,11 +29336,9 @@
         </is>
       </c>
       <c r="D1146" s="7">
-        <v>1.045</v>
-      </c>
-      <c r="E1146" s="6">
-        <v>45551</v>
-      </c>
+        <v>0.89</v>
+      </c>
+      <c r="E1146" s="6"/>
       <c r="F1146" s="7" t="inlineStr">
         <is>
           <t>월간</t>
@@ -29879,7 +29347,7 @@
     </row>
     <row r="1147" spans="1:6">
       <c r="A1147" s="6">
-        <v>45505</v>
+        <v>45536</v>
       </c>
       <c r="B1147" s="7" t="inlineStr">
         <is>
@@ -29892,11 +29360,9 @@
         </is>
       </c>
       <c r="D1147" s="7">
-        <v>0.89</v>
-      </c>
-      <c r="E1147" s="6">
-        <v>45551</v>
-      </c>
+        <v>0.855</v>
+      </c>
+      <c r="E1147" s="6"/>
       <c r="F1147" s="7" t="inlineStr">
         <is>
           <t>월간</t>
@@ -29905,7 +29371,7 @@
     </row>
     <row r="1148" spans="1:6">
       <c r="A1148" s="6">
-        <v>45536</v>
+        <v>45566</v>
       </c>
       <c r="B1148" s="7" t="inlineStr">
         <is>
@@ -29918,11 +29384,9 @@
         </is>
       </c>
       <c r="D1148" s="7">
-        <v>0.855</v>
-      </c>
-      <c r="E1148" s="6">
-        <v>45580</v>
-      </c>
+        <v>0.935</v>
+      </c>
+      <c r="E1148" s="6"/>
       <c r="F1148" s="7" t="inlineStr">
         <is>
           <t>월간</t>
@@ -29931,7 +29395,7 @@
     </row>
     <row r="1149" spans="1:6">
       <c r="A1149" s="6">
-        <v>45566</v>
+        <v>45597</v>
       </c>
       <c r="B1149" s="7" t="inlineStr">
         <is>
@@ -29944,11 +29408,9 @@
         </is>
       </c>
       <c r="D1149" s="7">
-        <v>0.935</v>
-      </c>
-      <c r="E1149" s="6">
-        <v>45611</v>
-      </c>
+        <v>1.05</v>
+      </c>
+      <c r="E1149" s="6"/>
       <c r="F1149" s="7" t="inlineStr">
         <is>
           <t>월간</t>
@@ -29957,7 +29419,7 @@
     </row>
     <row r="1150" spans="1:6">
       <c r="A1150" s="6">
-        <v>45597</v>
+        <v>45627</v>
       </c>
       <c r="B1150" s="7" t="inlineStr">
         <is>
@@ -29970,11 +29432,9 @@
         </is>
       </c>
       <c r="D1150" s="7">
-        <v>1.05</v>
-      </c>
-      <c r="E1150" s="6">
-        <v>45642</v>
-      </c>
+        <v>1.09</v>
+      </c>
+      <c r="E1150" s="6"/>
       <c r="F1150" s="7" t="inlineStr">
         <is>
           <t>월간</t>
@@ -29983,7 +29443,7 @@
     </row>
     <row r="1151" spans="1:6">
       <c r="A1151" s="6">
-        <v>45627</v>
+        <v>45658</v>
       </c>
       <c r="B1151" s="7" t="inlineStr">
         <is>
@@ -29996,11 +29456,9 @@
         </is>
       </c>
       <c r="D1151" s="7">
-        <v>1.09</v>
-      </c>
-      <c r="E1151" s="6">
-        <v>45672</v>
-      </c>
+        <v>1.245</v>
+      </c>
+      <c r="E1151" s="6"/>
       <c r="F1151" s="7" t="inlineStr">
         <is>
           <t>월간</t>
@@ -30009,7 +29467,7 @@
     </row>
     <row r="1152" spans="1:6">
       <c r="A1152" s="6">
-        <v>45658</v>
+        <v>45689</v>
       </c>
       <c r="B1152" s="7" t="inlineStr">
         <is>
@@ -30022,11 +29480,9 @@
         </is>
       </c>
       <c r="D1152" s="7">
-        <v>1.245</v>
-      </c>
-      <c r="E1152" s="6">
-        <v>45705</v>
-      </c>
+        <v>1.37</v>
+      </c>
+      <c r="E1152" s="6"/>
       <c r="F1152" s="7" t="inlineStr">
         <is>
           <t>월간</t>
@@ -30035,7 +29491,7 @@
     </row>
     <row r="1153" spans="1:6">
       <c r="A1153" s="6">
-        <v>45689</v>
+        <v>45717</v>
       </c>
       <c r="B1153" s="7" t="inlineStr">
         <is>
@@ -30048,11 +29504,9 @@
         </is>
       </c>
       <c r="D1153" s="7">
-        <v>1.37</v>
-      </c>
-      <c r="E1153" s="6">
-        <v>45733</v>
-      </c>
+        <v>1.485</v>
+      </c>
+      <c r="E1153" s="6"/>
       <c r="F1153" s="7" t="inlineStr">
         <is>
           <t>월간</t>
@@ -30061,7 +29515,7 @@
     </row>
     <row r="1154" spans="1:6">
       <c r="A1154" s="6">
-        <v>45717</v>
+        <v>45748</v>
       </c>
       <c r="B1154" s="7" t="inlineStr">
         <is>
@@ -30074,11 +29528,9 @@
         </is>
       </c>
       <c r="D1154" s="7">
-        <v>1.485</v>
-      </c>
-      <c r="E1154" s="6">
-        <v>45762</v>
-      </c>
+        <v>1.31</v>
+      </c>
+      <c r="E1154" s="6"/>
       <c r="F1154" s="7" t="inlineStr">
         <is>
           <t>월간</t>
@@ -30087,7 +29539,7 @@
     </row>
     <row r="1155" spans="1:6">
       <c r="A1155" s="6">
-        <v>45748</v>
+        <v>45778</v>
       </c>
       <c r="B1155" s="7" t="inlineStr">
         <is>
@@ -30100,11 +29552,9 @@
         </is>
       </c>
       <c r="D1155" s="7">
-        <v>1.31</v>
-      </c>
-      <c r="E1155" s="6">
-        <v>45792</v>
-      </c>
+        <v>1.5</v>
+      </c>
+      <c r="E1155" s="6"/>
       <c r="F1155" s="7" t="inlineStr">
         <is>
           <t>월간</t>
@@ -30113,7 +29563,7 @@
     </row>
     <row r="1156" spans="1:6">
       <c r="A1156" s="6">
-        <v>45778</v>
+        <v>45809</v>
       </c>
       <c r="B1156" s="7" t="inlineStr">
         <is>
@@ -30126,11 +29576,9 @@
         </is>
       </c>
       <c r="D1156" s="7">
-        <v>1.5</v>
-      </c>
-      <c r="E1156" s="6">
-        <v>45824</v>
-      </c>
+        <v>1.42</v>
+      </c>
+      <c r="E1156" s="6"/>
       <c r="F1156" s="7" t="inlineStr">
         <is>
           <t>월간</t>
@@ -30139,7 +29587,7 @@
     </row>
     <row r="1157" spans="1:6">
       <c r="A1157" s="6">
-        <v>45809</v>
+        <v>45839</v>
       </c>
       <c r="B1157" s="7" t="inlineStr">
         <is>
@@ -30152,11 +29600,9 @@
         </is>
       </c>
       <c r="D1157" s="7">
-        <v>1.42</v>
-      </c>
-      <c r="E1157" s="6">
-        <v>45853</v>
-      </c>
+        <v>1.545</v>
+      </c>
+      <c r="E1157" s="6"/>
       <c r="F1157" s="7" t="inlineStr">
         <is>
           <t>월간</t>
@@ -30165,7 +29611,7 @@
     </row>
     <row r="1158" spans="1:6">
       <c r="A1158" s="6">
-        <v>45839</v>
+        <v>45870</v>
       </c>
       <c r="B1158" s="7" t="inlineStr">
         <is>
@@ -30178,11 +29624,9 @@
         </is>
       </c>
       <c r="D1158" s="7">
-        <v>1.545</v>
-      </c>
-      <c r="E1158" s="6">
-        <v>45884</v>
-      </c>
+        <v>1.6</v>
+      </c>
+      <c r="E1158" s="6"/>
       <c r="F1158" s="7" t="inlineStr">
         <is>
           <t>월간</t>
@@ -30191,7 +29635,7 @@
     </row>
     <row r="1159" spans="1:6">
       <c r="A1159" s="6">
-        <v>45870</v>
+        <v>45901</v>
       </c>
       <c r="B1159" s="7" t="inlineStr">
         <is>
@@ -30204,11 +29648,9 @@
         </is>
       </c>
       <c r="D1159" s="7">
-        <v>1.6</v>
-      </c>
-      <c r="E1159" s="6">
-        <v>45915</v>
-      </c>
+        <v>1.645</v>
+      </c>
+      <c r="E1159" s="6"/>
       <c r="F1159" s="7" t="inlineStr">
         <is>
           <t>월간</t>
@@ -30217,7 +29659,7 @@
     </row>
     <row r="1160" spans="1:6">
       <c r="A1160" s="6">
-        <v>45901</v>
+        <v>45931</v>
       </c>
       <c r="B1160" s="7" t="inlineStr">
         <is>
@@ -30230,11 +29672,9 @@
         </is>
       </c>
       <c r="D1160" s="7">
-        <v>1.645</v>
-      </c>
-      <c r="E1160" s="6">
-        <v>45945</v>
-      </c>
+        <v>1.655</v>
+      </c>
+      <c r="E1160" s="6"/>
       <c r="F1160" s="7" t="inlineStr">
         <is>
           <t>월간</t>
@@ -30243,7 +29683,7 @@
     </row>
     <row r="1161" spans="1:6">
       <c r="A1161" s="6">
-        <v>45931</v>
+        <v>45962</v>
       </c>
       <c r="B1161" s="7" t="inlineStr">
         <is>
@@ -30256,11 +29696,9 @@
         </is>
       </c>
       <c r="D1161" s="7">
-        <v>1.655</v>
-      </c>
-      <c r="E1161" s="6">
-        <v>45978</v>
-      </c>
+        <v>1.805</v>
+      </c>
+      <c r="E1161" s="6"/>
       <c r="F1161" s="7" t="inlineStr">
         <is>
           <t>월간</t>
@@ -30269,7 +29707,7 @@
     </row>
     <row r="1162" spans="1:6">
       <c r="A1162" s="6">
-        <v>45962</v>
+        <v>45992</v>
       </c>
       <c r="B1162" s="7" t="inlineStr">
         <is>
@@ -30282,11 +29720,9 @@
         </is>
       </c>
       <c r="D1162" s="7">
-        <v>1.805</v>
-      </c>
-      <c r="E1162" s="6">
-        <v>46006</v>
-      </c>
+        <v>2.06</v>
+      </c>
+      <c r="E1162" s="6"/>
       <c r="F1162" s="7" t="inlineStr">
         <is>
           <t>월간</t>
@@ -30295,7 +29731,7 @@
     </row>
     <row r="1163" spans="1:6">
       <c r="A1163" s="6">
-        <v>45992</v>
+        <v>46023</v>
       </c>
       <c r="B1163" s="7" t="inlineStr">
         <is>
@@ -30308,11 +29744,9 @@
         </is>
       </c>
       <c r="D1163" s="7">
-        <v>2.06</v>
-      </c>
-      <c r="E1163" s="6">
-        <v>46037</v>
-      </c>
+        <v>2.24</v>
+      </c>
+      <c r="E1163" s="6"/>
       <c r="F1163" s="7" t="inlineStr">
         <is>
           <t>월간</t>
@@ -30321,7 +29755,7 @@
     </row>
     <row r="1164" spans="1:6">
       <c r="A1164" s="6">
-        <v>46023</v>
+        <v>46054</v>
       </c>
       <c r="B1164" s="7" t="inlineStr">
         <is>
@@ -30334,11 +29768,9 @@
         </is>
       </c>
       <c r="D1164" s="7">
-        <v>2.24</v>
-      </c>
-      <c r="E1164" s="6">
-        <v>46069</v>
-      </c>
+        <v>2.11</v>
+      </c>
+      <c r="E1164" s="6"/>
       <c r="F1164" s="7" t="inlineStr">
         <is>
           <t>월간</t>
@@ -30347,7 +29779,7 @@
     </row>
     <row r="1165" spans="1:6">
       <c r="A1165" s="6">
-        <v>46054</v>
+        <v>46082</v>
       </c>
       <c r="B1165" s="7" t="inlineStr">
         <is>
@@ -30360,11 +29792,9 @@
         </is>
       </c>
       <c r="D1165" s="7">
-        <v>2.11</v>
-      </c>
-      <c r="E1165" s="6">
-        <v>46097</v>
-      </c>
+        <v>2.345</v>
+      </c>
+      <c r="E1165" s="6"/>
       <c r="F1165" s="7" t="inlineStr">
         <is>
           <t>월간</t>
@@ -30373,7 +29803,7 @@
     </row>
     <row r="1166" spans="1:6">
       <c r="A1166" s="6">
-        <v>46082</v>
+        <v>46113</v>
       </c>
       <c r="B1166" s="7" t="inlineStr">
         <is>
@@ -30386,11 +29816,9 @@
         </is>
       </c>
       <c r="D1166" s="7">
-        <v>2.345</v>
-      </c>
-      <c r="E1166" s="6">
-        <v>46127</v>
-      </c>
+        <v>2.515</v>
+      </c>
+      <c r="E1166" s="6"/>
       <c r="F1166" s="7" t="inlineStr">
         <is>
           <t>월간</t>
@@ -30399,7 +29827,7 @@
     </row>
     <row r="1167" spans="1:6">
       <c r="A1167" s="6">
-        <v>46113</v>
+        <v>46143</v>
       </c>
       <c r="B1167" s="7" t="inlineStr">
         <is>
@@ -30412,11 +29840,9 @@
         </is>
       </c>
       <c r="D1167" s="7">
-        <v>2.515</v>
-      </c>
-      <c r="E1167" s="6">
-        <v>46157</v>
-      </c>
+        <v>2.65</v>
+      </c>
+      <c r="E1167" s="6"/>
       <c r="F1167" s="7" t="inlineStr">
         <is>
           <t>월간</t>
@@ -30425,7 +29851,7 @@
     </row>
     <row r="1168" spans="1:6">
       <c r="A1168" s="6">
-        <v>46143</v>
+        <v>46174</v>
       </c>
       <c r="B1168" s="7" t="inlineStr">
         <is>
@@ -30438,11 +29864,9 @@
         </is>
       </c>
       <c r="D1168" s="7">
-        <v>2.65</v>
-      </c>
-      <c r="E1168" s="6">
-        <v>46188</v>
-      </c>
+        <v>2.67</v>
+      </c>
+      <c r="E1168" s="6"/>
       <c r="F1168" s="7" t="inlineStr">
         <is>
           <t>월간</t>
@@ -30451,7 +29875,7 @@
     </row>
     <row r="1169" spans="1:6">
       <c r="A1169" s="6">
-        <v>46174</v>
+        <v>46204</v>
       </c>
       <c r="B1169" s="7" t="inlineStr">
         <is>
@@ -30464,11 +29888,9 @@
         </is>
       </c>
       <c r="D1169" s="7">
-        <v>2.67</v>
-      </c>
-      <c r="E1169" s="6">
-        <v>46219</v>
-      </c>
+        <v>2.79</v>
+      </c>
+      <c r="E1169" s="6"/>
       <c r="F1169" s="7" t="inlineStr">
         <is>
           <t>월간</t>
@@ -30477,7 +29899,7 @@
     </row>
     <row r="1170" spans="1:6">
       <c r="A1170" s="6">
-        <v>46204</v>
+        <v>46235</v>
       </c>
       <c r="B1170" s="7" t="inlineStr">
         <is>
@@ -30490,11 +29912,9 @@
         </is>
       </c>
       <c r="D1170" s="7">
-        <v>2.79</v>
-      </c>
-      <c r="E1170" s="6">
-        <v>46280</v>
-      </c>
+        <v>2.94</v>
+      </c>
+      <c r="E1170" s="6"/>
       <c r="F1170" s="7" t="inlineStr">
         <is>
           <t>월간</t>
@@ -30502,30 +29922,12 @@
       </c>
     </row>
     <row r="1171" spans="1:6">
-      <c r="A1171" s="6">
-        <v>46235</v>
-      </c>
-      <c r="B1171" s="7" t="inlineStr">
-        <is>
-          <t>일본</t>
-        </is>
-      </c>
-      <c r="C1171" s="7" t="inlineStr">
-        <is>
-          <t>국채10년</t>
-        </is>
-      </c>
-      <c r="D1171" s="7">
-        <v>2.94</v>
-      </c>
-      <c r="E1171" s="6">
-        <v>46280</v>
-      </c>
-      <c r="F1171" s="7" t="inlineStr">
-        <is>
-          <t>월간</t>
-        </is>
-      </c>
+      <c r="A1171" s="6"/>
+      <c r="B1171" s="7"/>
+      <c r="C1171" s="7"/>
+      <c r="D1171" s="7"/>
+      <c r="E1171" s="6"/>
+      <c r="F1171" s="7"/>
     </row>
     <row r="1172" spans="1:6">
       <c r="A1172" s="6"/>

--- a/매크로_트래커_로우데이터.xlsx
+++ b/매크로_트래커_로우데이터.xlsx
@@ -17,6 +17,7 @@
     <sheet name="로우데이터" sheetId="2" r:id="rId2"/>
     <sheet name="지표목록" sheetId="3" r:id="rId3"/>
     <sheet name="_목록" sheetId="4" state="hidden" r:id="rId4"/>
+    <sheet name="발표일정" sheetId="5" r:id="rId8"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">로우데이터!$A$1:$F$1</definedName>
@@ -71898,4 +71899,1223 @@
   <phoneticPr fontId="7" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:F40"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="17"/>
+  <cols>
+    <col min="1" max="1" width="12" customWidth="1"/>
+    <col min="2" max="2" width="10" customWidth="1"/>
+    <col min="3" max="3" width="22" customWidth="1"/>
+    <col min="4" max="4" width="12" customWidth="1"/>
+    <col min="5" max="5" width="16" customWidth="1"/>
+    <col min="6" max="6" width="34" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:6" ht="22" customHeight="1">
+      <c r="A1" s="5" t="inlineStr">
+        <is>
+          <t>예정일</t>
+        </is>
+      </c>
+      <c r="B1" s="5" t="inlineStr">
+        <is>
+          <t>국가</t>
+        </is>
+      </c>
+      <c r="C1" s="5" t="inlineStr">
+        <is>
+          <t>지표</t>
+        </is>
+      </c>
+      <c r="D1" s="5" t="inlineStr">
+        <is>
+          <t>대상기간</t>
+        </is>
+      </c>
+      <c r="E1" s="5" t="inlineStr">
+        <is>
+          <t>출처</t>
+        </is>
+      </c>
+      <c r="F1" s="5" t="inlineStr">
+        <is>
+          <t>비고</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" spans="1:6">
+      <c r="A2" s="6">
+        <v>46309</v>
+      </c>
+      <c r="B2" s="7" t="inlineStr">
+        <is>
+          <t>미국</t>
+        </is>
+      </c>
+      <c r="C2" s="7" t="inlineStr">
+        <is>
+          <t>CPI 헤드라인</t>
+        </is>
+      </c>
+      <c r="D2" s="7" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="E2" s="7" t="inlineStr">
+        <is>
+          <t>FRED(BLS release calendar)</t>
+        </is>
+      </c>
+      <c r="F2" s="7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="3" spans="1:6">
+      <c r="A3" s="6">
+        <v>46309</v>
+      </c>
+      <c r="B3" s="7" t="inlineStr">
+        <is>
+          <t>미국</t>
+        </is>
+      </c>
+      <c r="C3" s="7" t="inlineStr">
+        <is>
+          <t>CPI 근원</t>
+        </is>
+      </c>
+      <c r="D3" s="7" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="E3" s="7" t="inlineStr">
+        <is>
+          <t>FRED(BLS release calendar)</t>
+        </is>
+      </c>
+      <c r="F3" s="7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="4" spans="1:6">
+      <c r="A4" s="6">
+        <v>46336</v>
+      </c>
+      <c r="B4" s="7" t="inlineStr">
+        <is>
+          <t>미국</t>
+        </is>
+      </c>
+      <c r="C4" s="7" t="inlineStr">
+        <is>
+          <t>CPI 헤드라인</t>
+        </is>
+      </c>
+      <c r="D4" s="7" t="inlineStr">
+        <is>
+          <t>2026-10</t>
+        </is>
+      </c>
+      <c r="E4" s="7" t="inlineStr">
+        <is>
+          <t>FRED(BLS release calendar)</t>
+        </is>
+      </c>
+      <c r="F4" s="7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="5" spans="1:6">
+      <c r="A5" s="6">
+        <v>46336</v>
+      </c>
+      <c r="B5" s="7" t="inlineStr">
+        <is>
+          <t>미국</t>
+        </is>
+      </c>
+      <c r="C5" s="7" t="inlineStr">
+        <is>
+          <t>CPI 근원</t>
+        </is>
+      </c>
+      <c r="D5" s="7" t="inlineStr">
+        <is>
+          <t>2026-10</t>
+        </is>
+      </c>
+      <c r="E5" s="7" t="inlineStr">
+        <is>
+          <t>FRED(BLS release calendar)</t>
+        </is>
+      </c>
+      <c r="F5" s="7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="6" spans="1:6">
+      <c r="A6" s="6">
+        <v>46366</v>
+      </c>
+      <c r="B6" s="7" t="inlineStr">
+        <is>
+          <t>미국</t>
+        </is>
+      </c>
+      <c r="C6" s="7" t="inlineStr">
+        <is>
+          <t>CPI 헤드라인</t>
+        </is>
+      </c>
+      <c r="D6" s="7" t="inlineStr">
+        <is>
+          <t>2026-11</t>
+        </is>
+      </c>
+      <c r="E6" s="7" t="inlineStr">
+        <is>
+          <t>FRED(BLS release calendar)</t>
+        </is>
+      </c>
+      <c r="F6" s="7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="7" spans="1:6">
+      <c r="A7" s="6">
+        <v>46366</v>
+      </c>
+      <c r="B7" s="7" t="inlineStr">
+        <is>
+          <t>미국</t>
+        </is>
+      </c>
+      <c r="C7" s="7" t="inlineStr">
+        <is>
+          <t>CPI 근원</t>
+        </is>
+      </c>
+      <c r="D7" s="7" t="inlineStr">
+        <is>
+          <t>2026-11</t>
+        </is>
+      </c>
+      <c r="E7" s="7" t="inlineStr">
+        <is>
+          <t>FRED(BLS release calendar)</t>
+        </is>
+      </c>
+      <c r="F7" s="7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="8" spans="1:6">
+      <c r="A8" s="6">
+        <v>46297</v>
+      </c>
+      <c r="B8" s="7" t="inlineStr">
+        <is>
+          <t>미국</t>
+        </is>
+      </c>
+      <c r="C8" s="7" t="inlineStr">
+        <is>
+          <t>비농업고용</t>
+        </is>
+      </c>
+      <c r="D8" s="7" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="E8" s="7" t="inlineStr">
+        <is>
+          <t>FRED(BLS Employment Situation)</t>
+        </is>
+      </c>
+      <c r="F8" s="7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="9" spans="1:6">
+      <c r="A9" s="6">
+        <v>46297</v>
+      </c>
+      <c r="B9" s="7" t="inlineStr">
+        <is>
+          <t>미국</t>
+        </is>
+      </c>
+      <c r="C9" s="7" t="inlineStr">
+        <is>
+          <t>실업률</t>
+        </is>
+      </c>
+      <c r="D9" s="7" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="E9" s="7" t="inlineStr">
+        <is>
+          <t>FRED(BLS Employment Situation)</t>
+        </is>
+      </c>
+      <c r="F9" s="7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="10" spans="1:6">
+      <c r="A10" s="6">
+        <v>46332</v>
+      </c>
+      <c r="B10" s="7" t="inlineStr">
+        <is>
+          <t>미국</t>
+        </is>
+      </c>
+      <c r="C10" s="7" t="inlineStr">
+        <is>
+          <t>비농업고용</t>
+        </is>
+      </c>
+      <c r="D10" s="7" t="inlineStr">
+        <is>
+          <t>2026-10</t>
+        </is>
+      </c>
+      <c r="E10" s="7" t="inlineStr">
+        <is>
+          <t>FRED(BLS Employment Situation)</t>
+        </is>
+      </c>
+      <c r="F10" s="7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="11" spans="1:6">
+      <c r="A11" s="6">
+        <v>46332</v>
+      </c>
+      <c r="B11" s="7" t="inlineStr">
+        <is>
+          <t>미국</t>
+        </is>
+      </c>
+      <c r="C11" s="7" t="inlineStr">
+        <is>
+          <t>실업률</t>
+        </is>
+      </c>
+      <c r="D11" s="7" t="inlineStr">
+        <is>
+          <t>2026-10</t>
+        </is>
+      </c>
+      <c r="E11" s="7" t="inlineStr">
+        <is>
+          <t>FRED(BLS Employment Situation)</t>
+        </is>
+      </c>
+      <c r="F11" s="7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="12" spans="1:6">
+      <c r="A12" s="6">
+        <v>46360</v>
+      </c>
+      <c r="B12" s="7" t="inlineStr">
+        <is>
+          <t>미국</t>
+        </is>
+      </c>
+      <c r="C12" s="7" t="inlineStr">
+        <is>
+          <t>비농업고용</t>
+        </is>
+      </c>
+      <c r="D12" s="7" t="inlineStr">
+        <is>
+          <t>2026-11</t>
+        </is>
+      </c>
+      <c r="E12" s="7" t="inlineStr">
+        <is>
+          <t>FRED(BLS Employment Situation)</t>
+        </is>
+      </c>
+      <c r="F12" s="7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="13" spans="1:6">
+      <c r="A13" s="6">
+        <v>46360</v>
+      </c>
+      <c r="B13" s="7" t="inlineStr">
+        <is>
+          <t>미국</t>
+        </is>
+      </c>
+      <c r="C13" s="7" t="inlineStr">
+        <is>
+          <t>실업률</t>
+        </is>
+      </c>
+      <c r="D13" s="7" t="inlineStr">
+        <is>
+          <t>2026-11</t>
+        </is>
+      </c>
+      <c r="E13" s="7" t="inlineStr">
+        <is>
+          <t>FRED(BLS Employment Situation)</t>
+        </is>
+      </c>
+      <c r="F13" s="7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="14" spans="1:6">
+      <c r="A14" s="6">
+        <v>46295</v>
+      </c>
+      <c r="B14" s="7" t="inlineStr">
+        <is>
+          <t>미국</t>
+        </is>
+      </c>
+      <c r="C14" s="7" t="inlineStr">
+        <is>
+          <t>PCE 근원</t>
+        </is>
+      </c>
+      <c r="D14" s="7" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="E14" s="7" t="inlineStr">
+        <is>
+          <t>FRED(BEA Personal Income and Outlays)</t>
+        </is>
+      </c>
+      <c r="F14" s="7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="15" spans="1:6">
+      <c r="A15" s="6">
+        <v>46324</v>
+      </c>
+      <c r="B15" s="7" t="inlineStr">
+        <is>
+          <t>미국</t>
+        </is>
+      </c>
+      <c r="C15" s="7" t="inlineStr">
+        <is>
+          <t>PCE 근원</t>
+        </is>
+      </c>
+      <c r="D15" s="7" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="E15" s="7" t="inlineStr">
+        <is>
+          <t>FRED(BEA Personal Income and Outlays)</t>
+        </is>
+      </c>
+      <c r="F15" s="7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="16" spans="1:6">
+      <c r="A16" s="6">
+        <v>46351</v>
+      </c>
+      <c r="B16" s="7" t="inlineStr">
+        <is>
+          <t>미국</t>
+        </is>
+      </c>
+      <c r="C16" s="7" t="inlineStr">
+        <is>
+          <t>PCE 근원</t>
+        </is>
+      </c>
+      <c r="D16" s="7" t="inlineStr">
+        <is>
+          <t>2026-10</t>
+        </is>
+      </c>
+      <c r="E16" s="7" t="inlineStr">
+        <is>
+          <t>FRED(BEA Personal Income and Outlays)</t>
+        </is>
+      </c>
+      <c r="F16" s="7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="17" spans="1:6">
+      <c r="A17" s="6">
+        <v>46379</v>
+      </c>
+      <c r="B17" s="7" t="inlineStr">
+        <is>
+          <t>미국</t>
+        </is>
+      </c>
+      <c r="C17" s="7" t="inlineStr">
+        <is>
+          <t>PCE 근원</t>
+        </is>
+      </c>
+      <c r="D17" s="7" t="inlineStr">
+        <is>
+          <t>2026-11</t>
+        </is>
+      </c>
+      <c r="E17" s="7" t="inlineStr">
+        <is>
+          <t>FRED(BEA Personal Income and Outlays)</t>
+        </is>
+      </c>
+      <c r="F17" s="7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="18" spans="1:6">
+      <c r="A18" s="6">
+        <v>46324</v>
+      </c>
+      <c r="B18" s="7" t="inlineStr">
+        <is>
+          <t>미국</t>
+        </is>
+      </c>
+      <c r="C18" s="7" t="inlineStr">
+        <is>
+          <t>실질GDP 성장률</t>
+        </is>
+      </c>
+      <c r="D18" s="7" t="inlineStr">
+        <is>
+          <t>2026-Q3</t>
+        </is>
+      </c>
+      <c r="E18" s="7" t="inlineStr">
+        <is>
+          <t>FRED(BEA GDP release)</t>
+        </is>
+      </c>
+      <c r="F18" s="7" t="inlineStr">
+        <is>
+          <t>속보치(advance estimate)</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" spans="1:6">
+      <c r="A19" s="6">
+        <v>46323</v>
+      </c>
+      <c r="B19" s="7" t="inlineStr">
+        <is>
+          <t>미국</t>
+        </is>
+      </c>
+      <c r="C19" s="7" t="inlineStr">
+        <is>
+          <t>정책금리(상단)</t>
+        </is>
+      </c>
+      <c r="D19" s="7" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="E19" s="7" t="inlineStr">
+        <is>
+          <t>Federal Reserve(FOMC 공식 일정)</t>
+        </is>
+      </c>
+      <c r="F19" s="7" t="inlineStr">
+        <is>
+          <t>FOMC 10월 회의(10/27-28) 결정일</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" spans="1:6">
+      <c r="A20" s="6">
+        <v>46365</v>
+      </c>
+      <c r="B20" s="7" t="inlineStr">
+        <is>
+          <t>미국</t>
+        </is>
+      </c>
+      <c r="C20" s="7" t="inlineStr">
+        <is>
+          <t>정책금리(상단)</t>
+        </is>
+      </c>
+      <c r="D20" s="7" t="inlineStr">
+        <is>
+          <t>2026-12-9</t>
+        </is>
+      </c>
+      <c r="E20" s="7" t="inlineStr">
+        <is>
+          <t>Federal Reserve(FOMC 공식 일정)</t>
+        </is>
+      </c>
+      <c r="F20" s="7" t="inlineStr">
+        <is>
+          <t>FOMC 12월 회의(12/8-9) 결정일</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" spans="1:6">
+      <c r="A21" s="6">
+        <v>46317</v>
+      </c>
+      <c r="B21" s="7" t="inlineStr">
+        <is>
+          <t>한국</t>
+        </is>
+      </c>
+      <c r="C21" s="7" t="inlineStr">
+        <is>
+          <t>기준금리</t>
+        </is>
+      </c>
+      <c r="D21" s="7" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="E21" s="7" t="inlineStr">
+        <is>
+          <t>한국은행(통화정책방향 결정회의 공식 일정)</t>
+        </is>
+      </c>
+      <c r="F21" s="7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="22" spans="1:6">
+      <c r="A22" s="6">
+        <v>46352</v>
+      </c>
+      <c r="B22" s="7" t="inlineStr">
+        <is>
+          <t>한국</t>
+        </is>
+      </c>
+      <c r="C22" s="7" t="inlineStr">
+        <is>
+          <t>기준금리</t>
+        </is>
+      </c>
+      <c r="D22" s="7" t="inlineStr">
+        <is>
+          <t>2026-11-26</t>
+        </is>
+      </c>
+      <c r="E22" s="7" t="inlineStr">
+        <is>
+          <t>한국은행(통화정책방향 결정회의 공식 일정)</t>
+        </is>
+      </c>
+      <c r="F22" s="7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="23" spans="1:6">
+      <c r="A23" s="6">
+        <v>46283</v>
+      </c>
+      <c r="B23" s="7" t="inlineStr">
+        <is>
+          <t>일본</t>
+        </is>
+      </c>
+      <c r="C23" s="7" t="inlineStr">
+        <is>
+          <t>정책금리</t>
+        </is>
+      </c>
+      <c r="D23" s="7" t="inlineStr">
+        <is>
+          <t>2026-9-18</t>
+        </is>
+      </c>
+      <c r="E23" s="7" t="inlineStr">
+        <is>
+          <t>日本銀行(金融政策決定会合 공식 일정)</t>
+        </is>
+      </c>
+      <c r="F23" s="7" t="inlineStr">
+        <is>
+          <t>9/17-18 회의 결정일</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" spans="1:6">
+      <c r="A24" s="6">
+        <v>46325</v>
+      </c>
+      <c r="B24" s="7" t="inlineStr">
+        <is>
+          <t>일본</t>
+        </is>
+      </c>
+      <c r="C24" s="7" t="inlineStr">
+        <is>
+          <t>정책금리</t>
+        </is>
+      </c>
+      <c r="D24" s="7" t="inlineStr">
+        <is>
+          <t>2026-10-30</t>
+        </is>
+      </c>
+      <c r="E24" s="7" t="inlineStr">
+        <is>
+          <t>日本銀行(金融政策決定会合 공식 일정)</t>
+        </is>
+      </c>
+      <c r="F24" s="7" t="inlineStr">
+        <is>
+          <t>10/29-30 회의 결정일</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" spans="1:6">
+      <c r="A25" s="6">
+        <v>46374</v>
+      </c>
+      <c r="B25" s="7" t="inlineStr">
+        <is>
+          <t>일본</t>
+        </is>
+      </c>
+      <c r="C25" s="7" t="inlineStr">
+        <is>
+          <t>정책금리</t>
+        </is>
+      </c>
+      <c r="D25" s="7" t="inlineStr">
+        <is>
+          <t>2026-12-18</t>
+        </is>
+      </c>
+      <c r="E25" s="7" t="inlineStr">
+        <is>
+          <t>日本銀行(金融政策決定会合 공식 일정)</t>
+        </is>
+      </c>
+      <c r="F25" s="7" t="inlineStr">
+        <is>
+          <t>12/17-18 회의 결정일</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" spans="1:6">
+      <c r="A26" s="6">
+        <v>46283</v>
+      </c>
+      <c r="B26" s="7" t="inlineStr">
+        <is>
+          <t>일본</t>
+        </is>
+      </c>
+      <c r="C26" s="7" t="inlineStr">
+        <is>
+          <t>CPI 헤드라인</t>
+        </is>
+      </c>
+      <c r="D26" s="7" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="E26" s="7" t="inlineStr">
+        <is>
+          <t>e-Stat(총무성 소비자물가지수 공표예정)</t>
+        </is>
+      </c>
+      <c r="F26" s="7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="27" spans="1:6">
+      <c r="A27" s="6">
+        <v>46283</v>
+      </c>
+      <c r="B27" s="7" t="inlineStr">
+        <is>
+          <t>일본</t>
+        </is>
+      </c>
+      <c r="C27" s="7" t="inlineStr">
+        <is>
+          <t>CPI 근원</t>
+        </is>
+      </c>
+      <c r="D27" s="7" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="E27" s="7" t="inlineStr">
+        <is>
+          <t>e-Stat(총무성 소비자물가지수 공표예정)</t>
+        </is>
+      </c>
+      <c r="F27" s="7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="28" spans="1:6">
+      <c r="A28" s="6">
+        <v>46318</v>
+      </c>
+      <c r="B28" s="7" t="inlineStr">
+        <is>
+          <t>일본</t>
+        </is>
+      </c>
+      <c r="C28" s="7" t="inlineStr">
+        <is>
+          <t>CPI 헤드라인</t>
+        </is>
+      </c>
+      <c r="D28" s="7" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="E28" s="7" t="inlineStr">
+        <is>
+          <t>e-Stat(총무성 소비자물가지수 공표예정)</t>
+        </is>
+      </c>
+      <c r="F28" s="7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="29" spans="1:6">
+      <c r="A29" s="6">
+        <v>46318</v>
+      </c>
+      <c r="B29" s="7" t="inlineStr">
+        <is>
+          <t>일본</t>
+        </is>
+      </c>
+      <c r="C29" s="7" t="inlineStr">
+        <is>
+          <t>CPI 근원</t>
+        </is>
+      </c>
+      <c r="D29" s="7" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="E29" s="7" t="inlineStr">
+        <is>
+          <t>e-Stat(총무성 소비자물가지수 공표예정)</t>
+        </is>
+      </c>
+      <c r="F29" s="7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="30" spans="1:6">
+      <c r="A30" s="6">
+        <v>46346</v>
+      </c>
+      <c r="B30" s="7" t="inlineStr">
+        <is>
+          <t>일본</t>
+        </is>
+      </c>
+      <c r="C30" s="7" t="inlineStr">
+        <is>
+          <t>CPI 헤드라인</t>
+        </is>
+      </c>
+      <c r="D30" s="7" t="inlineStr">
+        <is>
+          <t>2026-10</t>
+        </is>
+      </c>
+      <c r="E30" s="7" t="inlineStr">
+        <is>
+          <t>e-Stat(총무성 소비자물가지수 공표예정)</t>
+        </is>
+      </c>
+      <c r="F30" s="7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="31" spans="1:6">
+      <c r="A31" s="6">
+        <v>46346</v>
+      </c>
+      <c r="B31" s="7" t="inlineStr">
+        <is>
+          <t>일본</t>
+        </is>
+      </c>
+      <c r="C31" s="7" t="inlineStr">
+        <is>
+          <t>CPI 근원</t>
+        </is>
+      </c>
+      <c r="D31" s="7" t="inlineStr">
+        <is>
+          <t>2026-10</t>
+        </is>
+      </c>
+      <c r="E31" s="7" t="inlineStr">
+        <is>
+          <t>e-Stat(총무성 소비자물가지수 공표예정)</t>
+        </is>
+      </c>
+      <c r="F31" s="7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="32" spans="1:6">
+      <c r="A32" s="6">
+        <v>46374</v>
+      </c>
+      <c r="B32" s="7" t="inlineStr">
+        <is>
+          <t>일본</t>
+        </is>
+      </c>
+      <c r="C32" s="7" t="inlineStr">
+        <is>
+          <t>CPI 헤드라인</t>
+        </is>
+      </c>
+      <c r="D32" s="7" t="inlineStr">
+        <is>
+          <t>2026-11</t>
+        </is>
+      </c>
+      <c r="E32" s="7" t="inlineStr">
+        <is>
+          <t>e-Stat(총무성 소비자물가지수 공표예정)</t>
+        </is>
+      </c>
+      <c r="F32" s="7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="33" spans="1:6">
+      <c r="A33" s="6">
+        <v>46374</v>
+      </c>
+      <c r="B33" s="7" t="inlineStr">
+        <is>
+          <t>일본</t>
+        </is>
+      </c>
+      <c r="C33" s="7" t="inlineStr">
+        <is>
+          <t>CPI 근원</t>
+        </is>
+      </c>
+      <c r="D33" s="7" t="inlineStr">
+        <is>
+          <t>2026-11</t>
+        </is>
+      </c>
+      <c r="E33" s="7" t="inlineStr">
+        <is>
+          <t>e-Stat(총무성 소비자물가지수 공표예정)</t>
+        </is>
+      </c>
+      <c r="F33" s="7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="34" spans="1:6">
+      <c r="A34" s="6">
+        <v>46342</v>
+      </c>
+      <c r="B34" s="7" t="inlineStr">
+        <is>
+          <t>일본</t>
+        </is>
+      </c>
+      <c r="C34" s="7" t="inlineStr">
+        <is>
+          <t>실질GDP 성장률</t>
+        </is>
+      </c>
+      <c r="D34" s="7" t="inlineStr">
+        <is>
+          <t>2026-Q3</t>
+        </is>
+      </c>
+      <c r="E34" s="7" t="inlineStr">
+        <is>
+          <t>内閣府 ESRI(공표예정 공식 페이지)</t>
+        </is>
+      </c>
+      <c r="F34" s="7" t="inlineStr">
+        <is>
+          <t>1次速報</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" spans="1:6">
+      <c r="A35" s="6">
+        <v>46308</v>
+      </c>
+      <c r="B35" s="7" t="inlineStr">
+        <is>
+          <t>독일</t>
+        </is>
+      </c>
+      <c r="C35" s="7" t="inlineStr">
+        <is>
+          <t>HICP 헤드라인</t>
+        </is>
+      </c>
+      <c r="D35" s="7" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="E35" s="7" t="inlineStr">
+        <is>
+          <t>Destatis(Veröffentlichungstermine, 최종결과)</t>
+        </is>
+      </c>
+      <c r="F35" s="7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="36" spans="1:6">
+      <c r="A36" s="6">
+        <v>46308</v>
+      </c>
+      <c r="B36" s="7" t="inlineStr">
+        <is>
+          <t>독일</t>
+        </is>
+      </c>
+      <c r="C36" s="7" t="inlineStr">
+        <is>
+          <t>HICP 근원</t>
+        </is>
+      </c>
+      <c r="D36" s="7" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="E36" s="7" t="inlineStr">
+        <is>
+          <t>Destatis(Veröffentlichungstermine, 최종결과)</t>
+        </is>
+      </c>
+      <c r="F36" s="7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="37" spans="1:6">
+      <c r="A37" s="6">
+        <v>46337</v>
+      </c>
+      <c r="B37" s="7" t="inlineStr">
+        <is>
+          <t>독일</t>
+        </is>
+      </c>
+      <c r="C37" s="7" t="inlineStr">
+        <is>
+          <t>HICP 헤드라인</t>
+        </is>
+      </c>
+      <c r="D37" s="7" t="inlineStr">
+        <is>
+          <t>2026-10</t>
+        </is>
+      </c>
+      <c r="E37" s="7" t="inlineStr">
+        <is>
+          <t>Destatis(Veröffentlichungstermine, 최종결과)</t>
+        </is>
+      </c>
+      <c r="F37" s="7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="38" spans="1:6">
+      <c r="A38" s="6">
+        <v>46337</v>
+      </c>
+      <c r="B38" s="7" t="inlineStr">
+        <is>
+          <t>독일</t>
+        </is>
+      </c>
+      <c r="C38" s="7" t="inlineStr">
+        <is>
+          <t>HICP 근원</t>
+        </is>
+      </c>
+      <c r="D38" s="7" t="inlineStr">
+        <is>
+          <t>2026-10</t>
+        </is>
+      </c>
+      <c r="E38" s="7" t="inlineStr">
+        <is>
+          <t>Destatis(Veröffentlichungstermine, 최종결과)</t>
+        </is>
+      </c>
+      <c r="F38" s="7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="39" spans="1:6">
+      <c r="A39" s="6">
+        <v>46366</v>
+      </c>
+      <c r="B39" s="7" t="inlineStr">
+        <is>
+          <t>독일</t>
+        </is>
+      </c>
+      <c r="C39" s="7" t="inlineStr">
+        <is>
+          <t>HICP 헤드라인</t>
+        </is>
+      </c>
+      <c r="D39" s="7" t="inlineStr">
+        <is>
+          <t>2026-11</t>
+        </is>
+      </c>
+      <c r="E39" s="7" t="inlineStr">
+        <is>
+          <t>Destatis(Veröffentlichungstermine, 최종결과)</t>
+        </is>
+      </c>
+      <c r="F39" s="7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="40" spans="1:6">
+      <c r="A40" s="6">
+        <v>46366</v>
+      </c>
+      <c r="B40" s="7" t="inlineStr">
+        <is>
+          <t>독일</t>
+        </is>
+      </c>
+      <c r="C40" s="7" t="inlineStr">
+        <is>
+          <t>HICP 근원</t>
+        </is>
+      </c>
+      <c r="D40" s="7" t="inlineStr">
+        <is>
+          <t>2026-11</t>
+        </is>
+      </c>
+      <c r="E40" s="7" t="inlineStr">
+        <is>
+          <t>Destatis(Veröffentlichungstermine, 최종결과)</t>
+        </is>
+      </c>
+      <c r="F40" s="7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+</worksheet>
 </file>
--- a/매크로_트래커_로우데이터.xlsx
+++ b/매크로_트래커_로우데이터.xlsx
@@ -71903,7 +71903,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F40"/>
+  <dimension ref="A1:F53"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="17"/>
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
@@ -72938,26 +72938,26 @@
     </row>
     <row r="35" spans="1:6">
       <c r="A35" s="6">
-        <v>46308</v>
+        <v>46297</v>
       </c>
       <c r="B35" s="7" t="inlineStr">
         <is>
-          <t>독일</t>
+          <t>일본</t>
         </is>
       </c>
       <c r="C35" s="7" t="inlineStr">
         <is>
-          <t>HICP 헤드라인</t>
+          <t>실업률</t>
         </is>
       </c>
       <c r="D35" s="7" t="inlineStr">
         <is>
-          <t>2026-09</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="E35" s="7" t="inlineStr">
         <is>
-          <t>Destatis(Veröffentlichungstermine, 최종결과)</t>
+          <t>総務省統計局(労働力調査 2026年公表予定日 PDF)</t>
         </is>
       </c>
       <c r="F35" s="7" t="inlineStr">
@@ -72968,16 +72968,16 @@
     </row>
     <row r="36" spans="1:6">
       <c r="A36" s="6">
-        <v>46308</v>
+        <v>46325</v>
       </c>
       <c r="B36" s="7" t="inlineStr">
         <is>
-          <t>독일</t>
+          <t>일본</t>
         </is>
       </c>
       <c r="C36" s="7" t="inlineStr">
         <is>
-          <t>HICP 근원</t>
+          <t>실업률</t>
         </is>
       </c>
       <c r="D36" s="7" t="inlineStr">
@@ -72987,7 +72987,7 @@
       </c>
       <c r="E36" s="7" t="inlineStr">
         <is>
-          <t>Destatis(Veröffentlichungstermine, 최종결과)</t>
+          <t>総務省統計局(労働力調査 2026年公表予定日 PDF)</t>
         </is>
       </c>
       <c r="F36" s="7" t="inlineStr">
@@ -72998,16 +72998,16 @@
     </row>
     <row r="37" spans="1:6">
       <c r="A37" s="6">
-        <v>46337</v>
+        <v>46357</v>
       </c>
       <c r="B37" s="7" t="inlineStr">
         <is>
-          <t>독일</t>
+          <t>일본</t>
         </is>
       </c>
       <c r="C37" s="7" t="inlineStr">
         <is>
-          <t>HICP 헤드라인</t>
+          <t>실업률</t>
         </is>
       </c>
       <c r="D37" s="7" t="inlineStr">
@@ -73017,7 +73017,7 @@
       </c>
       <c r="E37" s="7" t="inlineStr">
         <is>
-          <t>Destatis(Veröffentlichungstermine, 최종결과)</t>
+          <t>総務省統計局(労働力調査 2026年公表予定日 PDF)</t>
         </is>
       </c>
       <c r="F37" s="7" t="inlineStr">
@@ -73028,26 +73028,26 @@
     </row>
     <row r="38" spans="1:6">
       <c r="A38" s="6">
-        <v>46337</v>
+        <v>46381</v>
       </c>
       <c r="B38" s="7" t="inlineStr">
         <is>
-          <t>독일</t>
+          <t>일본</t>
         </is>
       </c>
       <c r="C38" s="7" t="inlineStr">
         <is>
-          <t>HICP 근원</t>
+          <t>실업률</t>
         </is>
       </c>
       <c r="D38" s="7" t="inlineStr">
         <is>
-          <t>2026-10</t>
+          <t>2026-11</t>
         </is>
       </c>
       <c r="E38" s="7" t="inlineStr">
         <is>
-          <t>Destatis(Veröffentlichungstermine, 최종결과)</t>
+          <t>総務省統計局(労働力調査 2026年公表予定日 PDF)</t>
         </is>
       </c>
       <c r="F38" s="7" t="inlineStr">
@@ -73058,26 +73058,26 @@
     </row>
     <row r="39" spans="1:6">
       <c r="A39" s="6">
-        <v>46366</v>
+        <v>46297</v>
       </c>
       <c r="B39" s="7" t="inlineStr">
         <is>
-          <t>독일</t>
+          <t>한국</t>
         </is>
       </c>
       <c r="C39" s="7" t="inlineStr">
         <is>
-          <t>HICP 헤드라인</t>
+          <t>CPI 헤드라인</t>
         </is>
       </c>
       <c r="D39" s="7" t="inlineStr">
         <is>
-          <t>2026-11</t>
+          <t>2026-09</t>
         </is>
       </c>
       <c r="E39" s="7" t="inlineStr">
         <is>
-          <t>Destatis(Veröffentlichungstermine, 최종결과)</t>
+          <t>국가데이터처(2026년 물가·고용·산업활동동향 보도계획 PDF)</t>
         </is>
       </c>
       <c r="F39" s="7" t="inlineStr">
@@ -73088,31 +73088,421 @@
     </row>
     <row r="40" spans="1:6">
       <c r="A40" s="6">
-        <v>46366</v>
+        <v>46297</v>
       </c>
       <c r="B40" s="7" t="inlineStr">
         <is>
-          <t>독일</t>
+          <t>한국</t>
         </is>
       </c>
       <c r="C40" s="7" t="inlineStr">
         <is>
-          <t>HICP 근원</t>
+          <t>CPI 근원</t>
         </is>
       </c>
       <c r="D40" s="7" t="inlineStr">
         <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="E40" s="7" t="inlineStr">
+        <is>
+          <t>국가데이터처(2026년 물가·고용·산업활동동향 보도계획 PDF)</t>
+        </is>
+      </c>
+      <c r="F40" s="7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="41" spans="1:6">
+      <c r="A41" s="6">
+        <v>46329</v>
+      </c>
+      <c r="B41" s="7" t="inlineStr">
+        <is>
+          <t>한국</t>
+        </is>
+      </c>
+      <c r="C41" s="7" t="inlineStr">
+        <is>
+          <t>CPI 헤드라인</t>
+        </is>
+      </c>
+      <c r="D41" s="7" t="inlineStr">
+        <is>
+          <t>2026-10</t>
+        </is>
+      </c>
+      <c r="E41" s="7" t="inlineStr">
+        <is>
+          <t>국가데이터처(2026년 물가·고용·산업활동동향 보도계획 PDF)</t>
+        </is>
+      </c>
+      <c r="F41" s="7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="42" spans="1:6">
+      <c r="A42" s="6">
+        <v>46329</v>
+      </c>
+      <c r="B42" s="7" t="inlineStr">
+        <is>
+          <t>한국</t>
+        </is>
+      </c>
+      <c r="C42" s="7" t="inlineStr">
+        <is>
+          <t>CPI 근원</t>
+        </is>
+      </c>
+      <c r="D42" s="7" t="inlineStr">
+        <is>
+          <t>2026-10</t>
+        </is>
+      </c>
+      <c r="E42" s="7" t="inlineStr">
+        <is>
+          <t>국가데이터처(2026년 물가·고용·산업활동동향 보도계획 PDF)</t>
+        </is>
+      </c>
+      <c r="F42" s="7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="43" spans="1:6">
+      <c r="A43" s="6">
+        <v>46358</v>
+      </c>
+      <c r="B43" s="7" t="inlineStr">
+        <is>
+          <t>한국</t>
+        </is>
+      </c>
+      <c r="C43" s="7" t="inlineStr">
+        <is>
+          <t>CPI 헤드라인</t>
+        </is>
+      </c>
+      <c r="D43" s="7" t="inlineStr">
+        <is>
           <t>2026-11</t>
         </is>
       </c>
-      <c r="E40" s="7" t="inlineStr">
-        <is>
-          <t>Destatis(Veröffentlichungstermine, 최종결과)</t>
-        </is>
-      </c>
-      <c r="F40" s="7" t="inlineStr">
+      <c r="E43" s="7" t="inlineStr">
+        <is>
+          <t>국가데이터처(2026년 물가·고용·산업활동동향 보도계획 PDF)</t>
+        </is>
+      </c>
+      <c r="F43" s="7" t="inlineStr">
         <is>
           <t/>
+        </is>
+      </c>
+    </row>
+    <row r="44" spans="1:6">
+      <c r="A44" s="6">
+        <v>46358</v>
+      </c>
+      <c r="B44" s="7" t="inlineStr">
+        <is>
+          <t>한국</t>
+        </is>
+      </c>
+      <c r="C44" s="7" t="inlineStr">
+        <is>
+          <t>CPI 근원</t>
+        </is>
+      </c>
+      <c r="D44" s="7" t="inlineStr">
+        <is>
+          <t>2026-11</t>
+        </is>
+      </c>
+      <c r="E44" s="7" t="inlineStr">
+        <is>
+          <t>국가데이터처(2026년 물가·고용·산업활동동향 보도계획 PDF)</t>
+        </is>
+      </c>
+      <c r="F44" s="7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="45" spans="1:6">
+      <c r="A45" s="6">
+        <v>46387</v>
+      </c>
+      <c r="B45" s="7" t="inlineStr">
+        <is>
+          <t>한국</t>
+        </is>
+      </c>
+      <c r="C45" s="7" t="inlineStr">
+        <is>
+          <t>CPI 헤드라인</t>
+        </is>
+      </c>
+      <c r="D45" s="7" t="inlineStr">
+        <is>
+          <t>2026-12</t>
+        </is>
+      </c>
+      <c r="E45" s="7" t="inlineStr">
+        <is>
+          <t>국가데이터처(2026년 물가·고용·산업활동동향 보도계획 PDF)</t>
+        </is>
+      </c>
+      <c r="F45" s="7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="46" spans="1:6">
+      <c r="A46" s="6">
+        <v>46387</v>
+      </c>
+      <c r="B46" s="7" t="inlineStr">
+        <is>
+          <t>한국</t>
+        </is>
+      </c>
+      <c r="C46" s="7" t="inlineStr">
+        <is>
+          <t>CPI 근원</t>
+        </is>
+      </c>
+      <c r="D46" s="7" t="inlineStr">
+        <is>
+          <t>2026-12</t>
+        </is>
+      </c>
+      <c r="E46" s="7" t="inlineStr">
+        <is>
+          <t>국가데이터처(2026년 물가·고용·산업활동동향 보도계획 PDF)</t>
+        </is>
+      </c>
+      <c r="F46" s="7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="47" spans="1:6">
+      <c r="A47" s="6">
+        <v>46311</v>
+      </c>
+      <c r="B47" s="7" t="inlineStr">
+        <is>
+          <t>한국</t>
+        </is>
+      </c>
+      <c r="C47" s="7" t="inlineStr">
+        <is>
+          <t>실업률</t>
+        </is>
+      </c>
+      <c r="D47" s="7" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="E47" s="7" t="inlineStr">
+        <is>
+          <t>국가데이터처(2026년 물가·고용·산업활동동향 보도계획 PDF)</t>
+        </is>
+      </c>
+      <c r="F47" s="7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="48" spans="1:6">
+      <c r="A48" s="6">
+        <v>46311</v>
+      </c>
+      <c r="B48" s="7" t="inlineStr">
+        <is>
+          <t>한국</t>
+        </is>
+      </c>
+      <c r="C48" s="7" t="inlineStr">
+        <is>
+          <t>취업자수</t>
+        </is>
+      </c>
+      <c r="D48" s="7" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="E48" s="7" t="inlineStr">
+        <is>
+          <t>국가데이터처(2026년 물가·고용·산업활동동향 보도계획 PDF)</t>
+        </is>
+      </c>
+      <c r="F48" s="7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="49" spans="1:6">
+      <c r="A49" s="6">
+        <v>46337</v>
+      </c>
+      <c r="B49" s="7" t="inlineStr">
+        <is>
+          <t>한국</t>
+        </is>
+      </c>
+      <c r="C49" s="7" t="inlineStr">
+        <is>
+          <t>실업률</t>
+        </is>
+      </c>
+      <c r="D49" s="7" t="inlineStr">
+        <is>
+          <t>2026-10</t>
+        </is>
+      </c>
+      <c r="E49" s="7" t="inlineStr">
+        <is>
+          <t>국가데이터처(2026년 물가·고용·산업활동동향 보도계획 PDF)</t>
+        </is>
+      </c>
+      <c r="F49" s="7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="50" spans="1:6">
+      <c r="A50" s="6">
+        <v>46337</v>
+      </c>
+      <c r="B50" s="7" t="inlineStr">
+        <is>
+          <t>한국</t>
+        </is>
+      </c>
+      <c r="C50" s="7" t="inlineStr">
+        <is>
+          <t>취업자수</t>
+        </is>
+      </c>
+      <c r="D50" s="7" t="inlineStr">
+        <is>
+          <t>2026-10</t>
+        </is>
+      </c>
+      <c r="E50" s="7" t="inlineStr">
+        <is>
+          <t>국가데이터처(2026년 물가·고용·산업활동동향 보도계획 PDF)</t>
+        </is>
+      </c>
+      <c r="F50" s="7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="51" spans="1:6">
+      <c r="A51" s="6">
+        <v>46372</v>
+      </c>
+      <c r="B51" s="7" t="inlineStr">
+        <is>
+          <t>한국</t>
+        </is>
+      </c>
+      <c r="C51" s="7" t="inlineStr">
+        <is>
+          <t>실업률</t>
+        </is>
+      </c>
+      <c r="D51" s="7" t="inlineStr">
+        <is>
+          <t>2026-11</t>
+        </is>
+      </c>
+      <c r="E51" s="7" t="inlineStr">
+        <is>
+          <t>국가데이터처(2026년 물가·고용·산업활동동향 보도계획 PDF)</t>
+        </is>
+      </c>
+      <c r="F51" s="7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="52" spans="1:6">
+      <c r="A52" s="6">
+        <v>46372</v>
+      </c>
+      <c r="B52" s="7" t="inlineStr">
+        <is>
+          <t>한국</t>
+        </is>
+      </c>
+      <c r="C52" s="7" t="inlineStr">
+        <is>
+          <t>취업자수</t>
+        </is>
+      </c>
+      <c r="D52" s="7" t="inlineStr">
+        <is>
+          <t>2026-11</t>
+        </is>
+      </c>
+      <c r="E52" s="7" t="inlineStr">
+        <is>
+          <t>국가데이터처(2026년 물가·고용·산업활동동향 보도계획 PDF)</t>
+        </is>
+      </c>
+      <c r="F52" s="7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="53" spans="1:6">
+      <c r="A53" s="6">
+        <v>46322</v>
+      </c>
+      <c r="B53" s="7" t="inlineStr">
+        <is>
+          <t>한국</t>
+        </is>
+      </c>
+      <c r="C53" s="7" t="inlineStr">
+        <is>
+          <t>실질GDP 성장률</t>
+        </is>
+      </c>
+      <c r="D53" s="7" t="inlineStr">
+        <is>
+          <t>2026-Q3</t>
+        </is>
+      </c>
+      <c r="E53" s="7" t="inlineStr">
+        <is>
+          <t>한국은행(국민소득 공표일정 공식 페이지)</t>
+        </is>
+      </c>
+      <c r="F53" s="7" t="inlineStr">
+        <is>
+          <t>속보치</t>
         </is>
       </c>
     </row>

--- a/매크로_트래커_로우데이터.xlsx
+++ b/매크로_트래커_로우데이터.xlsx
@@ -45235,12 +45235,30 @@
       </c>
     </row>
     <row r="1809" spans="1:6">
-      <c r="A1809" s="6"/>
-      <c r="B1809" s="7"/>
-      <c r="C1809" s="7"/>
-      <c r="D1809" s="7"/>
-      <c r="E1809" s="6"/>
-      <c r="F1809" s="7"/>
+      <c r="A1809" s="6">
+        <v>44440</v>
+      </c>
+      <c r="B1809" s="7" t="inlineStr">
+        <is>
+          <t>한국</t>
+        </is>
+      </c>
+      <c r="C1809" s="7" t="inlineStr">
+        <is>
+          <t>기준금리</t>
+        </is>
+      </c>
+      <c r="D1809" s="7">
+        <v>0.75</v>
+      </c>
+      <c r="E1809" s="6">
+        <v>44434</v>
+      </c>
+      <c r="F1809" s="7" t="inlineStr">
+        <is>
+          <t>수시</t>
+        </is>
+      </c>
     </row>
     <row r="1810" spans="1:6">
       <c r="A1810" s="6"/>

--- a/매크로_트래커_로우데이터.xlsx
+++ b/매크로_트래커_로우데이터.xlsx
@@ -10720,7 +10720,7 @@
     </row>
     <row r="379" spans="1:6">
       <c r="A379" s="6">
-        <v>44637</v>
+        <v>44636</v>
       </c>
       <c r="B379" s="7" t="inlineStr">
         <is>
@@ -10736,7 +10736,7 @@
         <v>0.5</v>
       </c>
       <c r="E379" s="6">
-        <v>44638</v>
+        <v>44636</v>
       </c>
       <c r="F379" s="7" t="inlineStr">
         <is>
@@ -10746,7 +10746,7 @@
     </row>
     <row r="380" spans="1:6">
       <c r="A380" s="6">
-        <v>44686</v>
+        <v>44685</v>
       </c>
       <c r="B380" s="7" t="inlineStr">
         <is>
@@ -10762,7 +10762,7 @@
         <v>1.0</v>
       </c>
       <c r="E380" s="6">
-        <v>44687</v>
+        <v>44685</v>
       </c>
       <c r="F380" s="7" t="inlineStr">
         <is>
@@ -10772,7 +10772,7 @@
     </row>
     <row r="381" spans="1:6">
       <c r="A381" s="6">
-        <v>44728</v>
+        <v>44727</v>
       </c>
       <c r="B381" s="7" t="inlineStr">
         <is>
@@ -10788,7 +10788,7 @@
         <v>1.75</v>
       </c>
       <c r="E381" s="6">
-        <v>44728</v>
+        <v>44727</v>
       </c>
       <c r="F381" s="7" t="inlineStr">
         <is>
@@ -10798,7 +10798,7 @@
     </row>
     <row r="382" spans="1:6">
       <c r="A382" s="6">
-        <v>44770</v>
+        <v>44769</v>
       </c>
       <c r="B382" s="7" t="inlineStr">
         <is>
@@ -10814,7 +10814,7 @@
         <v>2.5</v>
       </c>
       <c r="E382" s="6">
-        <v>44770</v>
+        <v>44769</v>
       </c>
       <c r="F382" s="7" t="inlineStr">
         <is>
@@ -10824,7 +10824,7 @@
     </row>
     <row r="383" spans="1:6">
       <c r="A383" s="6">
-        <v>44826</v>
+        <v>44825</v>
       </c>
       <c r="B383" s="7" t="inlineStr">
         <is>
@@ -10840,7 +10840,7 @@
         <v>3.25</v>
       </c>
       <c r="E383" s="6">
-        <v>44826</v>
+        <v>44825</v>
       </c>
       <c r="F383" s="7" t="inlineStr">
         <is>
@@ -10850,7 +10850,7 @@
     </row>
     <row r="384" spans="1:6">
       <c r="A384" s="6">
-        <v>44868</v>
+        <v>44867</v>
       </c>
       <c r="B384" s="7" t="inlineStr">
         <is>
@@ -10866,7 +10866,7 @@
         <v>4.0</v>
       </c>
       <c r="E384" s="6">
-        <v>44868</v>
+        <v>44867</v>
       </c>
       <c r="F384" s="7" t="inlineStr">
         <is>
@@ -10876,7 +10876,7 @@
     </row>
     <row r="385" spans="1:6">
       <c r="A385" s="6">
-        <v>44910</v>
+        <v>44909</v>
       </c>
       <c r="B385" s="7" t="inlineStr">
         <is>
@@ -10892,7 +10892,7 @@
         <v>4.5</v>
       </c>
       <c r="E385" s="6">
-        <v>44910</v>
+        <v>44909</v>
       </c>
       <c r="F385" s="7" t="inlineStr">
         <is>
@@ -10902,7 +10902,7 @@
     </row>
     <row r="386" spans="1:6">
       <c r="A386" s="6">
-        <v>44959</v>
+        <v>44958</v>
       </c>
       <c r="B386" s="7" t="inlineStr">
         <is>
@@ -10918,7 +10918,7 @@
         <v>4.75</v>
       </c>
       <c r="E386" s="6">
-        <v>44959</v>
+        <v>44958</v>
       </c>
       <c r="F386" s="7" t="inlineStr">
         <is>
@@ -10928,7 +10928,7 @@
     </row>
     <row r="387" spans="1:6">
       <c r="A387" s="6">
-        <v>45008</v>
+        <v>45007</v>
       </c>
       <c r="B387" s="7" t="inlineStr">
         <is>
@@ -10944,7 +10944,7 @@
         <v>5.0</v>
       </c>
       <c r="E387" s="6">
-        <v>45008</v>
+        <v>45007</v>
       </c>
       <c r="F387" s="7" t="inlineStr">
         <is>
@@ -10954,7 +10954,7 @@
     </row>
     <row r="388" spans="1:6">
       <c r="A388" s="6">
-        <v>45050</v>
+        <v>45049</v>
       </c>
       <c r="B388" s="7" t="inlineStr">
         <is>
@@ -10970,7 +10970,7 @@
         <v>5.25</v>
       </c>
       <c r="E388" s="6">
-        <v>45050</v>
+        <v>45049</v>
       </c>
       <c r="F388" s="7" t="inlineStr">
         <is>
@@ -10980,7 +10980,7 @@
     </row>
     <row r="389" spans="1:6">
       <c r="A389" s="6">
-        <v>45134</v>
+        <v>45133</v>
       </c>
       <c r="B389" s="7" t="inlineStr">
         <is>
@@ -10996,7 +10996,7 @@
         <v>5.5</v>
       </c>
       <c r="E389" s="6">
-        <v>45134</v>
+        <v>45133</v>
       </c>
       <c r="F389" s="7" t="inlineStr">
         <is>
@@ -11006,7 +11006,7 @@
     </row>
     <row r="390" spans="1:6">
       <c r="A390" s="6">
-        <v>45554</v>
+        <v>45553</v>
       </c>
       <c r="B390" s="7" t="inlineStr">
         <is>
@@ -11022,7 +11022,7 @@
         <v>5.0</v>
       </c>
       <c r="E390" s="6">
-        <v>45554</v>
+        <v>45553</v>
       </c>
       <c r="F390" s="7" t="inlineStr">
         <is>
@@ -11032,7 +11032,7 @@
     </row>
     <row r="391" spans="1:6">
       <c r="A391" s="6">
-        <v>45604</v>
+        <v>45603</v>
       </c>
       <c r="B391" s="7" t="inlineStr">
         <is>
@@ -11048,7 +11048,7 @@
         <v>4.75</v>
       </c>
       <c r="E391" s="6">
-        <v>45604</v>
+        <v>45603</v>
       </c>
       <c r="F391" s="7" t="inlineStr">
         <is>
@@ -11058,7 +11058,7 @@
     </row>
     <row r="392" spans="1:6">
       <c r="A392" s="6">
-        <v>45645</v>
+        <v>45644</v>
       </c>
       <c r="B392" s="7" t="inlineStr">
         <is>
@@ -11074,7 +11074,7 @@
         <v>4.5</v>
       </c>
       <c r="E392" s="6">
-        <v>45645</v>
+        <v>45644</v>
       </c>
       <c r="F392" s="7" t="inlineStr">
         <is>
@@ -11084,7 +11084,7 @@
     </row>
     <row r="393" spans="1:6">
       <c r="A393" s="6">
-        <v>45918</v>
+        <v>45917</v>
       </c>
       <c r="B393" s="7" t="inlineStr">
         <is>
@@ -11100,7 +11100,7 @@
         <v>4.25</v>
       </c>
       <c r="E393" s="6">
-        <v>45918</v>
+        <v>45917</v>
       </c>
       <c r="F393" s="7" t="inlineStr">
         <is>
@@ -11110,7 +11110,7 @@
     </row>
     <row r="394" spans="1:6">
       <c r="A394" s="6">
-        <v>45960</v>
+        <v>45959</v>
       </c>
       <c r="B394" s="7" t="inlineStr">
         <is>
@@ -11126,7 +11126,7 @@
         <v>4.0</v>
       </c>
       <c r="E394" s="6">
-        <v>45960</v>
+        <v>45959</v>
       </c>
       <c r="F394" s="7" t="inlineStr">
         <is>
@@ -11136,7 +11136,7 @@
     </row>
     <row r="395" spans="1:6">
       <c r="A395" s="6">
-        <v>46002</v>
+        <v>46001</v>
       </c>
       <c r="B395" s="7" t="inlineStr">
         <is>
@@ -11152,7 +11152,7 @@
         <v>3.75</v>
       </c>
       <c r="E395" s="6">
-        <v>46002</v>
+        <v>46001</v>
       </c>
       <c r="F395" s="7" t="inlineStr">
         <is>

--- a/매크로_트래커_로우데이터.xlsx
+++ b/매크로_트래커_로우데이터.xlsx
@@ -45261,12 +45261,30 @@
       </c>
     </row>
     <row r="1810" spans="1:6">
-      <c r="A1810" s="6"/>
-      <c r="B1810" s="7"/>
-      <c r="C1810" s="7"/>
-      <c r="D1810" s="7"/>
-      <c r="E1810" s="6"/>
-      <c r="F1810" s="7"/>
+      <c r="A1810" s="6">
+        <v>46281</v>
+      </c>
+      <c r="B1810" s="7" t="inlineStr">
+        <is>
+          <t>미국</t>
+        </is>
+      </c>
+      <c r="C1810" s="7" t="inlineStr">
+        <is>
+          <t>정책금리(상단)</t>
+        </is>
+      </c>
+      <c r="D1810" s="7">
+        <v>4.0</v>
+      </c>
+      <c r="E1810" s="6">
+        <v>46281</v>
+      </c>
+      <c r="F1810" s="7" t="inlineStr">
+        <is>
+          <t>수시</t>
+        </is>
+      </c>
     </row>
     <row r="1811" spans="1:6">
       <c r="A1811" s="6"/>

--- a/매크로_트래커_로우데이터.xlsx
+++ b/매크로_트래커_로우데이터.xlsx
@@ -45287,20 +45287,56 @@
       </c>
     </row>
     <row r="1811" spans="1:6">
-      <c r="A1811" s="6"/>
-      <c r="B1811" s="7"/>
-      <c r="C1811" s="7"/>
-      <c r="D1811" s="7"/>
-      <c r="E1811" s="6"/>
-      <c r="F1811" s="7"/>
+      <c r="A1811" s="6">
+        <v>46235</v>
+      </c>
+      <c r="B1811" s="7" t="inlineStr">
+        <is>
+          <t>일본</t>
+        </is>
+      </c>
+      <c r="C1811" s="7" t="inlineStr">
+        <is>
+          <t>CPI 헤드라인</t>
+        </is>
+      </c>
+      <c r="D1811" s="7">
+        <v>1.9</v>
+      </c>
+      <c r="E1811" s="6">
+        <v>46283</v>
+      </c>
+      <c r="F1811" s="7" t="inlineStr">
+        <is>
+          <t>월간</t>
+        </is>
+      </c>
     </row>
     <row r="1812" spans="1:6">
-      <c r="A1812" s="6"/>
-      <c r="B1812" s="7"/>
-      <c r="C1812" s="7"/>
-      <c r="D1812" s="7"/>
-      <c r="E1812" s="6"/>
-      <c r="F1812" s="7"/>
+      <c r="A1812" s="6">
+        <v>46235</v>
+      </c>
+      <c r="B1812" s="7" t="inlineStr">
+        <is>
+          <t>일본</t>
+        </is>
+      </c>
+      <c r="C1812" s="7" t="inlineStr">
+        <is>
+          <t>CPI 근원</t>
+        </is>
+      </c>
+      <c r="D1812" s="7">
+        <v>1.7</v>
+      </c>
+      <c r="E1812" s="6">
+        <v>46283</v>
+      </c>
+      <c r="F1812" s="7" t="inlineStr">
+        <is>
+          <t>월간</t>
+        </is>
+      </c>
     </row>
     <row r="1813" spans="1:6">
       <c r="A1813" s="6"/>

--- a/매크로_트래커_로우데이터.xlsx
+++ b/매크로_트래커_로우데이터.xlsx
@@ -45339,12 +45339,30 @@
       </c>
     </row>
     <row r="1813" spans="1:6">
-      <c r="A1813" s="6"/>
-      <c r="B1813" s="7"/>
-      <c r="C1813" s="7"/>
-      <c r="D1813" s="7"/>
-      <c r="E1813" s="6"/>
-      <c r="F1813" s="7"/>
+      <c r="A1813" s="6">
+        <v>46235</v>
+      </c>
+      <c r="B1813" s="7" t="inlineStr">
+        <is>
+          <t>미국</t>
+        </is>
+      </c>
+      <c r="C1813" s="7" t="inlineStr">
+        <is>
+          <t>PCE 근원</t>
+        </is>
+      </c>
+      <c r="D1813" s="7">
+        <v>3.0076</v>
+      </c>
+      <c r="E1813" s="6">
+        <v>46295</v>
+      </c>
+      <c r="F1813" s="7" t="inlineStr">
+        <is>
+          <t>월간</t>
+        </is>
+      </c>
     </row>
     <row r="1814" spans="1:6">
       <c r="A1814" s="6"/>

--- a/매크로_트래커_로우데이터.xlsx
+++ b/매크로_트래커_로우데이터.xlsx
@@ -45365,52 +45365,150 @@
       </c>
     </row>
     <row r="1814" spans="1:6">
-      <c r="A1814" s="6"/>
-      <c r="B1814" s="7"/>
-      <c r="C1814" s="7"/>
-      <c r="D1814" s="7"/>
+      <c r="A1814" s="6">
+        <v>46266</v>
+      </c>
+      <c r="B1814" s="7" t="inlineStr">
+        <is>
+          <t>미국</t>
+        </is>
+      </c>
+      <c r="C1814" s="7" t="inlineStr">
+        <is>
+          <t>WTI</t>
+        </is>
+      </c>
+      <c r="D1814" s="7">
+        <v>97.31</v>
+      </c>
       <c r="E1814" s="6"/>
-      <c r="F1814" s="7"/>
+      <c r="F1814" s="7" t="inlineStr">
+        <is>
+          <t>월간</t>
+        </is>
+      </c>
     </row>
     <row r="1815" spans="1:6">
-      <c r="A1815" s="6"/>
-      <c r="B1815" s="7"/>
-      <c r="C1815" s="7"/>
-      <c r="D1815" s="7"/>
-      <c r="E1815" s="6"/>
-      <c r="F1815" s="7"/>
+      <c r="A1815" s="6">
+        <v>46266</v>
+      </c>
+      <c r="B1815" s="7" t="inlineStr">
+        <is>
+          <t>미국</t>
+        </is>
+      </c>
+      <c r="C1815" s="7" t="inlineStr">
+        <is>
+          <t>국채10년</t>
+        </is>
+      </c>
+      <c r="D1815" s="7">
+        <v>4.99</v>
+      </c>
+      <c r="E1815" s="6">
+        <v>46296</v>
+      </c>
+      <c r="F1815" s="7" t="inlineStr">
+        <is>
+          <t>월간</t>
+        </is>
+      </c>
     </row>
     <row r="1816" spans="1:6">
-      <c r="A1816" s="6"/>
-      <c r="B1816" s="7"/>
-      <c r="C1816" s="7"/>
-      <c r="D1816" s="7"/>
+      <c r="A1816" s="6">
+        <v>46235</v>
+      </c>
+      <c r="B1816" s="7" t="inlineStr">
+        <is>
+          <t>독일</t>
+        </is>
+      </c>
+      <c r="C1816" s="7" t="inlineStr">
+        <is>
+          <t>실업률</t>
+        </is>
+      </c>
+      <c r="D1816" s="7">
+        <v>4.0</v>
+      </c>
       <c r="E1816" s="6"/>
-      <c r="F1816" s="7"/>
+      <c r="F1816" s="7" t="inlineStr">
+        <is>
+          <t>월간</t>
+        </is>
+      </c>
     </row>
     <row r="1817" spans="1:6">
-      <c r="A1817" s="6"/>
-      <c r="B1817" s="7"/>
-      <c r="C1817" s="7"/>
-      <c r="D1817" s="7"/>
+      <c r="A1817" s="6">
+        <v>46266</v>
+      </c>
+      <c r="B1817" s="7" t="inlineStr">
+        <is>
+          <t>독일</t>
+        </is>
+      </c>
+      <c r="C1817" s="7" t="inlineStr">
+        <is>
+          <t>브렌트</t>
+        </is>
+      </c>
+      <c r="D1817" s="7">
+        <v>114.08</v>
+      </c>
       <c r="E1817" s="6"/>
-      <c r="F1817" s="7"/>
+      <c r="F1817" s="7" t="inlineStr">
+        <is>
+          <t>월간</t>
+        </is>
+      </c>
     </row>
     <row r="1818" spans="1:6">
-      <c r="A1818" s="6"/>
-      <c r="B1818" s="7"/>
-      <c r="C1818" s="7"/>
-      <c r="D1818" s="7"/>
+      <c r="A1818" s="6">
+        <v>46235</v>
+      </c>
+      <c r="B1818" s="7" t="inlineStr">
+        <is>
+          <t>프랑스</t>
+        </is>
+      </c>
+      <c r="C1818" s="7" t="inlineStr">
+        <is>
+          <t>실업률</t>
+        </is>
+      </c>
+      <c r="D1818" s="7">
+        <v>8.2</v>
+      </c>
       <c r="E1818" s="6"/>
-      <c r="F1818" s="7"/>
+      <c r="F1818" s="7" t="inlineStr">
+        <is>
+          <t>월간</t>
+        </is>
+      </c>
     </row>
     <row r="1819" spans="1:6">
-      <c r="A1819" s="6"/>
-      <c r="B1819" s="7"/>
-      <c r="C1819" s="7"/>
-      <c r="D1819" s="7"/>
+      <c r="A1819" s="6">
+        <v>46266</v>
+      </c>
+      <c r="B1819" s="7" t="inlineStr">
+        <is>
+          <t>프랑스</t>
+        </is>
+      </c>
+      <c r="C1819" s="7" t="inlineStr">
+        <is>
+          <t>브렌트</t>
+        </is>
+      </c>
+      <c r="D1819" s="7">
+        <v>114.08</v>
+      </c>
       <c r="E1819" s="6"/>
-      <c r="F1819" s="7"/>
+      <c r="F1819" s="7" t="inlineStr">
+        <is>
+          <t>월간</t>
+        </is>
+      </c>
     </row>
     <row r="1820" spans="1:6">
       <c r="A1820" s="6"/>

--- a/매크로_트래커_로우데이터.xlsx
+++ b/매크로_트래커_로우데이터.xlsx
@@ -45511,52 +45511,152 @@
       </c>
     </row>
     <row r="1820" spans="1:6">
-      <c r="A1820" s="6"/>
-      <c r="B1820" s="7"/>
-      <c r="C1820" s="7"/>
-      <c r="D1820" s="7"/>
-      <c r="E1820" s="6"/>
-      <c r="F1820" s="7"/>
+      <c r="A1820" s="6">
+        <v>46266</v>
+      </c>
+      <c r="B1820" s="7" t="inlineStr">
+        <is>
+          <t>미국</t>
+        </is>
+      </c>
+      <c r="C1820" s="7" t="inlineStr">
+        <is>
+          <t>비농업고용</t>
+        </is>
+      </c>
+      <c r="D1820" s="7">
+        <v>159044.0</v>
+      </c>
+      <c r="E1820" s="6">
+        <v>46297</v>
+      </c>
+      <c r="F1820" s="7" t="inlineStr">
+        <is>
+          <t>월간</t>
+        </is>
+      </c>
     </row>
     <row r="1821" spans="1:6">
-      <c r="A1821" s="6"/>
-      <c r="B1821" s="7"/>
-      <c r="C1821" s="7"/>
-      <c r="D1821" s="7"/>
-      <c r="E1821" s="6"/>
-      <c r="F1821" s="7"/>
+      <c r="A1821" s="6">
+        <v>46266</v>
+      </c>
+      <c r="B1821" s="7" t="inlineStr">
+        <is>
+          <t>미국</t>
+        </is>
+      </c>
+      <c r="C1821" s="7" t="inlineStr">
+        <is>
+          <t>실업률</t>
+        </is>
+      </c>
+      <c r="D1821" s="7">
+        <v>4.2</v>
+      </c>
+      <c r="E1821" s="6">
+        <v>46297</v>
+      </c>
+      <c r="F1821" s="7" t="inlineStr">
+        <is>
+          <t>월간</t>
+        </is>
+      </c>
     </row>
     <row r="1822" spans="1:6">
-      <c r="A1822" s="6"/>
-      <c r="B1822" s="7"/>
-      <c r="C1822" s="7"/>
-      <c r="D1822" s="7"/>
+      <c r="A1822" s="6">
+        <v>46266</v>
+      </c>
+      <c r="B1822" s="7" t="inlineStr">
+        <is>
+          <t>독일</t>
+        </is>
+      </c>
+      <c r="C1822" s="7" t="inlineStr">
+        <is>
+          <t>HICP 헤드라인</t>
+        </is>
+      </c>
+      <c r="D1822" s="7">
+        <v>3.3</v>
+      </c>
       <c r="E1822" s="6"/>
-      <c r="F1822" s="7"/>
+      <c r="F1822" s="7" t="inlineStr">
+        <is>
+          <t>월간</t>
+        </is>
+      </c>
     </row>
     <row r="1823" spans="1:6">
-      <c r="A1823" s="6"/>
-      <c r="B1823" s="7"/>
-      <c r="C1823" s="7"/>
-      <c r="D1823" s="7"/>
+      <c r="A1823" s="6">
+        <v>46266</v>
+      </c>
+      <c r="B1823" s="7" t="inlineStr">
+        <is>
+          <t>독일</t>
+        </is>
+      </c>
+      <c r="C1823" s="7" t="inlineStr">
+        <is>
+          <t>HICP 근원</t>
+        </is>
+      </c>
+      <c r="D1823" s="7">
+        <v>2.5</v>
+      </c>
       <c r="E1823" s="6"/>
-      <c r="F1823" s="7"/>
+      <c r="F1823" s="7" t="inlineStr">
+        <is>
+          <t>월간</t>
+        </is>
+      </c>
     </row>
     <row r="1824" spans="1:6">
-      <c r="A1824" s="6"/>
-      <c r="B1824" s="7"/>
-      <c r="C1824" s="7"/>
-      <c r="D1824" s="7"/>
+      <c r="A1824" s="6">
+        <v>46266</v>
+      </c>
+      <c r="B1824" s="7" t="inlineStr">
+        <is>
+          <t>프랑스</t>
+        </is>
+      </c>
+      <c r="C1824" s="7" t="inlineStr">
+        <is>
+          <t>HICP 헤드라인</t>
+        </is>
+      </c>
+      <c r="D1824" s="7">
+        <v>3.4</v>
+      </c>
       <c r="E1824" s="6"/>
-      <c r="F1824" s="7"/>
+      <c r="F1824" s="7" t="inlineStr">
+        <is>
+          <t>월간</t>
+        </is>
+      </c>
     </row>
     <row r="1825" spans="1:6">
-      <c r="A1825" s="6"/>
-      <c r="B1825" s="7"/>
-      <c r="C1825" s="7"/>
-      <c r="D1825" s="7"/>
+      <c r="A1825" s="6">
+        <v>46266</v>
+      </c>
+      <c r="B1825" s="7" t="inlineStr">
+        <is>
+          <t>프랑스</t>
+        </is>
+      </c>
+      <c r="C1825" s="7" t="inlineStr">
+        <is>
+          <t>HICP 근원</t>
+        </is>
+      </c>
+      <c r="D1825" s="7">
+        <v>1.7</v>
+      </c>
       <c r="E1825" s="6"/>
-      <c r="F1825" s="7"/>
+      <c r="F1825" s="7" t="inlineStr">
+        <is>
+          <t>월간</t>
+        </is>
+      </c>
     </row>
     <row r="1826" spans="1:6">
       <c r="A1826" s="6"/>

--- a/매크로_트래커_로우데이터.xlsx
+++ b/매크로_트래커_로우데이터.xlsx
@@ -45659,20 +45659,56 @@
       </c>
     </row>
     <row r="1826" spans="1:6">
-      <c r="A1826" s="6"/>
-      <c r="B1826" s="7"/>
-      <c r="C1826" s="7"/>
-      <c r="D1826" s="7"/>
-      <c r="E1826" s="6"/>
-      <c r="F1826" s="7"/>
+      <c r="A1826" s="6">
+        <v>46266</v>
+      </c>
+      <c r="B1826" s="7" t="inlineStr">
+        <is>
+          <t>한국</t>
+        </is>
+      </c>
+      <c r="C1826" s="7" t="inlineStr">
+        <is>
+          <t>CPI 헤드라인</t>
+        </is>
+      </c>
+      <c r="D1826" s="7">
+        <v>2.88</v>
+      </c>
+      <c r="E1826" s="6">
+        <v>46297</v>
+      </c>
+      <c r="F1826" s="7" t="inlineStr">
+        <is>
+          <t>월간</t>
+        </is>
+      </c>
     </row>
     <row r="1827" spans="1:6">
-      <c r="A1827" s="6"/>
-      <c r="B1827" s="7"/>
-      <c r="C1827" s="7"/>
-      <c r="D1827" s="7"/>
-      <c r="E1827" s="6"/>
-      <c r="F1827" s="7"/>
+      <c r="A1827" s="6">
+        <v>46266</v>
+      </c>
+      <c r="B1827" s="7" t="inlineStr">
+        <is>
+          <t>한국</t>
+        </is>
+      </c>
+      <c r="C1827" s="7" t="inlineStr">
+        <is>
+          <t>CPI 근원</t>
+        </is>
+      </c>
+      <c r="D1827" s="7">
+        <v>2.73</v>
+      </c>
+      <c r="E1827" s="6">
+        <v>46297</v>
+      </c>
+      <c r="F1827" s="7" t="inlineStr">
+        <is>
+          <t>월간</t>
+        </is>
+      </c>
     </row>
     <row r="1828" spans="1:6">
       <c r="A1828" s="6"/>

--- a/매크로_트래커_로우데이터.xlsx
+++ b/매크로_트래커_로우데이터.xlsx
@@ -45711,20 +45711,52 @@
       </c>
     </row>
     <row r="1828" spans="1:6">
-      <c r="A1828" s="6"/>
-      <c r="B1828" s="7"/>
-      <c r="C1828" s="7"/>
-      <c r="D1828" s="7"/>
+      <c r="A1828" s="6">
+        <v>46235</v>
+      </c>
+      <c r="B1828" s="7" t="inlineStr">
+        <is>
+          <t>한국</t>
+        </is>
+      </c>
+      <c r="C1828" s="7" t="inlineStr">
+        <is>
+          <t>국채10년</t>
+        </is>
+      </c>
+      <c r="D1828" s="7">
+        <v>4.29</v>
+      </c>
       <c r="E1828" s="6"/>
-      <c r="F1828" s="7"/>
+      <c r="F1828" s="7" t="inlineStr">
+        <is>
+          <t>월간</t>
+        </is>
+      </c>
     </row>
     <row r="1829" spans="1:6">
-      <c r="A1829" s="6"/>
-      <c r="B1829" s="7"/>
-      <c r="C1829" s="7"/>
-      <c r="D1829" s="7"/>
+      <c r="A1829" s="6">
+        <v>46266</v>
+      </c>
+      <c r="B1829" s="7" t="inlineStr">
+        <is>
+          <t>한국</t>
+        </is>
+      </c>
+      <c r="C1829" s="7" t="inlineStr">
+        <is>
+          <t>국채10년</t>
+        </is>
+      </c>
+      <c r="D1829" s="7">
+        <v>4.45</v>
+      </c>
       <c r="E1829" s="6"/>
-      <c r="F1829" s="7"/>
+      <c r="F1829" s="7" t="inlineStr">
+        <is>
+          <t>월간</t>
+        </is>
+      </c>
     </row>
     <row r="1830" spans="1:6">
       <c r="A1830" s="6"/>
@@ -72096,10 +72128,12 @@
         <v>75</v>
       </c>
       <c r="F37" s="8" t="s">
-        <v>93</v>
-      </c>
-      <c r="G37" s="8" t="s">
-        <v>129</v>
+        <v>125</v>
+      </c>
+      <c r="G37" s="8" t="inlineStr">
+        <is>
+          <t>ECOS: 721Y001/5050000</t>
+        </is>
       </c>
       <c r="H37" s="8"/>
     </row>

--- a/매크로_트래커_로우데이터.xlsx
+++ b/매크로_트래커_로우데이터.xlsx
@@ -45759,20 +45759,52 @@
       </c>
     </row>
     <row r="1830" spans="1:6">
-      <c r="A1830" s="6"/>
-      <c r="B1830" s="7"/>
-      <c r="C1830" s="7"/>
-      <c r="D1830" s="7"/>
+      <c r="A1830" s="6">
+        <v>46266</v>
+      </c>
+      <c r="B1830" s="7" t="inlineStr">
+        <is>
+          <t>독일</t>
+        </is>
+      </c>
+      <c r="C1830" s="7" t="inlineStr">
+        <is>
+          <t>국채10년</t>
+        </is>
+      </c>
+      <c r="D1830" s="7">
+        <v>3.47</v>
+      </c>
       <c r="E1830" s="6"/>
-      <c r="F1830" s="7"/>
+      <c r="F1830" s="7" t="inlineStr">
+        <is>
+          <t>월간</t>
+        </is>
+      </c>
     </row>
     <row r="1831" spans="1:6">
-      <c r="A1831" s="6"/>
-      <c r="B1831" s="7"/>
-      <c r="C1831" s="7"/>
-      <c r="D1831" s="7"/>
+      <c r="A1831" s="6">
+        <v>46266</v>
+      </c>
+      <c r="B1831" s="7" t="inlineStr">
+        <is>
+          <t>프랑스</t>
+        </is>
+      </c>
+      <c r="C1831" s="7" t="inlineStr">
+        <is>
+          <t>국채10년</t>
+        </is>
+      </c>
+      <c r="D1831" s="7">
+        <v>4.44</v>
+      </c>
       <c r="E1831" s="6"/>
-      <c r="F1831" s="7"/>
+      <c r="F1831" s="7" t="inlineStr">
+        <is>
+          <t>월간</t>
+        </is>
+      </c>
     </row>
     <row r="1832" spans="1:6">
       <c r="A1832" s="6"/>

--- a/매크로_트래커_로우데이터.xlsx
+++ b/매크로_트래커_로우데이터.xlsx
@@ -45807,20 +45807,56 @@
       </c>
     </row>
     <row r="1832" spans="1:6">
-      <c r="A1832" s="6"/>
-      <c r="B1832" s="7"/>
-      <c r="C1832" s="7"/>
-      <c r="D1832" s="7"/>
-      <c r="E1832" s="6"/>
-      <c r="F1832" s="7"/>
+      <c r="A1832" s="6">
+        <v>46266</v>
+      </c>
+      <c r="B1832" s="7" t="inlineStr">
+        <is>
+          <t>미국</t>
+        </is>
+      </c>
+      <c r="C1832" s="7" t="inlineStr">
+        <is>
+          <t>CPI 헤드라인</t>
+        </is>
+      </c>
+      <c r="D1832" s="7">
+        <v>3.7172</v>
+      </c>
+      <c r="E1832" s="6">
+        <v>46309</v>
+      </c>
+      <c r="F1832" s="7" t="inlineStr">
+        <is>
+          <t>월간</t>
+        </is>
+      </c>
     </row>
     <row r="1833" spans="1:6">
-      <c r="A1833" s="6"/>
-      <c r="B1833" s="7"/>
-      <c r="C1833" s="7"/>
-      <c r="D1833" s="7"/>
-      <c r="E1833" s="6"/>
-      <c r="F1833" s="7"/>
+      <c r="A1833" s="6">
+        <v>46266</v>
+      </c>
+      <c r="B1833" s="7" t="inlineStr">
+        <is>
+          <t>미국</t>
+        </is>
+      </c>
+      <c r="C1833" s="7" t="inlineStr">
+        <is>
+          <t>CPI 근원</t>
+        </is>
+      </c>
+      <c r="D1833" s="7">
+        <v>2.5658</v>
+      </c>
+      <c r="E1833" s="6">
+        <v>46309</v>
+      </c>
+      <c r="F1833" s="7" t="inlineStr">
+        <is>
+          <t>월간</t>
+        </is>
+      </c>
     </row>
     <row r="1834" spans="1:6">
       <c r="A1834" s="6"/>

--- a/매크로_트래커_로우데이터.xlsx
+++ b/매크로_트래커_로우데이터.xlsx
@@ -45859,20 +45859,54 @@
       </c>
     </row>
     <row r="1834" spans="1:6">
-      <c r="A1834" s="6"/>
-      <c r="B1834" s="7"/>
-      <c r="C1834" s="7"/>
-      <c r="D1834" s="7"/>
-      <c r="E1834" s="6"/>
-      <c r="F1834" s="7"/>
+      <c r="A1834" s="6">
+        <v>46235</v>
+      </c>
+      <c r="B1834" s="7" t="inlineStr">
+        <is>
+          <t>일본</t>
+        </is>
+      </c>
+      <c r="C1834" s="7" t="inlineStr">
+        <is>
+          <t>실업률</t>
+        </is>
+      </c>
+      <c r="D1834" s="7">
+        <v>2.5</v>
+      </c>
+      <c r="E1834" s="6">
+        <v>46297</v>
+      </c>
+      <c r="F1834" s="7" t="inlineStr">
+        <is>
+          <t>월간</t>
+        </is>
+      </c>
     </row>
     <row r="1835" spans="1:6">
-      <c r="A1835" s="6"/>
-      <c r="B1835" s="7"/>
-      <c r="C1835" s="7"/>
-      <c r="D1835" s="7"/>
+      <c r="A1835" s="6">
+        <v>46266</v>
+      </c>
+      <c r="B1835" s="7" t="inlineStr">
+        <is>
+          <t>일본</t>
+        </is>
+      </c>
+      <c r="C1835" s="7" t="inlineStr">
+        <is>
+          <t>국채10년</t>
+        </is>
+      </c>
+      <c r="D1835" s="7">
+        <v>3.05</v>
+      </c>
       <c r="E1835" s="6"/>
-      <c r="F1835" s="7"/>
+      <c r="F1835" s="7" t="inlineStr">
+        <is>
+          <t>월간</t>
+        </is>
+      </c>
     </row>
     <row r="1836" spans="1:6">
       <c r="A1836" s="6"/>

--- a/매크로_트래커_로우데이터.xlsx
+++ b/매크로_트래커_로우데이터.xlsx
@@ -45875,9 +45875,7 @@
       <c r="D1834" s="7">
         <v>2.5</v>
       </c>
-      <c r="E1834" s="6">
-        <v>46297</v>
-      </c>
+      <c r="E1834" s="6"/>
       <c r="F1834" s="7" t="inlineStr">
         <is>
           <t>월간</t>
@@ -45909,20 +45907,56 @@
       </c>
     </row>
     <row r="1836" spans="1:6">
-      <c r="A1836" s="6"/>
-      <c r="B1836" s="7"/>
-      <c r="C1836" s="7"/>
-      <c r="D1836" s="7"/>
-      <c r="E1836" s="6"/>
-      <c r="F1836" s="7"/>
+      <c r="A1836" s="6">
+        <v>46266</v>
+      </c>
+      <c r="B1836" s="7" t="inlineStr">
+        <is>
+          <t>한국</t>
+        </is>
+      </c>
+      <c r="C1836" s="7" t="inlineStr">
+        <is>
+          <t>취업자수</t>
+        </is>
+      </c>
+      <c r="D1836" s="7">
+        <v>29266.0</v>
+      </c>
+      <c r="E1836" s="6">
+        <v>46311</v>
+      </c>
+      <c r="F1836" s="7" t="inlineStr">
+        <is>
+          <t>월간</t>
+        </is>
+      </c>
     </row>
     <row r="1837" spans="1:6">
-      <c r="A1837" s="6"/>
-      <c r="B1837" s="7"/>
-      <c r="C1837" s="7"/>
-      <c r="D1837" s="7"/>
-      <c r="E1837" s="6"/>
-      <c r="F1837" s="7"/>
+      <c r="A1837" s="6">
+        <v>46266</v>
+      </c>
+      <c r="B1837" s="7" t="inlineStr">
+        <is>
+          <t>한국</t>
+        </is>
+      </c>
+      <c r="C1837" s="7" t="inlineStr">
+        <is>
+          <t>실업률</t>
+        </is>
+      </c>
+      <c r="D1837" s="7">
+        <v>2.6</v>
+      </c>
+      <c r="E1837" s="6">
+        <v>46311</v>
+      </c>
+      <c r="F1837" s="7" t="inlineStr">
+        <is>
+          <t>월간</t>
+        </is>
+      </c>
     </row>
     <row r="1838" spans="1:6">
       <c r="A1838" s="6"/>

--- a/매크로_트래커_로우데이터.xlsx
+++ b/매크로_트래커_로우데이터.xlsx
@@ -45959,52 +45959,152 @@
       </c>
     </row>
     <row r="1838" spans="1:6">
-      <c r="A1838" s="6"/>
-      <c r="B1838" s="7"/>
-      <c r="C1838" s="7"/>
-      <c r="D1838" s="7"/>
-      <c r="E1838" s="6"/>
-      <c r="F1838" s="7"/>
+      <c r="A1838" s="6">
+        <v>46266</v>
+      </c>
+      <c r="B1838" s="7" t="inlineStr">
+        <is>
+          <t>일본</t>
+        </is>
+      </c>
+      <c r="C1838" s="7" t="inlineStr">
+        <is>
+          <t>CPI 헤드라인</t>
+        </is>
+      </c>
+      <c r="D1838" s="7">
+        <v>2.1</v>
+      </c>
+      <c r="E1838" s="6">
+        <v>46318</v>
+      </c>
+      <c r="F1838" s="7" t="inlineStr">
+        <is>
+          <t>월간</t>
+        </is>
+      </c>
     </row>
     <row r="1839" spans="1:6">
-      <c r="A1839" s="6"/>
-      <c r="B1839" s="7"/>
-      <c r="C1839" s="7"/>
-      <c r="D1839" s="7"/>
-      <c r="E1839" s="6"/>
-      <c r="F1839" s="7"/>
+      <c r="A1839" s="6">
+        <v>46266</v>
+      </c>
+      <c r="B1839" s="7" t="inlineStr">
+        <is>
+          <t>일본</t>
+        </is>
+      </c>
+      <c r="C1839" s="7" t="inlineStr">
+        <is>
+          <t>CPI 근원</t>
+        </is>
+      </c>
+      <c r="D1839" s="7">
+        <v>2.1</v>
+      </c>
+      <c r="E1839" s="6">
+        <v>46318</v>
+      </c>
+      <c r="F1839" s="7" t="inlineStr">
+        <is>
+          <t>월간</t>
+        </is>
+      </c>
     </row>
     <row r="1840" spans="1:6">
-      <c r="A1840" s="6"/>
-      <c r="B1840" s="7"/>
-      <c r="C1840" s="7"/>
-      <c r="D1840" s="7"/>
+      <c r="A1840" s="6">
+        <v>46235</v>
+      </c>
+      <c r="B1840" s="7" t="inlineStr">
+        <is>
+          <t>일본</t>
+        </is>
+      </c>
+      <c r="C1840" s="7" t="inlineStr">
+        <is>
+          <t>두바이유</t>
+        </is>
+      </c>
+      <c r="D1840" s="7">
+        <v>88.0533</v>
+      </c>
       <c r="E1840" s="6"/>
-      <c r="F1840" s="7"/>
+      <c r="F1840" s="7" t="inlineStr">
+        <is>
+          <t>월간</t>
+        </is>
+      </c>
     </row>
     <row r="1841" spans="1:6">
-      <c r="A1841" s="6"/>
-      <c r="B1841" s="7"/>
-      <c r="C1841" s="7"/>
-      <c r="D1841" s="7"/>
+      <c r="A1841" s="6">
+        <v>46266</v>
+      </c>
+      <c r="B1841" s="7" t="inlineStr">
+        <is>
+          <t>일본</t>
+        </is>
+      </c>
+      <c r="C1841" s="7" t="inlineStr">
+        <is>
+          <t>두바이유</t>
+        </is>
+      </c>
+      <c r="D1841" s="7">
+        <v>111.8252</v>
+      </c>
       <c r="E1841" s="6"/>
-      <c r="F1841" s="7"/>
+      <c r="F1841" s="7" t="inlineStr">
+        <is>
+          <t>월간</t>
+        </is>
+      </c>
     </row>
     <row r="1842" spans="1:6">
-      <c r="A1842" s="6"/>
-      <c r="B1842" s="7"/>
-      <c r="C1842" s="7"/>
-      <c r="D1842" s="7"/>
+      <c r="A1842" s="6">
+        <v>46235</v>
+      </c>
+      <c r="B1842" s="7" t="inlineStr">
+        <is>
+          <t>한국</t>
+        </is>
+      </c>
+      <c r="C1842" s="7" t="inlineStr">
+        <is>
+          <t>두바이유</t>
+        </is>
+      </c>
+      <c r="D1842" s="7">
+        <v>88.0533</v>
+      </c>
       <c r="E1842" s="6"/>
-      <c r="F1842" s="7"/>
+      <c r="F1842" s="7" t="inlineStr">
+        <is>
+          <t>월간</t>
+        </is>
+      </c>
     </row>
     <row r="1843" spans="1:6">
-      <c r="A1843" s="6"/>
-      <c r="B1843" s="7"/>
-      <c r="C1843" s="7"/>
-      <c r="D1843" s="7"/>
+      <c r="A1843" s="6">
+        <v>46266</v>
+      </c>
+      <c r="B1843" s="7" t="inlineStr">
+        <is>
+          <t>한국</t>
+        </is>
+      </c>
+      <c r="C1843" s="7" t="inlineStr">
+        <is>
+          <t>두바이유</t>
+        </is>
+      </c>
+      <c r="D1843" s="7">
+        <v>111.8252</v>
+      </c>
       <c r="E1843" s="6"/>
-      <c r="F1843" s="7"/>
+      <c r="F1843" s="7" t="inlineStr">
+        <is>
+          <t>월간</t>
+        </is>
+      </c>
     </row>
     <row r="1844" spans="1:6">
       <c r="A1844" s="6"/>

--- a/매크로_트래커_로우데이터.xlsx
+++ b/매크로_트래커_로우데이터.xlsx
@@ -46107,12 +46107,30 @@
       </c>
     </row>
     <row r="1844" spans="1:6">
-      <c r="A1844" s="6"/>
-      <c r="B1844" s="7"/>
-      <c r="C1844" s="7"/>
-      <c r="D1844" s="7"/>
-      <c r="E1844" s="6"/>
-      <c r="F1844" s="7"/>
+      <c r="A1844" s="6">
+        <v>46204</v>
+      </c>
+      <c r="B1844" s="7" t="inlineStr">
+        <is>
+          <t>한국</t>
+        </is>
+      </c>
+      <c r="C1844" s="7" t="inlineStr">
+        <is>
+          <t>실질GDP 성장률</t>
+        </is>
+      </c>
+      <c r="D1844" s="7">
+        <v>0.97</v>
+      </c>
+      <c r="E1844" s="6">
+        <v>46322</v>
+      </c>
+      <c r="F1844" s="7" t="inlineStr">
+        <is>
+          <t>분기</t>
+        </is>
+      </c>
     </row>
     <row r="1845" spans="1:6">
       <c r="A1845" s="6"/>

--- a/매크로_트래커_로우데이터.xlsx
+++ b/매크로_트래커_로우데이터.xlsx
@@ -46133,20 +46133,56 @@
       </c>
     </row>
     <row r="1845" spans="1:6">
-      <c r="A1845" s="6"/>
-      <c r="B1845" s="7"/>
-      <c r="C1845" s="7"/>
-      <c r="D1845" s="7"/>
-      <c r="E1845" s="6"/>
-      <c r="F1845" s="7"/>
+      <c r="A1845" s="6">
+        <v>46266</v>
+      </c>
+      <c r="B1845" s="7" t="inlineStr">
+        <is>
+          <t>미국</t>
+        </is>
+      </c>
+      <c r="C1845" s="7" t="inlineStr">
+        <is>
+          <t>PCE 근원</t>
+        </is>
+      </c>
+      <c r="D1845" s="7">
+        <v>3.1212</v>
+      </c>
+      <c r="E1845" s="6">
+        <v>46324</v>
+      </c>
+      <c r="F1845" s="7" t="inlineStr">
+        <is>
+          <t>월간</t>
+        </is>
+      </c>
     </row>
     <row r="1846" spans="1:6">
-      <c r="A1846" s="6"/>
-      <c r="B1846" s="7"/>
-      <c r="C1846" s="7"/>
-      <c r="D1846" s="7"/>
-      <c r="E1846" s="6"/>
-      <c r="F1846" s="7"/>
+      <c r="A1846" s="6">
+        <v>46204</v>
+      </c>
+      <c r="B1846" s="7" t="inlineStr">
+        <is>
+          <t>미국</t>
+        </is>
+      </c>
+      <c r="C1846" s="7" t="inlineStr">
+        <is>
+          <t>실질GDP 성장률</t>
+        </is>
+      </c>
+      <c r="D1846" s="7">
+        <v>3.4</v>
+      </c>
+      <c r="E1846" s="6">
+        <v>46324</v>
+      </c>
+      <c r="F1846" s="7" t="inlineStr">
+        <is>
+          <t>분기</t>
+        </is>
+      </c>
     </row>
     <row r="1847" spans="1:6">
       <c r="A1847" s="6"/>

--- a/매크로_트래커_로우데이터.xlsx
+++ b/매크로_트래커_로우데이터.xlsx
@@ -46185,36 +46185,100 @@
       </c>
     </row>
     <row r="1847" spans="1:6">
-      <c r="A1847" s="6"/>
-      <c r="B1847" s="7"/>
-      <c r="C1847" s="7"/>
-      <c r="D1847" s="7"/>
+      <c r="A1847" s="6">
+        <v>46266</v>
+      </c>
+      <c r="B1847" s="7" t="inlineStr">
+        <is>
+          <t>독일</t>
+        </is>
+      </c>
+      <c r="C1847" s="7" t="inlineStr">
+        <is>
+          <t>실업률</t>
+        </is>
+      </c>
+      <c r="D1847" s="7">
+        <v>4.1</v>
+      </c>
       <c r="E1847" s="6"/>
-      <c r="F1847" s="7"/>
+      <c r="F1847" s="7" t="inlineStr">
+        <is>
+          <t>월간</t>
+        </is>
+      </c>
     </row>
     <row r="1848" spans="1:6">
-      <c r="A1848" s="6"/>
-      <c r="B1848" s="7"/>
-      <c r="C1848" s="7"/>
-      <c r="D1848" s="7"/>
+      <c r="A1848" s="6">
+        <v>46204</v>
+      </c>
+      <c r="B1848" s="7" t="inlineStr">
+        <is>
+          <t>독일</t>
+        </is>
+      </c>
+      <c r="C1848" s="7" t="inlineStr">
+        <is>
+          <t>실질GDP 성장률</t>
+        </is>
+      </c>
+      <c r="D1848" s="7">
+        <v>0.2</v>
+      </c>
       <c r="E1848" s="6"/>
-      <c r="F1848" s="7"/>
+      <c r="F1848" s="7" t="inlineStr">
+        <is>
+          <t>분기</t>
+        </is>
+      </c>
     </row>
     <row r="1849" spans="1:6">
-      <c r="A1849" s="6"/>
-      <c r="B1849" s="7"/>
-      <c r="C1849" s="7"/>
-      <c r="D1849" s="7"/>
+      <c r="A1849" s="6">
+        <v>46266</v>
+      </c>
+      <c r="B1849" s="7" t="inlineStr">
+        <is>
+          <t>프랑스</t>
+        </is>
+      </c>
+      <c r="C1849" s="7" t="inlineStr">
+        <is>
+          <t>실업률</t>
+        </is>
+      </c>
+      <c r="D1849" s="7">
+        <v>8.5</v>
+      </c>
       <c r="E1849" s="6"/>
-      <c r="F1849" s="7"/>
+      <c r="F1849" s="7" t="inlineStr">
+        <is>
+          <t>월간</t>
+        </is>
+      </c>
     </row>
     <row r="1850" spans="1:6">
-      <c r="A1850" s="6"/>
-      <c r="B1850" s="7"/>
-      <c r="C1850" s="7"/>
-      <c r="D1850" s="7"/>
+      <c r="A1850" s="6">
+        <v>46204</v>
+      </c>
+      <c r="B1850" s="7" t="inlineStr">
+        <is>
+          <t>프랑스</t>
+        </is>
+      </c>
+      <c r="C1850" s="7" t="inlineStr">
+        <is>
+          <t>실질GDP 성장률</t>
+        </is>
+      </c>
+      <c r="D1850" s="7">
+        <v>-0.1</v>
+      </c>
       <c r="E1850" s="6"/>
-      <c r="F1850" s="7"/>
+      <c r="F1850" s="7" t="inlineStr">
+        <is>
+          <t>분기</t>
+        </is>
+      </c>
     </row>
     <row r="1851" spans="1:6">
       <c r="A1851" s="6"/>
